--- a/results/submission_predictions.xlsx
+++ b/results/submission_predictions.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1571,7 +1567,7 @@
         <v>0.03553853556513786</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03609273582696915</v>
+        <v>0.03609274327754974</v>
       </c>
       <c r="G2" t="n">
         <v>0.03546727076172829</v>
@@ -1583,7 +1579,7 @@
         <v>0.03462072461843491</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03485633060336113</v>
+        <v>0.03485633432865143</v>
       </c>
       <c r="K2" t="n">
         <v>0.03422610834240913</v>
@@ -1685,13 +1681,13 @@
         <v>0.08294537663459778</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.1072399839758873</v>
+        <v>0.1072399914264679</v>
       </c>
       <c r="AS2" t="n">
         <v>0.1139924004673958</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.114914558827877</v>
+        <v>0.1149145662784576</v>
       </c>
       <c r="AU2" t="n">
         <v>0.1169358789920807</v>
@@ -1727,7 +1723,7 @@
         <v>0.1017294079065323</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.1351375430822372</v>
+        <v>0.1351375579833984</v>
       </c>
       <c r="BG2" t="n">
         <v>0.1371277421712875</v>
@@ -1742,7 +1738,7 @@
         <v>0.1337656676769257</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.1279070228338242</v>
+        <v>0.1279070377349854</v>
       </c>
       <c r="BL2" t="n">
         <v>0.1275920271873474</v>
@@ -1757,7 +1753,7 @@
         <v>0.1247401759028435</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1169500574469566</v>
+        <v>0.1169500648975372</v>
       </c>
       <c r="BQ2" t="n">
         <v>0.1164049580693245</v>
@@ -1883,7 +1879,7 @@
         <v>0.1948543637990952</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.1894200891256332</v>
+        <v>0.1894201040267944</v>
       </c>
       <c r="DG2" t="n">
         <v>0.1865202188491821</v>
@@ -1898,7 +1894,7 @@
         <v>0.2457068562507629</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.2429618239402771</v>
+        <v>0.2429618388414383</v>
       </c>
       <c r="DL2" t="n">
         <v>0.2353169769048691</v>
@@ -2012,7 +2008,7 @@
         <v>0.246431291103363</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.2465380728244781</v>
+        <v>0.2465380877256393</v>
       </c>
       <c r="EX2" t="n">
         <v>0.2465481609106064</v>
@@ -2066,7 +2062,7 @@
         <v>0.2864341139793396</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.2868529558181763</v>
+        <v>0.2868529856204987</v>
       </c>
       <c r="FP2" t="n">
         <v>0.2789511382579803</v>
@@ -2117,7 +2113,7 @@
         <v>0.3034860193729401</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.3017010390758514</v>
+        <v>0.3017010688781738</v>
       </c>
       <c r="GG2" t="n">
         <v>0.3001542687416077</v>
@@ -2156,7 +2152,7 @@
         <v>0.3265229165554047</v>
       </c>
       <c r="GS2" t="n">
-        <v>0.3249167203903198</v>
+        <v>0.3249167501926422</v>
       </c>
       <c r="GT2" t="n">
         <v>0.3261618912220001</v>
@@ -2183,7 +2179,7 @@
         <v>0.3482560217380524</v>
       </c>
       <c r="HB2" t="n">
-        <v>0.3604863584041595</v>
+        <v>0.3604863882064819</v>
       </c>
       <c r="HC2" t="n">
         <v>0.3553192019462585</v>
@@ -2230,8 +2226,10 @@
       <c r="HQ2" t="n">
         <v>0.3446680307388306</v>
       </c>
-      <c r="HR2" s="1" t="n">
-        <v>55512</v>
+      <c r="HR2" t="inlineStr">
+        <is>
+          <t>24/12/2051</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -2241,7 +2239,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02405373938381672</v>
+        <v>0.02405374124646187</v>
       </c>
       <c r="C3" t="n">
         <v>0.03270313516259193</v>
@@ -2286,19 +2284,19 @@
         <v>0.04883988574147224</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.06013626605272293</v>
+        <v>0.06013627350330353</v>
       </c>
       <c r="R3" t="n">
         <v>0.06284879893064499</v>
       </c>
       <c r="S3" t="n">
-        <v>0.06389123946428299</v>
+        <v>0.06389124691486359</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06511685997247696</v>
+        <v>0.06511686742305756</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06285393238067627</v>
+        <v>0.06285393983125687</v>
       </c>
       <c r="V3" t="n">
         <v>0.06368936598300934</v>
@@ -2322,10 +2320,10 @@
         <v>0.05685501918196678</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.05827780067920685</v>
+        <v>0.05827780440449715</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.08020353317260742</v>
+        <v>0.08020354062318802</v>
       </c>
       <c r="AE3" t="n">
         <v>0.09205266088247299</v>
@@ -2367,7 +2365,7 @@
         <v>0.08378931879997253</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.1091591417789459</v>
+        <v>0.1091591492295265</v>
       </c>
       <c r="AS3" t="n">
         <v>0.1161635741591454</v>
@@ -2385,7 +2383,7 @@
         <v>0.1125217750668526</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1130005866289139</v>
+        <v>0.1130005940794945</v>
       </c>
       <c r="AY3" t="n">
         <v>0.1121794953942299</v>
@@ -2400,7 +2398,7 @@
         <v>0.1026151031255722</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1009214073419571</v>
+        <v>0.1009214147925377</v>
       </c>
       <c r="BD3" t="n">
         <v>0.09962698817253113</v>
@@ -2436,7 +2434,7 @@
         <v>0.1247759908437729</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.1260892152786255</v>
+        <v>0.1260892301797867</v>
       </c>
       <c r="BP3" t="n">
         <v>0.1180642545223236</v>
@@ -2460,7 +2458,7 @@
         <v>0.1656215339899063</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1656820327043533</v>
+        <v>0.1656820476055145</v>
       </c>
       <c r="BX3" t="n">
         <v>0.1639607101678848</v>
@@ -2502,7 +2500,7 @@
         <v>0.1925187855958939</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.1886909157037735</v>
+        <v>0.1886909306049347</v>
       </c>
       <c r="CL3" t="n">
         <v>0.1850903928279877</v>
@@ -2577,16 +2575,16 @@
         <v>0.189191535115242</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.2488144785165787</v>
+        <v>0.2488144934177399</v>
       </c>
       <c r="DK3" t="n">
         <v>0.2457433938980103</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.2378329932689667</v>
+        <v>0.2378330081701279</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.2362802028656006</v>
+        <v>0.2362802177667618</v>
       </c>
       <c r="DN3" t="n">
         <v>0.2294298559427261</v>
@@ -2601,7 +2599,7 @@
         <v>0.2190182507038116</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.2176065593957901</v>
+        <v>0.2176065891981125</v>
       </c>
       <c r="DS3" t="n">
         <v>0.2147616446018219</v>
@@ -2631,7 +2629,7 @@
         <v>0.2474002242088318</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.2468252182006836</v>
+        <v>0.2468252331018448</v>
       </c>
       <c r="EC3" t="n">
         <v>0.241018608212471</v>
@@ -2706,7 +2704,7 @@
         <v>0.2834609150886536</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.2839841544628143</v>
+        <v>0.2839841842651367</v>
       </c>
       <c r="FB3" t="n">
         <v>0.2734586000442505</v>
@@ -2748,7 +2746,7 @@
         <v>0.2875897884368896</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.2879283130168915</v>
+        <v>0.2879283428192139</v>
       </c>
       <c r="FP3" t="n">
         <v>0.2799690961837769</v>
@@ -2910,10 +2908,12 @@
         <v>0.3569716811180115</v>
       </c>
       <c r="HQ3" t="n">
-        <v>0.3456933796405792</v>
-      </c>
-      <c r="HR3" s="1" t="n">
-        <v>55513</v>
+        <v>0.3456934094429016</v>
+      </c>
+      <c r="HR3" t="inlineStr">
+        <is>
+          <t>26/12/2051</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2923,40 +2923,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02440594509243965</v>
+        <v>0.02440594881772995</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03310086950659752</v>
+        <v>0.03310087323188782</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03520696237683296</v>
+        <v>0.03520696610212326</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03676065802574158</v>
+        <v>0.03676066175103188</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03725502267479897</v>
+        <v>0.03725502640008926</v>
       </c>
       <c r="G4" t="n">
         <v>0.03656097874045372</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03599255904555321</v>
+        <v>0.03599256277084351</v>
       </c>
       <c r="I4" t="n">
         <v>0.03564152866601944</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03585303574800491</v>
+        <v>0.03585303947329521</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03517654538154602</v>
+        <v>0.03517654910683632</v>
       </c>
       <c r="L4" t="n">
         <v>0.03415499627590179</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03315304592251778</v>
+        <v>0.03315304964780807</v>
       </c>
       <c r="N4" t="n">
         <v>0.03307050094008446</v>
@@ -2965,46 +2965,46 @@
         <v>0.03364849463105202</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0494098886847496</v>
+        <v>0.0494098924100399</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0607617199420929</v>
+        <v>0.06076172739267349</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06350771337747574</v>
+        <v>0.06350772082805634</v>
       </c>
       <c r="S4" t="n">
         <v>0.0645090639591217</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0657382607460022</v>
+        <v>0.06573826819658279</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06342463940382004</v>
+        <v>0.06342464685440063</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0642491951584816</v>
+        <v>0.06424920260906219</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06379463523626328</v>
+        <v>0.06379464268684387</v>
       </c>
       <c r="X4" t="n">
         <v>0.06324773281812668</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06282945722341537</v>
+        <v>0.06282946467399597</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0597500167787075</v>
+        <v>0.0597500242292881</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05747367441654205</v>
+        <v>0.05747367814183235</v>
       </c>
       <c r="AB4" t="n">
         <v>0.05729715153574944</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.05871054530143738</v>
+        <v>0.05871054902672768</v>
       </c>
       <c r="AD4" t="n">
         <v>0.08093959093093872</v>
@@ -3013,61 +3013,61 @@
         <v>0.09287602454423904</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.09291137009859085</v>
+        <v>0.09291137754917145</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.09494400024414062</v>
+        <v>0.09494400769472122</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.09517054259777069</v>
+        <v>0.09517055004835129</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.09449223428964615</v>
+        <v>0.09449224919080734</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.09135963767766953</v>
+        <v>0.09135964512825012</v>
       </c>
       <c r="AK4" t="n">
         <v>0.09038989990949631</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.09065088629722595</v>
+        <v>0.09065089374780655</v>
       </c>
       <c r="AM4" t="n">
         <v>0.0876496210694313</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.08344297111034393</v>
+        <v>0.08344297856092453</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.08146142959594727</v>
+        <v>0.08146143704652786</v>
       </c>
       <c r="AP4" t="n">
         <v>0.08362265676259995</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.08433092385530472</v>
+        <v>0.08433093130588531</v>
       </c>
       <c r="AR4" t="n">
         <v>0.1100423559546471</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.1171707063913345</v>
+        <v>0.1171707138419151</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.1179169267416</v>
+        <v>0.1179169341921806</v>
       </c>
       <c r="AU4" t="n">
         <v>0.1195550784468651</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.1175246983766556</v>
+        <v>0.1175247058272362</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.1133393347263336</v>
+        <v>0.1133393421769142</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1138123497366905</v>
+        <v>0.1138123646378517</v>
       </c>
       <c r="AY4" t="n">
         <v>0.1129530891776085</v>
@@ -3076,37 +3076,37 @@
         <v>0.1115578413009644</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.1078924834728241</v>
+        <v>0.1078924909234047</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.1032412052154541</v>
+        <v>0.1032412126660347</v>
       </c>
       <c r="BC4" t="n">
         <v>0.1015353351831436</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.1002434492111206</v>
+        <v>0.1002434566617012</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.1032748520374298</v>
+        <v>0.1032748594880104</v>
       </c>
       <c r="BF4" t="n">
         <v>0.1383955925703049</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.140576496720314</v>
+        <v>0.1405765116214752</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.1400087475776672</v>
+        <v>0.1400087624788284</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.1366239041090012</v>
+        <v>0.1366239190101624</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.1367008835077286</v>
+        <v>0.1367008984088898</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.1305189579725266</v>
+        <v>0.1305189728736877</v>
       </c>
       <c r="BL4" t="n">
         <v>0.1299921125173569</v>
@@ -3118,37 +3118,37 @@
         <v>0.1255935877561569</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.1268680542707443</v>
+        <v>0.1268680691719055</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.1187395453453064</v>
+        <v>0.118739552795887</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.1180970594286919</v>
+        <v>0.1180970668792725</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.1174595803022385</v>
+        <v>0.1174595877528191</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.1173398569226265</v>
+        <v>0.1173398643732071</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.1730543375015259</v>
+        <v>0.1730543524026871</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.1711735725402832</v>
+        <v>0.1711735874414444</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1670238077640533</v>
+        <v>0.1670238226652145</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.166950985789299</v>
+        <v>0.1669510155916214</v>
       </c>
       <c r="BX4" t="n">
         <v>0.1651178598403931</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.1610991060733795</v>
+        <v>0.1610991209745407</v>
       </c>
       <c r="BZ4" t="n">
         <v>0.157201960682869</v>
@@ -3160,34 +3160,34 @@
         <v>0.1523000150918961</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.1481921076774597</v>
+        <v>0.1481921225786209</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.1445032060146332</v>
+        <v>0.1445032209157944</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.1378577202558517</v>
+        <v>0.1378577351570129</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.137981042265892</v>
+        <v>0.1379810571670532</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.1412186473608017</v>
+        <v>0.1412186622619629</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.1989464610815048</v>
+        <v>0.198946475982666</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.1968491971492767</v>
+        <v>0.1968492120504379</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.1940256357192993</v>
+        <v>0.1940256506204605</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.1900310665369034</v>
+        <v>0.1900310814380646</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.1863956451416016</v>
+        <v>0.1863956600427628</v>
       </c>
       <c r="CM4" t="n">
         <v>0.1797317117452621</v>
@@ -3205,28 +3205,28 @@
         <v>0.1732037663459778</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.1604510545730591</v>
+        <v>0.1604510694742203</v>
       </c>
       <c r="CS4" t="n">
         <v>0.1579433530569077</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.157959908246994</v>
+        <v>0.1579599231481552</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.1641116142272949</v>
+        <v>0.1641116291284561</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.234425276517868</v>
+        <v>0.2344253063201904</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.2218238860368729</v>
+        <v>0.2218239009380341</v>
       </c>
       <c r="CX4" t="n">
         <v>0.2217310965061188</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.2200888246297836</v>
+        <v>0.2200888395309448</v>
       </c>
       <c r="CZ4" t="n">
         <v>0.2108585834503174</v>
@@ -3238,7 +3238,7 @@
         <v>0.2078601270914078</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.2033772766590118</v>
+        <v>0.203377291560173</v>
       </c>
       <c r="DD4" t="n">
         <v>0.2028948664665222</v>
@@ -3250,10 +3250,10 @@
         <v>0.1915483474731445</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.1884981095790863</v>
+        <v>0.1884981393814087</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.187359482049942</v>
+        <v>0.1873594969511032</v>
       </c>
       <c r="DI4" t="n">
         <v>0.1899510324001312</v>
@@ -3262,22 +3262,22 @@
         <v>0.2506311237812042</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.2474002540111542</v>
+        <v>0.2474002838134766</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.2393234223127365</v>
+        <v>0.2393234372138977</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.2377154678106308</v>
+        <v>0.237715482711792</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.2307732403278351</v>
+        <v>0.2307732552289963</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.2318024784326553</v>
+        <v>0.2318024933338165</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.2260192483663559</v>
+        <v>0.2260192632675171</v>
       </c>
       <c r="DQ4" t="n">
         <v>0.2200573980808258</v>
@@ -3286,7 +3286,7 @@
         <v>0.2185904085636139</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2156789898872375</v>
+        <v>0.2156790047883987</v>
       </c>
       <c r="DT4" t="n">
         <v>0.2110443115234375</v>
@@ -3301,28 +3301,28 @@
         <v>0.2140649408102036</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.2673621773719788</v>
+        <v>0.2673622071743011</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.2573992908000946</v>
+        <v>0.257399320602417</v>
       </c>
       <c r="DZ4" t="n">
         <v>0.255962610244751</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.2486803233623505</v>
+        <v>0.2486803382635117</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.2480099946260452</v>
+        <v>0.2480100095272064</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.2421408146619797</v>
+        <v>0.2421408444643021</v>
       </c>
       <c r="ED4" t="n">
         <v>0.2394766062498093</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.2380269467830658</v>
+        <v>0.2380269765853882</v>
       </c>
       <c r="EF4" t="n">
         <v>0.2357321232557297</v>
@@ -3346,13 +3346,13 @@
         <v>0.2775877118110657</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.2743952870368958</v>
+        <v>0.2743953168392181</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.2702313363552094</v>
+        <v>0.2702313661575317</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.2634848654270172</v>
+        <v>0.2634848952293396</v>
       </c>
       <c r="EP4" t="n">
         <v>0.2666943967342377</v>
@@ -3376,7 +3376,7 @@
         <v>0.2481397092342377</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.248043566942215</v>
+        <v>0.2480435818433762</v>
       </c>
       <c r="EX4" t="n">
         <v>0.2479010969400406</v>
@@ -3394,7 +3394,7 @@
         <v>0.2742069363594055</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.2765864729881287</v>
+        <v>0.276586502790451</v>
       </c>
       <c r="FD4" t="n">
         <v>0.2670504450798035</v>
@@ -3418,16 +3418,16 @@
         <v>0.2614202797412872</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.2634250223636627</v>
+        <v>0.2634250521659851</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.2731781601905823</v>
+        <v>0.2731781899929047</v>
       </c>
       <c r="FM4" t="n">
         <v>0.28343465924263</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.2884003818035126</v>
+        <v>0.288400411605835</v>
       </c>
       <c r="FO4" t="n">
         <v>0.2886927425861359</v>
@@ -3451,10 +3451,10 @@
         <v>0.2800556123256683</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.2818794846534729</v>
+        <v>0.2818795144557953</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.2822479009628296</v>
+        <v>0.282247930765152</v>
       </c>
       <c r="FX4" t="n">
         <v>0.2814530730247498</v>
@@ -3469,7 +3469,7 @@
         <v>0.3110823929309845</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.3043985664844513</v>
+        <v>0.3043985962867737</v>
       </c>
       <c r="GC4" t="n">
         <v>0.3050969541072845</v>
@@ -3487,10 +3487,10 @@
         <v>0.302635669708252</v>
       </c>
       <c r="GH4" t="n">
-        <v>0.2989324629306793</v>
+        <v>0.2989324927330017</v>
       </c>
       <c r="GI4" t="n">
-        <v>0.2996359467506409</v>
+        <v>0.2996359765529633</v>
       </c>
       <c r="GJ4" t="n">
         <v>0.2999996840953827</v>
@@ -3502,16 +3502,16 @@
         <v>0.3104371726512909</v>
       </c>
       <c r="GM4" t="n">
-        <v>0.3168556988239288</v>
+        <v>0.3168557286262512</v>
       </c>
       <c r="GN4" t="n">
         <v>0.3321373164653778</v>
       </c>
       <c r="GO4" t="n">
-        <v>0.3398800790309906</v>
+        <v>0.339880108833313</v>
       </c>
       <c r="GP4" t="n">
-        <v>0.3328006863594055</v>
+        <v>0.3328007161617279</v>
       </c>
       <c r="GQ4" t="n">
         <v>0.3298621475696564</v>
@@ -3535,10 +3535,10 @@
         <v>0.3230894505977631</v>
       </c>
       <c r="GX4" t="n">
-        <v>0.3241716623306274</v>
+        <v>0.3241716921329498</v>
       </c>
       <c r="GY4" t="n">
-        <v>0.3244462013244629</v>
+        <v>0.3244462311267853</v>
       </c>
       <c r="GZ4" t="n">
         <v>0.3376578986644745</v>
@@ -3553,13 +3553,13 @@
         <v>0.3573117852210999</v>
       </c>
       <c r="HD4" t="n">
-        <v>0.3454219698905945</v>
+        <v>0.3454219996929169</v>
       </c>
       <c r="HE4" t="n">
         <v>0.3406133651733398</v>
       </c>
       <c r="HF4" t="n">
-        <v>0.3421693444252014</v>
+        <v>0.3421693742275238</v>
       </c>
       <c r="HG4" t="n">
         <v>0.3487009406089783</v>
@@ -3571,13 +3571,13 @@
         <v>0.3458665907382965</v>
       </c>
       <c r="HJ4" t="n">
-        <v>0.3484143614768982</v>
+        <v>0.3484143912792206</v>
       </c>
       <c r="HK4" t="n">
-        <v>0.3421349227428436</v>
+        <v>0.342134952545166</v>
       </c>
       <c r="HL4" t="n">
-        <v>0.3438485264778137</v>
+        <v>0.3438485562801361</v>
       </c>
       <c r="HM4" t="n">
         <v>0.3408194780349731</v>
@@ -3589,13 +3589,15 @@
         <v>0.3782960772514343</v>
       </c>
       <c r="HP4" t="n">
-        <v>0.3580786883831024</v>
+        <v>0.3580787181854248</v>
       </c>
       <c r="HQ4" t="n">
         <v>0.3464901149272919</v>
       </c>
-      <c r="HR4" s="1" t="n">
-        <v>55514</v>
+      <c r="HR4" t="inlineStr">
+        <is>
+          <t>27/12/2051</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3605,22 +3607,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02477490529417992</v>
+        <v>0.02477490715682507</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03348959609866142</v>
+        <v>0.03348959982395172</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03558918461203575</v>
+        <v>0.03558918833732605</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03713205829262733</v>
+        <v>0.03713206201791763</v>
       </c>
       <c r="F5" t="n">
         <v>0.03760436549782753</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03689340129494667</v>
+        <v>0.03689340502023697</v>
       </c>
       <c r="H5" t="n">
         <v>0.03631202504038811</v>
@@ -3629,46 +3631,46 @@
         <v>0.03596088662743568</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03616899996995926</v>
+        <v>0.03616900369524956</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03548309206962585</v>
+        <v>0.03548309579491615</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03444059938192368</v>
+        <v>0.03444060310721397</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03341441601514816</v>
+        <v>0.03341441974043846</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03333155065774918</v>
+        <v>0.03333155438303947</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03390952199697495</v>
+        <v>0.03390952572226524</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04998867586255074</v>
+        <v>0.04998867958784103</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06135455518960953</v>
+        <v>0.06135455891489983</v>
       </c>
       <c r="R5" t="n">
         <v>0.0641135647892952</v>
       </c>
       <c r="S5" t="n">
-        <v>0.065064437687397</v>
+        <v>0.0650644451379776</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06629300862550735</v>
+        <v>0.06629301607608795</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06393595784902573</v>
+        <v>0.06393596529960632</v>
       </c>
       <c r="V5" t="n">
         <v>0.06474974751472473</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06427901983261108</v>
+        <v>0.06427902728319168</v>
       </c>
       <c r="X5" t="n">
         <v>0.06373234838247299</v>
@@ -3680,7 +3682,7 @@
         <v>0.06017992272973061</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05788280814886093</v>
+        <v>0.05788281187415123</v>
       </c>
       <c r="AB5" t="n">
         <v>0.05771336704492569</v>
@@ -3689,16 +3691,16 @@
         <v>0.05912180244922638</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.08165702968835831</v>
+        <v>0.0816570371389389</v>
       </c>
       <c r="AE5" t="n">
         <v>0.09361825883388519</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.09366682171821594</v>
+        <v>0.09366682916879654</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.09562629461288452</v>
+        <v>0.09562630206346512</v>
       </c>
       <c r="AH5" t="n">
         <v>0.09585040062665939</v>
@@ -3707,13 +3709,13 @@
         <v>0.09515044838190079</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.09197987616062164</v>
+        <v>0.09197988361120224</v>
       </c>
       <c r="AK5" t="n">
         <v>0.09098777920007706</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.09125534445047379</v>
+        <v>0.09125535190105438</v>
       </c>
       <c r="AM5" t="n">
         <v>0.08822953701019287</v>
@@ -3725,7 +3727,7 @@
         <v>0.08196645230054855</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.08415248245000839</v>
+        <v>0.08415248990058899</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.08484955877065659</v>
@@ -3734,28 +3736,28 @@
         <v>0.1108589917421341</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.1180406883358955</v>
+        <v>0.1180407032370567</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.1187440752983093</v>
+        <v>0.1187440901994705</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1202830150723457</v>
+        <v>0.1202830225229263</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.1183508336544037</v>
+        <v>0.1183508411049843</v>
       </c>
       <c r="AW5" t="n">
         <v>0.1140555590391159</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1145311817526817</v>
+        <v>0.1145311892032623</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.1136466041207314</v>
+        <v>0.113646611571312</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.1122476980090141</v>
+        <v>0.1122477054595947</v>
       </c>
       <c r="BA5" t="n">
         <v>0.1085412129759789</v>
@@ -3764,10 +3766,10 @@
         <v>0.1038171276450157</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.1021154597401619</v>
+        <v>0.1021154671907425</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.1008310168981552</v>
+        <v>0.1008310243487358</v>
       </c>
       <c r="BE5" t="n">
         <v>0.1038637906312943</v>
@@ -3776,13 +3778,13 @@
         <v>0.1392594128847122</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.1415179520845413</v>
+        <v>0.1415179669857025</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.1408963054418564</v>
+        <v>0.1408963203430176</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.1374604552984238</v>
+        <v>0.137460470199585</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.1375902742147446</v>
@@ -3803,10 +3805,10 @@
         <v>0.1275741904973984</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1193665042519569</v>
+        <v>0.1193665117025375</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.1187270283699036</v>
+        <v>0.1187270358204842</v>
       </c>
       <c r="BR5" t="n">
         <v>0.1180975437164307</v>
@@ -3815,10 +3817,10 @@
         <v>0.1179642900824547</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.1742985844612122</v>
+        <v>0.1742985993623734</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.1723891496658325</v>
+        <v>0.1723891645669937</v>
       </c>
       <c r="BV5" t="n">
         <v>0.1682400405406952</v>
@@ -3830,7 +3832,7 @@
         <v>0.1661363840103149</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.1621057093143463</v>
+        <v>0.1621057242155075</v>
       </c>
       <c r="BZ5" t="n">
         <v>0.1581279933452606</v>
@@ -3857,28 +3859,28 @@
         <v>0.1419283300638199</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.2002800852060318</v>
+        <v>0.200280100107193</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.198260635137558</v>
+        <v>0.1982606649398804</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.1953572034835815</v>
+        <v>0.1953572183847427</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.1912230551242828</v>
+        <v>0.191223070025444</v>
       </c>
       <c r="CL5" t="n">
         <v>0.1875691264867783</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.180831715464592</v>
+        <v>0.1808317303657532</v>
       </c>
       <c r="CN5" t="n">
         <v>0.1813734620809555</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.174965888261795</v>
+        <v>0.1749659031629562</v>
       </c>
       <c r="CP5" t="n">
         <v>0.1733799576759338</v>
@@ -3893,37 +3895,37 @@
         <v>0.1586896926164627</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.1586892455816269</v>
+        <v>0.1586892604827881</v>
       </c>
       <c r="CU5" t="n">
         <v>0.1648840308189392</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.2358627766370773</v>
+        <v>0.2358627915382385</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.2233276814222336</v>
+        <v>0.2233276963233948</v>
       </c>
       <c r="CX5" t="n">
         <v>0.2230869382619858</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.221435546875</v>
+        <v>0.2214355617761612</v>
       </c>
       <c r="CZ5" t="n">
         <v>0.2120961099863052</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.2085774093866348</v>
+        <v>0.208577424287796</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.208969920873642</v>
+        <v>0.2089699357748032</v>
       </c>
       <c r="DC5" t="n">
         <v>0.2043729573488235</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.2038628160953522</v>
+        <v>0.2038628309965134</v>
       </c>
       <c r="DE5" t="n">
         <v>0.1982628107070923</v>
@@ -3938,13 +3940,13 @@
         <v>0.1881154328584671</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.190725713968277</v>
+        <v>0.1907257437705994</v>
       </c>
       <c r="DJ5" t="n">
         <v>0.2522956728935242</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.2489318996667862</v>
+        <v>0.2489319145679474</v>
       </c>
       <c r="DL5" t="n">
         <v>0.2407002151012421</v>
@@ -3956,7 +3958,7 @@
         <v>0.2320291697978973</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.2329266220331192</v>
+        <v>0.2329266369342804</v>
       </c>
       <c r="DP5" t="n">
         <v>0.2270579189062119</v>
@@ -3968,7 +3970,7 @@
         <v>0.2195329219102859</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.2165657877922058</v>
+        <v>0.2165658175945282</v>
       </c>
       <c r="DT5" t="n">
         <v>0.2118554562330246</v>
@@ -3977,22 +3979,22 @@
         <v>0.2103708535432816</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.2127471417188644</v>
+        <v>0.2127471566200256</v>
       </c>
       <c r="DW5" t="n">
         <v>0.2148200124502182</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.2688837349414825</v>
+        <v>0.2688837647438049</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.2588129937648773</v>
+        <v>0.2588130235671997</v>
       </c>
       <c r="DZ5" t="n">
         <v>0.2573569416999817</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.2498797178268433</v>
+        <v>0.2498797327280045</v>
       </c>
       <c r="EB5" t="n">
         <v>0.2491326779127121</v>
@@ -4007,7 +4009,7 @@
         <v>0.238980308175087</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.236628070473671</v>
+        <v>0.2366280853748322</v>
       </c>
       <c r="EG5" t="n">
         <v>0.2345291972160339</v>
@@ -4076,7 +4078,7 @@
         <v>0.2749622166156769</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.2773380875587463</v>
+        <v>0.2773381173610687</v>
       </c>
       <c r="FD5" t="n">
         <v>0.2677676975727081</v>
@@ -4100,7 +4102,7 @@
         <v>0.2621167302131653</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.2640602290630341</v>
+        <v>0.2640602588653564</v>
       </c>
       <c r="FL5" t="n">
         <v>0.2738323211669922</v>
@@ -4109,7 +4111,7 @@
         <v>0.2841176986694336</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.2892331480979919</v>
+        <v>0.2892331779003143</v>
       </c>
       <c r="FO5" t="n">
         <v>0.289486825466156</v>
@@ -4118,7 +4120,7 @@
         <v>0.2814616560935974</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.2795988917350769</v>
+        <v>0.2795989215373993</v>
       </c>
       <c r="FR5" t="n">
         <v>0.2849221229553223</v>
@@ -4127,7 +4129,7 @@
         <v>0.2826381623744965</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.2828284204006195</v>
+        <v>0.2828284502029419</v>
       </c>
       <c r="FU5" t="n">
         <v>0.2808769345283508</v>
@@ -4169,7 +4171,7 @@
         <v>0.3037469387054443</v>
       </c>
       <c r="GH5" t="n">
-        <v>0.3000350296497345</v>
+        <v>0.3000350594520569</v>
       </c>
       <c r="GI5" t="n">
         <v>0.3007134795188904</v>
@@ -4193,7 +4195,7 @@
         <v>0.3410508632659912</v>
       </c>
       <c r="GP5" t="n">
-        <v>0.3339481055736542</v>
+        <v>0.3339481353759766</v>
       </c>
       <c r="GQ5" t="n">
         <v>0.3309441804885864</v>
@@ -4205,7 +4207,7 @@
         <v>0.3282979726791382</v>
       </c>
       <c r="GT5" t="n">
-        <v>0.3296602666378021</v>
+        <v>0.3296602964401245</v>
       </c>
       <c r="GU5" t="n">
         <v>0.3239479064941406</v>
@@ -4217,31 +4219,31 @@
         <v>0.3242652416229248</v>
       </c>
       <c r="GX5" t="n">
-        <v>0.3253836929798126</v>
+        <v>0.325383722782135</v>
       </c>
       <c r="GY5" t="n">
-        <v>0.3256891667842865</v>
+        <v>0.3256891965866089</v>
       </c>
       <c r="GZ5" t="n">
-        <v>0.3388771116733551</v>
+        <v>0.3388771414756775</v>
       </c>
       <c r="HA5" t="n">
         <v>0.3517445623874664</v>
       </c>
       <c r="HB5" t="n">
-        <v>0.3643373250961304</v>
+        <v>0.3643373548984528</v>
       </c>
       <c r="HC5" t="n">
-        <v>0.3583309054374695</v>
+        <v>0.3583309352397919</v>
       </c>
       <c r="HD5" t="n">
         <v>0.3469274640083313</v>
       </c>
       <c r="HE5" t="n">
-        <v>0.3420506119728088</v>
+        <v>0.3420506715774536</v>
       </c>
       <c r="HF5" t="n">
-        <v>0.3436167240142822</v>
+        <v>0.3436167538166046</v>
       </c>
       <c r="HG5" t="n">
         <v>0.3501987755298615</v>
@@ -4250,13 +4252,13 @@
         <v>0.3490679562091827</v>
       </c>
       <c r="HI5" t="n">
-        <v>0.3474437296390533</v>
+        <v>0.3474437594413757</v>
       </c>
       <c r="HJ5" t="n">
         <v>0.3500360250473022</v>
       </c>
       <c r="HK5" t="n">
-        <v>0.3437706828117371</v>
+        <v>0.3437707126140594</v>
       </c>
       <c r="HL5" t="n">
         <v>0.3455227017402649</v>
@@ -4274,10 +4276,12 @@
         <v>0.3593225479125977</v>
       </c>
       <c r="HQ5" t="n">
-        <v>0.3474158048629761</v>
-      </c>
-      <c r="HR5" s="1" t="n">
-        <v>55515</v>
+        <v>0.3474158346652985</v>
+      </c>
+      <c r="HR5" t="inlineStr">
+        <is>
+          <t>29/12/2051</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4287,31 +4291,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02522354014217854</v>
+        <v>0.02522354759275913</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03395713865756989</v>
+        <v>0.03395714238286018</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03604546934366226</v>
+        <v>0.03604547306895256</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03757196664810181</v>
+        <v>0.0375719778239727</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03801929205656052</v>
+        <v>0.03801929950714111</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03728371113538742</v>
+        <v>0.03728371486067772</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03668216243386269</v>
+        <v>0.03668216615915298</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03632709756493568</v>
+        <v>0.03632710501551628</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03652737662196159</v>
+        <v>0.03652738034725189</v>
       </c>
       <c r="K6" t="n">
         <v>0.03582604974508286</v>
@@ -4320,7 +4324,7 @@
         <v>0.03475445881485939</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03368915989995003</v>
+        <v>0.03368916362524033</v>
       </c>
       <c r="N6" t="n">
         <v>0.033602524548769</v>
@@ -4329,28 +4333,28 @@
         <v>0.03417399153113365</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05067431181669235</v>
+        <v>0.05067432299256325</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.06207230687141418</v>
+        <v>0.06207231432199478</v>
       </c>
       <c r="R6" t="n">
-        <v>0.06484448164701462</v>
+        <v>0.06484449654817581</v>
       </c>
       <c r="S6" t="n">
         <v>0.06573161482810974</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06695108860731125</v>
+        <v>0.06695109605789185</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06452777981758118</v>
+        <v>0.06452778726816177</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06533069163560867</v>
+        <v>0.06533069908618927</v>
       </c>
       <c r="W6" t="n">
-        <v>0.06482532620429993</v>
+        <v>0.06482533365488052</v>
       </c>
       <c r="X6" t="n">
         <v>0.06428014487028122</v>
@@ -4359,112 +4363,112 @@
         <v>0.06382252275943756</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.06065203621983528</v>
+        <v>0.06065203994512558</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.05830798670649529</v>
+        <v>0.05830799415707588</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.05814253911375999</v>
+        <v>0.05814255028963089</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.05953730270266533</v>
+        <v>0.05953731015324593</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.08252640813589096</v>
+        <v>0.08252641558647156</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.09453823417425156</v>
+        <v>0.09453824162483215</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.09459768235683441</v>
+        <v>0.0945977047085762</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.09646134078502655</v>
+        <v>0.09646135568618774</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.09666330367326736</v>
+        <v>0.09666331112384796</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.09592657536268234</v>
+        <v>0.09592658281326294</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.09270170331001282</v>
+        <v>0.09270171076059341</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.09166421741247177</v>
+        <v>0.09166423231363297</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.09194351732730865</v>
+        <v>0.09194352477788925</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0888768658041954</v>
+        <v>0.088876873254776</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.08451274782419205</v>
+        <v>0.08451275527477264</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.08248945325613022</v>
+        <v>0.08248946070671082</v>
       </c>
       <c r="AP6" t="n">
         <v>0.08469582349061966</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.08537336438894272</v>
+        <v>0.08537337183952332</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.1118640378117561</v>
+        <v>0.1118640527129173</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.1191564276814461</v>
+        <v>0.1191564351320267</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.1197955384850502</v>
+        <v>0.1197955459356308</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1211981922388077</v>
+        <v>0.1211981996893883</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.1193279400467873</v>
+        <v>0.1193279549479485</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.1149034574627876</v>
+        <v>0.1149034649133682</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1153632625937462</v>
+        <v>0.1153632700443268</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.1144291609525681</v>
+        <v>0.1144291684031487</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.1130299717187881</v>
+        <v>0.1130299791693687</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.1092603504657745</v>
+        <v>0.1092603579163551</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.1044370457530022</v>
+        <v>0.1044370532035828</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.1027124673128128</v>
+        <v>0.1027124747633934</v>
       </c>
       <c r="BD6" t="n">
         <v>0.10142582654953</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.1044525802135468</v>
+        <v>0.1044525876641273</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.1403848528862</v>
+        <v>0.1403848677873611</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.1427127420902252</v>
+        <v>0.1427127718925476</v>
       </c>
       <c r="BH6" t="n">
         <v>0.142006054520607</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.1385051906108856</v>
+        <v>0.1385052055120468</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.1386381387710571</v>
@@ -4476,37 +4480,37 @@
         <v>0.1316160708665848</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.1290475577116013</v>
+        <v>0.1290475726127625</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.1271607130765915</v>
+        <v>0.1271607279777527</v>
       </c>
       <c r="BO6" t="n">
         <v>0.1283615678548813</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.120036356151104</v>
+        <v>0.1200363636016846</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.1193666011095047</v>
+        <v>0.1193666085600853</v>
       </c>
       <c r="BR6" t="n">
         <v>0.1187366172671318</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.1185799688100815</v>
+        <v>0.1185799762606621</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.1758566647768021</v>
+        <v>0.1758566796779633</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.1738847196102142</v>
+        <v>0.1738847345113754</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1697055399417877</v>
+        <v>0.1697055548429489</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.169389545917511</v>
+        <v>0.1693895608186722</v>
       </c>
       <c r="BX6" t="n">
         <v>0.1673218011856079</v>
@@ -4533,31 +4537,31 @@
         <v>0.1392474919557571</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.139367938041687</v>
+        <v>0.1393679529428482</v>
       </c>
       <c r="CG6" t="n">
         <v>0.1426165997982025</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.2018893212080002</v>
+        <v>0.2018893510103226</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.1999574303627014</v>
+        <v>0.1999574452638626</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.1969169080257416</v>
+        <v>0.196916937828064</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.1926058828830719</v>
+        <v>0.1926058977842331</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.1889018565416336</v>
+        <v>0.1889018714427948</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.1820531785488129</v>
+        <v>0.1820531934499741</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.1825180053710938</v>
+        <v>0.1825180202722549</v>
       </c>
       <c r="CO6" t="n">
         <v>0.1760341227054596</v>
@@ -4566,13 +4570,13 @@
         <v>0.1743953078985214</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.1750194877386093</v>
+        <v>0.1750195026397705</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.1620153784751892</v>
+        <v>0.1620153933763504</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.1594205647706985</v>
+        <v>0.1594205796718597</v>
       </c>
       <c r="CT6" t="n">
         <v>0.1593927592039108</v>
@@ -4581,34 +4585,34 @@
         <v>0.1656244844198227</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.2375306189060211</v>
+        <v>0.2375306338071823</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.225055143237114</v>
+        <v>0.2250551581382751</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.2246175706386566</v>
+        <v>0.2246175855398178</v>
       </c>
       <c r="CY6" t="n">
         <v>0.2229142487049103</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.2134500592947006</v>
+        <v>0.2134500741958618</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.209853321313858</v>
+        <v>0.2098533362150192</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.2101660370826721</v>
+        <v>0.2101660519838333</v>
       </c>
       <c r="DC6" t="n">
         <v>0.2054412215948105</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.2048725783824921</v>
+        <v>0.2048725932836533</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.1992050260305405</v>
+        <v>0.1992050409317017</v>
       </c>
       <c r="DF6" t="n">
         <v>0.19318488240242</v>
@@ -4632,13 +4636,13 @@
         <v>0.2422073781490326</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.240484282374382</v>
+        <v>0.2404842972755432</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.2333645075559616</v>
+        <v>0.2333645224571228</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.23412124812603</v>
+        <v>0.2341212630271912</v>
       </c>
       <c r="DP6" t="n">
         <v>0.2281384170055389</v>
@@ -4662,10 +4666,10 @@
         <v>0.2134488672018051</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.2155052125453949</v>
+        <v>0.2155052274465561</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.2705222070217133</v>
+        <v>0.2705222368240356</v>
       </c>
       <c r="DY6" t="n">
         <v>0.2603305876255035</v>
@@ -4677,16 +4681,16 @@
         <v>0.2511501014232635</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.2502939701080322</v>
+        <v>0.2502939999103546</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.2443028390407562</v>
+        <v>0.2443028688430786</v>
       </c>
       <c r="ED6" t="n">
         <v>0.24149489402771</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.239924356341362</v>
+        <v>0.2399243861436844</v>
       </c>
       <c r="EF6" t="n">
         <v>0.2375199049711227</v>
@@ -4713,10 +4717,10 @@
         <v>0.2767636775970459</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.2724239528179169</v>
+        <v>0.2724239826202393</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.2654723525047302</v>
+        <v>0.2654723823070526</v>
       </c>
       <c r="EP6" t="n">
         <v>0.268595963716507</v>
@@ -4725,7 +4729,7 @@
         <v>0.2575906217098236</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.2573244273662567</v>
+        <v>0.2573244571685791</v>
       </c>
       <c r="ES6" t="n">
         <v>0.2511412501335144</v>
@@ -4734,7 +4738,7 @@
         <v>0.2539514601230621</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.2530920505523682</v>
+        <v>0.2530920803546906</v>
       </c>
       <c r="EV6" t="n">
         <v>0.2495596557855606</v>
@@ -4746,7 +4750,7 @@
         <v>0.2491025924682617</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.2607878744602203</v>
+        <v>0.2607879042625427</v>
       </c>
       <c r="EZ6" t="n">
         <v>0.2858297526836395</v>
@@ -4770,7 +4774,7 @@
         <v>0.2695747017860413</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.2662915587425232</v>
+        <v>0.2662915885448456</v>
       </c>
       <c r="FH6" t="n">
         <v>0.2617667615413666</v>
@@ -4785,7 +4789,7 @@
         <v>0.2645911872386932</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.274368554353714</v>
+        <v>0.2743685841560364</v>
       </c>
       <c r="FM6" t="n">
         <v>0.2846744060516357</v>
@@ -4797,22 +4801,22 @@
         <v>0.2901950776576996</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.2821386456489563</v>
+        <v>0.2821386754512787</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.2802689075469971</v>
+        <v>0.2802689373493195</v>
       </c>
       <c r="FR6" t="n">
         <v>0.2856284379959106</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.2833361029624939</v>
+        <v>0.2833361327648163</v>
       </c>
       <c r="FT6" t="n">
         <v>0.2835452556610107</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.2815987169742584</v>
+        <v>0.2815987467765808</v>
       </c>
       <c r="FV6" t="n">
         <v>0.2834430634975433</v>
@@ -4827,10 +4831,10 @@
         <v>0.293546050786972</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.2979891896247864</v>
+        <v>0.2979892194271088</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.3126568794250488</v>
+        <v>0.3126569092273712</v>
       </c>
       <c r="GB6" t="n">
         <v>0.3064280450344086</v>
@@ -4839,16 +4843,16 @@
         <v>0.3071700930595398</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.3083421885967255</v>
+        <v>0.3083422183990479</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.3083177506923676</v>
+        <v>0.3083177804946899</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.3063856065273285</v>
+        <v>0.3063856363296509</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.3047313094139099</v>
+        <v>0.3047313392162323</v>
       </c>
       <c r="GH6" t="n">
         <v>0.3010034561157227</v>
@@ -4857,25 +4861,25 @@
         <v>0.3016247153282166</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.3020752370357513</v>
+        <v>0.3020752668380737</v>
       </c>
       <c r="GK6" t="n">
         <v>0.3059440553188324</v>
       </c>
       <c r="GL6" t="n">
-        <v>0.312444269657135</v>
+        <v>0.3124442994594574</v>
       </c>
       <c r="GM6" t="n">
-        <v>0.3187808394432068</v>
+        <v>0.3187808692455292</v>
       </c>
       <c r="GN6" t="n">
-        <v>0.3341204524040222</v>
+        <v>0.3341204822063446</v>
       </c>
       <c r="GO6" t="n">
         <v>0.3420371115207672</v>
       </c>
       <c r="GP6" t="n">
-        <v>0.3349483609199524</v>
+        <v>0.3349483907222748</v>
       </c>
       <c r="GQ6" t="n">
         <v>0.3318676352500916</v>
@@ -4884,13 +4888,13 @@
         <v>0.3308370113372803</v>
       </c>
       <c r="GS6" t="n">
-        <v>0.3292349576950073</v>
+        <v>0.3292349874973297</v>
       </c>
       <c r="GT6" t="n">
-        <v>0.3306314945220947</v>
+        <v>0.3306315243244171</v>
       </c>
       <c r="GU6" t="n">
-        <v>0.3249135613441467</v>
+        <v>0.3249135911464691</v>
       </c>
       <c r="GV6" t="n">
         <v>0.3301834464073181</v>
@@ -4902,7 +4906,7 @@
         <v>0.3264118134975433</v>
       </c>
       <c r="GY6" t="n">
-        <v>0.3267403841018677</v>
+        <v>0.3267404139041901</v>
       </c>
       <c r="GZ6" t="n">
         <v>0.3399000763893127</v>
@@ -4911,22 +4915,22 @@
         <v>0.3527229428291321</v>
       </c>
       <c r="HB6" t="n">
-        <v>0.3654146790504456</v>
+        <v>0.3654147088527679</v>
       </c>
       <c r="HC6" t="n">
-        <v>0.3591762483119965</v>
+        <v>0.3591762781143188</v>
       </c>
       <c r="HD6" t="n">
         <v>0.3481805026531219</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.3432444632053375</v>
+        <v>0.3432445228099823</v>
       </c>
       <c r="HF6" t="n">
         <v>0.3448282480239868</v>
       </c>
       <c r="HG6" t="n">
-        <v>0.3514571487903595</v>
+        <v>0.3514571785926819</v>
       </c>
       <c r="HH6" t="n">
         <v>0.3503752946853638</v>
@@ -4935,31 +4939,33 @@
         <v>0.3487776517868042</v>
       </c>
       <c r="HJ6" t="n">
-        <v>0.3514176309108734</v>
+        <v>0.3514176607131958</v>
       </c>
       <c r="HK6" t="n">
-        <v>0.3451667428016663</v>
+        <v>0.345166802406311</v>
       </c>
       <c r="HL6" t="n">
         <v>0.3469631969928741</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.3439945876598358</v>
+        <v>0.3439946472644806</v>
       </c>
       <c r="HN6" t="n">
         <v>0.3671712577342987</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.3814215958118439</v>
+        <v>0.3814216256141663</v>
       </c>
       <c r="HP6" t="n">
-        <v>0.3603777885437012</v>
+        <v>0.3603778183460236</v>
       </c>
       <c r="HQ6" t="n">
         <v>0.3481786847114563</v>
       </c>
-      <c r="HR6" s="1" t="n">
-        <v>55516</v>
+      <c r="HR6" t="inlineStr">
+        <is>
+          <t>30/12/2051</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4969,10 +4975,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02562805451452732</v>
+        <v>0.02562805823981762</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03436929360032082</v>
+        <v>0.03436929732561111</v>
       </c>
       <c r="D7" t="n">
         <v>0.03644922748208046</v>
@@ -4981,37 +4987,37 @@
         <v>0.03796205297112465</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03838392347097397</v>
+        <v>0.03838392719626427</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03762638941407204</v>
+        <v>0.03762639313936234</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03700553998351097</v>
+        <v>0.03700554370880127</v>
       </c>
       <c r="I7" t="n">
         <v>0.03664589673280716</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03683914616703987</v>
+        <v>0.03683914989233017</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03612423315644264</v>
+        <v>0.03612423688173294</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03502486273646355</v>
+        <v>0.03502486646175385</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03393165394663811</v>
+        <v>0.03393165767192841</v>
       </c>
       <c r="N7" t="n">
         <v>0.03384201601147652</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03441000357270241</v>
+        <v>0.03441000729799271</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0513003021478653</v>
+        <v>0.05130030587315559</v>
       </c>
       <c r="Q7" t="n">
         <v>0.06270501762628555</v>
@@ -5020,10 +5026,10 @@
         <v>0.06548599153757095</v>
       </c>
       <c r="S7" t="n">
-        <v>0.06631483137607574</v>
+        <v>0.06631483882665634</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06752477586269379</v>
+        <v>0.06752478331327438</v>
       </c>
       <c r="U7" t="n">
         <v>0.06504668295383453</v>
@@ -5038,19 +5044,19 @@
         <v>0.06474866718053818</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.06426893174648285</v>
+        <v>0.06426893919706345</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.06105054169893265</v>
+        <v>0.06105054542422295</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.05867773294448853</v>
+        <v>0.05867774039506912</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0585140734910965</v>
+        <v>0.05851408094167709</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.05990136787295341</v>
+        <v>0.05990137532353401</v>
       </c>
       <c r="AD7" t="n">
         <v>0.08329813182353973</v>
@@ -5062,58 +5068,58 @@
         <v>0.09540054947137833</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.09717480093240738</v>
+        <v>0.09717480838298798</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.09735792875289917</v>
+        <v>0.09735793620347977</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.09658827632665634</v>
+        <v>0.09658828377723694</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.09331237524747849</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.09223896265029907</v>
+        <v>0.09223897010087967</v>
       </c>
       <c r="AL7" t="n">
         <v>0.09251928329467773</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.08941950649023056</v>
+        <v>0.08941951394081116</v>
       </c>
       <c r="AN7" t="n">
         <v>0.08498422801494598</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.08293697237968445</v>
+        <v>0.08293697983026505</v>
       </c>
       <c r="AP7" t="n">
         <v>0.08515981584787369</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.08582130074501038</v>
+        <v>0.08582130819559097</v>
       </c>
       <c r="AR7" t="n">
         <v>0.1127525791525841</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.1201004907488823</v>
+        <v>0.1201004981994629</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.1206775680184364</v>
+        <v>0.120677575469017</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1219590157270432</v>
+        <v>0.1219590306282043</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.1201567947864532</v>
+        <v>0.1201568022370338</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.1156130060553551</v>
+        <v>0.1156130135059357</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1160600632429123</v>
+        <v>0.1160600781440735</v>
       </c>
       <c r="AY7" t="n">
         <v>0.1150865480303764</v>
@@ -5122,19 +5128,19 @@
         <v>0.1136777251958847</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.1098615154623985</v>
+        <v>0.1098615229129791</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.1049540415406227</v>
+        <v>0.1049540489912033</v>
       </c>
       <c r="BC7" t="n">
         <v>0.103217288851738</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.1019349172711372</v>
+        <v>0.1019349247217178</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.1049547269940376</v>
+        <v>0.1049547344446182</v>
       </c>
       <c r="BF7" t="n">
         <v>0.1413466781377792</v>
@@ -5146,13 +5152,13 @@
         <v>0.1429286599159241</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.1393507570028305</v>
+        <v>0.1393507719039917</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.1395094394683838</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.1330464035272598</v>
+        <v>0.133046418428421</v>
       </c>
       <c r="BL7" t="n">
         <v>0.1323313266038895</v>
@@ -5164,19 +5170,19 @@
         <v>0.1278405636548996</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.1290033757686615</v>
+        <v>0.1290033906698227</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1205901727080345</v>
+        <v>0.1205901801586151</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.119907982647419</v>
+        <v>0.1199079975485802</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.1192829310894012</v>
+        <v>0.1192829385399818</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.1191109493374825</v>
+        <v>0.119110956788063</v>
       </c>
       <c r="BT7" t="n">
         <v>0.1771750897169113</v>
@@ -5185,31 +5191,31 @@
         <v>0.1751107722520828</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1709050685167313</v>
+        <v>0.1709050834178925</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.1704538315534592</v>
+        <v>0.1704538464546204</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.1682902723550797</v>
+        <v>0.1682902872562408</v>
       </c>
       <c r="BY7" t="n">
         <v>0.164189800620079</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.1600387543439865</v>
+        <v>0.1600387692451477</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.1570315659046173</v>
+        <v>0.1570315808057785</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.1548685133457184</v>
+        <v>0.1548685282468796</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.1505695879459381</v>
+        <v>0.1505696028470993</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.1466484367847443</v>
+        <v>0.1466484516859055</v>
       </c>
       <c r="CE7" t="n">
         <v>0.1398404389619827</v>
@@ -5218,40 +5224,40 @@
         <v>0.1399616748094559</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.143212616443634</v>
+        <v>0.1432126313447952</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.2032133936882019</v>
+        <v>0.2032134085893631</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.2013147175312042</v>
+        <v>0.2013147324323654</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.1981805264949799</v>
+        <v>0.1981805562973022</v>
       </c>
       <c r="CK7" t="n">
         <v>0.1937174201011658</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.1899826973676682</v>
+        <v>0.1899827122688293</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.183054506778717</v>
+        <v>0.1830545216798782</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.183454766869545</v>
+        <v>0.1834547817707062</v>
       </c>
       <c r="CO7" t="n">
         <v>0.1769076287746429</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.1752196848392487</v>
+        <v>0.1752196997404099</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.1757816821336746</v>
+        <v>0.1757816970348358</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.1626796722412109</v>
+        <v>0.1626796871423721</v>
       </c>
       <c r="CS7" t="n">
         <v>0.1600495278835297</v>
@@ -5260,16 +5266,16 @@
         <v>0.1600085198879242</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.1662711948156357</v>
+        <v>0.1662712097167969</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.2388625741004944</v>
+        <v>0.2388625890016556</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.2264378815889359</v>
+        <v>0.2264379113912582</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.2258539795875549</v>
+        <v>0.2258539944887161</v>
       </c>
       <c r="CY7" t="n">
         <v>0.2241293787956238</v>
@@ -5281,19 +5287,19 @@
         <v>0.210890606045723</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.2111420929431915</v>
+        <v>0.2111421078443527</v>
       </c>
       <c r="DC7" t="n">
         <v>0.2063076049089432</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.2057186663150787</v>
+        <v>0.2057186812162399</v>
       </c>
       <c r="DE7" t="n">
         <v>0.1999949216842651</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.1938789486885071</v>
+        <v>0.1938789635896683</v>
       </c>
       <c r="DG7" t="n">
         <v>0.19071364402771</v>
@@ -5302,31 +5308,31 @@
         <v>0.1894662082195282</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.1920864433050156</v>
+        <v>0.1920864582061768</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.2556321024894714</v>
+        <v>0.2556321322917938</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.2519600093364716</v>
+        <v>0.2519600391387939</v>
       </c>
       <c r="DL7" t="n">
         <v>0.2434325069189072</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.2416587322950363</v>
+        <v>0.2416587471961975</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.2344612777233124</v>
+        <v>0.2344612926244736</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.2350915521383286</v>
+        <v>0.2350915670394897</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.2290369272232056</v>
+        <v>0.2290369421243668</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.2229118645191193</v>
+        <v>0.2229118943214417</v>
       </c>
       <c r="DR7" t="n">
         <v>0.2212967574596405</v>
@@ -5338,22 +5344,22 @@
         <v>0.2133280038833618</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.2116210907697678</v>
+        <v>0.2116211205720901</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.2140780091285706</v>
+        <v>0.2140780240297318</v>
       </c>
       <c r="DW7" t="n">
         <v>0.2161291092634201</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.2718741893768311</v>
+        <v>0.2718742191791534</v>
       </c>
       <c r="DY7" t="n">
         <v>0.2615775167942047</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.2600552141666412</v>
+        <v>0.2600552439689636</v>
       </c>
       <c r="EA7" t="n">
         <v>0.2521920204162598</v>
@@ -5362,22 +5368,22 @@
         <v>0.2512693107128143</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.2452240288257599</v>
+        <v>0.2452240586280823</v>
       </c>
       <c r="ED7" t="n">
         <v>0.2423636168241501</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.2407473772764206</v>
+        <v>0.240747407078743</v>
       </c>
       <c r="EF7" t="n">
         <v>0.2382859736680984</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.2361034899950027</v>
+        <v>0.2361035197973251</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.2240142971277237</v>
+        <v>0.2240143269300461</v>
       </c>
       <c r="EI7" t="n">
         <v>0.2274878025054932</v>
@@ -5392,7 +5398,7 @@
         <v>0.2813215851783752</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.277779221534729</v>
+        <v>0.2777792513370514</v>
       </c>
       <c r="EN7" t="n">
         <v>0.273372083902359</v>
@@ -5404,46 +5410,46 @@
         <v>0.2694180011749268</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.2583473324775696</v>
+        <v>0.258347362279892</v>
       </c>
       <c r="ER7" t="n">
         <v>0.2581373155117035</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.2518907785415649</v>
+        <v>0.2518908083438873</v>
       </c>
       <c r="ET7" t="n">
         <v>0.2546548247337341</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.2537471652030945</v>
+        <v>0.2537471950054169</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.2501920759677887</v>
+        <v>0.2501921057701111</v>
       </c>
       <c r="EW7" t="n">
         <v>0.249899834394455</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.2496478110551834</v>
+        <v>0.2496478408575058</v>
       </c>
       <c r="EY7" t="n">
         <v>0.2614216208457947</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.2865191698074341</v>
+        <v>0.2865191996097565</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.2870573699474335</v>
+        <v>0.2870573997497559</v>
       </c>
       <c r="FB7" t="n">
         <v>0.2763241529464722</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.2786831855773926</v>
+        <v>0.278683215379715</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.2690457403659821</v>
+        <v>0.2690457701683044</v>
       </c>
       <c r="FE7" t="n">
         <v>0.2705353200435638</v>
@@ -5455,46 +5461,46 @@
         <v>0.2669112980365753</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.2623741030693054</v>
+        <v>0.2623741328716278</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.2610801458358765</v>
+        <v>0.2610801756381989</v>
       </c>
       <c r="FJ7" t="n">
         <v>0.263323575258255</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.2651333510875702</v>
+        <v>0.2651333808898926</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.2749322950839996</v>
+        <v>0.274932324886322</v>
       </c>
       <c r="FM7" t="n">
         <v>0.2852621674537659</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.2907228469848633</v>
+        <v>0.2907228767871857</v>
       </c>
       <c r="FO7" t="n">
         <v>0.2908971905708313</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.2828101217746735</v>
+        <v>0.2828101515769958</v>
       </c>
       <c r="FQ7" t="n">
         <v>0.2809380292892456</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.2863253653049469</v>
+        <v>0.2863253951072693</v>
       </c>
       <c r="FS7" t="n">
         <v>0.2840283215045929</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.2842506766319275</v>
+        <v>0.2842507064342499</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.2823091149330139</v>
+        <v>0.2823091447353363</v>
       </c>
       <c r="FV7" t="n">
         <v>0.2841607928276062</v>
@@ -5506,7 +5512,7 @@
         <v>0.2836199998855591</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.2942115366458893</v>
+        <v>0.2942115664482117</v>
       </c>
       <c r="FZ7" t="n">
         <v>0.2987015247344971</v>
@@ -5521,37 +5527,37 @@
         <v>0.3080988228321075</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.3093124032020569</v>
+        <v>0.3093124330043793</v>
       </c>
       <c r="GE7" t="n">
         <v>0.3092990219593048</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.3073403835296631</v>
+        <v>0.3073404133319855</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.3056668043136597</v>
+        <v>0.3056668341159821</v>
       </c>
       <c r="GH7" t="n">
-        <v>0.301918625831604</v>
+        <v>0.3019186556339264</v>
       </c>
       <c r="GI7" t="n">
-        <v>0.3025008738040924</v>
+        <v>0.3025009036064148</v>
       </c>
       <c r="GJ7" t="n">
         <v>0.3030033707618713</v>
       </c>
       <c r="GK7" t="n">
-        <v>0.306885302066803</v>
+        <v>0.3068853318691254</v>
       </c>
       <c r="GL7" t="n">
-        <v>0.3133550584316254</v>
+        <v>0.3133550882339478</v>
       </c>
       <c r="GM7" t="n">
         <v>0.3196729421615601</v>
       </c>
       <c r="GN7" t="n">
-        <v>0.3350435495376587</v>
+        <v>0.3350435793399811</v>
       </c>
       <c r="GO7" t="n">
         <v>0.3430327475070953</v>
@@ -5563,85 +5569,87 @@
         <v>0.3327821493148804</v>
       </c>
       <c r="GR7" t="n">
-        <v>0.3317412436008453</v>
+        <v>0.3317412734031677</v>
       </c>
       <c r="GS7" t="n">
-        <v>0.3301486968994141</v>
+        <v>0.3301487267017365</v>
       </c>
       <c r="GT7" t="n">
         <v>0.3315800726413727</v>
       </c>
       <c r="GU7" t="n">
-        <v>0.3258622288703918</v>
+        <v>0.3258622586727142</v>
       </c>
       <c r="GV7" t="n">
         <v>0.3311708867549896</v>
       </c>
       <c r="GW7" t="n">
-        <v>0.3262558877468109</v>
+        <v>0.3262559175491333</v>
       </c>
       <c r="GX7" t="n">
-        <v>0.3274384438991547</v>
+        <v>0.3274384737014771</v>
       </c>
       <c r="GY7" t="n">
         <v>0.3277903199195862</v>
       </c>
       <c r="GZ7" t="n">
-        <v>0.340947687625885</v>
+        <v>0.3409477174282074</v>
       </c>
       <c r="HA7" t="n">
-        <v>0.3537092208862305</v>
+        <v>0.3537092506885529</v>
       </c>
       <c r="HB7" t="n">
-        <v>0.3665052354335785</v>
+        <v>0.3665052652359009</v>
       </c>
       <c r="HC7" t="n">
         <v>0.3600437939167023</v>
       </c>
       <c r="HD7" t="n">
-        <v>0.349468857049942</v>
+        <v>0.3494688868522644</v>
       </c>
       <c r="HE7" t="n">
-        <v>0.3444927632808685</v>
+        <v>0.3444928228855133</v>
       </c>
       <c r="HF7" t="n">
-        <v>0.3460768461227417</v>
+        <v>0.3460769057273865</v>
       </c>
       <c r="HG7" t="n">
         <v>0.3527370989322662</v>
       </c>
       <c r="HH7" t="n">
-        <v>0.3516972661018372</v>
+        <v>0.3516972959041595</v>
       </c>
       <c r="HI7" t="n">
-        <v>0.3501230478286743</v>
+        <v>0.3501230776309967</v>
       </c>
       <c r="HJ7" t="n">
-        <v>0.3527966141700745</v>
+        <v>0.3527966737747192</v>
       </c>
       <c r="HK7" t="n">
-        <v>0.3465596437454224</v>
+        <v>0.3465596735477448</v>
       </c>
       <c r="HL7" t="n">
-        <v>0.3483832180500031</v>
+        <v>0.3483832478523254</v>
       </c>
       <c r="HM7" t="n">
         <v>0.3454338908195496</v>
       </c>
       <c r="HN7" t="n">
-        <v>0.3685861229896545</v>
+        <v>0.3685861527919769</v>
       </c>
       <c r="HO7" t="n">
-        <v>0.3828193247318268</v>
+        <v>0.3828193545341492</v>
       </c>
       <c r="HP7" t="n">
-        <v>0.3614596724510193</v>
+        <v>0.3614597022533417</v>
       </c>
       <c r="HQ7" t="n">
         <v>0.348989725112915</v>
       </c>
-      <c r="HR7" s="1" t="n">
-        <v>55519</v>
+      <c r="HR7" t="inlineStr">
+        <is>
+          <t>01/01/2052</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/results/submission_predictions.xlsx
+++ b/results/submission_predictions.xlsx
@@ -1555,676 +1555,676 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02327247522771358</v>
+        <v>0.02318507432937622</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03185705095529556</v>
+        <v>0.03188405930995941</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03396112471818924</v>
+        <v>0.03397274389863014</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03553853556513786</v>
+        <v>0.03556628152728081</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03609274327754974</v>
+        <v>0.03612011671066284</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03546727076172829</v>
+        <v>0.03541716188192368</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03495826199650764</v>
+        <v>0.03495172411203384</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03462072461843491</v>
+        <v>0.03457061573863029</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03485633432865143</v>
+        <v>0.03480684757232666</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03422610834240913</v>
+        <v>0.0341881662607193</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03329165652394295</v>
+        <v>0.03328442573547363</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03239856287837029</v>
+        <v>0.03236930444836617</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03232935816049576</v>
+        <v>0.03230168670415878</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0329296737909317</v>
+        <v>0.03286618739366531</v>
       </c>
       <c r="P2" t="n">
-        <v>0.04761692136526108</v>
+        <v>0.04758042097091675</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05880685895681381</v>
+        <v>0.05885273218154907</v>
       </c>
       <c r="R2" t="n">
-        <v>0.06148029491305351</v>
+        <v>0.06157319620251656</v>
       </c>
       <c r="S2" t="n">
-        <v>0.06263396143913269</v>
+        <v>0.06270737946033478</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06388247013092041</v>
+        <v>0.06387840211391449</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06175613403320312</v>
+        <v>0.06166896224021912</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06262072175741196</v>
+        <v>0.06259685009717941</v>
       </c>
       <c r="W2" t="n">
-        <v>0.06226976960897446</v>
+        <v>0.0622728131711483</v>
       </c>
       <c r="X2" t="n">
-        <v>0.06172994151711464</v>
+        <v>0.06173666566610336</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.06138221919536591</v>
+        <v>0.06133612245321274</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.05846231803297997</v>
+        <v>0.05845404043793678</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05631870403885841</v>
+        <v>0.05624158680438995</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05613847076892853</v>
+        <v>0.05608374997973442</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.05759188160300255</v>
+        <v>0.05748163908720016</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.07860561460256577</v>
+        <v>0.07868769764900208</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0902911052107811</v>
+        <v>0.09039420634508133</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.09027779102325439</v>
+        <v>0.09040001779794693</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.09256616979837418</v>
+        <v>0.09256990253925323</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.09286519140005112</v>
+        <v>0.09288109838962555</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.09230515360832214</v>
+        <v>0.09219146519899368</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.08934227377176285</v>
+        <v>0.08933929353952408</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.08851178735494614</v>
+        <v>0.08846691995859146</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.08875288814306259</v>
+        <v>0.08870689570903778</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.08587278425693512</v>
+        <v>0.08581945300102234</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.08192781358957291</v>
+        <v>0.08184624463319778</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.08005694299936295</v>
+        <v>0.07998744398355484</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.08217130601406097</v>
+        <v>0.08206105977296829</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.08294537663459778</v>
+        <v>0.08279383182525635</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.1072399914264679</v>
+        <v>0.1073121428489685</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.1139924004673958</v>
+        <v>0.1142126098275185</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.1149145662784576</v>
+        <v>0.1150502264499664</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.1169358789920807</v>
+        <v>0.1171115413308144</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.1147647202014923</v>
+        <v>0.1148201674222946</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.1109625920653343</v>
+        <v>0.1110217571258545</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1114966571331024</v>
+        <v>0.1114648878574371</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.1107911393046379</v>
+        <v>0.1107443273067474</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1094115898013115</v>
+        <v>0.1092759072780609</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.1059253364801407</v>
+        <v>0.1058641523122787</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.101565845310688</v>
+        <v>0.1015690863132477</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.09994617104530334</v>
+        <v>0.09983118623495102</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.09866324067115784</v>
+        <v>0.09854790568351746</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.1017294079065323</v>
+        <v>0.1015737429261208</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.1351375579833984</v>
+        <v>0.1354335248470306</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.1371277421712875</v>
+        <v>0.1373955309391022</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.1368303298950195</v>
+        <v>0.1369575560092926</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.1336757689714432</v>
+        <v>0.133686289191246</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.1337656676769257</v>
+        <v>0.1338625103235245</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.1279070377349854</v>
+        <v>0.1278948485851288</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.1275920271873474</v>
+        <v>0.1276357173919678</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.1251614391803741</v>
+        <v>0.1251719146966934</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.1233372837305069</v>
+        <v>0.1231976300477982</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.1247401759028435</v>
+        <v>0.1246285364031792</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1169500648975372</v>
+        <v>0.1168414205312729</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.1164049580693245</v>
+        <v>0.1163686290383339</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.1157747134566307</v>
+        <v>0.1156098693609238</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.1157311424612999</v>
+        <v>0.115565225481987</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.1685404926538467</v>
+        <v>0.1687582731246948</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.1669156104326248</v>
+        <v>0.1671299040317535</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.1629242300987244</v>
+        <v>0.1630492359399796</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.163258820772171</v>
+        <v>0.1633277237415314</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.1618397533893585</v>
+        <v>0.1618521511554718</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.157964751124382</v>
+        <v>0.1578803956508636</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.1543385535478592</v>
+        <v>0.1542609184980392</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.1515934765338898</v>
+        <v>0.1514876037836075</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.1497592628002167</v>
+        <v>0.1496306508779526</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.1458503752946854</v>
+        <v>0.1458317041397095</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.1424503028392792</v>
+        <v>0.1424273550510406</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.1360291391611099</v>
+        <v>0.1358027011156082</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.136170282959938</v>
+        <v>0.1360290795564651</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.1394329220056534</v>
+        <v>0.139169305562973</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.1943817734718323</v>
+        <v>0.1946970373392105</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.1921618282794952</v>
+        <v>0.1923393160104752</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.1897423416376114</v>
+        <v>0.1897488087415695</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.1862662136554718</v>
+        <v>0.1863265931606293</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.1827801913022995</v>
+        <v>0.182867705821991</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.176430344581604</v>
+        <v>0.1761742681264877</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.1772531569004059</v>
+        <v>0.177157923579216</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.1711295694112778</v>
+        <v>0.1709623038768768</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.1697437167167664</v>
+        <v>0.1695875972509384</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.1706958413124084</v>
+        <v>0.1706136018037796</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.1583566814661026</v>
+        <v>0.158295601606369</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.1560402065515518</v>
+        <v>0.1559296697378159</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.1561319530010223</v>
+        <v>0.1559391021728516</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.1622046530246735</v>
+        <v>0.1619279235601425</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.2299002856016159</v>
+        <v>0.23005411028862</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.2171759009361267</v>
+        <v>0.2172192335128784</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.2175972163677216</v>
+        <v>0.2176186591386795</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.2161086201667786</v>
+        <v>0.2160163372755051</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.2072495371103287</v>
+        <v>0.207061842083931</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.2040142714977264</v>
+        <v>0.2037547081708908</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.2046861052513123</v>
+        <v>0.204533264040947</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.2005567401647568</v>
+        <v>0.20033098757267</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.2002120614051819</v>
+        <v>0.2001755237579346</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.1948543637990952</v>
+        <v>0.1947078108787537</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.1894201040267944</v>
+        <v>0.1893542557954788</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.1865202188491821</v>
+        <v>0.1862872242927551</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.185511127114296</v>
+        <v>0.1853335201740265</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.1881302744150162</v>
+        <v>0.1878730356693268</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.2457068562507629</v>
+        <v>0.2456095069646835</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.2429618388414383</v>
+        <v>0.2426550984382629</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.2353169769048691</v>
+        <v>0.2351501286029816</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.2338889241218567</v>
+        <v>0.2337103337049484</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.2272391617298126</v>
+        <v>0.2271200120449066</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.228662982583046</v>
+        <v>0.2286079972982407</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.2231682538986206</v>
+        <v>0.223124086856842</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.217379704117775</v>
+        <v>0.217056080698967</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.2160817086696625</v>
+        <v>0.2159292995929718</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.2133606970310211</v>
+        <v>0.2131413370370865</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.2090011686086655</v>
+        <v>0.2088631689548492</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.2079675048589706</v>
+        <v>0.207666739821434</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.2102058976888657</v>
+        <v>0.2099832594394684</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2123606353998184</v>
+        <v>0.2120786309242249</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.2630011141300201</v>
+        <v>0.2628280222415924</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.2533687651157379</v>
+        <v>0.2531485557556152</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.2520451545715332</v>
+        <v>0.2518391013145447</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.2453269809484482</v>
+        <v>0.2451137155294418</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.2449413239955902</v>
+        <v>0.2447262108325958</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.2392556369304657</v>
+        <v>0.2389983832836151</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.2367990761995316</v>
+        <v>0.2365098744630814</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.2355388402938843</v>
+        <v>0.2352452129125595</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.2333937436342239</v>
+        <v>0.2330702543258667</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.2314708381891251</v>
+        <v>0.2313346415758133</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.2198098301887512</v>
+        <v>0.2194636166095734</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.2237232774496078</v>
+        <v>0.2234306186437607</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.2250820696353912</v>
+        <v>0.2246885001659393</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.2265052497386932</v>
+        <v>0.2262192517518997</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.2740911841392517</v>
+        <v>0.2739260792732239</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.2712910175323486</v>
+        <v>0.2709437608718872</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.2673588395118713</v>
+        <v>0.267096608877182</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.2609067261219025</v>
+        <v>0.2605599761009216</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.2642337381839752</v>
+        <v>0.2639578878879547</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.2536183893680573</v>
+        <v>0.2534716427326202</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.2530957460403442</v>
+        <v>0.2529224753379822</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.2473649531602859</v>
+        <v>0.2470715045928955</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.2503708004951477</v>
+        <v>0.2500300705432892</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.2498073428869247</v>
+        <v>0.2494676113128662</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.246431291103363</v>
+        <v>0.2461328506469727</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.2465380877256393</v>
+        <v>0.2461767494678497</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.2465481609106064</v>
+        <v>0.2460965067148209</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.2578590512275696</v>
+        <v>0.2574259340763092</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.2823036313056946</v>
+        <v>0.2819767594337463</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.2828189134597778</v>
+        <v>0.2825010418891907</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.2723715901374817</v>
+        <v>0.2720599472522736</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.2747873067855835</v>
+        <v>0.2745133638381958</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.2653568387031555</v>
+        <v>0.2649905383586884</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.2668687701225281</v>
+        <v>0.2665752470493317</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.2665475308895111</v>
+        <v>0.266124427318573</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.2633043229579926</v>
+        <v>0.2629017233848572</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.2588370144367218</v>
+        <v>0.2585291862487793</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.2575743496417999</v>
+        <v>0.2572279870510101</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.2598845064640045</v>
+        <v>0.2595068216323853</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.2621243596076965</v>
+        <v>0.2616985440254211</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.27187180519104</v>
+        <v>0.2712526023387909</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.282090812921524</v>
+        <v>0.2815454602241516</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.2864341139793396</v>
+        <v>0.2860629260540009</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.2868529856204987</v>
+        <v>0.2864820063114166</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.2789511382579803</v>
+        <v>0.2785717844963074</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.2771092355251312</v>
+        <v>0.2765580713748932</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.2823024094104767</v>
+        <v>0.2819525599479675</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.2800577580928802</v>
+        <v>0.2795931100845337</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.2801862359046936</v>
+        <v>0.2797708213329315</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.2782211899757385</v>
+        <v>0.2777833342552185</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.2800509631633759</v>
+        <v>0.2795195579528809</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.2804012894630432</v>
+        <v>0.2799712717533112</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.2798058986663818</v>
+        <v>0.2792785465717316</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.2905955016613007</v>
+        <v>0.289819061756134</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.2948188483715057</v>
+        <v>0.2941228151321411</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.3093720972537994</v>
+        <v>0.308588057756424</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.3019457161426544</v>
+        <v>0.3014923632144928</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.3026081621646881</v>
+        <v>0.3019830286502838</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.3035686314105988</v>
+        <v>0.3030782639980316</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.3034860193729401</v>
+        <v>0.3029845654964447</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.3017010688781738</v>
+        <v>0.3011422455310822</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.3001542687416077</v>
+        <v>0.2996968328952789</v>
       </c>
       <c r="GH2" t="n">
-        <v>0.2965281903743744</v>
+        <v>0.2959887981414795</v>
       </c>
       <c r="GI2" t="n">
-        <v>0.2974534928798676</v>
+        <v>0.2968422472476959</v>
       </c>
       <c r="GJ2" t="n">
-        <v>0.2976043522357941</v>
+        <v>0.2970765233039856</v>
       </c>
       <c r="GK2" t="n">
-        <v>0.3014461994171143</v>
+        <v>0.3008762001991272</v>
       </c>
       <c r="GL2" t="n">
-        <v>0.3082232773303986</v>
+        <v>0.3073097765445709</v>
       </c>
       <c r="GM2" t="n">
-        <v>0.3147902488708496</v>
+        <v>0.3138381838798523</v>
       </c>
       <c r="GN2" t="n">
-        <v>0.3299872279167175</v>
+        <v>0.3290687501430511</v>
       </c>
       <c r="GO2" t="n">
-        <v>0.3375034034252167</v>
+        <v>0.3366119563579559</v>
       </c>
       <c r="GP2" t="n">
-        <v>0.3303440809249878</v>
+        <v>0.3296489119529724</v>
       </c>
       <c r="GQ2" t="n">
-        <v>0.3276189863681793</v>
+        <v>0.3269288539886475</v>
       </c>
       <c r="GR2" t="n">
-        <v>0.3265229165554047</v>
+        <v>0.3258122801780701</v>
       </c>
       <c r="GS2" t="n">
-        <v>0.3249167501926422</v>
+        <v>0.3241280615329742</v>
       </c>
       <c r="GT2" t="n">
-        <v>0.3261618912220001</v>
+        <v>0.3255454897880554</v>
       </c>
       <c r="GU2" t="n">
-        <v>0.3204724192619324</v>
+        <v>0.3198182582855225</v>
       </c>
       <c r="GV2" t="n">
-        <v>0.3255519866943359</v>
+        <v>0.3247554898262024</v>
       </c>
       <c r="GW2" t="n">
-        <v>0.3206559121608734</v>
+        <v>0.3198827505111694</v>
       </c>
       <c r="GX2" t="n">
-        <v>0.3216539323329926</v>
+        <v>0.3208956718444824</v>
       </c>
       <c r="GY2" t="n">
-        <v>0.3218827843666077</v>
+        <v>0.3210145533084869</v>
       </c>
       <c r="GZ2" t="n">
-        <v>0.335168182849884</v>
+        <v>0.3342933654785156</v>
       </c>
       <c r="HA2" t="n">
-        <v>0.3482560217380524</v>
+        <v>0.3474113643169403</v>
       </c>
       <c r="HB2" t="n">
-        <v>0.3604863882064819</v>
+        <v>0.3595223724842072</v>
       </c>
       <c r="HC2" t="n">
-        <v>0.3553192019462585</v>
+        <v>0.3544248640537262</v>
       </c>
       <c r="HD2" t="n">
-        <v>0.3424151539802551</v>
+        <v>0.3411796092987061</v>
       </c>
       <c r="HE2" t="n">
-        <v>0.3377165496349335</v>
+        <v>0.3362773060798645</v>
       </c>
       <c r="HF2" t="n">
-        <v>0.3392493426799774</v>
+        <v>0.3378927111625671</v>
       </c>
       <c r="HG2" t="n">
-        <v>0.3456778824329376</v>
+        <v>0.3444583714008331</v>
       </c>
       <c r="HH2" t="n">
-        <v>0.3443604111671448</v>
+        <v>0.343076765537262</v>
       </c>
       <c r="HI2" t="n">
-        <v>0.3426366448402405</v>
+        <v>0.3415813148021698</v>
       </c>
       <c r="HJ2" t="n">
-        <v>0.345059722661972</v>
+        <v>0.3437668681144714</v>
       </c>
       <c r="HK2" t="n">
-        <v>0.33873251080513</v>
+        <v>0.3375883102416992</v>
       </c>
       <c r="HL2" t="n">
-        <v>0.340332567691803</v>
+        <v>0.3392657339572906</v>
       </c>
       <c r="HM2" t="n">
-        <v>0.3372077941894531</v>
+        <v>0.3360197842121124</v>
       </c>
       <c r="HN2" t="n">
-        <v>0.3605554699897766</v>
+        <v>0.359351247549057</v>
       </c>
       <c r="HO2" t="n">
-        <v>0.3749498128890991</v>
+        <v>0.3735892176628113</v>
       </c>
       <c r="HP2" t="n">
-        <v>0.3555046021938324</v>
+        <v>0.3544781506061554</v>
       </c>
       <c r="HQ2" t="n">
-        <v>0.3446680307388306</v>
+        <v>0.3438026905059814</v>
       </c>
       <c r="HR2" t="inlineStr">
         <is>
@@ -2239,676 +2239,676 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02405374124646187</v>
+        <v>0.02356911636888981</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03270313516259193</v>
+        <v>0.03235921263694763</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03480244427919388</v>
+        <v>0.03444001078605652</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03635799884796143</v>
+        <v>0.03600489720702171</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03686953336000443</v>
+        <v>0.03652816265821457</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03619330748915672</v>
+        <v>0.03578531742095947</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03563909232616425</v>
+        <v>0.03527692705392838</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03528859466314316</v>
+        <v>0.03488093614578247</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03550473973155022</v>
+        <v>0.03509872779250145</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03484011441469193</v>
+        <v>0.03445488959550858</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03384307771921158</v>
+        <v>0.03350914642214775</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03287230432033539</v>
+        <v>0.03254776075482368</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03279175609350204</v>
+        <v>0.03246950730681419</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03337327763438225</v>
+        <v>0.03301634266972542</v>
       </c>
       <c r="P3" t="n">
-        <v>0.04883988574147224</v>
+        <v>0.04824093729257584</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.06013627350330353</v>
+        <v>0.05961683765053749</v>
       </c>
       <c r="R3" t="n">
-        <v>0.06284879893064499</v>
+        <v>0.06232976168394089</v>
       </c>
       <c r="S3" t="n">
-        <v>0.06389124691486359</v>
+        <v>0.0633748397231102</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06511686742305756</v>
+        <v>0.0645114853978157</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06285393983125687</v>
+        <v>0.06221058964729309</v>
       </c>
       <c r="V3" t="n">
-        <v>0.06368936598300934</v>
+        <v>0.06310365349054337</v>
       </c>
       <c r="W3" t="n">
-        <v>0.06325754523277283</v>
+        <v>0.06271705776453018</v>
       </c>
       <c r="X3" t="n">
-        <v>0.06271084398031235</v>
+        <v>0.06216413900256157</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06231236085295677</v>
+        <v>0.06173169985413551</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0592801608145237</v>
+        <v>0.05877585709095001</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.05703672021627426</v>
+        <v>0.05649960786104202</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.05685501918196678</v>
+        <v>0.05633308738470078</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.05827780440449715</v>
+        <v>0.05770982429385185</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.08020354062318802</v>
+        <v>0.07964672893285751</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.09205266088247299</v>
+        <v>0.09142682701349258</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09205666929483414</v>
+        <v>0.09138667583465576</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.09415910392999649</v>
+        <v>0.09341265261173248</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.09439294040203094</v>
+        <v>0.09364926069974899</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.09374450147151947</v>
+        <v>0.09288910776376724</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.09065951406955719</v>
+        <v>0.08994842320680618</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.08972308784723282</v>
+        <v>0.08899705111980438</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.08997636288404465</v>
+        <v>0.08923100680112839</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.08700769394636154</v>
+        <v>0.08629070967435837</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.08288320153951645</v>
+        <v>0.08221623301506042</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.08092474192380905</v>
+        <v>0.08028817921876907</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.08306273072957993</v>
+        <v>0.08235961198806763</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.08378931879997253</v>
+        <v>0.08305780589580536</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.1091591492295265</v>
+        <v>0.1084995344281197</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.1161635741591454</v>
+        <v>0.1154482960700989</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.1169488579034805</v>
+        <v>0.1161534860730171</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.1186951100826263</v>
+        <v>0.1180276200175285</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1165806874632835</v>
+        <v>0.1157027930021286</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1125217750668526</v>
+        <v>0.1117512658238411</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1130005940794945</v>
+        <v>0.1121401637792587</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.1121794953942299</v>
+        <v>0.1113379597663879</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1107886880636215</v>
+        <v>0.1098518818616867</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1071763262152672</v>
+        <v>0.1063722595572472</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.1026151031255722</v>
+        <v>0.1019623801112175</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1009214147925377</v>
+        <v>0.1001580953598022</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.09962698817253113</v>
+        <v>0.09885945171117783</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1026642248034477</v>
+        <v>0.1018539443612099</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1373827904462814</v>
+        <v>0.1368091851472855</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.1394602507352829</v>
+        <v>0.1386807262897491</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.1389601528644562</v>
+        <v>0.1380663365125656</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.1356379091739655</v>
+        <v>0.1346461027860641</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.135683462023735</v>
+        <v>0.1347574144601822</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.1296034604310989</v>
+        <v>0.1286541223526001</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.129142552614212</v>
+        <v>0.1283054798841476</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.1266267746686935</v>
+        <v>0.1257761120796204</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.1247759908437729</v>
+        <v>0.1237763538956642</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.1260892301797867</v>
+        <v>0.1251533776521683</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1180642545223236</v>
+        <v>0.11723692715168</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.1174353435635567</v>
+        <v>0.1167010366916656</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1167955175042152</v>
+        <v>0.1159260720014572</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.1166988462209702</v>
+        <v>0.1158436462283134</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.1715812087059021</v>
+        <v>0.1704394370317459</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.16973976790905</v>
+        <v>0.1685773134231567</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.1656215339899063</v>
+        <v>0.1643360704183578</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1656820476055145</v>
+        <v>0.1644235849380493</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.1639607101678848</v>
+        <v>0.1627896428108215</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.1599738597869873</v>
+        <v>0.1587362587451935</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.1561710685491562</v>
+        <v>0.1550012975931168</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.1533117294311523</v>
+        <v>0.1521618068218231</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.1513627171516418</v>
+        <v>0.1502479463815689</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.1473227292299271</v>
+        <v>0.1463856846094131</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.1437181681394577</v>
+        <v>0.1428627520799637</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.1371362805366516</v>
+        <v>0.1361413598060608</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.1372634619474411</v>
+        <v>0.1363509446382523</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.1404968947172165</v>
+        <v>0.1394581198692322</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.1973865032196045</v>
+        <v>0.1961809396743774</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.1952264457941055</v>
+        <v>0.1937480121850967</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.1925187855958939</v>
+        <v>0.1909684687852859</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.1886909306049347</v>
+        <v>0.1873478144407272</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.1850903928279877</v>
+        <v>0.1838088780641556</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.1785221099853516</v>
+        <v>0.1770009547472</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.1791964918375015</v>
+        <v>0.1779060810804367</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1729215234518051</v>
+        <v>0.1716238856315613</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.171438604593277</v>
+        <v>0.1702018529176712</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.1722618937492371</v>
+        <v>0.1711635738611221</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.1596356183290482</v>
+        <v>0.1587164700031281</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.1571788489818573</v>
+        <v>0.1562527567148209</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.1572201997041702</v>
+        <v>0.156233087182045</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.1633347570896149</v>
+        <v>0.1622145622968674</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.2328107804059982</v>
+        <v>0.2312717735767365</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.2201549708843231</v>
+        <v>0.2184235751628876</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.220228299498558</v>
+        <v>0.2186766862869263</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.2186175882816315</v>
+        <v>0.2169902622699738</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.2095150500535965</v>
+        <v>0.2078977525234222</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.2061324119567871</v>
+        <v>0.2045146077871323</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.2066648900508881</v>
+        <v>0.2052300870418549</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.2023081034421921</v>
+        <v>0.2009287178516388</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.2018661350011826</v>
+        <v>0.2007400989532471</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.1963828951120377</v>
+        <v>0.1952167004346848</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.1906967610120773</v>
+        <v>0.1897364407777786</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.1876973658800125</v>
+        <v>0.1865953207015991</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.1866022795438766</v>
+        <v>0.1856021583080292</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.189191535115242</v>
+        <v>0.1880968511104584</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.2488144934177399</v>
+        <v>0.2468183040618896</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.2457433938980103</v>
+        <v>0.2437084168195724</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.2378330081701279</v>
+        <v>0.2360710650682449</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.2362802177667618</v>
+        <v>0.2345727384090424</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.2294298559427261</v>
+        <v>0.2278788983821869</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.2306029349565506</v>
+        <v>0.229255199432373</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.2249195575714111</v>
+        <v>0.2237024307250977</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.2190182507038116</v>
+        <v>0.2175850719213486</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.2176065891981125</v>
+        <v>0.2164145708084106</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.2147616446018219</v>
+        <v>0.213573694229126</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.2102195769548416</v>
+        <v>0.2091973721981049</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.2089552581310272</v>
+        <v>0.2078927904367447</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.2112431675195694</v>
+        <v>0.2102069109678268</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.2133432179689407</v>
+        <v>0.2122444808483124</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.2657259404659271</v>
+        <v>0.26381516456604</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.255880206823349</v>
+        <v>0.2540440261363983</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.2544723153114319</v>
+        <v>0.2526901364326477</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.2474002242088318</v>
+        <v>0.2458129376173019</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.2468252331018448</v>
+        <v>0.2453471422195435</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.241018608212471</v>
+        <v>0.2395689338445663</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.238429993391037</v>
+        <v>0.2370270937681198</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.2370419651269913</v>
+        <v>0.2357065379619598</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.2348050326108932</v>
+        <v>0.2334993481636047</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.2327949404716492</v>
+        <v>0.231719970703125</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.2209609895944595</v>
+        <v>0.2197318226099014</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.2247340232133865</v>
+        <v>0.2236393541097641</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.2259444445371628</v>
+        <v>0.2248122692108154</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.227418527007103</v>
+        <v>0.2263548374176025</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.2762333750724792</v>
+        <v>0.2746123373508453</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.2731712162494659</v>
+        <v>0.2715171277523041</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.269093781709671</v>
+        <v>0.2676305174827576</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.2624540030956268</v>
+        <v>0.2610195577144623</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.2657108902931213</v>
+        <v>0.2643894553184509</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.2549499273300171</v>
+        <v>0.2538454830646515</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.2545367181301117</v>
+        <v>0.253344863653183</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.2486181408166885</v>
+        <v>0.2473891377449036</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.2515665292739868</v>
+        <v>0.2503513395786285</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.2508740723133087</v>
+        <v>0.2497098594903946</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.2474197894334793</v>
+        <v>0.246325746178627</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.2473997920751572</v>
+        <v>0.2463212758302689</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.2473072707653046</v>
+        <v>0.2461708337068558</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.2587508261203766</v>
+        <v>0.2575204074382782</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.2834609150886536</v>
+        <v>0.2822648882865906</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.2839841842651367</v>
+        <v>0.2827953994274139</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.2734586000442505</v>
+        <v>0.2723437547683716</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.2758464217185974</v>
+        <v>0.2747806012630463</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.2663503587245941</v>
+        <v>0.2652278542518616</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.2678406536579132</v>
+        <v>0.2667875289916992</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.2675229012966156</v>
+        <v>0.2663494050502777</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.2642578184604645</v>
+        <v>0.2631059288978577</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.2597732543945312</v>
+        <v>0.2587292194366455</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.2585018575191498</v>
+        <v>0.2574241757392883</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.2607651352882385</v>
+        <v>0.2596485018730164</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.2628520429134369</v>
+        <v>0.2617551982402802</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.2725976407527924</v>
+        <v>0.2712893187999725</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.2828343212604523</v>
+        <v>0.2815706431865692</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.2875897884368896</v>
+        <v>0.2863379120826721</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.2879283428192139</v>
+        <v>0.2867179214954376</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.2799690961837769</v>
+        <v>0.2787815034389496</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.2781053781509399</v>
+        <v>0.2767534255981445</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.2833696007728577</v>
+        <v>0.2821799516677856</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.2810865342617035</v>
+        <v>0.2797800302505493</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.2812434732913971</v>
+        <v>0.2799626588821411</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.2792788445949554</v>
+        <v>0.2779636681079865</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.2810961008071899</v>
+        <v>0.2796727418899536</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.2814562022686005</v>
+        <v>0.2801209986209869</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.2807246446609497</v>
+        <v>0.2793340086936951</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.2914254069328308</v>
+        <v>0.2898010313510895</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.2957299947738647</v>
+        <v>0.2941364943981171</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.31032794713974</v>
+        <v>0.3086096942424774</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.3033686876296997</v>
+        <v>0.3017751574516296</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.3040461540222168</v>
+        <v>0.3022575080394745</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.3050789833068848</v>
+        <v>0.3033629059791565</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.3050136268138885</v>
+        <v>0.3032724857330322</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.3031645119190216</v>
+        <v>0.3013935983181</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.3015779256820679</v>
+        <v>0.2999362349510193</v>
       </c>
       <c r="GH3" t="n">
-        <v>0.2978954017162323</v>
+        <v>0.2961760461330414</v>
       </c>
       <c r="GI3" t="n">
-        <v>0.2986606657505035</v>
+        <v>0.2968991994857788</v>
       </c>
       <c r="GJ3" t="n">
-        <v>0.2989616990089417</v>
+        <v>0.2972442805767059</v>
       </c>
       <c r="GK3" t="n">
-        <v>0.3027980625629425</v>
+        <v>0.3010176420211792</v>
       </c>
       <c r="GL3" t="n">
-        <v>0.3094542622566223</v>
+        <v>0.3073614835739136</v>
       </c>
       <c r="GM3" t="n">
-        <v>0.3159318268299103</v>
+        <v>0.313827782869339</v>
       </c>
       <c r="GN3" t="n">
-        <v>0.3311794102191925</v>
+        <v>0.3290977776050568</v>
       </c>
       <c r="GO3" t="n">
-        <v>0.3388373255729675</v>
+        <v>0.3366929888725281</v>
       </c>
       <c r="GP3" t="n">
-        <v>0.3317425847053528</v>
+        <v>0.3298345804214478</v>
       </c>
       <c r="GQ3" t="n">
-        <v>0.3288832008838654</v>
+        <v>0.3270477652549744</v>
       </c>
       <c r="GR3" t="n">
-        <v>0.3278137147426605</v>
+        <v>0.3259601891040802</v>
       </c>
       <c r="GS3" t="n">
-        <v>0.3262053430080414</v>
+        <v>0.3242695033550262</v>
       </c>
       <c r="GT3" t="n">
-        <v>0.3274994194507599</v>
+        <v>0.3256868124008179</v>
       </c>
       <c r="GU3" t="n">
-        <v>0.3217916190624237</v>
+        <v>0.3199363350868225</v>
       </c>
       <c r="GV3" t="n">
-        <v>0.3269315958023071</v>
+        <v>0.3248904645442963</v>
       </c>
       <c r="GW3" t="n">
-        <v>0.3220234215259552</v>
+        <v>0.3199995458126068</v>
       </c>
       <c r="GX3" t="n">
-        <v>0.3230704367160797</v>
+        <v>0.321024477481842</v>
       </c>
       <c r="GY3" t="n">
-        <v>0.3233212828636169</v>
+        <v>0.3211276233196259</v>
       </c>
       <c r="GZ3" t="n">
-        <v>0.336568683385849</v>
+        <v>0.3344019949436188</v>
       </c>
       <c r="HA3" t="n">
-        <v>0.3495566546916962</v>
+        <v>0.3474830687046051</v>
       </c>
       <c r="HB3" t="n">
-        <v>0.3619344830513</v>
+        <v>0.3596495091915131</v>
       </c>
       <c r="HC3" t="n">
-        <v>0.3564287424087524</v>
+        <v>0.3544704914093018</v>
       </c>
       <c r="HD3" t="n">
-        <v>0.3440993428230286</v>
+        <v>0.3413303196430206</v>
       </c>
       <c r="HE3" t="n">
-        <v>0.3393476903438568</v>
+        <v>0.336436927318573</v>
       </c>
       <c r="HF3" t="n">
-        <v>0.3408956527709961</v>
+        <v>0.3380511999130249</v>
       </c>
       <c r="HG3" t="n">
-        <v>0.3473794162273407</v>
+        <v>0.3446333408355713</v>
       </c>
       <c r="HH3" t="n">
-        <v>0.3461420834064484</v>
+        <v>0.3432861864566803</v>
       </c>
       <c r="HI3" t="n">
-        <v>0.3444597125053406</v>
+        <v>0.3418053686618805</v>
       </c>
       <c r="HJ3" t="n">
-        <v>0.3469578921794891</v>
+        <v>0.344031810760498</v>
       </c>
       <c r="HK3" t="n">
-        <v>0.3406603336334229</v>
+        <v>0.3378567695617676</v>
       </c>
       <c r="HL3" t="n">
-        <v>0.3423295617103577</v>
+        <v>0.3395670354366302</v>
       </c>
       <c r="HM3" t="n">
-        <v>0.3392661809921265</v>
+        <v>0.3363432288169861</v>
       </c>
       <c r="HN3" t="n">
-        <v>0.3625355958938599</v>
+        <v>0.3596974313259125</v>
       </c>
       <c r="HO3" t="n">
-        <v>0.3768281936645508</v>
+        <v>0.3738776445388794</v>
       </c>
       <c r="HP3" t="n">
-        <v>0.3569716811180115</v>
+        <v>0.3546992540359497</v>
       </c>
       <c r="HQ3" t="n">
-        <v>0.3456934094429016</v>
+        <v>0.3438780009746552</v>
       </c>
       <c r="HR3" t="inlineStr">
         <is>
@@ -2923,676 +2923,676 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02440594881772995</v>
+        <v>0.02394467778503895</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03310087323188782</v>
+        <v>0.03274791687726974</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03520696610212326</v>
+        <v>0.03482376784086227</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03676066175103188</v>
+        <v>0.03637958690524101</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03725502640008926</v>
+        <v>0.0368797555565834</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03656097874045372</v>
+        <v>0.03611873090267181</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03599256277084351</v>
+        <v>0.03559615835547447</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03564152866601944</v>
+        <v>0.03519834205508232</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03585303947329521</v>
+        <v>0.03541192784905434</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03517654910683632</v>
+        <v>0.03475736826658249</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03415499627590179</v>
+        <v>0.03378818556666374</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03315304964780807</v>
+        <v>0.0328030027449131</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03307050094008446</v>
+        <v>0.03272361680865288</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03364849463105202</v>
+        <v>0.03326942026615143</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0494098924100399</v>
+        <v>0.04882986471056938</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06076172739267349</v>
+        <v>0.06021257489919662</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06350772082805634</v>
+        <v>0.0629391074180603</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0645090639591217</v>
+        <v>0.06393446028232574</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06573826819658279</v>
+        <v>0.0650688037276268</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06342464685440063</v>
+        <v>0.06272167712450027</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06424920260906219</v>
+        <v>0.06360112130641937</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06379464268684387</v>
+        <v>0.06319559365510941</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06324773281812668</v>
+        <v>0.06263948976993561</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06282946467399597</v>
+        <v>0.06218819320201874</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0597500242292881</v>
+        <v>0.05919091403484344</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05747367814183235</v>
+        <v>0.05689381062984467</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05729715153574944</v>
+        <v>0.05673202499747276</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.05871054902672768</v>
+        <v>0.05810364335775375</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.08093959093093872</v>
+        <v>0.080368772149086</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.09287602454423904</v>
+        <v>0.09217680245637894</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.09291137754917145</v>
+        <v>0.09214639663696289</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.09494400769472122</v>
+        <v>0.09409680217504501</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.09517055004835129</v>
+        <v>0.0943276435136795</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.09449224919080734</v>
+        <v>0.0935412123799324</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.09135964512825012</v>
+        <v>0.09055797755718231</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.09038989990949631</v>
+        <v>0.08958134800195694</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.09065089374780655</v>
+        <v>0.08981776237487793</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0876496210694313</v>
+        <v>0.08685065805912018</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.08344297856092453</v>
+        <v>0.08271058648824692</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.08146143704652786</v>
+        <v>0.08076894283294678</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.08362265676259995</v>
+        <v>0.08286182582378387</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.08433093130588531</v>
+        <v>0.08354717493057251</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.1100423559546471</v>
+        <v>0.109328031539917</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.1171707138419151</v>
+        <v>0.1163261756300926</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.1179169341921806</v>
+        <v>0.1169846728444099</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.1195550784468651</v>
+        <v>0.1187557280063629</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.1175247058272362</v>
+        <v>0.116521067917347</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.1133393421769142</v>
+        <v>0.1124558821320534</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1138123646378517</v>
+        <v>0.112842433154583</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.1129530891776085</v>
+        <v>0.1120108515024185</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.1115578413009644</v>
+        <v>0.1105165034532547</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.1078924909234047</v>
+        <v>0.1069958955049515</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.1032412126660347</v>
+        <v>0.1025100275874138</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.1015353351831436</v>
+        <v>0.1007051691412926</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.1002434566617012</v>
+        <v>0.09941384941339493</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.1032748594880104</v>
+        <v>0.102405920624733</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.1383955925703049</v>
+        <v>0.1376911699771881</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.1405765116214752</v>
+        <v>0.1396297365427017</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.1400087624788284</v>
+        <v>0.1389529407024384</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.1366239190101624</v>
+        <v>0.1354691237211227</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.1367008984088898</v>
+        <v>0.1356273144483566</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.1305189728736877</v>
+        <v>0.1294401884078979</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.1299921125173569</v>
+        <v>0.1290325522422791</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.1274586170911789</v>
+        <v>0.1264968514442444</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.1255935877561569</v>
+        <v>0.1244805529713631</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.1268680691719055</v>
+        <v>0.1258241981267929</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.118739552795887</v>
+        <v>0.1178288012742996</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.1180970668792725</v>
+        <v>0.1172918677330017</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.1174595877528191</v>
+        <v>0.1165244355797768</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.1173398643732071</v>
+        <v>0.1164281889796257</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.1730543524026871</v>
+        <v>0.1716930568218231</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.1711735874414444</v>
+        <v>0.1697725504636765</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1670238226652145</v>
+        <v>0.1655238419771194</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.1669510155916214</v>
+        <v>0.1654845923185349</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.1651178598403931</v>
+        <v>0.1637720614671707</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.1610991209745407</v>
+        <v>0.1597033888101578</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.157201960682869</v>
+        <v>0.1558858454227448</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.154305562376976</v>
+        <v>0.1530193686485291</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.1523000150918961</v>
+        <v>0.1510583907365799</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.1481921225786209</v>
+        <v>0.1471385061740875</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.1445032209157944</v>
+        <v>0.143550917506218</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.1378577351570129</v>
+        <v>0.1367909461259842</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.1379810571670532</v>
+        <v>0.1370028853416443</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.1412186622619629</v>
+        <v>0.1401191651821136</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.198946475982666</v>
+        <v>0.1974893659353256</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.1968492120504379</v>
+        <v>0.1951069682836533</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.1940256506204605</v>
+        <v>0.1922495067119598</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.1900310814380646</v>
+        <v>0.1884855479001999</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.1863956600427628</v>
+        <v>0.1849269568920135</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.1797317117452621</v>
+        <v>0.1780464649200439</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.180334284901619</v>
+        <v>0.1788898557424545</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.1739858686923981</v>
+        <v>0.1725489348173141</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.1724490076303482</v>
+        <v>0.1710768789052963</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.1732037663459778</v>
+        <v>0.1719772666692734</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.1604510694742203</v>
+        <v>0.1594391465187073</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.1579433530569077</v>
+        <v>0.1569477319717407</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.1579599231481552</v>
+        <v>0.156914085149765</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.1641116291284561</v>
+        <v>0.1629329323768616</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.2344253063201904</v>
+        <v>0.2326398342847824</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.2218239009380341</v>
+        <v>0.2198518663644791</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.2217310965061188</v>
+        <v>0.2199625223875046</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.2200888395309448</v>
+        <v>0.2182664573192596</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.2108585834503174</v>
+        <v>0.209063708782196</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.2074020206928253</v>
+        <v>0.2056188434362411</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.2078601270914078</v>
+        <v>0.2062719464302063</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.203377291560173</v>
+        <v>0.2018590271472931</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.2028948664665222</v>
+        <v>0.2016502022743225</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.197349488735199</v>
+        <v>0.1960723847150803</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.1915483474731445</v>
+        <v>0.1905017495155334</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.1884981393814087</v>
+        <v>0.1873256862163544</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.1873594969511032</v>
+        <v>0.1863026767969131</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.1899510324001312</v>
+        <v>0.1888147741556168</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.2506311237812042</v>
+        <v>0.2483952790498734</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.2474002838134766</v>
+        <v>0.2451576292514801</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.2393234372138977</v>
+        <v>0.2373667657375336</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.237715482711792</v>
+        <v>0.2358222752809525</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.2307732552289963</v>
+        <v>0.2290566712617874</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.2318024933338165</v>
+        <v>0.2303018867969513</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.2260192632675171</v>
+        <v>0.2246742248535156</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.2200573980808258</v>
+        <v>0.2185084074735641</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.2185904085636139</v>
+        <v>0.2172982841730118</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2156790047883987</v>
+        <v>0.2144074589014053</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.2110443115234375</v>
+        <v>0.209953248500824</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.2096602767705917</v>
+        <v>0.2085453718900681</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.2119884490966797</v>
+        <v>0.210909366607666</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.2140649408102036</v>
+        <v>0.2129415422677994</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.2673622071743011</v>
+        <v>0.2652502954006195</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.257399320602417</v>
+        <v>0.2553731203079224</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.255962610244751</v>
+        <v>0.2540010213851929</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.2486803382635117</v>
+        <v>0.246935248374939</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.2480100095272064</v>
+        <v>0.2464011162519455</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.2421408444643021</v>
+        <v>0.2405679374933243</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.2394766062498093</v>
+        <v>0.2379695177078247</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.2380269765853882</v>
+        <v>0.2366025894880295</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.2357321232557297</v>
+        <v>0.2343362271785736</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.2336732447147369</v>
+        <v>0.2325188666582108</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.2217616587877274</v>
+        <v>0.2204881459474564</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.2254489958286285</v>
+        <v>0.224327340722084</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.2265894263982773</v>
+        <v>0.225450336933136</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.2281021326780319</v>
+        <v>0.2270261347293854</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.2775877118110657</v>
+        <v>0.2758156061172485</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.2743953168392181</v>
+        <v>0.2726238667964935</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.2702313661575317</v>
+        <v>0.2686633169651031</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.2634848952293396</v>
+        <v>0.2619600892066956</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.2666943967342377</v>
+        <v>0.2652880251407623</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.2558491826057434</v>
+        <v>0.2546746432781219</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.2554868459701538</v>
+        <v>0.2542271316051483</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.249471515417099</v>
+        <v>0.2482046335935593</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.2523757815361023</v>
+        <v>0.2511157393455505</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.2516210079193115</v>
+        <v>0.2504267692565918</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.2481397092342377</v>
+        <v>0.247024267911911</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.2480435818433762</v>
+        <v>0.2469576299190521</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.2479010969400406</v>
+        <v>0.2467741519212723</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.2594200670719147</v>
+        <v>0.258211612701416</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.284261018037796</v>
+        <v>0.2830198109149933</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.2847856283187866</v>
+        <v>0.2835594713687897</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.2742069363594055</v>
+        <v>0.2730579376220703</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.276586502790451</v>
+        <v>0.2754926085472107</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.2670504450798035</v>
+        <v>0.2659078240394592</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.2685386538505554</v>
+        <v>0.267470508813858</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.2682174444198608</v>
+        <v>0.2670276761054993</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.2649437785148621</v>
+        <v>0.2637802362442017</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.2604452669620514</v>
+        <v>0.2593900561332703</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.2591677904129028</v>
+        <v>0.2580794394016266</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.2614202797412872</v>
+        <v>0.2603049874305725</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.2634250521659851</v>
+        <v>0.2623497545719147</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.2731781899929047</v>
+        <v>0.2719038128852844</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.28343465924263</v>
+        <v>0.2822108268737793</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.288400411605835</v>
+        <v>0.2871353328227997</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.2886927425861359</v>
+        <v>0.287476658821106</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.2806988954544067</v>
+        <v>0.2795082032680511</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.2788337767124176</v>
+        <v>0.277479350566864</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.2841305434703827</v>
+        <v>0.282934159040451</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.2818417251110077</v>
+        <v>0.2805340588092804</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.2820154130458832</v>
+        <v>0.280731737613678</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.2800556123256683</v>
+        <v>0.2787397801876068</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.2818795144557953</v>
+        <v>0.2804596424102783</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.282247930765152</v>
+        <v>0.2809173166751862</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.2814530730247498</v>
+        <v>0.2800874412059784</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.2921136319637299</v>
+        <v>0.2905344069004059</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.2964669167995453</v>
+        <v>0.294917494058609</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.3110823929309845</v>
+        <v>0.3094175159931183</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.3043985962867737</v>
+        <v>0.3027800023555756</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.3050969541072845</v>
+        <v>0.3032824993133545</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.3061757683753967</v>
+        <v>0.3044335544109344</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.3061245679855347</v>
+        <v>0.3043559491634369</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.3042453229427338</v>
+        <v>0.3024516701698303</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.302635669708252</v>
+        <v>0.3009735941886902</v>
       </c>
       <c r="GH4" t="n">
-        <v>0.2989324927330017</v>
+        <v>0.2971974909305573</v>
       </c>
       <c r="GI4" t="n">
-        <v>0.2996359765529633</v>
+        <v>0.2978857457637787</v>
       </c>
       <c r="GJ4" t="n">
-        <v>0.2999996840953827</v>
+        <v>0.2982776761054993</v>
       </c>
       <c r="GK4" t="n">
-        <v>0.3038435578346252</v>
+        <v>0.3020663261413574</v>
       </c>
       <c r="GL4" t="n">
-        <v>0.3104371726512909</v>
+        <v>0.3083752393722534</v>
       </c>
       <c r="GM4" t="n">
-        <v>0.3168557286262512</v>
+        <v>0.3148097991943359</v>
       </c>
       <c r="GN4" t="n">
-        <v>0.3321373164653778</v>
+        <v>0.3301120400428772</v>
       </c>
       <c r="GO4" t="n">
-        <v>0.339880108833313</v>
+        <v>0.3377858996391296</v>
       </c>
       <c r="GP4" t="n">
-        <v>0.3328007161617279</v>
+        <v>0.3309009373188019</v>
       </c>
       <c r="GQ4" t="n">
-        <v>0.3298621475696564</v>
+        <v>0.3280543386936188</v>
       </c>
       <c r="GR4" t="n">
-        <v>0.3288111388683319</v>
+        <v>0.3269633054733276</v>
       </c>
       <c r="GS4" t="n">
-        <v>0.3272055983543396</v>
+        <v>0.3252811133861542</v>
       </c>
       <c r="GT4" t="n">
-        <v>0.328530877828598</v>
+        <v>0.326734870672226</v>
       </c>
       <c r="GU4" t="n">
-        <v>0.3228175044059753</v>
+        <v>0.3209854662418365</v>
       </c>
       <c r="GV4" t="n">
-        <v>0.3280035555362701</v>
+        <v>0.3259828388690948</v>
       </c>
       <c r="GW4" t="n">
-        <v>0.3230894505977631</v>
+        <v>0.3210959434509277</v>
       </c>
       <c r="GX4" t="n">
-        <v>0.3241716921329498</v>
+        <v>0.3221557140350342</v>
       </c>
       <c r="GY4" t="n">
-        <v>0.3244462311267853</v>
+        <v>0.3222864270210266</v>
       </c>
       <c r="GZ4" t="n">
-        <v>0.3376578986644745</v>
+        <v>0.3355458080768585</v>
       </c>
       <c r="HA4" t="n">
-        <v>0.350580245256424</v>
+        <v>0.3485662639141083</v>
       </c>
       <c r="HB4" t="n">
-        <v>0.3630596995353699</v>
+        <v>0.3608402907848358</v>
       </c>
       <c r="HC4" t="n">
-        <v>0.3573117852210999</v>
+        <v>0.3554198443889618</v>
       </c>
       <c r="HD4" t="n">
-        <v>0.3454219996929169</v>
+        <v>0.3427362442016602</v>
       </c>
       <c r="HE4" t="n">
-        <v>0.3406133651733398</v>
+        <v>0.3377911448478699</v>
       </c>
       <c r="HF4" t="n">
-        <v>0.3421693742275238</v>
+        <v>0.339409351348877</v>
       </c>
       <c r="HG4" t="n">
-        <v>0.3487009406089783</v>
+        <v>0.3460326194763184</v>
       </c>
       <c r="HH4" t="n">
-        <v>0.3475192189216614</v>
+        <v>0.3447322249412537</v>
       </c>
       <c r="HI4" t="n">
-        <v>0.3458665907382965</v>
+        <v>0.3432777225971222</v>
       </c>
       <c r="HJ4" t="n">
-        <v>0.3484143912792206</v>
+        <v>0.3455418646335602</v>
       </c>
       <c r="HK4" t="n">
-        <v>0.342134952545166</v>
+        <v>0.3393828272819519</v>
       </c>
       <c r="HL4" t="n">
-        <v>0.3438485562801361</v>
+        <v>0.3411253988742828</v>
       </c>
       <c r="HM4" t="n">
-        <v>0.3408194780349731</v>
+        <v>0.3379257023334503</v>
       </c>
       <c r="HN4" t="n">
-        <v>0.3640466034412384</v>
+        <v>0.3612489402294159</v>
       </c>
       <c r="HO4" t="n">
-        <v>0.3782960772514343</v>
+        <v>0.3754151165485382</v>
       </c>
       <c r="HP4" t="n">
-        <v>0.3580787181854248</v>
+        <v>0.3558709323406219</v>
       </c>
       <c r="HQ4" t="n">
-        <v>0.3464901149272919</v>
+        <v>0.3447533845901489</v>
       </c>
       <c r="HR4" t="inlineStr">
         <is>
@@ -3607,676 +3607,676 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02477490715682507</v>
+        <v>0.02428045310080051</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03348959982395172</v>
+        <v>0.03306932747364044</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03558918833732605</v>
+        <v>0.03513673320412636</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03713206201791763</v>
+        <v>0.03668530657887459</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03760436549782753</v>
+        <v>0.03716649487614632</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03689340502023697</v>
+        <v>0.03639362752437592</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03631202504038811</v>
+        <v>0.03586333617568016</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03596088662743568</v>
+        <v>0.0354657955467701</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03616900369524956</v>
+        <v>0.03567793965339661</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03548309579491615</v>
+        <v>0.03501613438129425</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03444060310721397</v>
+        <v>0.03403052315115929</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03341441974043846</v>
+        <v>0.03302732482552528</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03333155438303947</v>
+        <v>0.03294821083545685</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03390952572226524</v>
+        <v>0.03349566832184792</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04998867958784103</v>
+        <v>0.04932495206594467</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06135455891489983</v>
+        <v>0.06069227308034897</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0641135647892952</v>
+        <v>0.06343076378107071</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0650644451379776</v>
+        <v>0.06438831239938736</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06629301607608795</v>
+        <v>0.06552331149578094</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06393596529960632</v>
+        <v>0.06314282864332199</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06474974751472473</v>
+        <v>0.06401647627353668</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06427902728319168</v>
+        <v>0.063600093126297</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06373234838247299</v>
+        <v>0.06304512172937393</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06329771131277084</v>
+        <v>0.06257937848567963</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.06017992272973061</v>
+        <v>0.05955279991030693</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05788281187415123</v>
+        <v>0.05724228546023369</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.05771336704492569</v>
+        <v>0.05708720535039902</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.05912180244922638</v>
+        <v>0.05845579504966736</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0816570371389389</v>
+        <v>0.08094382286071777</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.09361825883388519</v>
+        <v>0.09276342391967773</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.09366682916879654</v>
+        <v>0.09274956583976746</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.09562630206346512</v>
+        <v>0.09464509785175323</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.09585040062665939</v>
+        <v>0.09488098323345184</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.09515044838190079</v>
+        <v>0.09407995641231537</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.09197988361120224</v>
+        <v>0.09106907993555069</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.09098777920007706</v>
+        <v>0.09007719159126282</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.09125535190105438</v>
+        <v>0.09031965583562851</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.08822953701019287</v>
+        <v>0.08733217418193817</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.08395705372095108</v>
+        <v>0.08314216136932373</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.08196645230054855</v>
+        <v>0.08119696378707886</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.08415248990058899</v>
+        <v>0.08331167697906494</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.08484955877065659</v>
+        <v>0.08398965746164322</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.1108589917421341</v>
+        <v>0.1099623218178749</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.1180407032370567</v>
+        <v>0.1170125305652618</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.1187440901994705</v>
+        <v>0.1176448687911034</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1202830225229263</v>
+        <v>0.1193395778536797</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.1183508411049843</v>
+        <v>0.1171949952840805</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1140555590391159</v>
+        <v>0.1130440160632133</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1145311892032623</v>
+        <v>0.1134351342916489</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.113646611571312</v>
+        <v>0.1125858202576637</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.1122477054595947</v>
+        <v>0.1110889241099358</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.1085412129759789</v>
+        <v>0.1075357422232628</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.1038171276450157</v>
+        <v>0.1029909253120422</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.1021154671907425</v>
+        <v>0.1011948063969612</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.1008310243487358</v>
+        <v>0.09991206228733063</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.1038637906312943</v>
+        <v>0.102907769382</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.1392594128847122</v>
+        <v>0.1383511424064636</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.1415179669857025</v>
+        <v>0.1403716504573822</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.1408963203430176</v>
+        <v>0.1396647542715073</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.137460470199585</v>
+        <v>0.1361466348171234</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.1375902742147446</v>
+        <v>0.136353924870491</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.1313266456127167</v>
+        <v>0.1301047056913376</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.1307452917098999</v>
+        <v>0.1296540051698685</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1282086223363876</v>
+        <v>0.1271184384822845</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.1263309866189957</v>
+        <v>0.1250929683446884</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.1275741904973984</v>
+        <v>0.1264103949069977</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1193665117025375</v>
+        <v>0.1183532699942589</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.1187270358204842</v>
+        <v>0.117823138833046</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.1180975437164307</v>
+        <v>0.1170663386583328</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.1179642900824547</v>
+        <v>0.1169622763991356</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.1742985993623734</v>
+        <v>0.1726709455251694</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.1723891645669937</v>
+        <v>0.1707371771335602</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1682400405406952</v>
+        <v>0.166514664888382</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.1680512279272079</v>
+        <v>0.1663887351751328</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.1661363840103149</v>
+        <v>0.164607360959053</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.1621057242155075</v>
+        <v>0.160533145070076</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.1581279933452606</v>
+        <v>0.156655952334404</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.1552079766988754</v>
+        <v>0.1537687033414841</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.153154581785202</v>
+        <v>0.1517687737941742</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.1489870548248291</v>
+        <v>0.1478013396263123</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.1452370584011078</v>
+        <v>0.1441655308008194</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1385517716407776</v>
+        <v>0.1373798698186874</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.1386766582727432</v>
+        <v>0.1375969350337982</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.1419283300638199</v>
+        <v>0.1407262682914734</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.200280100107193</v>
+        <v>0.1985630691051483</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.1982606649398804</v>
+        <v>0.1962621212005615</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.1953572183847427</v>
+        <v>0.1933489292860031</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.191223070025444</v>
+        <v>0.189473420381546</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.1875691264867783</v>
+        <v>0.1859030872583389</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.1808317303657532</v>
+        <v>0.1789625436067581</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.1813734620809555</v>
+        <v>0.1797547042369843</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.1749659031629562</v>
+        <v>0.1733665019273758</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.1733799576759338</v>
+        <v>0.1718570739030838</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.1740734279155731</v>
+        <v>0.1727056205272675</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.1612235307693481</v>
+        <v>0.160087987780571</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.1586896926164627</v>
+        <v>0.1575833559036255</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.1586892604827881</v>
+        <v>0.1575389355421066</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.1648840308189392</v>
+        <v>0.1635973006486893</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.2358627915382385</v>
+        <v>0.2338370531797409</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.2233276963233948</v>
+        <v>0.2211133390665054</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.2230869382619858</v>
+        <v>0.2210904210805893</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.2214355617761612</v>
+        <v>0.2193886339664459</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.2120961099863052</v>
+        <v>0.2101006060838699</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.208577424287796</v>
+        <v>0.2066051363945007</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.2089699357748032</v>
+        <v>0.2072048038244247</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.2043729573488235</v>
+        <v>0.2026967108249664</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.2038628309965134</v>
+        <v>0.202465757727623</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.1982628107070923</v>
+        <v>0.1968396008014679</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.1923715174198151</v>
+        <v>0.1911967247724533</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.1892872899770737</v>
+        <v>0.1880013793706894</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.1881154328584671</v>
+        <v>0.186952069401741</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1907257437705994</v>
+        <v>0.1894867569208145</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.2522956728935242</v>
+        <v>0.2497884184122086</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.2489319145679474</v>
+        <v>0.2464401423931122</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.2407002151012421</v>
+        <v>0.2385258972644806</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.2390447556972504</v>
+        <v>0.2369376122951508</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.2320291697978973</v>
+        <v>0.2301130443811417</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.2329266369342804</v>
+        <v>0.2312492728233337</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.2270579189062119</v>
+        <v>0.2255504578351974</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.2210442870855331</v>
+        <v>0.2193414866924286</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.2195329219102859</v>
+        <v>0.2180948555469513</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.2165658175945282</v>
+        <v>0.2151604294776917</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.2118554562330246</v>
+        <v>0.2106459140777588</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.2103708535432816</v>
+        <v>0.2091535329818726</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.2127471566200256</v>
+        <v>0.2115652412176132</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.2148200124502182</v>
+        <v>0.2136024087667465</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.2688837647438049</v>
+        <v>0.2665332555770874</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.2588130235671997</v>
+        <v>0.2565624415874481</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.2573569416999817</v>
+        <v>0.2551742196083069</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.2498797327280045</v>
+        <v>0.2479469776153564</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.2491326779127121</v>
+        <v>0.2473519742488861</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.2432083487510681</v>
+        <v>0.2414699047803879</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.2404797822237015</v>
+        <v>0.2388197183609009</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.238980308175087</v>
+        <v>0.2374129891395569</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.2366280853748322</v>
+        <v>0.2350932955741882</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.2345291972160339</v>
+        <v>0.2332474142313004</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.2225697040557861</v>
+        <v>0.2211896181106567</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.2261844277381897</v>
+        <v>0.2249705046415329</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.2272761762142181</v>
+        <v>0.2260552197694778</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.228827491402626</v>
+        <v>0.2276627123355865</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.2788768112659454</v>
+        <v>0.2769090831279755</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.2755783200263977</v>
+        <v>0.2736299335956573</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.2713322937488556</v>
+        <v>0.2695979177951813</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.2644893229007721</v>
+        <v>0.2628132104873657</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.2676548659801483</v>
+        <v>0.2661051154136658</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.2567349672317505</v>
+        <v>0.2554310262203217</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.2564178109169006</v>
+        <v>0.2550277709960938</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.250331699848175</v>
+        <v>0.2489535063505173</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.2531840205192566</v>
+        <v>0.2518136501312256</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.2523845732212067</v>
+        <v>0.2510911822319031</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.2488869577646255</v>
+        <v>0.2476742714643478</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.2487245053052902</v>
+        <v>0.2475506514310837</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.2485504895448685</v>
+        <v>0.247345894575119</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.2601541578769684</v>
+        <v>0.2588684856891632</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.2850684523582458</v>
+        <v>0.2837150990962982</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.2855959534645081</v>
+        <v>0.2842604219913483</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.2749622166156769</v>
+        <v>0.2737078368663788</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.2773381173610687</v>
+        <v>0.276138961315155</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.2677676975727081</v>
+        <v>0.2665272355079651</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.2692611217498779</v>
+        <v>0.2680960595607758</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.2689321339130402</v>
+        <v>0.2676443457603455</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.265655905008316</v>
+        <v>0.2643975615501404</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.261142909526825</v>
+        <v>0.2599951028823853</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.259859561920166</v>
+        <v>0.2586808502674103</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.2621167302131653</v>
+        <v>0.260915219783783</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.2640602588653564</v>
+        <v>0.2629120349884033</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.2738323211669922</v>
+        <v>0.2724833190441132</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.2841176986694336</v>
+        <v>0.2828172743320465</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.2892331779003143</v>
+        <v>0.2878579795360565</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.289486825466156</v>
+        <v>0.2881673276424408</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.2814616560935974</v>
+        <v>0.2801734507083893</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.2795989215373993</v>
+        <v>0.2781437933444977</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.2849221229553223</v>
+        <v>0.2836247682571411</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.2826381623744965</v>
+        <v>0.2812284529209137</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.2828284502029419</v>
+        <v>0.2814436256885529</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.2808769345283508</v>
+        <v>0.2794608771800995</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.2827164828777313</v>
+        <v>0.2811963856220245</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.2830949127674103</v>
+        <v>0.2816641926765442</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.2822609543800354</v>
+        <v>0.2808051705360413</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.2929043173789978</v>
+        <v>0.2912441492080688</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.2973033785820007</v>
+        <v>0.29566690325737</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.3119429349899292</v>
+        <v>0.3101934492588043</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.3054675757884979</v>
+        <v>0.3037129342556</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.3061912059783936</v>
+        <v>0.3042365610599518</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.307316929101944</v>
+        <v>0.3054337203502655</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.3072801232337952</v>
+        <v>0.3053682446479797</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.305377870798111</v>
+        <v>0.3034441769123077</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.3037469387054443</v>
+        <v>0.3019466400146484</v>
       </c>
       <c r="GH5" t="n">
-        <v>0.3000350594520569</v>
+        <v>0.2981670498847961</v>
       </c>
       <c r="GI5" t="n">
-        <v>0.3007134795188904</v>
+        <v>0.2988418936729431</v>
       </c>
       <c r="GJ5" t="n">
-        <v>0.3011108338832855</v>
+        <v>0.2992578446865082</v>
       </c>
       <c r="GK5" t="n">
-        <v>0.304972380399704</v>
+        <v>0.3030657470226288</v>
       </c>
       <c r="GL5" t="n">
-        <v>0.3115286827087402</v>
+        <v>0.3093507587909698</v>
       </c>
       <c r="GM5" t="n">
-        <v>0.3179110586643219</v>
+        <v>0.3157642185688019</v>
       </c>
       <c r="GN5" t="n">
-        <v>0.333223819732666</v>
+        <v>0.331085205078125</v>
       </c>
       <c r="GO5" t="n">
-        <v>0.3410508632659912</v>
+        <v>0.3388335108757019</v>
       </c>
       <c r="GP5" t="n">
-        <v>0.3339481353759766</v>
+        <v>0.3319107294082642</v>
       </c>
       <c r="GQ5" t="n">
-        <v>0.3309441804885864</v>
+        <v>0.3290127217769623</v>
       </c>
       <c r="GR5" t="n">
-        <v>0.3298976421356201</v>
+        <v>0.3279174566268921</v>
       </c>
       <c r="GS5" t="n">
-        <v>0.3282979726791382</v>
+        <v>0.3262421190738678</v>
       </c>
       <c r="GT5" t="n">
-        <v>0.3296602964401245</v>
+        <v>0.3277332484722137</v>
       </c>
       <c r="GU5" t="n">
-        <v>0.3239479064941406</v>
+        <v>0.3219878673553467</v>
       </c>
       <c r="GV5" t="n">
-        <v>0.3291791975498199</v>
+        <v>0.3270226418972015</v>
       </c>
       <c r="GW5" t="n">
-        <v>0.3242652416229248</v>
+        <v>0.3221406042575836</v>
       </c>
       <c r="GX5" t="n">
-        <v>0.325383722782135</v>
+        <v>0.323233038187027</v>
       </c>
       <c r="GY5" t="n">
-        <v>0.3256891965866089</v>
+        <v>0.3233921527862549</v>
       </c>
       <c r="GZ5" t="n">
-        <v>0.3388771414756775</v>
+        <v>0.3366313278675079</v>
       </c>
       <c r="HA5" t="n">
-        <v>0.3517445623874664</v>
+        <v>0.349608302116394</v>
       </c>
       <c r="HB5" t="n">
-        <v>0.3643373548984528</v>
+        <v>0.3619728684425354</v>
       </c>
       <c r="HC5" t="n">
-        <v>0.3583309352397919</v>
+        <v>0.3563314080238342</v>
       </c>
       <c r="HD5" t="n">
-        <v>0.3469274640083313</v>
+        <v>0.3440693914890289</v>
       </c>
       <c r="HE5" t="n">
-        <v>0.3420506715774536</v>
+        <v>0.3390647172927856</v>
       </c>
       <c r="HF5" t="n">
-        <v>0.3436167538166046</v>
+        <v>0.3406950235366821</v>
       </c>
       <c r="HG5" t="n">
-        <v>0.3501987755298615</v>
+        <v>0.3473580181598663</v>
       </c>
       <c r="HH5" t="n">
-        <v>0.3490679562091827</v>
+        <v>0.3460981547832489</v>
       </c>
       <c r="HI5" t="n">
-        <v>0.3474437594413757</v>
+        <v>0.3446662724018097</v>
       </c>
       <c r="HJ5" t="n">
-        <v>0.3500360250473022</v>
+        <v>0.3469628095626831</v>
       </c>
       <c r="HK5" t="n">
-        <v>0.3437707126140594</v>
+        <v>0.3408189415931702</v>
       </c>
       <c r="HL5" t="n">
-        <v>0.3455227017402649</v>
+        <v>0.3425921499729156</v>
       </c>
       <c r="HM5" t="n">
-        <v>0.342519223690033</v>
+        <v>0.3394136428833008</v>
       </c>
       <c r="HN5" t="n">
-        <v>0.3657254278659821</v>
+        <v>0.362697422504425</v>
       </c>
       <c r="HO5" t="n">
-        <v>0.3799819052219391</v>
+        <v>0.3768655955791473</v>
       </c>
       <c r="HP5" t="n">
-        <v>0.3593225479125977</v>
+        <v>0.3569588661193848</v>
       </c>
       <c r="HQ5" t="n">
-        <v>0.3474158346652985</v>
+        <v>0.3455806970596313</v>
       </c>
       <c r="HR5" t="inlineStr">
         <is>
@@ -4291,676 +4291,676 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02522354759275913</v>
+        <v>0.02460705302655697</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03395714238286018</v>
+        <v>0.03341708704829216</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03604547306895256</v>
+        <v>0.03547610715031624</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0375719778239727</v>
+        <v>0.03701156005263329</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03801929950714111</v>
+        <v>0.03747506439685822</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03728371486067772</v>
+        <v>0.03667999431490898</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03668216615915298</v>
+        <v>0.03613075241446495</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03632710501551628</v>
+        <v>0.03572705015540123</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03652738034725189</v>
+        <v>0.0359305813908577</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03582604974508286</v>
+        <v>0.03525371477007866</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03475445881485939</v>
+        <v>0.03424281999468803</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03368916362524033</v>
+        <v>0.03320405632257462</v>
       </c>
       <c r="N6" t="n">
-        <v>0.033602524548769</v>
+        <v>0.03311967104673386</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03417399153113365</v>
+        <v>0.03365733847022057</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05067432299256325</v>
+        <v>0.04981594532728195</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.06207231432199478</v>
+        <v>0.06123309209942818</v>
       </c>
       <c r="R6" t="n">
-        <v>0.06484449654817581</v>
+        <v>0.06398165971040726</v>
       </c>
       <c r="S6" t="n">
-        <v>0.06573161482810974</v>
+        <v>0.06489022076129913</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06695109605789185</v>
+        <v>0.06601246446371078</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06452778726816177</v>
+        <v>0.06357074528932571</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06533069908618927</v>
+        <v>0.06443619728088379</v>
       </c>
       <c r="W6" t="n">
-        <v>0.06482533365488052</v>
+        <v>0.06398253887891769</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06428014487028122</v>
+        <v>0.06342794746160507</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.06382252275943756</v>
+        <v>0.06294155865907669</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.06065203994512558</v>
+        <v>0.05986968800425529</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.05830799415707588</v>
+        <v>0.05751020833849907</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.05814255028963089</v>
+        <v>0.05735443904995918</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.05953731015324593</v>
+        <v>0.05870767682790756</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.08252641558647156</v>
+        <v>0.08159530907869339</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.09453824162483215</v>
+        <v>0.09347858279943466</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0945977047085762</v>
+        <v>0.09346684068441391</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.09646135568618774</v>
+        <v>0.09528391808271408</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.09666331112384796</v>
+        <v>0.09548895061016083</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.09592658281326294</v>
+        <v>0.09464908391237259</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.09270171076059341</v>
+        <v>0.09158938378095627</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.09166423231363297</v>
+        <v>0.09054999798536301</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.09194352477788925</v>
+        <v>0.09080177545547485</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.088876873254776</v>
+        <v>0.08777552098035812</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.08451275527477264</v>
+        <v>0.08350837975740433</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.08248946070671082</v>
+        <v>0.08152252435684204</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.08469582349061966</v>
+        <v>0.08364541083574295</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.08537337183952332</v>
+        <v>0.08430401235818863</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.1118640527129173</v>
+        <v>0.1107385605573654</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.1191564351320267</v>
+        <v>0.1179048493504524</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.1197955459356308</v>
+        <v>0.1184771507978439</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1211981996893883</v>
+        <v>0.1200564131140709</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.1193279549479485</v>
+        <v>0.1179159358143806</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.1149034649133682</v>
+        <v>0.113666720688343</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1153632700443268</v>
+        <v>0.1140308976173401</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.1144291684031487</v>
+        <v>0.113130085170269</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.1130299791693687</v>
+        <v>0.1116330176591873</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.1092603579163551</v>
+        <v>0.1080236062407494</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.1044370532035828</v>
+        <v>0.1033954918384552</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.1027124747633934</v>
+        <v>0.101562075316906</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.10142582654953</v>
+        <v>0.1002699583768845</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.1044525876641273</v>
+        <v>0.1032546013593674</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.1403848677873611</v>
+        <v>0.1392720490694046</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.1427127718925476</v>
+        <v>0.141321212053299</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.142006054520607</v>
+        <v>0.1405320018529892</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.1385052055120468</v>
+        <v>0.1369553804397583</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.1386381387710571</v>
+        <v>0.1371202617883682</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.1322669833898544</v>
+        <v>0.1307817548513412</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.1316160708665848</v>
+        <v>0.1302730590105057</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.1290475726127625</v>
+        <v>0.127693310379982</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.1271607279777527</v>
+        <v>0.1256627291440964</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.1283615678548813</v>
+        <v>0.1269440352916718</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.1200363636016846</v>
+        <v>0.1187839955091476</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.1193666085600853</v>
+        <v>0.118208259344101</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.1187366172671318</v>
+        <v>0.1174440160393715</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.1185799762606621</v>
+        <v>0.117316335439682</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.1758566796779633</v>
+        <v>0.173898309469223</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.1738847345113754</v>
+        <v>0.1718874126672745</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1697055548429489</v>
+        <v>0.1676141768693924</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.1693895608186722</v>
+        <v>0.1673941016197205</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.1673218011856079</v>
+        <v>0.1654598563909531</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.1632469147443771</v>
+        <v>0.1613284200429916</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.1591824293136597</v>
+        <v>0.1573907434940338</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.156210720539093</v>
+        <v>0.1544471979141235</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.1540966629981995</v>
+        <v>0.1523996442556381</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.1498568505048752</v>
+        <v>0.1483790725469589</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.1460101008415222</v>
+        <v>0.1446533203125</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.1392474919557571</v>
+        <v>0.1377899348735809</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.1393679529428482</v>
+        <v>0.1379992961883545</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.1426165997982025</v>
+        <v>0.1411112695932388</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.2018893510103226</v>
+        <v>0.1997801810503006</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.1999574452638626</v>
+        <v>0.1975298374891281</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.196916937828064</v>
+        <v>0.1944806724786758</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.1926058977842331</v>
+        <v>0.1904609799385071</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.1889018714427948</v>
+        <v>0.186832383275032</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.1820531934499741</v>
+        <v>0.1797910332679749</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.1825180202722549</v>
+        <v>0.1805211156606674</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.1760341227054596</v>
+        <v>0.1740712225437164</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.1743953078985214</v>
+        <v>0.1725258678197861</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.1750195026397705</v>
+        <v>0.1733249574899673</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.1620153933763504</v>
+        <v>0.1605703681707382</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.1594205796718597</v>
+        <v>0.1579979807138443</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.1593927592039108</v>
+        <v>0.1579279005527496</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.1656244844198227</v>
+        <v>0.1640014350414276</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.2375306338071823</v>
+        <v>0.2350352704524994</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.2250551581382751</v>
+        <v>0.2223368436098099</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.2246175855398178</v>
+        <v>0.2221514880657196</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.2229142487049103</v>
+        <v>0.2203788906335831</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.2134500741958618</v>
+        <v>0.2110003978013992</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.2098533362150192</v>
+        <v>0.2074425518512726</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.2101660519838333</v>
+        <v>0.207981675863266</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.2054412215948105</v>
+        <v>0.2033853381872177</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.2048725932836533</v>
+        <v>0.203095942735672</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.1992050409317017</v>
+        <v>0.1974184960126877</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.19318488240242</v>
+        <v>0.1916654109954834</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.1900564283132553</v>
+        <v>0.1884322166442871</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.1888368427753448</v>
+        <v>0.1873411983251572</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1914438456296921</v>
+        <v>0.1898517459630966</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.2541299164295197</v>
+        <v>0.2510277628898621</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.2505872249603271</v>
+        <v>0.2475284785032272</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.2422073781490326</v>
+        <v>0.2395270466804504</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.2404842972755432</v>
+        <v>0.2378806918859482</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.2333645224571228</v>
+        <v>0.2309673726558685</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.2341212630271912</v>
+        <v>0.2320092767477036</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.2281384170055389</v>
+        <v>0.2262208163738251</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.2220607548952103</v>
+        <v>0.2199631184339523</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.2204837203025818</v>
+        <v>0.2186598479747772</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.2174445241689682</v>
+        <v>0.2156688421964645</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.212642639875412</v>
+        <v>0.2110839039087296</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.2110385149717331</v>
+        <v>0.209501713514328</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.2134488672018051</v>
+        <v>0.2119202017784119</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.2155052274465561</v>
+        <v>0.2139301896095276</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.2705222368240356</v>
+        <v>0.2676028907299042</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.2603305876255035</v>
+        <v>0.2575468719005585</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.2588317692279816</v>
+        <v>0.2561133503913879</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.2511501014232635</v>
+        <v>0.2487548589706421</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.2502939999103546</v>
+        <v>0.2480689138174057</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.2443028688430786</v>
+        <v>0.2421355694532394</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.24149489402771</v>
+        <v>0.2394254505634308</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.2399243861436844</v>
+        <v>0.2379584908485413</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.2375199049711227</v>
+        <v>0.2356108427047729</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.2353735715150833</v>
+        <v>0.2337293773889542</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.2233297824859619</v>
+        <v>0.2215874046087265</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.2268642038106918</v>
+        <v>0.2253105342388153</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.2278842031955719</v>
+        <v>0.2263267189264297</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.2294723242521286</v>
+        <v>0.227954164147377</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.2802110612392426</v>
+        <v>0.2777300179004669</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.2767636775970459</v>
+        <v>0.2743258476257324</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.2724239826202393</v>
+        <v>0.2702299654483795</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.2654723823070526</v>
+        <v>0.263369619846344</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.268595963716507</v>
+        <v>0.2666372358798981</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.2575906217098236</v>
+        <v>0.2559027373790741</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.2573244571685791</v>
+        <v>0.255536675453186</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.2511412501335144</v>
+        <v>0.2493764609098434</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.2539514601230621</v>
+        <v>0.2522217333316803</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.2530920803546906</v>
+        <v>0.2514459192752838</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.2495596557855606</v>
+        <v>0.247990757226944</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.2493229508399963</v>
+        <v>0.2478127032518387</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.2491025924682617</v>
+        <v>0.2475616037845612</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.2607879042625427</v>
+        <v>0.2591246962547302</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.2858297526836395</v>
+        <v>0.2841117680072784</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.2863557636737823</v>
+        <v>0.2846524119377136</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.2756669521331787</v>
+        <v>0.2740681171417236</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.2780280709266663</v>
+        <v>0.2764789462089539</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.2684195935726166</v>
+        <v>0.2668399214744568</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.2699086666107178</v>
+        <v>0.2683956325054169</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.2695747017860413</v>
+        <v>0.2679440975189209</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.2662915885448456</v>
+        <v>0.2646878957748413</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.2617667615413666</v>
+        <v>0.2602812051773071</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.2604780197143555</v>
+        <v>0.2589644491672516</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.262723833322525</v>
+        <v>0.2611733675003052</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.2645911872386932</v>
+        <v>0.2631045877933502</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.2743685841560364</v>
+        <v>0.2726605236530304</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.2846744060516357</v>
+        <v>0.2829947769641876</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.2899834513664246</v>
+        <v>0.2882095873355865</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.2901950776576996</v>
+        <v>0.2884892821311951</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.2821386754512787</v>
+        <v>0.2804761826992035</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.2802689373493195</v>
+        <v>0.278432160615921</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.2856284379959106</v>
+        <v>0.2839459776878357</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.2833361327648163</v>
+        <v>0.2815297245979309</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.2835452556610107</v>
+        <v>0.2817589044570923</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.2815987467765808</v>
+        <v>0.2797756493091583</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.2834430634975433</v>
+        <v>0.2815014719963074</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.2838298380374908</v>
+        <v>0.2819725275039673</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.2829365134239197</v>
+        <v>0.2810517847537994</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.293546050786972</v>
+        <v>0.2914472818374634</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.2979892194271088</v>
+        <v>0.2958943247795105</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.3126569092273712</v>
+        <v>0.3104393780231476</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.3064280450344086</v>
+        <v>0.3041634559631348</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.3071700930595398</v>
+        <v>0.3046909868717194</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.3083422183990479</v>
+        <v>0.3059156239032745</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.3083177804946899</v>
+        <v>0.3058555126190186</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.3063856363296509</v>
+        <v>0.3039059937000275</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.3047313392162323</v>
+        <v>0.3023922145366669</v>
       </c>
       <c r="GH6" t="n">
-        <v>0.3010034561157227</v>
+        <v>0.2985939085483551</v>
       </c>
       <c r="GI6" t="n">
-        <v>0.3016247153282166</v>
+        <v>0.2991956174373627</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.3020752668380737</v>
+        <v>0.2996683120727539</v>
       </c>
       <c r="GK6" t="n">
-        <v>0.3059440553188324</v>
+        <v>0.3034679889678955</v>
       </c>
       <c r="GL6" t="n">
-        <v>0.3124442994594574</v>
+        <v>0.3096942007541656</v>
       </c>
       <c r="GM6" t="n">
-        <v>0.3187808692455292</v>
+        <v>0.3160593509674072</v>
       </c>
       <c r="GN6" t="n">
-        <v>0.3341204822063446</v>
+        <v>0.3313930630683899</v>
       </c>
       <c r="GO6" t="n">
-        <v>0.3420371115207672</v>
+        <v>0.3392008543014526</v>
       </c>
       <c r="GP6" t="n">
-        <v>0.3349483907222748</v>
+        <v>0.3323333263397217</v>
       </c>
       <c r="GQ6" t="n">
-        <v>0.3318676352500916</v>
+        <v>0.3293745517730713</v>
       </c>
       <c r="GR6" t="n">
-        <v>0.3308370113372803</v>
+        <v>0.3283050954341888</v>
       </c>
       <c r="GS6" t="n">
-        <v>0.3292349874973297</v>
+        <v>0.3266196548938751</v>
       </c>
       <c r="GT6" t="n">
-        <v>0.3306315243244171</v>
+        <v>0.3281265795230865</v>
       </c>
       <c r="GU6" t="n">
-        <v>0.3249135911464691</v>
+        <v>0.3223705589771271</v>
       </c>
       <c r="GV6" t="n">
-        <v>0.3301834464073181</v>
+        <v>0.3274224698543549</v>
       </c>
       <c r="GW6" t="n">
-        <v>0.3252623379230499</v>
+        <v>0.3225273191928864</v>
       </c>
       <c r="GX6" t="n">
-        <v>0.3264118134975433</v>
+        <v>0.3236326277256012</v>
       </c>
       <c r="GY6" t="n">
-        <v>0.3267404139041901</v>
+        <v>0.3237964808940887</v>
       </c>
       <c r="GZ6" t="n">
-        <v>0.3399000763893127</v>
+        <v>0.3370065093040466</v>
       </c>
       <c r="HA6" t="n">
-        <v>0.3527229428291321</v>
+        <v>0.3499677777290344</v>
       </c>
       <c r="HB6" t="n">
-        <v>0.3654147088527679</v>
+        <v>0.3623718023300171</v>
       </c>
       <c r="HC6" t="n">
-        <v>0.3591762781143188</v>
+        <v>0.3566235303878784</v>
       </c>
       <c r="HD6" t="n">
-        <v>0.3481805026531219</v>
+        <v>0.3445188403129578</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.3432445228099823</v>
+        <v>0.3394883573055267</v>
       </c>
       <c r="HF6" t="n">
-        <v>0.3448282480239868</v>
+        <v>0.341137558221817</v>
       </c>
       <c r="HG6" t="n">
-        <v>0.3514571785926819</v>
+        <v>0.3478275835514069</v>
       </c>
       <c r="HH6" t="n">
-        <v>0.3503752946853638</v>
+        <v>0.346596896648407</v>
       </c>
       <c r="HI6" t="n">
-        <v>0.3487776517868042</v>
+        <v>0.3451794981956482</v>
       </c>
       <c r="HJ6" t="n">
-        <v>0.3514176607131958</v>
+        <v>0.3475086092948914</v>
       </c>
       <c r="HK6" t="n">
-        <v>0.345166802406311</v>
+        <v>0.3413757383823395</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.3469631969928741</v>
+        <v>0.3431837558746338</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.3439946472644806</v>
+        <v>0.3400381207466125</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.3671712577342987</v>
+        <v>0.3632882535457611</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.3814216256141663</v>
+        <v>0.3774294257164001</v>
       </c>
       <c r="HP6" t="n">
-        <v>0.3603778183460236</v>
+        <v>0.3573618233203888</v>
       </c>
       <c r="HQ6" t="n">
-        <v>0.3481786847114563</v>
+        <v>0.3458356857299805</v>
       </c>
       <c r="HR6" t="inlineStr">
         <is>
@@ -4975,676 +4975,676 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02562805823981762</v>
+        <v>0.02491172961890697</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03436929732561111</v>
+        <v>0.03374115750193596</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03644922748208046</v>
+        <v>0.03579409047961235</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03796205297112465</v>
+        <v>0.0373169481754303</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03838392719626427</v>
+        <v>0.03776048496365547</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03762639313936234</v>
+        <v>0.03694488108158112</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03700554370880127</v>
+        <v>0.0363769493997097</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03664589673280716</v>
+        <v>0.03596757352352142</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03683914989233017</v>
+        <v>0.0361633375287056</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03612423688173294</v>
+        <v>0.03547380492091179</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03502486646175385</v>
+        <v>0.03443851321935654</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03393165767192841</v>
+        <v>0.03337437286973</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03384201601147652</v>
+        <v>0.03328611329197884</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03441000729799271</v>
+        <v>0.03381798043847084</v>
       </c>
       <c r="P7" t="n">
-        <v>0.05130030587315559</v>
+        <v>0.05029672756791115</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.06270501762628555</v>
+        <v>0.06173799932003021</v>
       </c>
       <c r="R7" t="n">
-        <v>0.06548599153757095</v>
+        <v>0.06449098885059357</v>
       </c>
       <c r="S7" t="n">
-        <v>0.06631483882665634</v>
+        <v>0.06535004824399948</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06752478331327438</v>
+        <v>0.06646016240119934</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06504668295383453</v>
+        <v>0.06396835297346115</v>
       </c>
       <c r="V7" t="n">
-        <v>0.06583278626203537</v>
+        <v>0.064818374812603</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06529945880174637</v>
+        <v>0.06433554738759995</v>
       </c>
       <c r="X7" t="n">
-        <v>0.06474866718053818</v>
+        <v>0.06377511471509933</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.06426893919706345</v>
+        <v>0.0632694736123085</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.06105054542422295</v>
+        <v>0.06015623360872269</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.05867774039506912</v>
+        <v>0.05776670575141907</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.05851408094167709</v>
+        <v>0.05760959535837173</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.05990137532353401</v>
+        <v>0.05895422771573067</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.08329813182353973</v>
+        <v>0.08221510052680969</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.09533967077732086</v>
+        <v>0.09413212537765503</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.09540054947137833</v>
+        <v>0.09411287307739258</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.09717480838298798</v>
+        <v>0.095852330327034</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.09735793620347977</v>
+        <v>0.09603110700845718</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.09658828377723694</v>
+        <v>0.09515831619501114</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09331237524747849</v>
+        <v>0.09205211699008942</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.09223897010087967</v>
+        <v>0.09097646921873093</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.09251928329467773</v>
+        <v>0.09122805297374725</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.08941951394081116</v>
+        <v>0.08817145973443985</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.08498422801494598</v>
+        <v>0.08384405076503754</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.08293697983026505</v>
+        <v>0.08182965219020844</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.08515981584787369</v>
+        <v>0.08396071195602417</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.08582130819559097</v>
+        <v>0.0846036970615387</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.1127525791525841</v>
+        <v>0.1114697307348251</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.1201004981994629</v>
+        <v>0.1186830326914787</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.120677575469017</v>
+        <v>0.1191943660378456</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1219590306282043</v>
+        <v>0.120667926967144</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.1201568022370338</v>
+        <v>0.1185555160045624</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.1156130135059357</v>
+        <v>0.1142097115516663</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1160600781440735</v>
+        <v>0.1145544052124023</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.1150865480303764</v>
+        <v>0.113614410161972</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.1136777251958847</v>
+        <v>0.1121088638901711</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.1098615229129791</v>
+        <v>0.1084583923220634</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.1049540489912033</v>
+        <v>0.103759877383709</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.103217288851738</v>
+        <v>0.1019050031900406</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.1019349247217178</v>
+        <v>0.1006120964884758</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.1049547344446182</v>
+        <v>0.1035867556929588</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.1413466781377792</v>
+        <v>0.1400866955518723</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.1437164843082428</v>
+        <v>0.1421418339014053</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.1429286599159241</v>
+        <v>0.1412712633609772</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.1393507719039917</v>
+        <v>0.1376228183507919</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.1395094394683838</v>
+        <v>0.1377846598625183</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.133046418428421</v>
+        <v>0.1313681453466415</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.1323313266038895</v>
+        <v>0.1308053582906723</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.1297451257705688</v>
+        <v>0.1282011270523071</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.1278405636548996</v>
+        <v>0.1261565387248993</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.1290033906698227</v>
+        <v>0.1274057626724243</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1205901801586151</v>
+        <v>0.1191698983311653</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.1199079975485802</v>
+        <v>0.1185713931918144</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.1192829385399818</v>
+        <v>0.1178064420819283</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.119110956788063</v>
+        <v>0.1176631674170494</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.1771750897169113</v>
+        <v>0.1749716401100159</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.1751107722520828</v>
+        <v>0.1728587448596954</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1709050834178925</v>
+        <v>0.1685409545898438</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.1704538464546204</v>
+        <v>0.1682096272706985</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.1682902872562408</v>
+        <v>0.1661857515573502</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.164189800620079</v>
+        <v>0.1620218902826309</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.1600387692451477</v>
+        <v>0.1580159962177277</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.1570315808057785</v>
+        <v>0.1550374627113342</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.1548685282468796</v>
+        <v>0.1529505103826523</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.1505696028470993</v>
+        <v>0.1488844007253647</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.1466484516859055</v>
+        <v>0.1450918465852737</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.1398404389619827</v>
+        <v>0.1381827294826508</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.1399616748094559</v>
+        <v>0.1383894681930542</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.1432126313447952</v>
+        <v>0.1414945870637894</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.2032134085893631</v>
+        <v>0.2008123695850372</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.2013147324323654</v>
+        <v>0.1985662132501602</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.1981805562973022</v>
+        <v>0.1954275965690613</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.1937174201011658</v>
+        <v>0.191281720995903</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.1899827122688293</v>
+        <v>0.1876197010278702</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.1830545216798782</v>
+        <v>0.1805095374584198</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.1834547817707062</v>
+        <v>0.1811885684728622</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.1769076287746429</v>
+        <v>0.1746875494718552</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.1752196997404099</v>
+        <v>0.1731042563915253</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.1757816970348358</v>
+        <v>0.1738568991422653</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.1626796871423721</v>
+        <v>0.1610179245471954</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.1600495278835297</v>
+        <v>0.158405676484108</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.1600085198879242</v>
+        <v>0.1583227515220642</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.1662712097167969</v>
+        <v>0.1644121408462524</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.2388625890016556</v>
+        <v>0.2360170930624008</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.2264379113912582</v>
+        <v>0.2233453840017319</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.2258539944887161</v>
+        <v>0.2230462580919266</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.2241293787956238</v>
+        <v>0.2212433665990829</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.2145507633686066</v>
+        <v>0.2117759138345718</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.210890606045723</v>
+        <v>0.2081676423549652</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.2111421078443527</v>
+        <v>0.2086606472730637</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.2063076049089432</v>
+        <v>0.2039832919836044</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.2057186812162399</v>
+        <v>0.2036736011505127</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1999949216842651</v>
+        <v>0.1979534476995468</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.1938789635896683</v>
+        <v>0.1921189725399017</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.19071364402771</v>
+        <v>0.18885238468647</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.1894662082195282</v>
+        <v>0.1877376735210419</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.1920864582061768</v>
+        <v>0.1902466118335724</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.2556321322917938</v>
+        <v>0.2520974576473236</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.2519600391387939</v>
+        <v>0.2484943270683289</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.2434325069189072</v>
+        <v>0.2403879761695862</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.2416587471961975</v>
+        <v>0.2387012541294098</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.2344612926244736</v>
+        <v>0.2317229062318802</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.2350915670394897</v>
+        <v>0.232672706246376</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.2290369421243668</v>
+        <v>0.2268296331167221</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.2229118943214417</v>
+        <v>0.220536932349205</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.2212967574596405</v>
+        <v>0.2192016094923019</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.2182101756334305</v>
+        <v>0.2161734104156494</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.2133280038833618</v>
+        <v>0.2115243375301361</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.2116211205720901</v>
+        <v>0.209862232208252</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.2140780240297318</v>
+        <v>0.2123061865568161</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.2161291092634201</v>
+        <v>0.2143038958311081</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.2718742191791534</v>
+        <v>0.2685453593730927</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.2615775167942047</v>
+        <v>0.2584132850170135</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.2600552439689636</v>
+        <v>0.2569560408592224</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.2521920204162598</v>
+        <v>0.2494686394929886</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.2512693107128143</v>
+        <v>0.2487283200025558</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.2452240586280823</v>
+        <v>0.2427545636892319</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.2423636168241501</v>
+        <v>0.2400051802396774</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.240747407078743</v>
+        <v>0.2385001629590988</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.2382859736680984</v>
+        <v>0.2361153215169907</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.2361035197973251</v>
+        <v>0.2342046350240707</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.2240143269300461</v>
+        <v>0.2220157235860825</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.2274878025054932</v>
+        <v>0.2256937921047211</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.2284591346979141</v>
+        <v>0.2266656160354614</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.2300752252340317</v>
+        <v>0.228309839963913</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.2813215851783752</v>
+        <v>0.2784765958786011</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.2777792513370514</v>
+        <v>0.2749962508678436</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.273372083902359</v>
+        <v>0.270853579044342</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.2663323283195496</v>
+        <v>0.263929694890976</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.2694180011749268</v>
+        <v>0.2671717703342438</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.258347362279892</v>
+        <v>0.2563892304897308</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.2581373155117035</v>
+        <v>0.2560660839080811</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.2518908083438873</v>
+        <v>0.2498506307601929</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.2546548247337341</v>
+        <v>0.2526704370975494</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.2537471950054169</v>
+        <v>0.2518519461154938</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.2501921057701111</v>
+        <v>0.2483733892440796</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.249899834394455</v>
+        <v>0.2481552958488464</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.2496478408575058</v>
+        <v>0.2478736490011215</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.2614216208457947</v>
+        <v>0.2594927847385406</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.2865191996097565</v>
+        <v>0.2845450937747955</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.2870573997497559</v>
+        <v>0.2850936651229858</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.2763241529464722</v>
+        <v>0.2744829058647156</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.278683215379715</v>
+        <v>0.2768887579441071</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.2690457701683044</v>
+        <v>0.2672285139560699</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.2705353200435638</v>
+        <v>0.2687789797782898</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.2701991498470306</v>
+        <v>0.2683294713497162</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.2669112980365753</v>
+        <v>0.2650664150714874</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.2623741328716278</v>
+        <v>0.2606525421142578</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.2610801756381989</v>
+        <v>0.2593319118022919</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.263323575258255</v>
+        <v>0.2615293264389038</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.2651333808898926</v>
+        <v>0.2634123265743256</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.274932324886322</v>
+        <v>0.272977352142334</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.2852621674537659</v>
+        <v>0.2833219468593597</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.2907228767871857</v>
+        <v>0.2886684536933899</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.2908971905708313</v>
+        <v>0.2889202833175659</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.2828101515769958</v>
+        <v>0.2808852791786194</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.2809380292892456</v>
+        <v>0.278835654258728</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.2863253951072693</v>
+        <v>0.2843719124794006</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.2840283215045929</v>
+        <v>0.2819454669952393</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.2842507064342499</v>
+        <v>0.2821829319000244</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.2823091447353363</v>
+        <v>0.2802005112171173</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.2841607928276062</v>
+        <v>0.2819242477416992</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.2845554351806641</v>
+        <v>0.2823989987373352</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.2836199998855591</v>
+        <v>0.2814373373985291</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.2942115664482117</v>
+        <v>0.2918093204498291</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.2987015247344971</v>
+        <v>0.2962886691093445</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.3133973181247711</v>
+        <v>0.3108537495136261</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.307341456413269</v>
+        <v>0.3047176897525787</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.3080988228321075</v>
+        <v>0.3052516877651215</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.3093124330043793</v>
+        <v>0.3065022528171539</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.3092990219593048</v>
+        <v>0.3064484298229218</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.3073404133319855</v>
+        <v>0.3044771254062653</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.3056668341159821</v>
+        <v>0.302949458360672</v>
       </c>
       <c r="GH7" t="n">
-        <v>0.3019186556339264</v>
+        <v>0.2991301119327545</v>
       </c>
       <c r="GI7" t="n">
-        <v>0.3025009036064148</v>
+        <v>0.2996842861175537</v>
       </c>
       <c r="GJ7" t="n">
-        <v>0.3030033707618713</v>
+        <v>0.3002084195613861</v>
       </c>
       <c r="GK7" t="n">
-        <v>0.3068853318691254</v>
+        <v>0.3040100932121277</v>
       </c>
       <c r="GL7" t="n">
-        <v>0.3133550882339478</v>
+        <v>0.310204803943634</v>
       </c>
       <c r="GM7" t="n">
-        <v>0.3196729421615601</v>
+        <v>0.3165501356124878</v>
       </c>
       <c r="GN7" t="n">
-        <v>0.3350435793399811</v>
+        <v>0.3319069445133209</v>
       </c>
       <c r="GO7" t="n">
-        <v>0.3430327475070953</v>
+        <v>0.3397648930549622</v>
       </c>
       <c r="GP7" t="n">
-        <v>0.3359159529209137</v>
+        <v>0.3328987061977386</v>
       </c>
       <c r="GQ7" t="n">
-        <v>0.3327821493148804</v>
+        <v>0.3298988938331604</v>
       </c>
       <c r="GR7" t="n">
-        <v>0.3317412734031677</v>
+        <v>0.3288272619247437</v>
       </c>
       <c r="GS7" t="n">
-        <v>0.3301487267017365</v>
+        <v>0.3271455466747284</v>
       </c>
       <c r="GT7" t="n">
-        <v>0.3315800726413727</v>
+        <v>0.3286726474761963</v>
       </c>
       <c r="GU7" t="n">
-        <v>0.3258622586727142</v>
+        <v>0.3229126930236816</v>
       </c>
       <c r="GV7" t="n">
-        <v>0.3311708867549896</v>
+        <v>0.3279891610145569</v>
       </c>
       <c r="GW7" t="n">
-        <v>0.3262559175491333</v>
+        <v>0.3230946063995361</v>
       </c>
       <c r="GX7" t="n">
-        <v>0.3274384737014771</v>
+        <v>0.3242194354534149</v>
       </c>
       <c r="GY7" t="n">
-        <v>0.3277903199195862</v>
+        <v>0.3243945240974426</v>
       </c>
       <c r="GZ7" t="n">
-        <v>0.3409477174282074</v>
+        <v>0.337603896856308</v>
       </c>
       <c r="HA7" t="n">
-        <v>0.3537092506885529</v>
+        <v>0.3505237400531769</v>
       </c>
       <c r="HB7" t="n">
-        <v>0.3665052652359009</v>
+        <v>0.3629949688911438</v>
       </c>
       <c r="HC7" t="n">
-        <v>0.3600437939167023</v>
+        <v>0.3571094572544098</v>
       </c>
       <c r="HD7" t="n">
-        <v>0.3494688868522644</v>
+        <v>0.345252513885498</v>
       </c>
       <c r="HE7" t="n">
-        <v>0.3444928228855133</v>
+        <v>0.3402054309844971</v>
       </c>
       <c r="HF7" t="n">
-        <v>0.3460769057273865</v>
+        <v>0.3418548107147217</v>
       </c>
       <c r="HG7" t="n">
-        <v>0.3527370989322662</v>
+        <v>0.3485631048679352</v>
       </c>
       <c r="HH7" t="n">
-        <v>0.3516972959041595</v>
+        <v>0.3473607301712036</v>
       </c>
       <c r="HI7" t="n">
-        <v>0.3501230776309967</v>
+        <v>0.3459585309028625</v>
       </c>
       <c r="HJ7" t="n">
-        <v>0.3527966737747192</v>
+        <v>0.3483117818832397</v>
       </c>
       <c r="HK7" t="n">
-        <v>0.3465596735477448</v>
+        <v>0.3421881496906281</v>
       </c>
       <c r="HL7" t="n">
-        <v>0.3483832478523254</v>
+        <v>0.3440155982971191</v>
       </c>
       <c r="HM7" t="n">
-        <v>0.3454338908195496</v>
+        <v>0.3408867418766022</v>
       </c>
       <c r="HN7" t="n">
-        <v>0.3685861527919769</v>
+        <v>0.3641227185726166</v>
       </c>
       <c r="HO7" t="n">
-        <v>0.3828193545341492</v>
+        <v>0.3782405257225037</v>
       </c>
       <c r="HP7" t="n">
-        <v>0.3614597022533417</v>
+        <v>0.357998788356781</v>
       </c>
       <c r="HQ7" t="n">
-        <v>0.348989725112915</v>
+        <v>0.3462979793548584</v>
       </c>
       <c r="HR7" t="inlineStr">
         <is>

--- a/results/submission_predictions.xlsx
+++ b/results/submission_predictions.xlsx
@@ -1555,676 +1555,676 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02318507432937622</v>
+        <v>0.02318527735769749</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03188405930995941</v>
+        <v>0.03188502043485641</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03397274389863014</v>
+        <v>0.03397325053811073</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03556628152728081</v>
+        <v>0.03556691110134125</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03612011671066284</v>
+        <v>0.03612112998962402</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03541716188192368</v>
+        <v>0.03541815653443336</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03495172411203384</v>
+        <v>0.03495240956544876</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03457061573863029</v>
+        <v>0.03457081317901611</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03480684757232666</v>
+        <v>0.03480730578303337</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0341881662607193</v>
+        <v>0.03418846800923347</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03328442573547363</v>
+        <v>0.03328529745340347</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03236930444836617</v>
+        <v>0.03237009793519974</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03230168670415878</v>
+        <v>0.03230211511254311</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03286618739366531</v>
+        <v>0.03286706656217575</v>
       </c>
       <c r="P2" t="n">
-        <v>0.04758042097091675</v>
+        <v>0.04758084937930107</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05885273218154907</v>
+        <v>0.05885307118296623</v>
       </c>
       <c r="R2" t="n">
-        <v>0.06157319620251656</v>
+        <v>0.06157467886805534</v>
       </c>
       <c r="S2" t="n">
-        <v>0.06270737946033478</v>
+        <v>0.06270849704742432</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06387840211391449</v>
+        <v>0.06387853622436523</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06166896224021912</v>
+        <v>0.06166817992925644</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06259685009717941</v>
+        <v>0.06259722262620926</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0622728131711483</v>
+        <v>0.0622740313410759</v>
       </c>
       <c r="X2" t="n">
-        <v>0.06173666566610336</v>
+        <v>0.06173783913254738</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.06133612245321274</v>
+        <v>0.06133751943707466</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.05845404043793678</v>
+        <v>0.05845507979393005</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05624158680438995</v>
+        <v>0.0562426932156086</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05608374997973442</v>
+        <v>0.05608548223972321</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.05748163908720016</v>
+        <v>0.05748221650719643</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.07868769764900208</v>
+        <v>0.07868804782629013</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.09039420634508133</v>
+        <v>0.0903950110077858</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.09040001779794693</v>
+        <v>0.09040234982967377</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.09256990253925323</v>
+        <v>0.09256979078054428</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.09288109838962555</v>
+        <v>0.09288154542446136</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.09219146519899368</v>
+        <v>0.092193603515625</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.08933929353952408</v>
+        <v>0.08934059739112854</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.08846691995859146</v>
+        <v>0.08846811205148697</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.08870689570903778</v>
+        <v>0.08870746940374374</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.08581945300102234</v>
+        <v>0.08582083135843277</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.08184624463319778</v>
+        <v>0.08184751123189926</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.07998744398355484</v>
+        <v>0.07998926192522049</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.08206105977296829</v>
+        <v>0.08206334710121155</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.08279383182525635</v>
+        <v>0.08279544115066528</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.1073121428489685</v>
+        <v>0.1073106527328491</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.1142126098275185</v>
+        <v>0.1142154037952423</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.1150502264499664</v>
+        <v>0.1150528118014336</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.1171115413308144</v>
+        <v>0.1171131432056427</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.1148201674222946</v>
+        <v>0.114821769297123</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.1110217571258545</v>
+        <v>0.1110234335064888</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1114648878574371</v>
+        <v>0.1114681512117386</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.1107443273067474</v>
+        <v>0.1107455343008041</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1092759072780609</v>
+        <v>0.109277181327343</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.1058641523122787</v>
+        <v>0.1058662012219429</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.1015690863132477</v>
+        <v>0.1015706956386566</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.09983118623495102</v>
+        <v>0.09983222931623459</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.09854790568351746</v>
+        <v>0.0985487699508667</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.1015737429261208</v>
+        <v>0.1015746667981148</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.1354335248470306</v>
+        <v>0.1354343742132187</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.1373955309391022</v>
+        <v>0.1373967528343201</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.1369575560092926</v>
+        <v>0.1369593292474747</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.133686289191246</v>
+        <v>0.1336890608072281</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.1338625103235245</v>
+        <v>0.1338646411895752</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.1278948485851288</v>
+        <v>0.127896249294281</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.1276357173919678</v>
+        <v>0.1276388615369797</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.1251719146966934</v>
+        <v>0.1251740008592606</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.1231976300477982</v>
+        <v>0.1231999173760414</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.1246285364031792</v>
+        <v>0.1246304214000702</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1168414205312729</v>
+        <v>0.1168431490659714</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.1163686290383339</v>
+        <v>0.1163709461688995</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.1156098693609238</v>
+        <v>0.1156119182705879</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.115565225481987</v>
+        <v>0.1155664995312691</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.1687582731246948</v>
+        <v>0.1687597632408142</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.1671299040317535</v>
+        <v>0.1671306937932968</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.1630492359399796</v>
+        <v>0.1630528420209885</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.1633277237415314</v>
+        <v>0.1633303016424179</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.1618521511554718</v>
+        <v>0.1618534326553345</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.1578803956508636</v>
+        <v>0.1578836441040039</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.1542609184980392</v>
+        <v>0.1542636305093765</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.1514876037836075</v>
+        <v>0.1514884233474731</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.1496306508779526</v>
+        <v>0.1496325135231018</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.1458317041397095</v>
+        <v>0.1458341628313065</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.1424273550510406</v>
+        <v>0.1424296498298645</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.1358027011156082</v>
+        <v>0.1358036547899246</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.1360290795564651</v>
+        <v>0.1360304355621338</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.139169305562973</v>
+        <v>0.1391713470220566</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.1946970373392105</v>
+        <v>0.1947022378444672</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.1923393160104752</v>
+        <v>0.1923429369926453</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.1897488087415695</v>
+        <v>0.1897494345903397</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.1863265931606293</v>
+        <v>0.1863304227590561</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.182867705821991</v>
+        <v>0.1828717291355133</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.1761742681264877</v>
+        <v>0.1761751919984818</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.177157923579216</v>
+        <v>0.1771607547998428</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.1709623038768768</v>
+        <v>0.1709644794464111</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.1695875972509384</v>
+        <v>0.1695911437273026</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.1706136018037796</v>
+        <v>0.1706171929836273</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.158295601606369</v>
+        <v>0.1582984179258347</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.1559296697378159</v>
+        <v>0.1559316217899323</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.1559391021728516</v>
+        <v>0.1559416353702545</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.1619279235601425</v>
+        <v>0.1619297415018082</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.23005411028862</v>
+        <v>0.2300594449043274</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.2172192335128784</v>
+        <v>0.2172216773033142</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.2176186591386795</v>
+        <v>0.217623382806778</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.2160163372755051</v>
+        <v>0.2160202413797379</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.207061842083931</v>
+        <v>0.2070626616477966</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.2037547081708908</v>
+        <v>0.2037569433450699</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.204533264040947</v>
+        <v>0.2045344710350037</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.20033098757267</v>
+        <v>0.2003335803747177</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.2001755237579346</v>
+        <v>0.2001804709434509</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.1947078108787537</v>
+        <v>0.1947091966867447</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.1893542557954788</v>
+        <v>0.1893568336963654</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.1862872242927551</v>
+        <v>0.1862892657518387</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.1853335201740265</v>
+        <v>0.1853362768888474</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.1878730356693268</v>
+        <v>0.1878752410411835</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.2456095069646835</v>
+        <v>0.2456152141094208</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.2426550984382629</v>
+        <v>0.242657944560051</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.2351501286029816</v>
+        <v>0.2351531088352203</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.2337103337049484</v>
+        <v>0.2337130606174469</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.2271200120449066</v>
+        <v>0.2271253168582916</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.2286079972982407</v>
+        <v>0.2286129146814346</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.223124086856842</v>
+        <v>0.2231282889842987</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.217056080698967</v>
+        <v>0.2170570939779282</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.2159292995929718</v>
+        <v>0.2159329503774643</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.2131413370370865</v>
+        <v>0.2131416499614716</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.2088631689548492</v>
+        <v>0.2088657319545746</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.207666739821434</v>
+        <v>0.2076674252748489</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.2099832594394684</v>
+        <v>0.2099850326776505</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2120786309242249</v>
+        <v>0.2120806574821472</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.2628280222415924</v>
+        <v>0.2628293931484222</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.2531485557556152</v>
+        <v>0.2531515657901764</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.2518391013145447</v>
+        <v>0.2518408596515656</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.2451137155294418</v>
+        <v>0.2451161295175552</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.2447262108325958</v>
+        <v>0.2447293102741241</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.2389983832836151</v>
+        <v>0.2390013188123703</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.2365098744630814</v>
+        <v>0.2365118414163589</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.2352452129125595</v>
+        <v>0.2352461963891983</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.2330702543258667</v>
+        <v>0.2330721765756607</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.2313346415758133</v>
+        <v>0.2313371449708939</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.2194636166095734</v>
+        <v>0.2194640785455704</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.2234306186437607</v>
+        <v>0.2234320491552353</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.2246885001659393</v>
+        <v>0.224687933921814</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.2262192517518997</v>
+        <v>0.2262211591005325</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.2739260792732239</v>
+        <v>0.2739299833774567</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.2709437608718872</v>
+        <v>0.2709447741508484</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.267096608877182</v>
+        <v>0.2671000063419342</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.2605599761009216</v>
+        <v>0.2605608999729156</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.2639578878879547</v>
+        <v>0.2639603912830353</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.2534716427326202</v>
+        <v>0.2534740567207336</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.2529224753379822</v>
+        <v>0.2529250681400299</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.2470715045928955</v>
+        <v>0.2470730692148209</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.2500300705432892</v>
+        <v>0.2500320971012115</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.2494676113128662</v>
+        <v>0.2494688034057617</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.2461328506469727</v>
+        <v>0.2461345642805099</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.2461767494678497</v>
+        <v>0.2461782097816467</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.2460965067148209</v>
+        <v>0.2460962235927582</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.2574259340763092</v>
+        <v>0.2574263513088226</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.2819767594337463</v>
+        <v>0.2819781005382538</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.2825010418891907</v>
+        <v>0.2825032770633698</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.2720599472522736</v>
+        <v>0.2720603048801422</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.2745133638381958</v>
+        <v>0.274514228105545</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.2649905383586884</v>
+        <v>0.2649913132190704</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.2665752470493317</v>
+        <v>0.2665762007236481</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.266124427318573</v>
+        <v>0.2661234736442566</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.2629017233848572</v>
+        <v>0.2629014849662781</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.2585291862487793</v>
+        <v>0.2585301995277405</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.2572279870510101</v>
+        <v>0.2572287321090698</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.2595068216323853</v>
+        <v>0.2595072388648987</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.2616985440254211</v>
+        <v>0.2616986334323883</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.2712526023387909</v>
+        <v>0.2712508141994476</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.2815454602241516</v>
+        <v>0.2815452814102173</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.2860629260540009</v>
+        <v>0.2860642075538635</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.2864820063114166</v>
+        <v>0.286483108997345</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.2785717844963074</v>
+        <v>0.2785726487636566</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.2765580713748932</v>
+        <v>0.2765581011772156</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.2819525599479675</v>
+        <v>0.2819544672966003</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.2795931100845337</v>
+        <v>0.2795933187007904</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.2797708213329315</v>
+        <v>0.2797719836235046</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.2777833342552185</v>
+        <v>0.2777838408946991</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.2795195579528809</v>
+        <v>0.2795205414295197</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.2799712717533112</v>
+        <v>0.2799724638462067</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.2792785465717316</v>
+        <v>0.2792787551879883</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.289819061756134</v>
+        <v>0.2898177802562714</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.2941228151321411</v>
+        <v>0.2941237688064575</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.308588057756424</v>
+        <v>0.3085883855819702</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.3014923632144928</v>
+        <v>0.3014943897724152</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.3019830286502838</v>
+        <v>0.3019839227199554</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.3030782639980316</v>
+        <v>0.3030796349048615</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.3029845654964447</v>
+        <v>0.302986741065979</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.3011422455310822</v>
+        <v>0.3011429607868195</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.2996968328952789</v>
+        <v>0.2996999621391296</v>
       </c>
       <c r="GH2" t="n">
-        <v>0.2959887981414795</v>
+        <v>0.2959907054901123</v>
       </c>
       <c r="GI2" t="n">
-        <v>0.2968422472476959</v>
+        <v>0.296845018863678</v>
       </c>
       <c r="GJ2" t="n">
-        <v>0.2970765233039856</v>
+        <v>0.2970795631408691</v>
       </c>
       <c r="GK2" t="n">
-        <v>0.3008762001991272</v>
+        <v>0.3008785843849182</v>
       </c>
       <c r="GL2" t="n">
-        <v>0.3073097765445709</v>
+        <v>0.3073105812072754</v>
       </c>
       <c r="GM2" t="n">
-        <v>0.3138381838798523</v>
+        <v>0.313839465379715</v>
       </c>
       <c r="GN2" t="n">
-        <v>0.3290687501430511</v>
+        <v>0.3290679752826691</v>
       </c>
       <c r="GO2" t="n">
-        <v>0.3366119563579559</v>
+        <v>0.3366119861602783</v>
       </c>
       <c r="GP2" t="n">
-        <v>0.3296489119529724</v>
+        <v>0.3296506702899933</v>
       </c>
       <c r="GQ2" t="n">
-        <v>0.3269288539886475</v>
+        <v>0.3269298672676086</v>
       </c>
       <c r="GR2" t="n">
-        <v>0.3258122801780701</v>
+        <v>0.3258111178874969</v>
       </c>
       <c r="GS2" t="n">
-        <v>0.3241280615329742</v>
+        <v>0.3241283595561981</v>
       </c>
       <c r="GT2" t="n">
-        <v>0.3255454897880554</v>
+        <v>0.3255466222763062</v>
       </c>
       <c r="GU2" t="n">
-        <v>0.3198182582855225</v>
+        <v>0.3198201060295105</v>
       </c>
       <c r="GV2" t="n">
-        <v>0.3247554898262024</v>
+        <v>0.3247559666633606</v>
       </c>
       <c r="GW2" t="n">
-        <v>0.3198827505111694</v>
+        <v>0.3198831379413605</v>
       </c>
       <c r="GX2" t="n">
-        <v>0.3208956718444824</v>
+        <v>0.3208977580070496</v>
       </c>
       <c r="GY2" t="n">
-        <v>0.3210145533084869</v>
+        <v>0.3210129737854004</v>
       </c>
       <c r="GZ2" t="n">
-        <v>0.3342933654785156</v>
+        <v>0.3342941999435425</v>
       </c>
       <c r="HA2" t="n">
-        <v>0.3474113643169403</v>
+        <v>0.3474116921424866</v>
       </c>
       <c r="HB2" t="n">
-        <v>0.3595223724842072</v>
+        <v>0.3595235049724579</v>
       </c>
       <c r="HC2" t="n">
-        <v>0.3544248640537262</v>
+        <v>0.3544241189956665</v>
       </c>
       <c r="HD2" t="n">
-        <v>0.3411796092987061</v>
+        <v>0.3411827683448792</v>
       </c>
       <c r="HE2" t="n">
-        <v>0.3362773060798645</v>
+        <v>0.3362759947776794</v>
       </c>
       <c r="HF2" t="n">
-        <v>0.3378927111625671</v>
+        <v>0.3378902673721313</v>
       </c>
       <c r="HG2" t="n">
-        <v>0.3444583714008331</v>
+        <v>0.3444583415985107</v>
       </c>
       <c r="HH2" t="n">
-        <v>0.343076765537262</v>
+        <v>0.3430765271186829</v>
       </c>
       <c r="HI2" t="n">
-        <v>0.3415813148021698</v>
+        <v>0.3415817320346832</v>
       </c>
       <c r="HJ2" t="n">
-        <v>0.3437668681144714</v>
+        <v>0.3437683880329132</v>
       </c>
       <c r="HK2" t="n">
-        <v>0.3375883102416992</v>
+        <v>0.337588906288147</v>
       </c>
       <c r="HL2" t="n">
-        <v>0.3392657339572906</v>
+        <v>0.3392682373523712</v>
       </c>
       <c r="HM2" t="n">
-        <v>0.3360197842121124</v>
+        <v>0.3360185325145721</v>
       </c>
       <c r="HN2" t="n">
-        <v>0.359351247549057</v>
+        <v>0.3593526184558868</v>
       </c>
       <c r="HO2" t="n">
-        <v>0.3735892176628113</v>
+        <v>0.3735889196395874</v>
       </c>
       <c r="HP2" t="n">
-        <v>0.3544781506061554</v>
+        <v>0.3544758260250092</v>
       </c>
       <c r="HQ2" t="n">
-        <v>0.3438026905059814</v>
+        <v>0.3438026607036591</v>
       </c>
       <c r="HR2" t="inlineStr">
         <is>
@@ -2239,676 +2239,676 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02356911636888981</v>
+        <v>0.02356982044875622</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03235921263694763</v>
+        <v>0.03236067667603493</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03444001078605652</v>
+        <v>0.03444099053740501</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03600489720702171</v>
+        <v>0.03600599244236946</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03652816265821457</v>
+        <v>0.03652967512607574</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03578531742095947</v>
+        <v>0.03578683361411095</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03527692705392838</v>
+        <v>0.0352780818939209</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03488093614578247</v>
+        <v>0.03488162159919739</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03509872779250145</v>
+        <v>0.03509967774152756</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03445488959550858</v>
+        <v>0.03445563837885857</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03350914642214775</v>
+        <v>0.03351052850484848</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03254776075482368</v>
+        <v>0.03254895284771919</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03246950730681419</v>
+        <v>0.03247029334306717</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03301634266972542</v>
+        <v>0.0330176055431366</v>
       </c>
       <c r="P3" t="n">
-        <v>0.04824093729257584</v>
+        <v>0.04824197664856911</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.05961683765053749</v>
+        <v>0.05961787328124046</v>
       </c>
       <c r="R3" t="n">
-        <v>0.06232976168394089</v>
+        <v>0.06233206763863564</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0633748397231102</v>
+        <v>0.06337681412696838</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0645114853978157</v>
+        <v>0.06451231241226196</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06221058964729309</v>
+        <v>0.06221060082316399</v>
       </c>
       <c r="V3" t="n">
-        <v>0.06310365349054337</v>
+        <v>0.06310483813285828</v>
       </c>
       <c r="W3" t="n">
-        <v>0.06271705776453018</v>
+        <v>0.06271903961896896</v>
       </c>
       <c r="X3" t="n">
-        <v>0.06216413900256157</v>
+        <v>0.06216609850525856</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06173169985413551</v>
+        <v>0.06173383817076683</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.05877585709095001</v>
+        <v>0.05877760797739029</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.05649960786104202</v>
+        <v>0.05650127679109573</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.05633308738470078</v>
+        <v>0.05633546411991119</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.05770982429385185</v>
+        <v>0.05771094560623169</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.07964672893285751</v>
+        <v>0.07964780181646347</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.09142682701349258</v>
+        <v>0.09142863005399704</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09138667583465576</v>
+        <v>0.09139027446508408</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.09341265261173248</v>
+        <v>0.09341365844011307</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.09364926069974899</v>
+        <v>0.09365074336528778</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.09288910776376724</v>
+        <v>0.09289241582155228</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.08994842320680618</v>
+        <v>0.08995084464550018</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.08899705111980438</v>
+        <v>0.08899909257888794</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.08923100680112839</v>
+        <v>0.08923257142305374</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.08629070967435837</v>
+        <v>0.08629298210144043</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.08221623301506042</v>
+        <v>0.08221833407878876</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.08028817921876907</v>
+        <v>0.0802907794713974</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.08235961198806763</v>
+        <v>0.08236271888017654</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.08305780589580536</v>
+        <v>0.08306009322404861</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.1084995344281197</v>
+        <v>0.1084988564252853</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.1154482960700989</v>
+        <v>0.1154525876045227</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.1161534860730171</v>
+        <v>0.116157591342926</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.1180276200175285</v>
+        <v>0.1180304959416389</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1157027930021286</v>
+        <v>0.1157056540250778</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1117512658238411</v>
+        <v>0.1117540821433067</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1121401637792587</v>
+        <v>0.1121445894241333</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.1113379597663879</v>
+        <v>0.11134023219347</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1098518818616867</v>
+        <v>0.1098543703556061</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1063722595572472</v>
+        <v>0.106375478208065</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.1019623801112175</v>
+        <v>0.101964920759201</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1001580953598022</v>
+        <v>0.1001599803566933</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.09885945171117783</v>
+        <v>0.09886113554239273</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1018539443612099</v>
+        <v>0.101855605840683</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1368091851472855</v>
+        <v>0.136811375617981</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.1386807262897491</v>
+        <v>0.13868348300457</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.1380663365125656</v>
+        <v>0.1380697339773178</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.1346461027860641</v>
+        <v>0.1346503049135208</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.1347574144601822</v>
+        <v>0.1347611099481583</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.1286541223526001</v>
+        <v>0.1286568641662598</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.1283054798841476</v>
+        <v>0.1283099949359894</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.1257761120796204</v>
+        <v>0.125779464840889</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.1237763538956642</v>
+        <v>0.1237799599766731</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.1251533776521683</v>
+        <v>0.1251563876867294</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.11723692715168</v>
+        <v>0.1172395050525665</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.1167010366916656</v>
+        <v>0.1167042851448059</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1159260720014572</v>
+        <v>0.1159291118383408</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.1158436462283134</v>
+        <v>0.1158457547426224</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.1704394370317459</v>
+        <v>0.1704429537057877</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.1685773134231567</v>
+        <v>0.1685802191495895</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.1643360704183578</v>
+        <v>0.1643417030572891</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1644235849380493</v>
+        <v>0.164428174495697</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.1627896428108215</v>
+        <v>0.1627926677465439</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.1587362587451935</v>
+        <v>0.1587414145469666</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.1550012975931168</v>
+        <v>0.155005544424057</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.1521618068218231</v>
+        <v>0.1521640866994858</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.1502479463815689</v>
+        <v>0.1502512246370316</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.1463856846094131</v>
+        <v>0.1463893949985504</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.1428627520799637</v>
+        <v>0.1428662836551666</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.1361413598060608</v>
+        <v>0.1361432820558548</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.1363509446382523</v>
+        <v>0.1363532841205597</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.1394581198692322</v>
+        <v>0.1394610404968262</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.1961809396743774</v>
+        <v>0.1961884498596191</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.1937480121850967</v>
+        <v>0.1937541961669922</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.1909684687852859</v>
+        <v>0.1909713596105576</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.1873478144407272</v>
+        <v>0.1873538792133331</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.1838088780641556</v>
+        <v>0.1838150173425674</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.1770009547472</v>
+        <v>0.1770038157701492</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.1779060810804367</v>
+        <v>0.1779107004404068</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1716238856315613</v>
+        <v>0.1716274619102478</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.1702018529176712</v>
+        <v>0.1702072024345398</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.1711635738611221</v>
+        <v>0.1711686700582504</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.1587164700031281</v>
+        <v>0.158720463514328</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.1562527567148209</v>
+        <v>0.1562557965517044</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.156233087182045</v>
+        <v>0.1562366187572479</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.1622145622968674</v>
+        <v>0.1622173190116882</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.2312717735767365</v>
+        <v>0.2312795221805573</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.2184235751628876</v>
+        <v>0.2184284776449203</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.2186766862869263</v>
+        <v>0.2186836749315262</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.2169902622699738</v>
+        <v>0.2169964462518692</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.2078977525234222</v>
+        <v>0.2079004645347595</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.2045146077871323</v>
+        <v>0.2045188844203949</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.2052300870418549</v>
+        <v>0.2052331864833832</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.2009287178516388</v>
+        <v>0.200932964682579</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.2007400989532471</v>
+        <v>0.2007467299699783</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.1952167004346848</v>
+        <v>0.195219412446022</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.1897364407777786</v>
+        <v>0.1897402405738831</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.1865953207015991</v>
+        <v>0.1865984946489334</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.1856021583080292</v>
+        <v>0.1856058835983276</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.1880968511104584</v>
+        <v>0.1880999505519867</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.2468183040618896</v>
+        <v>0.2468264997005463</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.2437084168195724</v>
+        <v>0.2437136918306351</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.2360710650682449</v>
+        <v>0.2360765486955643</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.2345727384090424</v>
+        <v>0.2345776855945587</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.2278788983821869</v>
+        <v>0.2278861254453659</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.229255199432373</v>
+        <v>0.2292621731758118</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.2237024307250977</v>
+        <v>0.223708301782608</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.2175850719213486</v>
+        <v>0.2175873965024948</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.2164145708084106</v>
+        <v>0.2164195775985718</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.213573694229126</v>
+        <v>0.2135752290487289</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.2091973721981049</v>
+        <v>0.2092009782791138</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.2078927904367447</v>
+        <v>0.2078943997621536</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.2102069109678268</v>
+        <v>0.2102096229791641</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.2122444808483124</v>
+        <v>0.2122473418712616</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.26381516456604</v>
+        <v>0.2638189494609833</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.2540440261363983</v>
+        <v>0.2540492415428162</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.2526901364326477</v>
+        <v>0.25269415974617</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.2458129376173019</v>
+        <v>0.2458173036575317</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.2453471422195435</v>
+        <v>0.2453519701957703</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.2395689338445663</v>
+        <v>0.2395735085010529</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.2370270937681198</v>
+        <v>0.2370304614305496</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.2357065379619598</v>
+        <v>0.2357088476419449</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.2334993481636047</v>
+        <v>0.2335023581981659</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.231719970703125</v>
+        <v>0.2317237257957458</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.2197318226099014</v>
+        <v>0.2197331041097641</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.2236393541097641</v>
+        <v>0.2236415445804596</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.2248122692108154</v>
+        <v>0.2248123735189438</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.2263548374176025</v>
+        <v>0.2263575345277786</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.2746123373508453</v>
+        <v>0.2746183574199677</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.2715171277523041</v>
+        <v>0.271519809961319</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.2676305174827576</v>
+        <v>0.2676354348659515</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.2610195577144623</v>
+        <v>0.2610218226909637</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.2643894553184509</v>
+        <v>0.2643932104110718</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.2538454830646515</v>
+        <v>0.2538490891456604</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.253344863653183</v>
+        <v>0.2533486783504486</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.2473891377449036</v>
+        <v>0.2473917454481125</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.2503513395786285</v>
+        <v>0.2503543794155121</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.2497098594903946</v>
+        <v>0.2497120499610901</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.246325746178627</v>
+        <v>0.2463282346725464</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.2463212758302689</v>
+        <v>0.2463233470916748</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.2461708337068558</v>
+        <v>0.2461711168289185</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.2575204074382782</v>
+        <v>0.2575215697288513</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.2822648882865906</v>
+        <v>0.2822671830654144</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.2827953994274139</v>
+        <v>0.2827985882759094</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.2723437547683716</v>
+        <v>0.2723449170589447</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.2747806012630463</v>
+        <v>0.2747822105884552</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.2652278542518616</v>
+        <v>0.2652293741703033</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.2667875289916992</v>
+        <v>0.2667892277240753</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.2663494050502777</v>
+        <v>0.2663490474224091</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.2631059288978577</v>
+        <v>0.2631063759326935</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.2587292194366455</v>
+        <v>0.2587307989597321</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.2574241757392883</v>
+        <v>0.2574256360530853</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.2596485018730164</v>
+        <v>0.2596495151519775</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.2617551982402802</v>
+        <v>0.2617558538913727</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.2712893187999725</v>
+        <v>0.2712878882884979</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.2815706431865692</v>
+        <v>0.2815710306167603</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.2863379120826721</v>
+        <v>0.2863399684429169</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.2867179214954376</v>
+        <v>0.2867196798324585</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.2787815034389496</v>
+        <v>0.2787830829620361</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.2767534255981445</v>
+        <v>0.276754230260849</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.2821799516677856</v>
+        <v>0.2821827232837677</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.2797800302505493</v>
+        <v>0.2797808945178986</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.2799626588821411</v>
+        <v>0.2799645364284515</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.2779636681079865</v>
+        <v>0.2779649198055267</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.2796727418899536</v>
+        <v>0.279674619436264</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.2801209986209869</v>
+        <v>0.2801230549812317</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.2793340086936951</v>
+        <v>0.2793348431587219</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.2898010313510895</v>
+        <v>0.2898004353046417</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.2941364943981171</v>
+        <v>0.2941381931304932</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.3086096942424774</v>
+        <v>0.308610588312149</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.3017751574516296</v>
+        <v>0.3017783164978027</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.3022575080394745</v>
+        <v>0.3022595643997192</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.3033629059791565</v>
+        <v>0.3033655285835266</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.3032724857330322</v>
+        <v>0.3032759428024292</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.3013935983181</v>
+        <v>0.301395446062088</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.2999362349510193</v>
+        <v>0.2999404668807983</v>
       </c>
       <c r="GH3" t="n">
-        <v>0.2961760461330414</v>
+        <v>0.2961790859699249</v>
       </c>
       <c r="GI3" t="n">
-        <v>0.2968991994857788</v>
+        <v>0.2969030737876892</v>
       </c>
       <c r="GJ3" t="n">
-        <v>0.2972442805767059</v>
+        <v>0.2972484827041626</v>
       </c>
       <c r="GK3" t="n">
-        <v>0.3010176420211792</v>
+        <v>0.3010211586952209</v>
       </c>
       <c r="GL3" t="n">
-        <v>0.3073614835739136</v>
+        <v>0.307362973690033</v>
       </c>
       <c r="GM3" t="n">
-        <v>0.313827782869339</v>
+        <v>0.3138299584388733</v>
       </c>
       <c r="GN3" t="n">
-        <v>0.3290977776050568</v>
+        <v>0.3290977478027344</v>
       </c>
       <c r="GO3" t="n">
-        <v>0.3366929888725281</v>
+        <v>0.3366938531398773</v>
       </c>
       <c r="GP3" t="n">
-        <v>0.3298345804214478</v>
+        <v>0.3298374712467194</v>
       </c>
       <c r="GQ3" t="n">
-        <v>0.3270477652549744</v>
+        <v>0.3270496726036072</v>
       </c>
       <c r="GR3" t="n">
-        <v>0.3259601891040802</v>
+        <v>0.3259600698947906</v>
       </c>
       <c r="GS3" t="n">
-        <v>0.3242695033550262</v>
+        <v>0.3242708444595337</v>
       </c>
       <c r="GT3" t="n">
-        <v>0.3256868124008179</v>
+        <v>0.3256890177726746</v>
       </c>
       <c r="GU3" t="n">
-        <v>0.3199363350868225</v>
+        <v>0.3199392557144165</v>
       </c>
       <c r="GV3" t="n">
-        <v>0.3248904645442963</v>
+        <v>0.3248919248580933</v>
       </c>
       <c r="GW3" t="n">
-        <v>0.3199995458126068</v>
+        <v>0.3200008571147919</v>
       </c>
       <c r="GX3" t="n">
-        <v>0.321024477481842</v>
+        <v>0.3210278153419495</v>
       </c>
       <c r="GY3" t="n">
-        <v>0.3211276233196259</v>
+        <v>0.3211270272731781</v>
       </c>
       <c r="GZ3" t="n">
-        <v>0.3344019949436188</v>
+        <v>0.3344038128852844</v>
       </c>
       <c r="HA3" t="n">
-        <v>0.3474830687046051</v>
+        <v>0.3474842309951782</v>
       </c>
       <c r="HB3" t="n">
-        <v>0.3596495091915131</v>
+        <v>0.3596517443656921</v>
       </c>
       <c r="HC3" t="n">
-        <v>0.3544704914093018</v>
+        <v>0.354470431804657</v>
       </c>
       <c r="HD3" t="n">
-        <v>0.3413303196430206</v>
+        <v>0.3413346409797668</v>
       </c>
       <c r="HE3" t="n">
-        <v>0.336436927318573</v>
+        <v>0.3364366590976715</v>
       </c>
       <c r="HF3" t="n">
-        <v>0.3380511999130249</v>
+        <v>0.3380496799945831</v>
       </c>
       <c r="HG3" t="n">
-        <v>0.3446333408355713</v>
+        <v>0.3446343243122101</v>
       </c>
       <c r="HH3" t="n">
-        <v>0.3432861864566803</v>
+        <v>0.3432871699333191</v>
       </c>
       <c r="HI3" t="n">
-        <v>0.3418053686618805</v>
+        <v>0.3418069779872894</v>
       </c>
       <c r="HJ3" t="n">
-        <v>0.344031810760498</v>
+        <v>0.3440347909927368</v>
       </c>
       <c r="HK3" t="n">
-        <v>0.3378567695617676</v>
+        <v>0.3378585875034332</v>
       </c>
       <c r="HL3" t="n">
-        <v>0.3395670354366302</v>
+        <v>0.3395709991455078</v>
       </c>
       <c r="HM3" t="n">
-        <v>0.3363432288169861</v>
+        <v>0.3363429307937622</v>
       </c>
       <c r="HN3" t="n">
-        <v>0.3596974313259125</v>
+        <v>0.3597000539302826</v>
       </c>
       <c r="HO3" t="n">
-        <v>0.3738776445388794</v>
+        <v>0.3738785982131958</v>
       </c>
       <c r="HP3" t="n">
-        <v>0.3546992540359497</v>
+        <v>0.3546977043151855</v>
       </c>
       <c r="HQ3" t="n">
-        <v>0.3438780009746552</v>
+        <v>0.3438787162303925</v>
       </c>
       <c r="HR3" t="inlineStr">
         <is>
@@ -2923,676 +2923,676 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02394467778503895</v>
+        <v>0.02394563890993595</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03274791687726974</v>
+        <v>0.0327497124671936</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03482376784086227</v>
+        <v>0.03482511639595032</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03637958690524101</v>
+        <v>0.0363810770213604</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0368797555565834</v>
+        <v>0.03688165172934532</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03611873090267181</v>
+        <v>0.03612060844898224</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03559615835547447</v>
+        <v>0.03559769690036774</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03519834205508232</v>
+        <v>0.03519939631223679</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03541192784905434</v>
+        <v>0.03541324660181999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03475736826658249</v>
+        <v>0.03475847840309143</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03378818556666374</v>
+        <v>0.03378989920020103</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0328030027449131</v>
+        <v>0.03280447795987129</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03272361680865288</v>
+        <v>0.03272469341754913</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03326942026615143</v>
+        <v>0.0332709364593029</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04882986471056938</v>
+        <v>0.04883131384849548</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06021257489919662</v>
+        <v>0.06021417304873466</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0629391074180603</v>
+        <v>0.06294205784797668</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06393446028232574</v>
+        <v>0.06393706053495407</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0650688037276268</v>
+        <v>0.06507035344839096</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06272167712450027</v>
+        <v>0.06272225081920624</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06360112130641937</v>
+        <v>0.06360291689634323</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06319559365510941</v>
+        <v>0.06319817155599594</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06263948976993561</v>
+        <v>0.06264206022024155</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06218819320201874</v>
+        <v>0.06219096854329109</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05919091403484344</v>
+        <v>0.05919323116540909</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05689381062984467</v>
+        <v>0.05689595267176628</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05673202499747276</v>
+        <v>0.05673487484455109</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.05810364335775375</v>
+        <v>0.05810520425438881</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.080368772149086</v>
+        <v>0.0803704634308815</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.09217680245637894</v>
+        <v>0.09217942506074905</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.09214639663696289</v>
+        <v>0.09215086698532104</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.09409680217504501</v>
+        <v>0.09409867972135544</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0943276435136795</v>
+        <v>0.0943300724029541</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0935412123799324</v>
+        <v>0.0935453325510025</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.09055797755718231</v>
+        <v>0.09056121855974197</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.08958134800195694</v>
+        <v>0.08958420157432556</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.08981776237487793</v>
+        <v>0.08982016146183014</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.08685065805912018</v>
+        <v>0.0868537425994873</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.08271058648824692</v>
+        <v>0.08271332085132599</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.08076894283294678</v>
+        <v>0.08077213168144226</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.08286182582378387</v>
+        <v>0.08286554366350174</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.08354717493057251</v>
+        <v>0.08355006575584412</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.109328031539917</v>
+        <v>0.1093281507492065</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.1163261756300926</v>
+        <v>0.1163316443562508</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.1169846728444099</v>
+        <v>0.1169899702072144</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.1187557280063629</v>
+        <v>0.1187597438693047</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.116521067917347</v>
+        <v>0.1165250986814499</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.1124558821320534</v>
+        <v>0.1124597862362862</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.112842433154583</v>
+        <v>0.1128479242324829</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.1120108515024185</v>
+        <v>0.1120140925049782</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.1105165034532547</v>
+        <v>0.1105199530720711</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.1069958955049515</v>
+        <v>0.1069999560713768</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.1025100275874138</v>
+        <v>0.1025133579969406</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.1007051691412926</v>
+        <v>0.1007077842950821</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.09941384941339493</v>
+        <v>0.09941622614860535</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.102405920624733</v>
+        <v>0.1024082601070404</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.1376911699771881</v>
+        <v>0.137694463133812</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.1396297365427017</v>
+        <v>0.1396339386701584</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.1389529407024384</v>
+        <v>0.138957679271698</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.1354691237211227</v>
+        <v>0.1354747861623764</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.1356273144483566</v>
+        <v>0.1356323212385178</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.1294401884078979</v>
+        <v>0.1294441521167755</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.1290325522422791</v>
+        <v>0.1290381997823715</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.1264968514442444</v>
+        <v>0.1265012472867966</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.1244805529713631</v>
+        <v>0.1244851872324944</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.1258241981267929</v>
+        <v>0.1258282959461212</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.1178288012742996</v>
+        <v>0.1178323030471802</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.1172918677330017</v>
+        <v>0.1172958761453629</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.1165244355797768</v>
+        <v>0.1165281608700752</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.1164281889796257</v>
+        <v>0.1164309680461884</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.1716930568218231</v>
+        <v>0.1716983616352081</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.1697725504636765</v>
+        <v>0.1697773635387421</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1655238419771194</v>
+        <v>0.1655314415693283</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.1654845923185349</v>
+        <v>0.165491059422493</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.1637720614671707</v>
+        <v>0.163776621222496</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.1597033888101578</v>
+        <v>0.1597098708152771</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.1558858454227448</v>
+        <v>0.155891552567482</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.1530193686485291</v>
+        <v>0.1530229598283768</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.1510583907365799</v>
+        <v>0.1510629057884216</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.1471385061740875</v>
+        <v>0.1471433937549591</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.143550917506218</v>
+        <v>0.1435554027557373</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.1367909461259842</v>
+        <v>0.1367936581373215</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.1370028853416443</v>
+        <v>0.1370059996843338</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.1401191651821136</v>
+        <v>0.1401228457689285</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.1974893659353256</v>
+        <v>0.1974989473819733</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.1951069682836533</v>
+        <v>0.1951154470443726</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.1922495067119598</v>
+        <v>0.1922544687986374</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.1884855479001999</v>
+        <v>0.1884935200214386</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.1849269568920135</v>
+        <v>0.1849348694086075</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.1780464649200439</v>
+        <v>0.1780509054660797</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.1788898557424545</v>
+        <v>0.178895890712738</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.1725489348173141</v>
+        <v>0.1725539714097977</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.1710768789052963</v>
+        <v>0.1710834801197052</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.1719772666692734</v>
+        <v>0.1719836294651031</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.1594391465187073</v>
+        <v>0.159444123506546</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.1569477319717407</v>
+        <v>0.1569515466690063</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.156914085149765</v>
+        <v>0.1569183468818665</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.1629329323768616</v>
+        <v>0.1629364639520645</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.2326398342847824</v>
+        <v>0.2326499074697495</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.2198518663644791</v>
+        <v>0.2198592275381088</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.2199625223875046</v>
+        <v>0.2199716120958328</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.2182664573192596</v>
+        <v>0.2182745337486267</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.209063708782196</v>
+        <v>0.2090682834386826</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.2056188434362411</v>
+        <v>0.2056247591972351</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.2062719464302063</v>
+        <v>0.206276535987854</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.2018590271472931</v>
+        <v>0.2018646597862244</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.2016502022743225</v>
+        <v>0.2016579508781433</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.1960723847150803</v>
+        <v>0.1960762441158295</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.1905017495155334</v>
+        <v>0.1905064582824707</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.1873256862163544</v>
+        <v>0.1873297095298767</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.1863026767969131</v>
+        <v>0.1863071918487549</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.1888147741556168</v>
+        <v>0.1888185739517212</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.2483952790498734</v>
+        <v>0.2484059035778046</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.2451576292514801</v>
+        <v>0.2451649159193039</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.2373667657375336</v>
+        <v>0.2373741269111633</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.2358222752809525</v>
+        <v>0.2358291000127792</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.2290566712617874</v>
+        <v>0.2290656715631485</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.2303018867969513</v>
+        <v>0.2303103059530258</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.2246742248535156</v>
+        <v>0.2246814370155334</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.2185084074735641</v>
+        <v>0.2185119539499283</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.2172982841730118</v>
+        <v>0.2173043638467789</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2144074589014053</v>
+        <v>0.2144099324941635</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.209953248500824</v>
+        <v>0.2099577039480209</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.2085453718900681</v>
+        <v>0.2085476219654083</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.210909366607666</v>
+        <v>0.210912749171257</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.2129415422677994</v>
+        <v>0.2129449844360352</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.2652502954006195</v>
+        <v>0.2652561664581299</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.2553731203079224</v>
+        <v>0.2553802728652954</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.2540010213851929</v>
+        <v>0.2540068030357361</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.246935248374939</v>
+        <v>0.2469412237405777</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.2464011162519455</v>
+        <v>0.2464073151350021</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.2405679374933243</v>
+        <v>0.2405737191438675</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.2379695177078247</v>
+        <v>0.2379740476608276</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.2366025894880295</v>
+        <v>0.2366058677434921</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.2343362271785736</v>
+        <v>0.2343402504920959</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.2325188666582108</v>
+        <v>0.232523500919342</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.2204881459474564</v>
+        <v>0.2204901874065399</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.224327340722084</v>
+        <v>0.2243301570415497</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.225450336933136</v>
+        <v>0.2254508882761002</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.2270261347293854</v>
+        <v>0.2270293235778809</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.2758156061172485</v>
+        <v>0.2758232057094574</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.2726238667964935</v>
+        <v>0.2726278603076935</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.2686633169651031</v>
+        <v>0.2686693966388702</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.2619600892066956</v>
+        <v>0.2619633376598358</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.2652880251407623</v>
+        <v>0.2652927339076996</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.2546746432781219</v>
+        <v>0.2546790838241577</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.2542271316051483</v>
+        <v>0.254231870174408</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.2482046335935593</v>
+        <v>0.2482078969478607</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.2511157393455505</v>
+        <v>0.2511194050312042</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.2504267692565918</v>
+        <v>0.2504294514656067</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.247024267911911</v>
+        <v>0.2470272928476334</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.2469576299190521</v>
+        <v>0.2469601184129715</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.2467741519212723</v>
+        <v>0.24677474796772</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.258211612701416</v>
+        <v>0.258213073015213</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.2830198109149933</v>
+        <v>0.2830227911472321</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.2835594713687897</v>
+        <v>0.2835632860660553</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.2730579376220703</v>
+        <v>0.2730596959590912</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.2754926085472107</v>
+        <v>0.2754947543144226</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.2659078240394592</v>
+        <v>0.2659097611904144</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.267470508813858</v>
+        <v>0.2674726247787476</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.2670276761054993</v>
+        <v>0.2670277655124664</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.2637802362442017</v>
+        <v>0.2637810707092285</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.2593900561332703</v>
+        <v>0.259392112493515</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.2580794394016266</v>
+        <v>0.2580812573432922</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.2603049874305725</v>
+        <v>0.2603063583374023</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.2623497545719147</v>
+        <v>0.2623505890369415</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.2719038128852844</v>
+        <v>0.2719025909900665</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.2822108268737793</v>
+        <v>0.2822113633155823</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.2871353328227997</v>
+        <v>0.2871378660202026</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.287476658821106</v>
+        <v>0.287478893995285</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.2795082032680511</v>
+        <v>0.2795101702213287</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.277479350566864</v>
+        <v>0.2774804532527924</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.282934159040451</v>
+        <v>0.2829373478889465</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.2805340588092804</v>
+        <v>0.2805353105068207</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.280731737613678</v>
+        <v>0.2807340621948242</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.2787397801876068</v>
+        <v>0.2787415087223053</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.2804596424102783</v>
+        <v>0.2804619073867798</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.2809173166751862</v>
+        <v>0.2809197604656219</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.2800874412059784</v>
+        <v>0.2800886034965515</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.2905344069004059</v>
+        <v>0.2905339598655701</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.294917494058609</v>
+        <v>0.2949193716049194</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.3094175159931183</v>
+        <v>0.3094187080860138</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.3027800023555756</v>
+        <v>0.3027839064598083</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.3032824993133545</v>
+        <v>0.3032852411270142</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.3044335544109344</v>
+        <v>0.3044368922710419</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.3043559491634369</v>
+        <v>0.3043600916862488</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.3024516701698303</v>
+        <v>0.3024542331695557</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.3009735941886902</v>
+        <v>0.3009785711765289</v>
       </c>
       <c r="GH4" t="n">
-        <v>0.2971974909305573</v>
+        <v>0.2972011864185333</v>
       </c>
       <c r="GI4" t="n">
-        <v>0.2978857457637787</v>
+        <v>0.2978901863098145</v>
       </c>
       <c r="GJ4" t="n">
-        <v>0.2982776761054993</v>
+        <v>0.2982824444770813</v>
       </c>
       <c r="GK4" t="n">
-        <v>0.3020663261413574</v>
+        <v>0.3020704984664917</v>
       </c>
       <c r="GL4" t="n">
-        <v>0.3083752393722534</v>
+        <v>0.3083773255348206</v>
       </c>
       <c r="GM4" t="n">
-        <v>0.3148097991943359</v>
+        <v>0.3148122727870941</v>
       </c>
       <c r="GN4" t="n">
-        <v>0.3301120400428772</v>
+        <v>0.3301123678684235</v>
       </c>
       <c r="GO4" t="n">
-        <v>0.3377858996391296</v>
+        <v>0.3377872407436371</v>
       </c>
       <c r="GP4" t="n">
-        <v>0.3309009373188019</v>
+        <v>0.3309043645858765</v>
       </c>
       <c r="GQ4" t="n">
-        <v>0.3280543386936188</v>
+        <v>0.3280567526817322</v>
       </c>
       <c r="GR4" t="n">
-        <v>0.3269633054733276</v>
+        <v>0.3269637227058411</v>
       </c>
       <c r="GS4" t="n">
-        <v>0.3252811133861542</v>
+        <v>0.3252829611301422</v>
       </c>
       <c r="GT4" t="n">
-        <v>0.326734870672226</v>
+        <v>0.3267376124858856</v>
       </c>
       <c r="GU4" t="n">
-        <v>0.3209854662418365</v>
+        <v>0.3209889233112335</v>
       </c>
       <c r="GV4" t="n">
-        <v>0.3259828388690948</v>
+        <v>0.3259848654270172</v>
       </c>
       <c r="GW4" t="n">
-        <v>0.3210959434509277</v>
+        <v>0.3210977911949158</v>
       </c>
       <c r="GX4" t="n">
-        <v>0.3221557140350342</v>
+        <v>0.3221595287322998</v>
       </c>
       <c r="GY4" t="n">
-        <v>0.3222864270210266</v>
+        <v>0.3222863674163818</v>
       </c>
       <c r="GZ4" t="n">
-        <v>0.3355458080768585</v>
+        <v>0.3355480134487152</v>
       </c>
       <c r="HA4" t="n">
-        <v>0.3485662639141083</v>
+        <v>0.348567932844162</v>
       </c>
       <c r="HB4" t="n">
-        <v>0.3608402907848358</v>
+        <v>0.3608429133892059</v>
       </c>
       <c r="HC4" t="n">
-        <v>0.3554198443889618</v>
+        <v>0.3554200828075409</v>
       </c>
       <c r="HD4" t="n">
-        <v>0.3427362442016602</v>
+        <v>0.3427410125732422</v>
       </c>
       <c r="HE4" t="n">
         <v>0.3377911448478699</v>
       </c>
       <c r="HF4" t="n">
-        <v>0.339409351348877</v>
+        <v>0.3394082188606262</v>
       </c>
       <c r="HG4" t="n">
-        <v>0.3460326194763184</v>
+        <v>0.3460340797901154</v>
       </c>
       <c r="HH4" t="n">
-        <v>0.3447322249412537</v>
+        <v>0.3447336554527283</v>
       </c>
       <c r="HI4" t="n">
-        <v>0.3432777225971222</v>
+        <v>0.3432798683643341</v>
       </c>
       <c r="HJ4" t="n">
-        <v>0.3455418646335602</v>
+        <v>0.3455453813076019</v>
       </c>
       <c r="HK4" t="n">
-        <v>0.3393828272819519</v>
+        <v>0.3393853306770325</v>
       </c>
       <c r="HL4" t="n">
-        <v>0.3411253988742828</v>
+        <v>0.3411300480365753</v>
       </c>
       <c r="HM4" t="n">
-        <v>0.3379257023334503</v>
+        <v>0.3379263579845428</v>
       </c>
       <c r="HN4" t="n">
-        <v>0.3612489402294159</v>
+        <v>0.3612522482872009</v>
       </c>
       <c r="HO4" t="n">
-        <v>0.3754151165485382</v>
+        <v>0.37541663646698</v>
       </c>
       <c r="HP4" t="n">
-        <v>0.3558709323406219</v>
+        <v>0.3558698296546936</v>
       </c>
       <c r="HQ4" t="n">
-        <v>0.3447533845901489</v>
+        <v>0.3447541892528534</v>
       </c>
       <c r="HR4" t="inlineStr">
         <is>
@@ -3607,676 +3607,676 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02428045310080051</v>
+        <v>0.02428161539137363</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03306932747364044</v>
+        <v>0.03307140618562698</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03513673320412636</v>
+        <v>0.03513837233185768</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03668530657887459</v>
+        <v>0.03668710589408875</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03716649487614632</v>
+        <v>0.0371687114238739</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03639362752437592</v>
+        <v>0.0363958515226841</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03586333617568016</v>
+        <v>0.03586520254611969</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0354657955467701</v>
+        <v>0.03546717762947083</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03567793965339661</v>
+        <v>0.03567960485816002</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03501613438129425</v>
+        <v>0.03501757234334946</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03403052315115929</v>
+        <v>0.03403256461024284</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03302732482552528</v>
+        <v>0.03302906081080437</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03294821083545685</v>
+        <v>0.0329495370388031</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03349566832184792</v>
+        <v>0.03349742293357849</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04932495206594467</v>
+        <v>0.04932667687535286</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06069227308034897</v>
+        <v>0.06069430708885193</v>
       </c>
       <c r="R5" t="n">
-        <v>0.06343076378107071</v>
+        <v>0.06343423575162888</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06438831239938736</v>
+        <v>0.06439146399497986</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06552331149578094</v>
+        <v>0.06552542001008987</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06314282864332199</v>
+        <v>0.06314390897750854</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06401647627353668</v>
+        <v>0.06401883810758591</v>
       </c>
       <c r="W5" t="n">
-        <v>0.063600093126297</v>
+        <v>0.06360320001840591</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06304512172937393</v>
+        <v>0.06304826587438583</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06257937848567963</v>
+        <v>0.06258271634578705</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05955279991030693</v>
+        <v>0.05955564230680466</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05724228546023369</v>
+        <v>0.05724482238292694</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.05708720535039902</v>
+        <v>0.05709048360586166</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.05845579504966736</v>
+        <v>0.05845773220062256</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.08094382286071777</v>
+        <v>0.0809459388256073</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.09276342391967773</v>
+        <v>0.09276671707630157</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.09274956583976746</v>
+        <v>0.09275485575199127</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.09464509785175323</v>
+        <v>0.09464776515960693</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.09488098323345184</v>
+        <v>0.09488420933485031</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.09407995641231537</v>
+        <v>0.09408487379550934</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.09106907993555069</v>
+        <v>0.09107310324907303</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.09007719159126282</v>
+        <v>0.09008074551820755</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.09031965583562851</v>
+        <v>0.09032281488180161</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.08733217418193817</v>
+        <v>0.0873359814286232</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.08314216136932373</v>
+        <v>0.08314549922943115</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.08119696378707886</v>
+        <v>0.08120071142911911</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.08331167697906494</v>
+        <v>0.08331596851348877</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.08398965746164322</v>
+        <v>0.08399307727813721</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.1099623218178749</v>
+        <v>0.1099630072712898</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.1170125305652618</v>
+        <v>0.1170190721750259</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.1176448687911034</v>
+        <v>0.1176512986421585</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1193395778536797</v>
+        <v>0.1193445920944214</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.1171949952840805</v>
+        <v>0.1172000244259834</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1130440160632133</v>
+        <v>0.1130488738417625</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1134351342916489</v>
+        <v>0.1134415939450264</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.1125858202576637</v>
+        <v>0.112589955329895</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.1110889241099358</v>
+        <v>0.1110932901501656</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.1075357422232628</v>
+        <v>0.1075406447052956</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.1029909253120422</v>
+        <v>0.1029949709773064</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.1011948063969612</v>
+        <v>0.1011980846524239</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.09991206228733063</v>
+        <v>0.0999150350689888</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.102907769382</v>
+        <v>0.1029106825590134</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.1383511424064636</v>
+        <v>0.1383553892374039</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.1403716504573822</v>
+        <v>0.1403771340847015</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.1396647542715073</v>
+        <v>0.1396708339452744</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.1361466348171234</v>
+        <v>0.1361535936594009</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.136353924870491</v>
+        <v>0.1363601386547089</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.1301047056913376</v>
+        <v>0.1301098018884659</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.1296540051698685</v>
+        <v>0.1296607255935669</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1271184384822845</v>
+        <v>0.1271238178014755</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.1250929683446884</v>
+        <v>0.1250986009836197</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.1264103949069977</v>
+        <v>0.1264154464006424</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1183532699942589</v>
+        <v>0.1183575242757797</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.117823138833046</v>
+        <v>0.1178278401494026</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.1170663386583328</v>
+        <v>0.1170707494020462</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.1169622763991356</v>
+        <v>0.1169656589627266</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.1726709455251694</v>
+        <v>0.1726778298616409</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.1707371771335602</v>
+        <v>0.1707437783479691</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.166514664888382</v>
+        <v>0.1665240079164505</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.1663887351751328</v>
+        <v>0.1663969457149506</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.164607360959053</v>
+        <v>0.1646133363246918</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.160533145070076</v>
+        <v>0.1605410128831863</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.156655952334404</v>
+        <v>0.1566629558801651</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.1537687033414841</v>
+        <v>0.1537734568119049</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.1517687737941742</v>
+        <v>0.1517744362354279</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.1478013396263123</v>
+        <v>0.1478072702884674</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.1441655308008194</v>
+        <v>0.1441709250211716</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1373798698186874</v>
+        <v>0.1373832821846008</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.1375969350337982</v>
+        <v>0.1376007348299026</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.1407262682914734</v>
+        <v>0.1407306045293808</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.1985630691051483</v>
+        <v>0.1985745280981064</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.1962621212005615</v>
+        <v>0.1962727010250092</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.1933489292860031</v>
+        <v>0.1933558136224747</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.189473420381546</v>
+        <v>0.189483255147934</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.1859030872583389</v>
+        <v>0.1859126538038254</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.1789625436067581</v>
+        <v>0.1789685189723969</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.1797547042369843</v>
+        <v>0.17976213991642</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.1733665019273758</v>
+        <v>0.1733727753162384</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.1718570739030838</v>
+        <v>0.1718649864196777</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.1727056205272675</v>
+        <v>0.1727131605148315</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.160087987780571</v>
+        <v>0.1600938737392426</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.1575833559036255</v>
+        <v>0.1575878858566284</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.1575389355421066</v>
+        <v>0.1575438380241394</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.1635973006486893</v>
+        <v>0.1636014878749847</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.2338370531797409</v>
+        <v>0.2338492423295975</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.2211133390665054</v>
+        <v>0.2211229056119919</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.2210904210805893</v>
+        <v>0.2211014330387115</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.2193886339664459</v>
+        <v>0.2193984985351562</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.2101006060838699</v>
+        <v>0.2101068645715714</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.2066051363945007</v>
+        <v>0.2066126614809036</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.2072048038244247</v>
+        <v>0.2072108387947083</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.2026967108249664</v>
+        <v>0.202703669667244</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.202465757727623</v>
+        <v>0.2024746686220169</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.1968396008014679</v>
+        <v>0.1968444734811783</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.1911967247724533</v>
+        <v>0.1912022680044174</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.1880013793706894</v>
+        <v>0.1880062073469162</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.186952069401741</v>
+        <v>0.1869572550058365</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1894867569208145</v>
+        <v>0.1894911229610443</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.2497884184122086</v>
+        <v>0.2498011738061905</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.2464401423931122</v>
+        <v>0.2464492917060852</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.2385258972644806</v>
+        <v>0.2385351806879044</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.2369376122951508</v>
+        <v>0.2369461953639984</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.2301130443811417</v>
+        <v>0.2301236838102341</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.2312492728233337</v>
+        <v>0.2312591820955276</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.2255504578351974</v>
+        <v>0.2255589216947556</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.2193414866924286</v>
+        <v>0.2193460911512375</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.2180948555469513</v>
+        <v>0.2181019186973572</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.2151604294776917</v>
+        <v>0.2151637375354767</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.2106459140777588</v>
+        <v>0.2106511145830154</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.2091535329818726</v>
+        <v>0.2091563940048218</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.2115652412176132</v>
+        <v>0.2115691900253296</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.2136024087667465</v>
+        <v>0.2136063575744629</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.2665332555770874</v>
+        <v>0.2665410339832306</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.2565624415874481</v>
+        <v>0.2565713822841644</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.2551742196083069</v>
+        <v>0.2551817297935486</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.2479469776153564</v>
+        <v>0.2479544281959534</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.2473519742488861</v>
+        <v>0.247359499335289</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.2414699047803879</v>
+        <v>0.2414768934249878</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.2388197183609009</v>
+        <v>0.2388252913951874</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.2374129891395569</v>
+        <v>0.2374171614646912</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.2350932955741882</v>
+        <v>0.235098123550415</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.2332474142313004</v>
+        <v>0.2332528680562973</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.2211896181106567</v>
+        <v>0.2211922109127045</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.2249705046415329</v>
+        <v>0.2249737977981567</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.2260552197694778</v>
+        <v>0.2260561138391495</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.2276627123355865</v>
+        <v>0.2276663184165955</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.2769090831279755</v>
+        <v>0.2769182026386261</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.2736299335956573</v>
+        <v>0.2736349999904633</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.2695979177951813</v>
+        <v>0.2696051299571991</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.2628132104873657</v>
+        <v>0.2628173530101776</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.2661051154136658</v>
+        <v>0.2661106884479523</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.2554310262203217</v>
+        <v>0.2554362416267395</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.2550277709960938</v>
+        <v>0.2550332844257355</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.2489535063505173</v>
+        <v>0.2489573508501053</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.2518136501312256</v>
+        <v>0.2518178522586823</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.2510911822319031</v>
+        <v>0.2510943710803986</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.2476742714643478</v>
+        <v>0.2476777136325836</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.2475506514310837</v>
+        <v>0.2475534528493881</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.247345894575119</v>
+        <v>0.2473466992378235</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.2588684856891632</v>
+        <v>0.2588701546192169</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.2837150990962982</v>
+        <v>0.2837186455726624</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.2842604219913483</v>
+        <v>0.2842648327350616</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.2737078368663788</v>
+        <v>0.2737100720405579</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.276138961315155</v>
+        <v>0.2761415243148804</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.2665272355079651</v>
+        <v>0.2665295302867889</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.2680960595607758</v>
+        <v>0.2680985033512115</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.2676443457603455</v>
+        <v>0.2676447033882141</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.2643975615501404</v>
+        <v>0.2643986940383911</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.2599951028823853</v>
+        <v>0.2599974274635315</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.2586808502674103</v>
+        <v>0.2586829960346222</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.260915219783783</v>
+        <v>0.2609168589115143</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.2629120349884033</v>
+        <v>0.2629130184650421</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.2724833190441132</v>
+        <v>0.2724821269512177</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.2828172743320465</v>
+        <v>0.2828178703784943</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.2878579795360565</v>
+        <v>0.2878608405590057</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.2881673276424408</v>
+        <v>0.2881698906421661</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.2801734507083893</v>
+        <v>0.2801757156848907</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.2781437933444977</v>
+        <v>0.2781451940536499</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.2836247682571411</v>
+        <v>0.2836282849311829</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.2812284529209137</v>
+        <v>0.2812299728393555</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.2814436256885529</v>
+        <v>0.2814462780952454</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.2794608771800995</v>
+        <v>0.2794629037380219</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.2811963856220245</v>
+        <v>0.2811989486217499</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.2816641926765442</v>
+        <v>0.2816669344902039</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.2808051705360413</v>
+        <v>0.2808065116405487</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.2912441492080688</v>
+        <v>0.2912438213825226</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.29566690325737</v>
+        <v>0.29566890001297</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.3101934492588043</v>
+        <v>0.3101947009563446</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.3037129342556</v>
+        <v>0.3037173748016357</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.3042365610599518</v>
+        <v>0.3042398691177368</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.3054337203502655</v>
+        <v>0.3054376542568207</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.3053682446479797</v>
+        <v>0.3053730428218842</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.3034441769123077</v>
+        <v>0.3034473061561584</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.3019466400146484</v>
+        <v>0.3019521534442902</v>
       </c>
       <c r="GH5" t="n">
-        <v>0.2981670498847961</v>
+        <v>0.2981713116168976</v>
       </c>
       <c r="GI5" t="n">
-        <v>0.2988418936729431</v>
+        <v>0.2988467812538147</v>
       </c>
       <c r="GJ5" t="n">
-        <v>0.2992578446865082</v>
+        <v>0.2992630898952484</v>
       </c>
       <c r="GK5" t="n">
-        <v>0.3030657470226288</v>
+        <v>0.3030703365802765</v>
       </c>
       <c r="GL5" t="n">
-        <v>0.3093507587909698</v>
+        <v>0.3093530833721161</v>
       </c>
       <c r="GM5" t="n">
-        <v>0.3157642185688019</v>
+        <v>0.3157668113708496</v>
       </c>
       <c r="GN5" t="n">
-        <v>0.331085205078125</v>
+        <v>0.3310856819152832</v>
       </c>
       <c r="GO5" t="n">
-        <v>0.3388335108757019</v>
+        <v>0.3388350903987885</v>
       </c>
       <c r="GP5" t="n">
-        <v>0.3319107294082642</v>
+        <v>0.3319146335124969</v>
       </c>
       <c r="GQ5" t="n">
-        <v>0.3290127217769623</v>
+        <v>0.3290154039859772</v>
       </c>
       <c r="GR5" t="n">
-        <v>0.3279174566268921</v>
+        <v>0.3279182314872742</v>
       </c>
       <c r="GS5" t="n">
-        <v>0.3262421190738678</v>
+        <v>0.3262442946434021</v>
       </c>
       <c r="GT5" t="n">
-        <v>0.3277332484722137</v>
+        <v>0.3277364075183868</v>
       </c>
       <c r="GU5" t="n">
-        <v>0.3219878673553467</v>
+        <v>0.3219917118549347</v>
       </c>
       <c r="GV5" t="n">
-        <v>0.3270226418972015</v>
+        <v>0.3270249664783478</v>
       </c>
       <c r="GW5" t="n">
-        <v>0.3221406042575836</v>
+        <v>0.3221427798271179</v>
       </c>
       <c r="GX5" t="n">
-        <v>0.323233038187027</v>
+        <v>0.3232372105121613</v>
       </c>
       <c r="GY5" t="n">
-        <v>0.3233921527862549</v>
+        <v>0.323392391204834</v>
       </c>
       <c r="GZ5" t="n">
-        <v>0.3366313278675079</v>
+        <v>0.3366337716579437</v>
       </c>
       <c r="HA5" t="n">
-        <v>0.349608302116394</v>
+        <v>0.3496101498603821</v>
       </c>
       <c r="HB5" t="n">
-        <v>0.3619728684425354</v>
+        <v>0.3619756400585175</v>
       </c>
       <c r="HC5" t="n">
-        <v>0.3563314080238342</v>
+        <v>0.3563317656517029</v>
       </c>
       <c r="HD5" t="n">
-        <v>0.3440693914890289</v>
+        <v>0.3440744280815125</v>
       </c>
       <c r="HE5" t="n">
-        <v>0.3390647172927856</v>
+        <v>0.3390648066997528</v>
       </c>
       <c r="HF5" t="n">
-        <v>0.3406950235366821</v>
+        <v>0.3406940400600433</v>
       </c>
       <c r="HG5" t="n">
-        <v>0.3473580181598663</v>
+        <v>0.3473596572875977</v>
       </c>
       <c r="HH5" t="n">
-        <v>0.3460981547832489</v>
+        <v>0.3460998237133026</v>
       </c>
       <c r="HI5" t="n">
-        <v>0.3446662724018097</v>
+        <v>0.3446686565876007</v>
       </c>
       <c r="HJ5" t="n">
-        <v>0.3469628095626831</v>
+        <v>0.3469666540622711</v>
       </c>
       <c r="HK5" t="n">
-        <v>0.3408189415931702</v>
+        <v>0.3408218026161194</v>
       </c>
       <c r="HL5" t="n">
-        <v>0.3425921499729156</v>
+        <v>0.3425973057746887</v>
       </c>
       <c r="HM5" t="n">
-        <v>0.3394136428833008</v>
+        <v>0.3394147753715515</v>
       </c>
       <c r="HN5" t="n">
-        <v>0.362697422504425</v>
+        <v>0.3627010583877563</v>
       </c>
       <c r="HO5" t="n">
-        <v>0.3768655955791473</v>
+        <v>0.3768674433231354</v>
       </c>
       <c r="HP5" t="n">
-        <v>0.3569588661193848</v>
+        <v>0.3569578528404236</v>
       </c>
       <c r="HQ5" t="n">
-        <v>0.3455806970596313</v>
+        <v>0.3455815315246582</v>
       </c>
       <c r="HR5" t="inlineStr">
         <is>
@@ -4291,676 +4291,676 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02460705302655697</v>
+        <v>0.02460830099880695</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03341708704829216</v>
+        <v>0.03341932967305183</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03547610715031624</v>
+        <v>0.03547793254256248</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03701156005263329</v>
+        <v>0.03701359033584595</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03747506439685822</v>
+        <v>0.03747750818729401</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03667999431490898</v>
+        <v>0.03668248280882835</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03613075241446495</v>
+        <v>0.03613289818167686</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03572705015540123</v>
+        <v>0.03572870045900345</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0359305813908577</v>
+        <v>0.03593254834413528</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03525371477007866</v>
+        <v>0.03525543957948685</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03424281999468803</v>
+        <v>0.03424514457583427</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03320405632257462</v>
+        <v>0.0332060419023037</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03311967104673386</v>
+        <v>0.03312124684453011</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03365733847022057</v>
+        <v>0.03365932404994965</v>
       </c>
       <c r="P6" t="n">
-        <v>0.04981594532728195</v>
+        <v>0.04981780797243118</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.06123309209942818</v>
+        <v>0.06123539432883263</v>
       </c>
       <c r="R6" t="n">
-        <v>0.06398165971040726</v>
+        <v>0.06398546695709229</v>
       </c>
       <c r="S6" t="n">
-        <v>0.06489022076129913</v>
+        <v>0.06489376723766327</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06601246446371078</v>
+        <v>0.06601506471633911</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06357074528932571</v>
+        <v>0.06357222050428391</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06443619728088379</v>
+        <v>0.06443902105093002</v>
       </c>
       <c r="W6" t="n">
-        <v>0.06398253887891769</v>
+        <v>0.06398611515760422</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06342794746160507</v>
+        <v>0.06343159079551697</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.06294155865907669</v>
+        <v>0.0629454180598259</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.05986968800425529</v>
+        <v>0.05987302586436272</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.05751020833849907</v>
+        <v>0.05751315876841545</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.05735443904995918</v>
+        <v>0.05735813826322556</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.05870767682790756</v>
+        <v>0.0587100088596344</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.08159530907869339</v>
+        <v>0.08159765601158142</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.09347858279943466</v>
+        <v>0.09348231554031372</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.09346684068441391</v>
+        <v>0.0934726893901825</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.09528391808271408</v>
+        <v>0.09528716653585434</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.09548895061016083</v>
+        <v>0.09549286961555481</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.09464908391237259</v>
+        <v>0.09465458989143372</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.09158938378095627</v>
+        <v>0.09159407019615173</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.09054999798536301</v>
+        <v>0.09055422246456146</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.09080177545547485</v>
+        <v>0.09080562740564346</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.08777552098035812</v>
+        <v>0.08778002858161926</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.08350837975740433</v>
+        <v>0.08351228386163712</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.08152252435684204</v>
+        <v>0.08152683079242706</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.08364541083574295</v>
+        <v>0.08365027606487274</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.08430401235818863</v>
+        <v>0.08430801331996918</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.1107385605573654</v>
+        <v>0.1107395812869072</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.1179048493504524</v>
+        <v>0.1179121434688568</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.1184771507978439</v>
+        <v>0.1184844151139259</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1200564131140709</v>
+        <v>0.1200622543692589</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.1179159358143806</v>
+        <v>0.117921844124794</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.113666720688343</v>
+        <v>0.1136724352836609</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1140308976173401</v>
+        <v>0.1140382662415504</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.113130085170269</v>
+        <v>0.1131350547075272</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.1116330176591873</v>
+        <v>0.1116382256150246</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.1080236062407494</v>
+        <v>0.1080292835831642</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.1033954918384552</v>
+        <v>0.1034002304077148</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.101562075316906</v>
+        <v>0.1015660613775253</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.1002699583768845</v>
+        <v>0.1002735570073128</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.1032546013593674</v>
+        <v>0.1032581627368927</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.1392720490694046</v>
+        <v>0.1392768770456314</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.141321212053299</v>
+        <v>0.1413277089595795</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.1405320018529892</v>
+        <v>0.1405391544103622</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.1369553804397583</v>
+        <v>0.1369635313749313</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.1371202617883682</v>
+        <v>0.137127548456192</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.1307817548513412</v>
+        <v>0.1307879239320755</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.1302730590105057</v>
+        <v>0.1302807629108429</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.127693310379982</v>
+        <v>0.127699613571167</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.1256627291440964</v>
+        <v>0.1256693005561829</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.1269440352916718</v>
+        <v>0.1269500404596329</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.1187839955091476</v>
+        <v>0.1187890470027924</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.118208259344101</v>
+        <v>0.1182136759161949</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.1174440160393715</v>
+        <v>0.1174491345882416</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.117316335439682</v>
+        <v>0.1173203960061073</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.173898309469223</v>
+        <v>0.1739064753055573</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.1718874126672745</v>
+        <v>0.1718955934047699</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1676141768693924</v>
+        <v>0.1676251292228699</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.1673941016197205</v>
+        <v>0.1674039512872696</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.1654598563909531</v>
+        <v>0.1654671132564545</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.1613284200429916</v>
+        <v>0.1613375097513199</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.1573907434940338</v>
+        <v>0.1573990434408188</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.1544471979141235</v>
+        <v>0.1544530987739563</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.1523996442556381</v>
+        <v>0.1524064391851425</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.1483790725469589</v>
+        <v>0.1483860462903976</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.1446533203125</v>
+        <v>0.144659623503685</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.1377899348735809</v>
+        <v>0.1377941071987152</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.1379992961883545</v>
+        <v>0.1380038559436798</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.1411112695932388</v>
+        <v>0.1411163508892059</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.1997801810503006</v>
+        <v>0.1997932642698288</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.1975298374891281</v>
+        <v>0.1975423246622086</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.1944806724786758</v>
+        <v>0.194489374756813</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.1904609799385071</v>
+        <v>0.1904725432395935</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.186832383275032</v>
+        <v>0.1868435591459274</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.1797910332679749</v>
+        <v>0.1797984689474106</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.1805211156606674</v>
+        <v>0.1805299073457718</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.1740712225437164</v>
+        <v>0.1740788072347641</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.1725258678197861</v>
+        <v>0.1725350469350815</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.1733249574899673</v>
+        <v>0.1733337044715881</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.1605703681707382</v>
+        <v>0.160577192902565</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.1579979807138443</v>
+        <v>0.1580032855272293</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.1579279005527496</v>
+        <v>0.1579334735870361</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.1640014350414276</v>
+        <v>0.164006382226944</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.2350352704524994</v>
+        <v>0.2350495010614395</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.2223368436098099</v>
+        <v>0.2223486304283142</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.2221514880657196</v>
+        <v>0.2221644073724747</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.2203788906335831</v>
+        <v>0.2203904986381531</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.2110003978013992</v>
+        <v>0.2110083997249603</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.2074425518512726</v>
+        <v>0.207451656460762</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.207981675863266</v>
+        <v>0.2079890966415405</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.2033853381872177</v>
+        <v>0.2033936530351639</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.203095942735672</v>
+        <v>0.2031059414148331</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.1974184960126877</v>
+        <v>0.1974244564771652</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.1916654109954834</v>
+        <v>0.1916718184947968</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.1884322166442871</v>
+        <v>0.1884379237890244</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.1873411983251572</v>
+        <v>0.1873471587896347</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1898517459630966</v>
+        <v>0.1898567527532578</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.2510277628898621</v>
+        <v>0.2510426938533783</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.2475284785032272</v>
+        <v>0.2475395053625107</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.2395270466804504</v>
+        <v>0.2395381480455399</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.2378806918859482</v>
+        <v>0.2378909885883331</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.2309673726558685</v>
+        <v>0.230979710817337</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.2320092767477036</v>
+        <v>0.2320206016302109</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.2262208163738251</v>
+        <v>0.2262305170297623</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.2199631184339523</v>
+        <v>0.2199688404798508</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.2186598479747772</v>
+        <v>0.2186679244041443</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.2156688421964645</v>
+        <v>0.2156730145215988</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.2110839039087296</v>
+        <v>0.2110899090766907</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.209501713514328</v>
+        <v>0.2095052450895309</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.2119202017784119</v>
+        <v>0.2119248360395432</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.2139301896095276</v>
+        <v>0.2139346897602081</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.2676028907299042</v>
+        <v>0.267612636089325</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.2575468719005585</v>
+        <v>0.257557600736618</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.2561133503913879</v>
+        <v>0.2561226189136505</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.2487548589706421</v>
+        <v>0.2487638294696808</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.2480689138174057</v>
+        <v>0.2480778098106384</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.2421355694532394</v>
+        <v>0.2421437501907349</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.2394254505634308</v>
+        <v>0.2394320964813232</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.2379584908485413</v>
+        <v>0.2379635870456696</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.2356108427047729</v>
+        <v>0.2356166243553162</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.2337293773889542</v>
+        <v>0.233735665678978</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.2215874046087265</v>
+        <v>0.2215907275676727</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.2253105342388153</v>
+        <v>0.2253143787384033</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.2263267189264297</v>
+        <v>0.2263280600309372</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.227954164147377</v>
+        <v>0.2279582619667053</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.2777300179004669</v>
+        <v>0.2777406871318817</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.2743258476257324</v>
+        <v>0.274332195520401</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.2702299654483795</v>
+        <v>0.2702383100986481</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.263369619846344</v>
+        <v>0.2633747458457947</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.2666372358798981</v>
+        <v>0.2666437923908234</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.2559027373790741</v>
+        <v>0.2559087574481964</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.255536675453186</v>
+        <v>0.2555429637432098</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.2493764609098434</v>
+        <v>0.2493809461593628</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.2522217333316803</v>
+        <v>0.2522265017032623</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.2514459192752838</v>
+        <v>0.2514496147632599</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.247990757226944</v>
+        <v>0.2479947507381439</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.2478127032518387</v>
+        <v>0.2478159070014954</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.2475616037845612</v>
+        <v>0.2475627362728119</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.2591246962547302</v>
+        <v>0.2591266930103302</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.2841117680072784</v>
+        <v>0.2841159999370575</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.2846524119377136</v>
+        <v>0.2846574485301971</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.2740681171417236</v>
+        <v>0.2740708887577057</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.2764789462089539</v>
+        <v>0.2764819860458374</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.2668399214744568</v>
+        <v>0.2668426632881165</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.2683956325054169</v>
+        <v>0.2683984935283661</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.2679440975189209</v>
+        <v>0.2679448127746582</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.2646878957748413</v>
+        <v>0.2646893858909607</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.2602812051773071</v>
+        <v>0.2602839171886444</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.2589644491672516</v>
+        <v>0.2589669823646545</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.2611733675003052</v>
+        <v>0.2611753046512604</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.2631045877933502</v>
+        <v>0.2631058096885681</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.2726605236530304</v>
+        <v>0.2726595103740692</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.2829947769641876</v>
+        <v>0.2829955518245697</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.2882095873355865</v>
+        <v>0.2882128357887268</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.2884892821311951</v>
+        <v>0.2884922325611115</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.2804761826992035</v>
+        <v>0.2804787755012512</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.278432160615921</v>
+        <v>0.2784338891506195</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.2839459776878357</v>
+        <v>0.2839498817920685</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.2815297245979309</v>
+        <v>0.2815316021442413</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.2817589044570923</v>
+        <v>0.2817619740962982</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.2797756493091583</v>
+        <v>0.2797780930995941</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.2815014719963074</v>
+        <v>0.2815043926239014</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.2819725275039673</v>
+        <v>0.2819756865501404</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.2810517847537994</v>
+        <v>0.2810534536838531</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.2914472818374634</v>
+        <v>0.2914471626281738</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.2958943247795105</v>
+        <v>0.2958965003490448</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.3104393780231476</v>
+        <v>0.310440868139267</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.3041634559631348</v>
+        <v>0.3041685521602631</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.3046909868717194</v>
+        <v>0.3046949803829193</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.3059156239032745</v>
+        <v>0.305920273065567</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.3058555126190186</v>
+        <v>0.3058610558509827</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.3039059937000275</v>
+        <v>0.3039098978042603</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.3023922145366669</v>
+        <v>0.3023984432220459</v>
       </c>
       <c r="GH6" t="n">
-        <v>0.2985939085483551</v>
+        <v>0.2985987961292267</v>
       </c>
       <c r="GI6" t="n">
-        <v>0.2991956174373627</v>
+        <v>0.2992011308670044</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.2996683120727539</v>
+        <v>0.2996741235256195</v>
       </c>
       <c r="GK6" t="n">
-        <v>0.3034679889678955</v>
+        <v>0.3034732341766357</v>
       </c>
       <c r="GL6" t="n">
-        <v>0.3096942007541656</v>
+        <v>0.3096971213817596</v>
       </c>
       <c r="GM6" t="n">
-        <v>0.3160593509674072</v>
+        <v>0.3160622119903564</v>
       </c>
       <c r="GN6" t="n">
-        <v>0.3313930630683899</v>
+        <v>0.3313938677310944</v>
       </c>
       <c r="GO6" t="n">
-        <v>0.3392008543014526</v>
+        <v>0.339202880859375</v>
       </c>
       <c r="GP6" t="n">
-        <v>0.3323333263397217</v>
+        <v>0.3323378264904022</v>
       </c>
       <c r="GQ6" t="n">
-        <v>0.3293745517730713</v>
+        <v>0.329377681016922</v>
       </c>
       <c r="GR6" t="n">
-        <v>0.3283050954341888</v>
+        <v>0.3283064067363739</v>
       </c>
       <c r="GS6" t="n">
-        <v>0.3266196548938751</v>
+        <v>0.3266223073005676</v>
       </c>
       <c r="GT6" t="n">
-        <v>0.3281265795230865</v>
+        <v>0.3281302750110626</v>
       </c>
       <c r="GU6" t="n">
-        <v>0.3223705589771271</v>
+        <v>0.3223749101161957</v>
       </c>
       <c r="GV6" t="n">
-        <v>0.3274224698543549</v>
+        <v>0.3274253010749817</v>
       </c>
       <c r="GW6" t="n">
-        <v>0.3225273191928864</v>
+        <v>0.3225300312042236</v>
       </c>
       <c r="GX6" t="n">
-        <v>0.3236326277256012</v>
+        <v>0.3236373662948608</v>
       </c>
       <c r="GY6" t="n">
-        <v>0.3237964808940887</v>
+        <v>0.3237972557544708</v>
       </c>
       <c r="GZ6" t="n">
-        <v>0.3370065093040466</v>
+        <v>0.3370093703269958</v>
       </c>
       <c r="HA6" t="n">
-        <v>0.3499677777290344</v>
+        <v>0.3499701321125031</v>
       </c>
       <c r="HB6" t="n">
-        <v>0.3623718023300171</v>
+        <v>0.3623749613761902</v>
       </c>
       <c r="HC6" t="n">
-        <v>0.3566235303878784</v>
+        <v>0.3566241860389709</v>
       </c>
       <c r="HD6" t="n">
-        <v>0.3445188403129578</v>
+        <v>0.3445243537425995</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.3394883573055267</v>
+        <v>0.3394887745380402</v>
       </c>
       <c r="HF6" t="n">
-        <v>0.341137558221817</v>
+        <v>0.3411369025707245</v>
       </c>
       <c r="HG6" t="n">
-        <v>0.3478275835514069</v>
+        <v>0.3478296995162964</v>
       </c>
       <c r="HH6" t="n">
-        <v>0.346596896648407</v>
+        <v>0.3465990424156189</v>
       </c>
       <c r="HI6" t="n">
-        <v>0.3451794981956482</v>
+        <v>0.3451824188232422</v>
       </c>
       <c r="HJ6" t="n">
-        <v>0.3475086092948914</v>
+        <v>0.3475129306316376</v>
       </c>
       <c r="HK6" t="n">
-        <v>0.3413757383823395</v>
+        <v>0.3413792252540588</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.3431837558746338</v>
+        <v>0.3431896269321442</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.3400381207466125</v>
+        <v>0.3400400578975677</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.3632882535457611</v>
+        <v>0.3632923364639282</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.3774294257164001</v>
+        <v>0.3774318993091583</v>
       </c>
       <c r="HP6" t="n">
-        <v>0.3573618233203888</v>
+        <v>0.3573610782623291</v>
       </c>
       <c r="HQ6" t="n">
-        <v>0.3458356857299805</v>
+        <v>0.3458366692066193</v>
       </c>
       <c r="HR6" t="inlineStr">
         <is>
@@ -4975,676 +4975,676 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02491172961890697</v>
+        <v>0.02491302788257599</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03374115750193596</v>
+        <v>0.0337434858083725</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03579409047961235</v>
+        <v>0.03579605370759964</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0373169481754303</v>
+        <v>0.03731916099786758</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03776048496365547</v>
+        <v>0.03776314854621887</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03694488108158112</v>
+        <v>0.0369475819170475</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0363769493997097</v>
+        <v>0.03637934848666191</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03596757352352142</v>
+        <v>0.03596951439976692</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0361633375287056</v>
+        <v>0.03616558387875557</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03547380492091179</v>
+        <v>0.03547583147883415</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03443851321935654</v>
+        <v>0.03444110602140427</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03337437286973</v>
+        <v>0.03337658196687698</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03328611329197884</v>
+        <v>0.03328792750835419</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03381798043847084</v>
+        <v>0.03382018581032753</v>
       </c>
       <c r="P7" t="n">
-        <v>0.05029672756791115</v>
+        <v>0.05029862746596336</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.06173799932003021</v>
+        <v>0.06174049898982048</v>
       </c>
       <c r="R7" t="n">
-        <v>0.06449098885059357</v>
+        <v>0.06449510902166367</v>
       </c>
       <c r="S7" t="n">
-        <v>0.06535004824399948</v>
+        <v>0.06535394489765167</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06646016240119934</v>
+        <v>0.06646320968866348</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06396835297346115</v>
+        <v>0.06397023797035217</v>
       </c>
       <c r="V7" t="n">
-        <v>0.064818374812603</v>
+        <v>0.06482165306806564</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06433554738759995</v>
+        <v>0.06433954834938049</v>
       </c>
       <c r="X7" t="n">
-        <v>0.06377511471509933</v>
+        <v>0.06377924978733063</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0632694736123085</v>
+        <v>0.06327381730079651</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.06015623360872269</v>
+        <v>0.06016005575656891</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.05776670575141907</v>
+        <v>0.05777007713913918</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.05760959535837173</v>
+        <v>0.05761370435357094</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.05895422771573067</v>
+        <v>0.05895696952939034</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.08221510052680969</v>
+        <v>0.08221755176782608</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.09413212537765503</v>
+        <v>0.09413620829582214</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.09411287307739258</v>
+        <v>0.09411920607089996</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.095852330327034</v>
+        <v>0.09585623443126678</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.09603110700845718</v>
+        <v>0.09603569656610489</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.09515831619501114</v>
+        <v>0.09516448527574539</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09205211699008942</v>
+        <v>0.09205745160579681</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.09097646921873093</v>
+        <v>0.0909813866019249</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.09122805297374725</v>
+        <v>0.09123264998197556</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.08817145973443985</v>
+        <v>0.0881766676902771</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.08384405076503754</v>
+        <v>0.08384855091571808</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.08182965219020844</v>
+        <v>0.08183448761701584</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.08396071195602417</v>
+        <v>0.08396614342927933</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0846036970615387</v>
+        <v>0.0846082791686058</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.1114697307348251</v>
+        <v>0.1114709973335266</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.1186830326914787</v>
+        <v>0.1186909973621368</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.1191943660378456</v>
+        <v>0.1192024126648903</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.120667926967144</v>
+        <v>0.1206746175885201</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.1185555160045624</v>
+        <v>0.118562325835228</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.1142097115516663</v>
+        <v>0.1142162829637527</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1145544052124023</v>
+        <v>0.114562600851059</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.113614410161972</v>
+        <v>0.113620214164257</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.1121088638901711</v>
+        <v>0.1121149584650993</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.1084583923220634</v>
+        <v>0.1084648296236992</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.103759877383709</v>
+        <v>0.1037653163075447</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.1019050031900406</v>
+        <v>0.1019096374511719</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.1006120964884758</v>
+        <v>0.1006163284182549</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.1035867556929588</v>
+        <v>0.1035910025238991</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.1400866955518723</v>
+        <v>0.1400920897722244</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.1421418339014053</v>
+        <v>0.1421492695808411</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.1412712633609772</v>
+        <v>0.141279399394989</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.1376228183507919</v>
+        <v>0.1376321911811829</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.1377846598625183</v>
+        <v>0.1377930045127869</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.1313681453466415</v>
+        <v>0.131375327706337</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.1308053582906723</v>
+        <v>0.1308140307664871</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.1282011270523071</v>
+        <v>0.1282083541154861</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.1261565387248993</v>
+        <v>0.1261641085147858</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.1274057626724243</v>
+        <v>0.1274127662181854</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1191698983311653</v>
+        <v>0.1191757991909981</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.1185713931918144</v>
+        <v>0.1185775101184845</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.1178064420819283</v>
+        <v>0.1178122088313103</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.1176631674170494</v>
+        <v>0.1176678836345673</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.1749716401100159</v>
+        <v>0.1749810129404068</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.1728587448596954</v>
+        <v>0.1728684306144714</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1685409545898438</v>
+        <v>0.1685534715652466</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.1682096272706985</v>
+        <v>0.1682211607694626</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.1661857515573502</v>
+        <v>0.166194424033165</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1620218902826309</v>
+        <v>0.1620322167873383</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.1580159962177277</v>
+        <v>0.1580256223678589</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.1550374627113342</v>
+        <v>0.1550446003675461</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.1529505103826523</v>
+        <v>0.1529584378004074</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.1488844007253647</v>
+        <v>0.1488924473524094</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.1450918465852737</v>
+        <v>0.1450990587472916</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.1381827294826508</v>
+        <v>0.1381876468658447</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.1383894681930542</v>
+        <v>0.138394758105278</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.1414945870637894</v>
+        <v>0.141500398516655</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.2008123695850372</v>
+        <v>0.2008271366357803</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.1985662132501602</v>
+        <v>0.1985807716846466</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.1954275965690613</v>
+        <v>0.1954381465911865</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.191281720995903</v>
+        <v>0.1912948787212372</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.1876197010278702</v>
+        <v>0.1876324117183685</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.1805095374584198</v>
+        <v>0.1805183589458466</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.1811885684728622</v>
+        <v>0.1811987459659576</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.1746875494718552</v>
+        <v>0.1746965199708939</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.1731042563915253</v>
+        <v>0.1731146425008774</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.1738568991422653</v>
+        <v>0.173866868019104</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.1610179245471954</v>
+        <v>0.1610256135463715</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.158405676484108</v>
+        <v>0.1584117263555527</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.1583227515220642</v>
+        <v>0.1583289951086044</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.1644121408462524</v>
+        <v>0.1644178479909897</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.2360170930624008</v>
+        <v>0.2360334545373917</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.2233453840017319</v>
+        <v>0.2233593314886093</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.2230462580919266</v>
+        <v>0.2230610698461533</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.2212433665990829</v>
+        <v>0.2212566435337067</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.2117759138345718</v>
+        <v>0.2117855995893478</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.2081676423549652</v>
+        <v>0.2081783264875412</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.2086606472730637</v>
+        <v>0.2086696028709412</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.2039832919836044</v>
+        <v>0.203993022441864</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.2036736011505127</v>
+        <v>0.2036846876144409</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1979534476995468</v>
+        <v>0.1979604959487915</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.1921189725399017</v>
+        <v>0.1921262443065643</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.18885238468647</v>
+        <v>0.1888589262962341</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.1877376735210419</v>
+        <v>0.1877443343400955</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.1902466118335724</v>
+        <v>0.190252274274826</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.2520974576473236</v>
+        <v>0.2521146237850189</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.2484943270683289</v>
+        <v>0.2485072761774063</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.2403879761695862</v>
+        <v>0.2404009103775024</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.2387012541294098</v>
+        <v>0.2387133091688156</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.2317229062318802</v>
+        <v>0.2317368239164352</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.232672706246376</v>
+        <v>0.2326855212450027</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.2268296331167221</v>
+        <v>0.2268405705690384</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.220536932349205</v>
+        <v>0.2205439507961273</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.2192016094923019</v>
+        <v>0.2192106992006302</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.2161734104156494</v>
+        <v>0.2161784619092941</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.2115243375301361</v>
+        <v>0.2115311324596405</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.209862232208252</v>
+        <v>0.2098664492368698</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.2123061865568161</v>
+        <v>0.2123114168643951</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.2143038958311081</v>
+        <v>0.2143089473247528</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.2685453593730927</v>
+        <v>0.2685570120811462</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.2584132850170135</v>
+        <v>0.2584259212017059</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.2569560408592224</v>
+        <v>0.2569670081138611</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.2494686394929886</v>
+        <v>0.2494791746139526</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.2487283200025558</v>
+        <v>0.2487384974956512</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.2427545636892319</v>
+        <v>0.24276402592659</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.2400051802396774</v>
+        <v>0.2400128990411758</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.2385001629590988</v>
+        <v>0.2385061979293823</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.2361153215169907</v>
+        <v>0.2361221015453339</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.2342046350240707</v>
+        <v>0.234211802482605</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.2220157235860825</v>
+        <v>0.222019761800766</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.2256937921047211</v>
+        <v>0.2256982028484344</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.2266656160354614</v>
+        <v>0.2266673743724823</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.228309839963913</v>
+        <v>0.2283143699169159</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.2784765958786011</v>
+        <v>0.2784887850284576</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.2749962508678436</v>
+        <v>0.2750038504600525</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.270853579044342</v>
+        <v>0.2708629667758942</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.263929694890976</v>
+        <v>0.2639358043670654</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.2671717703342438</v>
+        <v>0.2671792209148407</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.2563892304897308</v>
+        <v>0.2563960254192352</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.2560660839080811</v>
+        <v>0.2560731172561646</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.2498506307601929</v>
+        <v>0.2498556673526764</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.2526704370975494</v>
+        <v>0.2526758313179016</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.2518519461154938</v>
+        <v>0.2518561482429504</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.2483733892440796</v>
+        <v>0.248377799987793</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.2481552958488464</v>
+        <v>0.2481588423252106</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.2478736490011215</v>
+        <v>0.2478750348091125</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.2594927847385406</v>
+        <v>0.2594949901103973</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.2845450937747955</v>
+        <v>0.2845499813556671</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.2850936651229858</v>
+        <v>0.2850992381572723</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.2744829058647156</v>
+        <v>0.2744861841201782</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.2768887579441071</v>
+        <v>0.2768921852111816</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.2672285139560699</v>
+        <v>0.2672316133975983</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.2687789797782898</v>
+        <v>0.2687821686267853</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.2683294713497162</v>
+        <v>0.2683305740356445</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.2650664150714874</v>
+        <v>0.2650682330131531</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.2606525421142578</v>
+        <v>0.2606555819511414</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.2593319118022919</v>
+        <v>0.2593347132205963</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.2615293264389038</v>
+        <v>0.2615315616130829</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.2634123265743256</v>
+        <v>0.2634136974811554</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.272977352142334</v>
+        <v>0.2729765176773071</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.2833219468593597</v>
+        <v>0.2833227515220642</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.2886684536933899</v>
+        <v>0.2886720597743988</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.2889202833175659</v>
+        <v>0.2889235317707062</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.2808852791786194</v>
+        <v>0.280888170003891</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.278835654258728</v>
+        <v>0.2788376212120056</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.2843719124794006</v>
+        <v>0.2843760848045349</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.2819454669952393</v>
+        <v>0.2819477021694183</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.2821829319000244</v>
+        <v>0.2821863293647766</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.2802005112171173</v>
+        <v>0.2802032828330994</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.2819242477416992</v>
+        <v>0.2819274961948395</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.2823989987373352</v>
+        <v>0.282402515411377</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.2814373373985291</v>
+        <v>0.2814392447471619</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.2918093204498291</v>
+        <v>0.2918093800544739</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.2962886691093445</v>
+        <v>0.2962910234928131</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.3108537495136261</v>
+        <v>0.310855507850647</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.3047176897525787</v>
+        <v>0.3047233521938324</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.3052516877651215</v>
+        <v>0.3052563369274139</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.3065022528171539</v>
+        <v>0.3065075576305389</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.3064484298229218</v>
+        <v>0.3064546287059784</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.3044771254062653</v>
+        <v>0.3044816851615906</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.302949458360672</v>
+        <v>0.3029563128948212</v>
       </c>
       <c r="GH7" t="n">
-        <v>0.2991301119327545</v>
+        <v>0.2991357147693634</v>
       </c>
       <c r="GI7" t="n">
-        <v>0.2996842861175537</v>
+        <v>0.299690306186676</v>
       </c>
       <c r="GJ7" t="n">
-        <v>0.3002084195613861</v>
+        <v>0.3002147972583771</v>
       </c>
       <c r="GK7" t="n">
-        <v>0.3040100932121277</v>
+        <v>0.3040158748626709</v>
       </c>
       <c r="GL7" t="n">
-        <v>0.310204803943634</v>
+        <v>0.3102082312107086</v>
       </c>
       <c r="GM7" t="n">
-        <v>0.3165501356124878</v>
+        <v>0.3165533244609833</v>
       </c>
       <c r="GN7" t="n">
-        <v>0.3319069445133209</v>
+        <v>0.3319080770015717</v>
       </c>
       <c r="GO7" t="n">
-        <v>0.3397648930549622</v>
+        <v>0.3397673368453979</v>
       </c>
       <c r="GP7" t="n">
-        <v>0.3328987061977386</v>
+        <v>0.3329037129878998</v>
       </c>
       <c r="GQ7" t="n">
-        <v>0.3298988938331604</v>
+        <v>0.3299024701118469</v>
       </c>
       <c r="GR7" t="n">
-        <v>0.3288272619247437</v>
+        <v>0.3288291692733765</v>
       </c>
       <c r="GS7" t="n">
-        <v>0.3271455466747284</v>
+        <v>0.3271486759185791</v>
       </c>
       <c r="GT7" t="n">
-        <v>0.3286726474761963</v>
+        <v>0.3286767899990082</v>
       </c>
       <c r="GU7" t="n">
-        <v>0.3229126930236816</v>
+        <v>0.3229175209999084</v>
       </c>
       <c r="GV7" t="n">
-        <v>0.3279891610145569</v>
+        <v>0.3279925286769867</v>
       </c>
       <c r="GW7" t="n">
-        <v>0.3230946063995361</v>
+        <v>0.3230977356433868</v>
       </c>
       <c r="GX7" t="n">
-        <v>0.3242194354534149</v>
+        <v>0.3242245018482208</v>
       </c>
       <c r="GY7" t="n">
-        <v>0.3243945240974426</v>
+        <v>0.3243957757949829</v>
       </c>
       <c r="GZ7" t="n">
-        <v>0.337603896856308</v>
+        <v>0.3376069962978363</v>
       </c>
       <c r="HA7" t="n">
-        <v>0.3505237400531769</v>
+        <v>0.3505263924598694</v>
       </c>
       <c r="HB7" t="n">
-        <v>0.3629949688911438</v>
+        <v>0.3629983961582184</v>
       </c>
       <c r="HC7" t="n">
-        <v>0.3571094572544098</v>
+        <v>0.357110321521759</v>
       </c>
       <c r="HD7" t="n">
-        <v>0.345252513885498</v>
+        <v>0.3452581167221069</v>
       </c>
       <c r="HE7" t="n">
-        <v>0.3402054309844971</v>
+        <v>0.3402059674263</v>
       </c>
       <c r="HF7" t="n">
-        <v>0.3418548107147217</v>
+        <v>0.3418543934822083</v>
       </c>
       <c r="HG7" t="n">
-        <v>0.3485631048679352</v>
+        <v>0.348565548658371</v>
       </c>
       <c r="HH7" t="n">
-        <v>0.3473607301712036</v>
+        <v>0.3473632335662842</v>
       </c>
       <c r="HI7" t="n">
-        <v>0.3459585309028625</v>
+        <v>0.3459617793560028</v>
       </c>
       <c r="HJ7" t="n">
-        <v>0.3483117818832397</v>
+        <v>0.348316490650177</v>
       </c>
       <c r="HK7" t="n">
-        <v>0.3421881496906281</v>
+        <v>0.3421920537948608</v>
       </c>
       <c r="HL7" t="n">
-        <v>0.3440155982971191</v>
+        <v>0.3440219461917877</v>
       </c>
       <c r="HM7" t="n">
-        <v>0.3408867418766022</v>
+        <v>0.3408894836902618</v>
       </c>
       <c r="HN7" t="n">
-        <v>0.3641227185726166</v>
+        <v>0.3641273975372314</v>
       </c>
       <c r="HO7" t="n">
-        <v>0.3782405257225037</v>
+        <v>0.3782435059547424</v>
       </c>
       <c r="HP7" t="n">
-        <v>0.357998788356781</v>
+        <v>0.357998251914978</v>
       </c>
       <c r="HQ7" t="n">
-        <v>0.3462979793548584</v>
+        <v>0.34629887342453</v>
       </c>
       <c r="HR7" t="inlineStr">
         <is>

--- a/results/submission_predictions.xlsx
+++ b/results/submission_predictions.xlsx
@@ -1555,676 +1555,676 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02318527735769749</v>
+        <v>0.02326624281704426</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03188502043485641</v>
+        <v>0.03184730932116508</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03397325053811073</v>
+        <v>0.03395084664225578</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03556691110134125</v>
+        <v>0.03552864119410515</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03612112998962402</v>
+        <v>0.03608324378728867</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03541815653443336</v>
+        <v>0.03545859828591347</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03495240956544876</v>
+        <v>0.03495080769062042</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03457081317901611</v>
+        <v>0.03461355343461037</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03480730578303337</v>
+        <v>0.0348496101796627</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03418846800923347</v>
+        <v>0.03421995788812637</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03328529745340347</v>
+        <v>0.03328651562333107</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03237009793519974</v>
+        <v>0.03239406272768974</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03230211511254311</v>
+        <v>0.03232501447200775</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03286706656217575</v>
+        <v>0.03292563557624817</v>
       </c>
       <c r="P2" t="n">
-        <v>0.04758084937930107</v>
+        <v>0.04760322719812393</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05885307118296623</v>
+        <v>0.0587894506752491</v>
       </c>
       <c r="R2" t="n">
-        <v>0.06157467886805534</v>
+        <v>0.06146266311407089</v>
       </c>
       <c r="S2" t="n">
-        <v>0.06270849704742432</v>
+        <v>0.06261803209781647</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06387853622436523</v>
+        <v>0.06386690586805344</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06166817992925644</v>
+        <v>0.06174226850271225</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06259722262620926</v>
+        <v>0.06260816752910614</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0622740313410759</v>
+        <v>0.06225843727588654</v>
       </c>
       <c r="X2" t="n">
-        <v>0.06173783913254738</v>
+        <v>0.06171950697898865</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.06133751943707466</v>
+        <v>0.06137225776910782</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.05845507979393005</v>
+        <v>0.05845443159341812</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0562426932156086</v>
+        <v>0.05631149187684059</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05608548223972321</v>
+        <v>0.05613158643245697</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.05748221650719643</v>
+        <v>0.05758491903543472</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.07868804782629013</v>
+        <v>0.07858073711395264</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0903950110077858</v>
+        <v>0.09026511758565903</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.09040234982967377</v>
+        <v>0.09025271236896515</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.09256979078054428</v>
+        <v>0.09254395216703415</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.09288154542446136</v>
+        <v>0.09284490346908569</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.092193603515625</v>
+        <v>0.09228673577308655</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.08934059739112854</v>
+        <v>0.08932638168334961</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.08846811205148697</v>
+        <v>0.0884973406791687</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.08870746940374374</v>
+        <v>0.08873913437128067</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.08582083135843277</v>
+        <v>0.08585983514785767</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.08184751123189926</v>
+        <v>0.08191733062267303</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.07998926192522049</v>
+        <v>0.08004793524742126</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.08206334710121155</v>
+        <v>0.08216208219528198</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.08279544115066528</v>
+        <v>0.0829370841383934</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.1073106527328491</v>
+        <v>0.1072095707058907</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.1142154037952423</v>
+        <v>0.1139610186219215</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.1150528118014336</v>
+        <v>0.1148864105343819</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.1171131432056427</v>
+        <v>0.116911418735981</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.114821769297123</v>
+        <v>0.1147406846284866</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.1110234335064888</v>
+        <v>0.1109433472156525</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1114681512117386</v>
+        <v>0.1114782765507698</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.1107455343008041</v>
+        <v>0.1107744351029396</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.109277181327343</v>
+        <v>0.1093958616256714</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.1058662012219429</v>
+        <v>0.1059109047055244</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.1015706956386566</v>
+        <v>0.1015538275241852</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.09983222931623459</v>
+        <v>0.09993546456098557</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.0985487699508667</v>
+        <v>0.09865272045135498</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.1015746667981148</v>
+        <v>0.1017197370529175</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.1354343742132187</v>
+        <v>0.1351003646850586</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.1373967528343201</v>
+        <v>0.1370925307273865</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.1369593292474747</v>
+        <v>0.136800229549408</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.1336890608072281</v>
+        <v>0.1336499750614166</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.1338646411895752</v>
+        <v>0.1337406486272812</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.127896249294281</v>
+        <v>0.1278858780860901</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.1276388615369797</v>
+        <v>0.1275735795497894</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.1251740008592606</v>
+        <v>0.1251439899206161</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.1231999173760414</v>
+        <v>0.1233212053775787</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.1246304214000702</v>
+        <v>0.1247251257300377</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1168431490659714</v>
+        <v>0.1169379726052284</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.1163709461688995</v>
+        <v>0.1163929328322411</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.1156119182705879</v>
+        <v>0.1157632023096085</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.1155664995312691</v>
+        <v>0.1157198846340179</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.1687597632408142</v>
+        <v>0.1684930026531219</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.1671306937932968</v>
+        <v>0.1668724417686462</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.1630528420209885</v>
+        <v>0.1628893613815308</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.1633303016424179</v>
+        <v>0.16323022544384</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.1618534326553345</v>
+        <v>0.1618122160434723</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.1578836441040039</v>
+        <v>0.1579392850399017</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.1542636305093765</v>
+        <v>0.1543184369802475</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.1514884233474731</v>
+        <v>0.1515738219022751</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.1496325135231018</v>
+        <v>0.1497409492731094</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.1458341628313065</v>
+        <v>0.1458337157964706</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.1424296498298645</v>
+        <v>0.1424359530210495</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.1358036547899246</v>
+        <v>0.1360165029764175</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.1360304355621338</v>
+        <v>0.1361581981182098</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.1391713470220566</v>
+        <v>0.1394180804491043</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.1947022378444672</v>
+        <v>0.1943377554416656</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.1923429369926453</v>
+        <v>0.1921221911907196</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.1897494345903397</v>
+        <v>0.1897089034318924</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.1863304227590561</v>
+        <v>0.1862373948097229</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.1828717291355133</v>
+        <v>0.1827536672353745</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.1761751919984818</v>
+        <v>0.1764062792062759</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.1771607547998428</v>
+        <v>0.1772307753562927</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.1709644794464111</v>
+        <v>0.1711097806692123</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.1695911437273026</v>
+        <v>0.1697260737419128</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.1706171929836273</v>
+        <v>0.1706794202327728</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.1582984179258347</v>
+        <v>0.1583408862352371</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.1559316217899323</v>
+        <v>0.1560250073671341</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.1559416353702545</v>
+        <v>0.1561156660318375</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.1619297415018082</v>
+        <v>0.1621867418289185</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.2300594449043274</v>
+        <v>0.2298654615879059</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.2172216773033142</v>
+        <v>0.2171444743871689</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.217623382806778</v>
+        <v>0.217566192150116</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.2160202413797379</v>
+        <v>0.2160788029432297</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.2070626616477966</v>
+        <v>0.2072250545024872</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.2037569433450699</v>
+        <v>0.2039920687675476</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.2045344710350037</v>
+        <v>0.2046655565500259</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.2003335803747177</v>
+        <v>0.2005384266376495</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.2001804709434509</v>
+        <v>0.2001926302909851</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.1947091966867447</v>
+        <v>0.1948353499174118</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.1893568336963654</v>
+        <v>0.1894027441740036</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.1862892657518387</v>
+        <v>0.1865027993917465</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.1853362768888474</v>
+        <v>0.1854919940233231</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.1878752410411835</v>
+        <v>0.1881078332662582</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.2456152141094208</v>
+        <v>0.2456706762313843</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.242657944560051</v>
+        <v>0.2429290115833282</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.2351531088352203</v>
+        <v>0.235290914773941</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.2337130606174469</v>
+        <v>0.2338629513978958</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.2271253168582916</v>
+        <v>0.2272153496742249</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.2286129146814346</v>
+        <v>0.2286425828933716</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.2231282889842987</v>
+        <v>0.223147913813591</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.2170570939779282</v>
+        <v>0.2173605859279633</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.2159329503774643</v>
+        <v>0.216062068939209</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.2131416499614716</v>
+        <v>0.21334208548069</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.2088657319545746</v>
+        <v>0.2089819759130478</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.2076674252748489</v>
+        <v>0.2079463750123978</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.2099850326776505</v>
+        <v>0.2101826518774033</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2120806574821472</v>
+        <v>0.2123355269432068</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.2628293931484222</v>
+        <v>0.2629711925983429</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.2531515657901764</v>
+        <v>0.2533411681652069</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.2518408596515656</v>
+        <v>0.2520175874233246</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.2451161295175552</v>
+        <v>0.2453045099973679</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.2447293102741241</v>
+        <v>0.2449192851781845</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.2390013188123703</v>
+        <v>0.2392342835664749</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.2365118414163589</v>
+        <v>0.2367788702249527</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.2352461963891983</v>
+        <v>0.2355187833309174</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.2330721765756607</v>
+        <v>0.2333745062351227</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.2313371449708939</v>
+        <v>0.2314516752958298</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.2194640785455704</v>
+        <v>0.2197874039411545</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.2234320491552353</v>
+        <v>0.2237004488706589</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.224687933921814</v>
+        <v>0.2250558584928513</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.2262211591005325</v>
+        <v>0.2264781594276428</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.2739299833774567</v>
+        <v>0.2740674316883087</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.2709447741508484</v>
+        <v>0.2712678015232086</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.2671000063419342</v>
+        <v>0.2673355340957642</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.2605608999729156</v>
+        <v>0.2608833014965057</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.2639603912830353</v>
+        <v>0.264211118221283</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.2534740567207336</v>
+        <v>0.2535957992076874</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.2529250681400299</v>
+        <v>0.2530747056007385</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.2470730692148209</v>
+        <v>0.2473413497209549</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.2500320971012115</v>
+        <v>0.2503487765789032</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.2494688034057617</v>
+        <v>0.2497831881046295</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.2461345642805099</v>
+        <v>0.2464046031236649</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.2461782097816467</v>
+        <v>0.2465107887983322</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.2460962235927582</v>
+        <v>0.2465187460184097</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.2574263513088226</v>
+        <v>0.2578244805335999</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.2819781005382538</v>
+        <v>0.2822791934013367</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.2825032770633698</v>
+        <v>0.2827942967414856</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.2720603048801422</v>
+        <v>0.2723480761051178</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.274514228105545</v>
+        <v>0.2747620940208435</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.2649913132190704</v>
+        <v>0.2653318643569946</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.2665762007236481</v>
+        <v>0.2668420374393463</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.2661234736442566</v>
+        <v>0.2665213644504547</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.2629014849662781</v>
+        <v>0.2632776200771332</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.2585301995277405</v>
+        <v>0.2588111758232117</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.2572287321090698</v>
+        <v>0.2575487494468689</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.2595072388648987</v>
+        <v>0.2598561346530914</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.2616986334323883</v>
+        <v>0.2620879709720612</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.2712508141994476</v>
+        <v>0.2718250751495361</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.2815452814102173</v>
+        <v>0.2820399403572083</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.2860642075538635</v>
+        <v>0.2864048779010773</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.286483108997345</v>
+        <v>0.2868222296237946</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.2785726487636566</v>
+        <v>0.2789211869239807</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.2765581011772156</v>
+        <v>0.2770764231681824</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.2819544672966003</v>
+        <v>0.2822731733322144</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.2795933187007904</v>
+        <v>0.2800259590148926</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.2797719836235046</v>
+        <v>0.2801548540592194</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.2777838408946991</v>
+        <v>0.2781893610954285</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.2795205414295197</v>
+        <v>0.2800170183181763</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.2799724638462067</v>
+        <v>0.280366837978363</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.2792787551879883</v>
+        <v>0.2797637581825256</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.2898177802562714</v>
+        <v>0.2905438244342804</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.2941237688064575</v>
+        <v>0.294764518737793</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.3085883855819702</v>
+        <v>0.3093151450157166</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.3014943897724152</v>
+        <v>0.3019087016582489</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.3019839227199554</v>
+        <v>0.3025695085525513</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.3030796349048615</v>
+        <v>0.3035298585891724</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.302986741065979</v>
+        <v>0.3034467995166779</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.3011429607868195</v>
+        <v>0.3016608953475952</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.2996999621391296</v>
+        <v>0.3001139461994171</v>
       </c>
       <c r="GH2" t="n">
-        <v>0.2959907054901123</v>
+        <v>0.2964869439601898</v>
       </c>
       <c r="GI2" t="n">
-        <v>0.296845018863678</v>
+        <v>0.2974066734313965</v>
       </c>
       <c r="GJ2" t="n">
-        <v>0.2970795631408691</v>
+        <v>0.2975610792636871</v>
       </c>
       <c r="GK2" t="n">
-        <v>0.3008785843849182</v>
+        <v>0.3014009296894073</v>
       </c>
       <c r="GL2" t="n">
-        <v>0.3073105812072754</v>
+        <v>0.3081745505332947</v>
       </c>
       <c r="GM2" t="n">
-        <v>0.313839465379715</v>
+        <v>0.3147276937961578</v>
       </c>
       <c r="GN2" t="n">
-        <v>0.3290679752826691</v>
+        <v>0.3299196660518646</v>
       </c>
       <c r="GO2" t="n">
-        <v>0.3366119861602783</v>
+        <v>0.3374396860599518</v>
       </c>
       <c r="GP2" t="n">
-        <v>0.3296506702899933</v>
+        <v>0.3302976787090302</v>
       </c>
       <c r="GQ2" t="n">
-        <v>0.3269298672676086</v>
+        <v>0.327569454908371</v>
       </c>
       <c r="GR2" t="n">
-        <v>0.3258111178874969</v>
+        <v>0.3264769613742828</v>
       </c>
       <c r="GS2" t="n">
-        <v>0.3241283595561981</v>
+        <v>0.324869692325592</v>
       </c>
       <c r="GT2" t="n">
-        <v>0.3255466222763062</v>
+        <v>0.326114296913147</v>
       </c>
       <c r="GU2" t="n">
-        <v>0.3198201060295105</v>
+        <v>0.3204239010810852</v>
       </c>
       <c r="GV2" t="n">
-        <v>0.3247559666633606</v>
+        <v>0.3255016207695007</v>
       </c>
       <c r="GW2" t="n">
-        <v>0.3198831379413605</v>
+        <v>0.3206013739109039</v>
       </c>
       <c r="GX2" t="n">
-        <v>0.3208977580070496</v>
+        <v>0.3215973079204559</v>
       </c>
       <c r="GY2" t="n">
-        <v>0.3210129737854004</v>
+        <v>0.3218244016170502</v>
       </c>
       <c r="GZ2" t="n">
-        <v>0.3342941999435425</v>
+        <v>0.3350946605205536</v>
       </c>
       <c r="HA2" t="n">
-        <v>0.3474116921424866</v>
+        <v>0.348188579082489</v>
       </c>
       <c r="HB2" t="n">
-        <v>0.3595235049724579</v>
+        <v>0.3604069948196411</v>
       </c>
       <c r="HC2" t="n">
-        <v>0.3544241189956665</v>
+        <v>0.3552491068840027</v>
       </c>
       <c r="HD2" t="n">
-        <v>0.3411827683448792</v>
+        <v>0.342313289642334</v>
       </c>
       <c r="HE2" t="n">
-        <v>0.3362759947776794</v>
+        <v>0.3376103043556213</v>
       </c>
       <c r="HF2" t="n">
-        <v>0.3378902673721313</v>
+        <v>0.3391501903533936</v>
       </c>
       <c r="HG2" t="n">
-        <v>0.3444583415985107</v>
+        <v>0.3455820679664612</v>
       </c>
       <c r="HH2" t="n">
-        <v>0.3430765271186829</v>
+        <v>0.3442666828632355</v>
       </c>
       <c r="HI2" t="n">
-        <v>0.3415817320346832</v>
+        <v>0.3425435125827789</v>
       </c>
       <c r="HJ2" t="n">
-        <v>0.3437683880329132</v>
+        <v>0.3449710607528687</v>
       </c>
       <c r="HK2" t="n">
-        <v>0.337588906288147</v>
+        <v>0.3386457860469818</v>
       </c>
       <c r="HL2" t="n">
-        <v>0.3392682373523712</v>
+        <v>0.3402526676654816</v>
       </c>
       <c r="HM2" t="n">
-        <v>0.3360185325145721</v>
+        <v>0.3371363580226898</v>
       </c>
       <c r="HN2" t="n">
-        <v>0.3593526184558868</v>
+        <v>0.360469788312912</v>
       </c>
       <c r="HO2" t="n">
-        <v>0.3735889196395874</v>
+        <v>0.3748536705970764</v>
       </c>
       <c r="HP2" t="n">
-        <v>0.3544758260250092</v>
+        <v>0.3554169535636902</v>
       </c>
       <c r="HQ2" t="n">
-        <v>0.3438026607036591</v>
+        <v>0.3445872962474823</v>
       </c>
       <c r="HR2" t="inlineStr">
         <is>
@@ -2239,676 +2239,676 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02356982044875622</v>
+        <v>0.02403732948005199</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03236067667603493</v>
+        <v>0.03268427401781082</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03444099053740501</v>
+        <v>0.03478318825364113</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03600599244236946</v>
+        <v>0.0363391749560833</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03652967512607574</v>
+        <v>0.0368516631424427</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03578683361411095</v>
+        <v>0.03617646172642708</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0352780818939209</v>
+        <v>0.03562355414032936</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03488162159919739</v>
+        <v>0.03527325391769409</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03509967774152756</v>
+        <v>0.03548981249332428</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03445563837885857</v>
+        <v>0.03482587262988091</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03351052850484848</v>
+        <v>0.03383027389645576</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03254895284771919</v>
+        <v>0.03286043927073479</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03247029334306717</v>
+        <v>0.0327799879014492</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0330176055431366</v>
+        <v>0.03336161747574806</v>
       </c>
       <c r="P3" t="n">
-        <v>0.04824197664856911</v>
+        <v>0.04881107434630394</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.05961787328124046</v>
+        <v>0.06010539084672928</v>
       </c>
       <c r="R3" t="n">
-        <v>0.06233206763863564</v>
+        <v>0.06281717866659164</v>
       </c>
       <c r="S3" t="n">
-        <v>0.06337681412696838</v>
+        <v>0.06386222690343857</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06451231241226196</v>
+        <v>0.06508798897266388</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06221060082316399</v>
+        <v>0.06282736361026764</v>
       </c>
       <c r="V3" t="n">
-        <v>0.06310483813285828</v>
+        <v>0.06366428732872009</v>
       </c>
       <c r="W3" t="n">
-        <v>0.06271903961896896</v>
+        <v>0.06323368847370148</v>
       </c>
       <c r="X3" t="n">
-        <v>0.06216609850525856</v>
+        <v>0.06268788874149323</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06173383817076683</v>
+        <v>0.06229023635387421</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.05877760797739029</v>
+        <v>0.05926084145903587</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.05650127679109573</v>
+        <v>0.05701804533600807</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.05633546411991119</v>
+        <v>0.05683641880750656</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.05771094560623169</v>
+        <v>0.05825904756784439</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.07964780181646347</v>
+        <v>0.08016257733106613</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.09142863005399704</v>
+        <v>0.09201079607009888</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09139027446508408</v>
+        <v>0.0920148566365242</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.09341365844011307</v>
+        <v>0.09412144124507904</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.09365074336528778</v>
+        <v>0.09435664117336273</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.09289241582155228</v>
+        <v>0.09371016174554825</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.08995084464550018</v>
+        <v>0.09062831103801727</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.08899909257888794</v>
+        <v>0.08969339728355408</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.08923257142305374</v>
+        <v>0.08994727581739426</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.08629298210144043</v>
+        <v>0.08697980642318726</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.08221833407878876</v>
+        <v>0.08285895735025406</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0802907794713974</v>
+        <v>0.08090165257453918</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.08236271888017654</v>
+        <v>0.08303867280483246</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.08306009322404861</v>
+        <v>0.08376628160476685</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.1084988564252853</v>
+        <v>0.1091116219758987</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.1154525876045227</v>
+        <v>0.1161142066121101</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.116157591342926</v>
+        <v>0.1169030070304871</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.1180304959416389</v>
+        <v>0.1186547726392746</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1157056540250778</v>
+        <v>0.1165369302034378</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1117540821433067</v>
+        <v>0.1124852672219276</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1121445894241333</v>
+        <v>0.1129644364118576</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.11134023219347</v>
+        <v>0.1121451631188393</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1098543703556061</v>
+        <v>0.110755480825901</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.106375478208065</v>
+        <v>0.1071450784802437</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.101964920759201</v>
+        <v>0.1025877892971039</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1001599803566933</v>
+        <v>0.1008946225047112</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.09886113554239273</v>
+        <v>0.09959989041090012</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.101855605840683</v>
+        <v>0.1026377305388451</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.136811375617981</v>
+        <v>0.1373291611671448</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.13868348300457</v>
+        <v>0.1394053548574448</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.1380697339773178</v>
+        <v>0.138910710811615</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.1346503049135208</v>
+        <v>0.1355936676263809</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.1347611099481583</v>
+        <v>0.1356372237205505</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.1286568641662598</v>
+        <v>0.1295625865459442</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.1283099949359894</v>
+        <v>0.1291055381298065</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.125779464840889</v>
+        <v>0.1265901476144791</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.1237799599766731</v>
+        <v>0.1247411295771599</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.1251563876867294</v>
+        <v>0.1260560601949692</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1172395050525665</v>
+        <v>0.1180353760719299</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.1167042851448059</v>
+        <v>0.1174057275056839</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1159291118383408</v>
+        <v>0.1167658567428589</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.1158457547426224</v>
+        <v>0.1166694164276123</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.1704429537057877</v>
+        <v>0.1715075224637985</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.1685802191495895</v>
+        <v>0.1696704924106598</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.1643417030572891</v>
+        <v>0.1655588746070862</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.164428174495697</v>
+        <v>0.1656283438205719</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.1627926677465439</v>
+        <v>0.1639087051153183</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.1587414145469666</v>
+        <v>0.1599232852458954</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.155005544424057</v>
+        <v>0.1561277061700821</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.1521640866994858</v>
+        <v>0.153268963098526</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.1502512246370316</v>
+        <v>0.1513223052024841</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.1463893949985504</v>
+        <v>0.1472853720188141</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.1428662836551666</v>
+        <v>0.1436840444803238</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.1361432820558548</v>
+        <v>0.1371039152145386</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.1363532841205597</v>
+        <v>0.1372312754392624</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.1394610404968262</v>
+        <v>0.1404612213373184</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.1961884498596191</v>
+        <v>0.1973127871751785</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.1937541961669922</v>
+        <v>0.1951549202203751</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.1909713596105576</v>
+        <v>0.1924537122249603</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.1873538792133331</v>
+        <v>0.1886332482099533</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.1838150173425674</v>
+        <v>0.1850346624851227</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.1770038157701492</v>
+        <v>0.1784699261188507</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.1779107004404068</v>
+        <v>0.1791473031044006</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1716274619102478</v>
+        <v>0.1728760898113251</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.1702072024345398</v>
+        <v>0.1713965833187103</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.1711686700582504</v>
+        <v>0.1722226589918137</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.158720463514328</v>
+        <v>0.1595985144376755</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.1562557965517044</v>
+        <v>0.1571419835090637</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.1562366187572479</v>
+        <v>0.1571822315454483</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.1622173190116882</v>
+        <v>0.1632937341928482</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.2312795221805573</v>
+        <v>0.2327416390180588</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.2184284776449203</v>
+        <v>0.2200867235660553</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.2186836749315262</v>
+        <v>0.2201635837554932</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.2169964462518692</v>
+        <v>0.2185530960559845</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.2079004645347595</v>
+        <v>0.2094584554433823</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.2045188844203949</v>
+        <v>0.2060793787240982</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.2052331864833832</v>
+        <v>0.2066149264574051</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.200932964682579</v>
+        <v>0.2022633105516434</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.2007467299699783</v>
+        <v>0.2018202096223831</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.195219412446022</v>
+        <v>0.1963387727737427</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.1897402405738831</v>
+        <v>0.190655991435051</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.1865984946489334</v>
+        <v>0.1876568645238876</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.1856058835983276</v>
+        <v>0.1865604370832443</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.1880999505519867</v>
+        <v>0.1891448944807053</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.2468264997005463</v>
+        <v>0.2487358301877975</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.2437136918306351</v>
+        <v>0.245670422911644</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.2360765486955643</v>
+        <v>0.2377710342407227</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.2345776855945587</v>
+        <v>0.2362193316221237</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.2278861254453659</v>
+        <v>0.2293724566698074</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.2292621731758118</v>
+        <v>0.2305524498224258</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.223708301782608</v>
+        <v>0.2248707562685013</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.2175873965024948</v>
+        <v>0.2189717888832092</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.2164195775985718</v>
+        <v>0.2175602465867996</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.2135752290487289</v>
+        <v>0.2147173285484314</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.2092009782791138</v>
+        <v>0.2101764231920242</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.2078943997621536</v>
+        <v>0.2089126855134964</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.2102096229791641</v>
+        <v>0.2111962735652924</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.2122473418712616</v>
+        <v>0.2132936418056488</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.2638189494609833</v>
+        <v>0.2656556963920593</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.2540492415428162</v>
+        <v>0.2558151483535767</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.25269415974617</v>
+        <v>0.2544072270393372</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.2458173036575317</v>
+        <v>0.2473454922437668</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.2453519701957703</v>
+        <v>0.2467721253633499</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.2395735085010529</v>
+        <v>0.2409675717353821</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.2370304614305496</v>
+        <v>0.2383812963962555</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.2357088476419449</v>
+        <v>0.2369942218065262</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.2335023581981659</v>
+        <v>0.2347601056098938</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.2317237257957458</v>
+        <v>0.2327508181333542</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.2197331041097641</v>
+        <v>0.220913365483284</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.2236415445804596</v>
+        <v>0.2246875315904617</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.2248123735189438</v>
+        <v>0.225895032286644</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.2263575345277786</v>
+        <v>0.2273672521114349</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.2746183574199677</v>
+        <v>0.2761739790439606</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.271519809961319</v>
+        <v>0.2731141149997711</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.2676354348659515</v>
+        <v>0.2690387070178986</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.2610218226909637</v>
+        <v>0.2624012231826782</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.2643932104110718</v>
+        <v>0.2656601071357727</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.2538490891456604</v>
+        <v>0.2549009025096893</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.2533486783504486</v>
+        <v>0.2544876039028168</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.2473917454481125</v>
+        <v>0.2485671937465668</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.2503543794155121</v>
+        <v>0.2515192925930023</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.2497120499610901</v>
+        <v>0.2508253455162048</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.2463282346725464</v>
+        <v>0.2473685592412949</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.2463233470916748</v>
+        <v>0.2473494112491608</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.2461711168289185</v>
+        <v>0.2472548186779022</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.2575215697288513</v>
+        <v>0.258689671754837</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.2822671830654144</v>
+        <v>0.2834113538265228</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.2827985882759094</v>
+        <v>0.2839338481426239</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.2723449170589447</v>
+        <v>0.2734110951423645</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.2747822105884552</v>
+        <v>0.2757968902587891</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.2652293741703033</v>
+        <v>0.2663017809391022</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.2667892277240753</v>
+        <v>0.2677897810935974</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.2663490474224091</v>
+        <v>0.267472892999649</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.2631063759326935</v>
+        <v>0.2642071545124054</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.2587307989597321</v>
+        <v>0.2597238719463348</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.2574256360530853</v>
+        <v>0.2584528923034668</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.2596495151519775</v>
+        <v>0.2607125043869019</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.2617558538913727</v>
+        <v>0.2627922892570496</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.2712878882884979</v>
+        <v>0.2725261151790619</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.2815710306167603</v>
+        <v>0.2827572822570801</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.2863399684429169</v>
+        <v>0.2875323891639709</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.2867196798324585</v>
+        <v>0.2878704071044922</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.2787830829620361</v>
+        <v>0.2799128293991089</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.276754230260849</v>
+        <v>0.2780460119247437</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.2821827232837677</v>
+        <v>0.2833132743835449</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.2797808945178986</v>
+        <v>0.2810271382331848</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.2799645364284515</v>
+        <v>0.2811840176582336</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.2779649198055267</v>
+        <v>0.2792185544967651</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.279674619436264</v>
+        <v>0.2810328602790833</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.2801230549812317</v>
+        <v>0.2813920676708221</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.2793348431587219</v>
+        <v>0.2806528806686401</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.2898004353046417</v>
+        <v>0.2913435101509094</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.2941381931304932</v>
+        <v>0.2956438660621643</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.308610588312149</v>
+        <v>0.3102382123470306</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.3017783164978027</v>
+        <v>0.3032962381839752</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.3022595643997192</v>
+        <v>0.3039712309837341</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.3033655285835266</v>
+        <v>0.3050023913383484</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.3032759428024292</v>
+        <v>0.3049361705780029</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.301395446062088</v>
+        <v>0.3030866086483002</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.2999404668807983</v>
+        <v>0.3015004396438599</v>
       </c>
       <c r="GH3" t="n">
-        <v>0.2961790859699249</v>
+        <v>0.2978169918060303</v>
       </c>
       <c r="GI3" t="n">
-        <v>0.2969030737876892</v>
+        <v>0.2985759675502777</v>
       </c>
       <c r="GJ3" t="n">
-        <v>0.2972484827041626</v>
+        <v>0.2988802492618561</v>
       </c>
       <c r="GK3" t="n">
-        <v>0.3010211586952209</v>
+        <v>0.3027134835720062</v>
       </c>
       <c r="GL3" t="n">
-        <v>0.307362973690033</v>
+        <v>0.3093658983707428</v>
       </c>
       <c r="GM3" t="n">
-        <v>0.3138299584388733</v>
+        <v>0.3158291876316071</v>
       </c>
       <c r="GN3" t="n">
-        <v>0.3290977478027344</v>
+        <v>0.3310709893703461</v>
       </c>
       <c r="GO3" t="n">
-        <v>0.3366938531398773</v>
+        <v>0.3387305736541748</v>
       </c>
       <c r="GP3" t="n">
-        <v>0.3298374712467194</v>
+        <v>0.3316564857959747</v>
       </c>
       <c r="GQ3" t="n">
-        <v>0.3270496726036072</v>
+        <v>0.3287949860095978</v>
       </c>
       <c r="GR3" t="n">
-        <v>0.3259600698947906</v>
+        <v>0.3277302086353302</v>
       </c>
       <c r="GS3" t="n">
-        <v>0.3242708444595337</v>
+        <v>0.3261200785636902</v>
       </c>
       <c r="GT3" t="n">
-        <v>0.3256890177726746</v>
+        <v>0.3274120986461639</v>
       </c>
       <c r="GU3" t="n">
-        <v>0.3199392557144165</v>
+        <v>0.3217029869556427</v>
       </c>
       <c r="GV3" t="n">
-        <v>0.3248919248580933</v>
+        <v>0.3268396556377411</v>
       </c>
       <c r="GW3" t="n">
-        <v>0.3200008571147919</v>
+        <v>0.3219266533851624</v>
       </c>
       <c r="GX3" t="n">
-        <v>0.3210278153419495</v>
+        <v>0.3229702711105347</v>
       </c>
       <c r="GY3" t="n">
-        <v>0.3211270272731781</v>
+        <v>0.3232180774211884</v>
       </c>
       <c r="GZ3" t="n">
-        <v>0.3344038128852844</v>
+        <v>0.3364500999450684</v>
       </c>
       <c r="HA3" t="n">
-        <v>0.3474842309951782</v>
+        <v>0.3494464159011841</v>
       </c>
       <c r="HB3" t="n">
-        <v>0.3596517443656921</v>
+        <v>0.3618084788322449</v>
       </c>
       <c r="HC3" t="n">
-        <v>0.354470431804657</v>
+        <v>0.3563204705715179</v>
       </c>
       <c r="HD3" t="n">
-        <v>0.3413346409797668</v>
+        <v>0.3439421355724335</v>
       </c>
       <c r="HE3" t="n">
-        <v>0.3364366590976715</v>
+        <v>0.3391879796981812</v>
       </c>
       <c r="HF3" t="n">
-        <v>0.3380496799945831</v>
+        <v>0.3407431840896606</v>
       </c>
       <c r="HG3" t="n">
-        <v>0.3446343243122101</v>
+        <v>0.3472293019294739</v>
       </c>
       <c r="HH3" t="n">
-        <v>0.3432871699333191</v>
+        <v>0.3459927439689636</v>
       </c>
       <c r="HI3" t="n">
-        <v>0.3418069779872894</v>
+        <v>0.3443102836608887</v>
       </c>
       <c r="HJ3" t="n">
-        <v>0.3440347909927368</v>
+        <v>0.3468121886253357</v>
       </c>
       <c r="HK3" t="n">
-        <v>0.3378585875034332</v>
+        <v>0.3405160307884216</v>
       </c>
       <c r="HL3" t="n">
-        <v>0.3395709991455078</v>
+        <v>0.342191606760025</v>
       </c>
       <c r="HM3" t="n">
-        <v>0.3363429307937622</v>
+        <v>0.3391364812850952</v>
       </c>
       <c r="HN3" t="n">
-        <v>0.3597000539302826</v>
+        <v>0.3623926937580109</v>
       </c>
       <c r="HO3" t="n">
-        <v>0.3738785982131958</v>
+        <v>0.3766745626926422</v>
       </c>
       <c r="HP3" t="n">
-        <v>0.3546977043151855</v>
+        <v>0.3568391799926758</v>
       </c>
       <c r="HQ3" t="n">
-        <v>0.3438787162303925</v>
+        <v>0.3455772697925568</v>
       </c>
       <c r="HR3" t="inlineStr">
         <is>
@@ -2923,676 +2923,676 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02394563890993595</v>
+        <v>0.02437747269868851</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0327497124671936</v>
+        <v>0.03307125717401505</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03482511639595032</v>
+        <v>0.03517702966928482</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0363810770213604</v>
+        <v>0.03673110157251358</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03688165172934532</v>
+        <v>0.03722700849175453</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03612060844898224</v>
+        <v>0.0365341454744339</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03559769690036774</v>
+        <v>0.03596702590584755</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03519939631223679</v>
+        <v>0.03561603650450706</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03541324660181999</v>
+        <v>0.03582786396145821</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03475847840309143</v>
+        <v>0.03515215590596199</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03378989920020103</v>
+        <v>0.03413248807191849</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03280447795987129</v>
+        <v>0.03313186764717102</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03272469341754913</v>
+        <v>0.03304930776357651</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0332709364593029</v>
+        <v>0.03362715616822243</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04883131384849548</v>
+        <v>0.04936326667666435</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06021417304873466</v>
+        <v>0.06071498245000839</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06294205784797668</v>
+        <v>0.0634593740105629</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06393706053495407</v>
+        <v>0.06446421146392822</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06507035344839096</v>
+        <v>0.06569310277700424</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06272225081920624</v>
+        <v>0.06338238716125488</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06360291689634323</v>
+        <v>0.06420854479074478</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06319817155599594</v>
+        <v>0.0637550950050354</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06264206022024155</v>
+        <v>0.06320900470018387</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06219096854329109</v>
+        <v>0.06279194355010986</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05919323116540909</v>
+        <v>0.0597161203622818</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05689595267176628</v>
+        <v>0.0574403740465641</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05673487484455109</v>
+        <v>0.0572635792195797</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.05810520425438881</v>
+        <v>0.05867672339081764</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0803704634308815</v>
+        <v>0.08087998628616333</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.09217942506074905</v>
+        <v>0.09281545132398605</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.09215086698532104</v>
+        <v>0.09284943342208862</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.09409867972135544</v>
+        <v>0.09488745033740997</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0943300724029541</v>
+        <v>0.09511441737413406</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0935453325510025</v>
+        <v>0.09443804621696472</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.09056121855974197</v>
+        <v>0.09130918234586716</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.08958420157432556</v>
+        <v>0.09034091234207153</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.08982016146183014</v>
+        <v>0.0906023234128952</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0868537425994873</v>
+        <v>0.08760269731283188</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.08271332085132599</v>
+        <v>0.08340112864971161</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.08077213168144226</v>
+        <v>0.08142030239105225</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.08286554366350174</v>
+        <v>0.08357953280210495</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.08355006575584412</v>
+        <v>0.08428891003131866</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.1093281507492065</v>
+        <v>0.1099750846624374</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.1163316443562508</v>
+        <v>0.1170998513698578</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.1169899702072144</v>
+        <v>0.1178495362401009</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.1187597438693047</v>
+        <v>0.1194950938224792</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.1165250986814499</v>
+        <v>0.1174563467502594</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.1124597862362862</v>
+        <v>0.1132811009883881</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1128479242324829</v>
+        <v>0.1137536913156509</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.1120140925049782</v>
+        <v>0.1128963157534599</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.1105199530720711</v>
+        <v>0.1115022897720337</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.1069999560713768</v>
+        <v>0.1078397408127785</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.1025133579969406</v>
+        <v>0.1031942218542099</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.1007077842950821</v>
+        <v>0.101487822830677</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.09941622614860535</v>
+        <v>0.1001950055360794</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.1024082601070404</v>
+        <v>0.1032266840338707</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.137694463133812</v>
+        <v>0.1383228600025177</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.1396339386701584</v>
+        <v>0.140497624874115</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.138957679271698</v>
+        <v>0.1399353593587875</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.1354747861623764</v>
+        <v>0.1365563720464706</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.1356323212385178</v>
+        <v>0.1366278380155563</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.1294441521167755</v>
+        <v>0.1304530501365662</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.1290381997823715</v>
+        <v>0.1299313604831696</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.1265012472867966</v>
+        <v>0.1273974478244781</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.1244851872324944</v>
+        <v>0.1255345940589905</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.1258282959461212</v>
+        <v>0.1268115490674973</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.1178323030471802</v>
+        <v>0.1186889708042145</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.1172958761453629</v>
+        <v>0.1180447265505791</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.1165281608700752</v>
+        <v>0.1174065470695496</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.1164309680461884</v>
+        <v>0.1172870397567749</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.1716983616352081</v>
+        <v>0.1729487329721451</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.1697773635387421</v>
+        <v>0.1710714995861053</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1655314415693283</v>
+        <v>0.1669260263442993</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.165491059422493</v>
+        <v>0.1668651849031448</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.163776621222496</v>
+        <v>0.1650345176458359</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.1597098708152771</v>
+        <v>0.1610164195299149</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.155891552567482</v>
+        <v>0.1571286767721176</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.1530229598283768</v>
+        <v>0.154232993721962</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.1510629057884216</v>
+        <v>0.1522310972213745</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.1471433937549591</v>
+        <v>0.148128017783165</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.1435554027557373</v>
+        <v>0.144443467259407</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.1367936581373215</v>
+        <v>0.1377998888492584</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.1370059996843338</v>
+        <v>0.1379229873418808</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.1401228457689285</v>
+        <v>0.1411560922861099</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.1974989473819733</v>
+        <v>0.1988352686166763</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.1951154470443726</v>
+        <v>0.1967368870973587</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.1922544687986374</v>
+        <v>0.1939200311899185</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.1884935200214386</v>
+        <v>0.1899362653493881</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.1849348694086075</v>
+        <v>0.1863023340702057</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.1780509054660797</v>
+        <v>0.1796433329582214</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.178895890712738</v>
+        <v>0.1802505105733871</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.1725539714097977</v>
+        <v>0.1739073246717453</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.1710834801197052</v>
+        <v>0.1723753809928894</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.1719836294651031</v>
+        <v>0.1731348931789398</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.159444123506546</v>
+        <v>0.1603864133358002</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.1569515466690063</v>
+        <v>0.1578785181045532</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.1569183468818665</v>
+        <v>0.1578940600156784</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.1629364639520645</v>
+        <v>0.1640408039093018</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.2326499074697495</v>
+        <v>0.2343118190765381</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.2198592275381088</v>
+        <v>0.2217081487178802</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.2199716120958328</v>
+        <v>0.2216228991746902</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.2182745337486267</v>
+        <v>0.2199796438217163</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.2090682834386826</v>
+        <v>0.2107603996992111</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.2056247591972351</v>
+        <v>0.2073090225458145</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.206276535987854</v>
+        <v>0.2077720314264297</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.2018646597862244</v>
+        <v>0.2032981067895889</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.2016579508781433</v>
+        <v>0.2028147280216217</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.1960762441158295</v>
+        <v>0.1972729116678238</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.1905064582824707</v>
+        <v>0.1914772838354111</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.1873297095298767</v>
+        <v>0.188427746295929</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.1863071918487549</v>
+        <v>0.1872883886098862</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.1888185739517212</v>
+        <v>0.1898732930421829</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.2484059035778046</v>
+        <v>0.2504976689815521</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.2451649159193039</v>
+        <v>0.2472755759954453</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.2373741269111633</v>
+        <v>0.2392150163650513</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.2358291000127792</v>
+        <v>0.2376093864440918</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.2290656715631485</v>
+        <v>0.2306723296642303</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.2303103059530258</v>
+        <v>0.2317129075527191</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.2246814370155334</v>
+        <v>0.225933626294136</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.2185119539499283</v>
+        <v>0.2199755907058716</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.2173043638467789</v>
+        <v>0.2185096889734268</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2144099324941635</v>
+        <v>0.2156016528606415</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.2099577039480209</v>
+        <v>0.2109702676534653</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.2085476219654083</v>
+        <v>0.209589958190918</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.210912749171257</v>
+        <v>0.2119111269712448</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.2129449844360352</v>
+        <v>0.2139839679002762</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.2652561664581299</v>
+        <v>0.2672398686408997</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.2553802728652954</v>
+        <v>0.2572857141494751</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.2540068030357361</v>
+        <v>0.2558490335941315</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.2469412237405777</v>
+        <v>0.2485837787389755</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.2464073151350021</v>
+        <v>0.2479168027639389</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.2405737191438675</v>
+        <v>0.2420514076948166</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.2379740476608276</v>
+        <v>0.2393912225961685</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.2366058677434921</v>
+        <v>0.2379436641931534</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.2343402504920959</v>
+        <v>0.2356540709733963</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.232523500919342</v>
+        <v>0.2335969805717468</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.2204901874065399</v>
+        <v>0.2216816991567612</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.2243301570415497</v>
+        <v>0.2253722250461578</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.2254508882761002</v>
+        <v>0.2265103459358215</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.2270293235778809</v>
+        <v>0.2280198335647583</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.2758232057094574</v>
+        <v>0.2774821817874908</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.2726278603076935</v>
+        <v>0.2742945551872253</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.2686693966388702</v>
+        <v>0.2701353132724762</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.2619633376598358</v>
+        <v>0.2633942663669586</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.2652927339076996</v>
+        <v>0.2666073143482208</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.2546790838241577</v>
+        <v>0.2557661235332489</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.254231870174408</v>
+        <v>0.2554018199443817</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.2482078969478607</v>
+        <v>0.2493857145309448</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.2511194050312042</v>
+        <v>0.2522963583469391</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.2504294514656067</v>
+        <v>0.2515408992767334</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.2470272928476334</v>
+        <v>0.2480570822954178</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.2469601184129715</v>
+        <v>0.2479637265205383</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.24677474796772</v>
+        <v>0.2478193044662476</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.258213073015213</v>
+        <v>0.259325236082077</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.2830227911472321</v>
+        <v>0.2841792404651642</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.2835632860660553</v>
+        <v>0.2847025394439697</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.2730596959590912</v>
+        <v>0.2741288244724274</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.2754947543144226</v>
+        <v>0.2765059769153595</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.2659097611904144</v>
+        <v>0.2669718265533447</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.2674726247787476</v>
+        <v>0.2684570848941803</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.2670277655124664</v>
+        <v>0.268137127161026</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.2637810707092285</v>
+        <v>0.2648625671863556</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.259392112493515</v>
+        <v>0.2603660225868225</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.2580812573432922</v>
+        <v>0.2590891718864441</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.2603063583374023</v>
+        <v>0.2613368332386017</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.2623505890369415</v>
+        <v>0.2633356750011444</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.2719025909900665</v>
+        <v>0.2730752527713776</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.2822113633155823</v>
+        <v>0.2833245694637299</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.2871378660202026</v>
+        <v>0.288307398557663</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.287478893995285</v>
+        <v>0.2886003851890564</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.2795101702213287</v>
+        <v>0.2806093692779541</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.2774804532527924</v>
+        <v>0.2787407636642456</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.2829373478889465</v>
+        <v>0.2840398848056793</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.2805353105068207</v>
+        <v>0.2817472517490387</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.2807340621948242</v>
+        <v>0.2819203734397888</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.2787415087223053</v>
+        <v>0.2799591422080994</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.2804619073867798</v>
+        <v>0.2817789912223816</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.2809197604656219</v>
+        <v>0.2821460068225861</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.2800886034965515</v>
+        <v>0.2813436985015869</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.2905339598655701</v>
+        <v>0.2919933795928955</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.2949193716049194</v>
+        <v>0.2963405251502991</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.3094187080860138</v>
+        <v>0.3109511435031891</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.3027839064598083</v>
+        <v>0.3042809069156647</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.3032852411270142</v>
+        <v>0.3049757182598114</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.3044368922710419</v>
+        <v>0.3060508668422699</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.3043600916862488</v>
+        <v>0.3059982061386108</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.3024542331695557</v>
+        <v>0.3041191399097443</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.3009785711765289</v>
+        <v>0.3025106489658356</v>
       </c>
       <c r="GH4" t="n">
-        <v>0.2972011864185333</v>
+        <v>0.2988065183162689</v>
       </c>
       <c r="GI4" t="n">
-        <v>0.2978901863098145</v>
+        <v>0.2995027899742126</v>
       </c>
       <c r="GJ4" t="n">
-        <v>0.2982824444770813</v>
+        <v>0.2998694479465485</v>
       </c>
       <c r="GK4" t="n">
-        <v>0.3020704984664917</v>
+        <v>0.3037088513374329</v>
       </c>
       <c r="GL4" t="n">
-        <v>0.3083773255348206</v>
+        <v>0.3102984130382538</v>
       </c>
       <c r="GM4" t="n">
-        <v>0.3148122727870941</v>
+        <v>0.316702276468277</v>
       </c>
       <c r="GN4" t="n">
-        <v>0.3301123678684235</v>
+        <v>0.3319770991802216</v>
       </c>
       <c r="GO4" t="n">
-        <v>0.3377872407436371</v>
+        <v>0.3397187888622284</v>
       </c>
       <c r="GP4" t="n">
-        <v>0.3309043645858765</v>
+        <v>0.3326640129089355</v>
       </c>
       <c r="GQ4" t="n">
-        <v>0.3280567526817322</v>
+        <v>0.3297248184680939</v>
       </c>
       <c r="GR4" t="n">
-        <v>0.3269637227058411</v>
+        <v>0.3286796808242798</v>
       </c>
       <c r="GS4" t="n">
-        <v>0.3252829611301422</v>
+        <v>0.3270716667175293</v>
       </c>
       <c r="GT4" t="n">
-        <v>0.3267376124858856</v>
+        <v>0.3283929824829102</v>
       </c>
       <c r="GU4" t="n">
-        <v>0.3209889233112335</v>
+        <v>0.3226777613162994</v>
       </c>
       <c r="GV4" t="n">
-        <v>0.3259848654270172</v>
+        <v>0.3278586566448212</v>
       </c>
       <c r="GW4" t="n">
-        <v>0.3210977911949158</v>
+        <v>0.3229389488697052</v>
       </c>
       <c r="GX4" t="n">
-        <v>0.3221595287322998</v>
+        <v>0.3240161538124084</v>
       </c>
       <c r="GY4" t="n">
-        <v>0.3222863674163818</v>
+        <v>0.3242860436439514</v>
       </c>
       <c r="GZ4" t="n">
-        <v>0.3355480134487152</v>
+        <v>0.3374823331832886</v>
       </c>
       <c r="HA4" t="n">
-        <v>0.348567932844162</v>
+        <v>0.3504157960414886</v>
       </c>
       <c r="HB4" t="n">
-        <v>0.3608429133892059</v>
+        <v>0.3628747165203094</v>
       </c>
       <c r="HC4" t="n">
-        <v>0.3554200828075409</v>
+        <v>0.3571552932262421</v>
       </c>
       <c r="HD4" t="n">
-        <v>0.3427410125732422</v>
+        <v>0.3451950252056122</v>
       </c>
       <c r="HE4" t="n">
-        <v>0.3377911448478699</v>
+        <v>0.3403863608837128</v>
       </c>
       <c r="HF4" t="n">
-        <v>0.3394082188606262</v>
+        <v>0.3419497311115265</v>
       </c>
       <c r="HG4" t="n">
-        <v>0.3460340797901154</v>
+        <v>0.3484822511672974</v>
       </c>
       <c r="HH4" t="n">
-        <v>0.3447336554527283</v>
+        <v>0.3472996950149536</v>
       </c>
       <c r="HI4" t="n">
-        <v>0.3432798683643341</v>
+        <v>0.3456459045410156</v>
       </c>
       <c r="HJ4" t="n">
-        <v>0.3455453813076019</v>
+        <v>0.3481964766979218</v>
       </c>
       <c r="HK4" t="n">
-        <v>0.3393853306770325</v>
+        <v>0.3419178128242493</v>
       </c>
       <c r="HL4" t="n">
-        <v>0.3411300480365753</v>
+        <v>0.3436370193958282</v>
       </c>
       <c r="HM4" t="n">
-        <v>0.3379263579845428</v>
+        <v>0.3406157791614532</v>
       </c>
       <c r="HN4" t="n">
-        <v>0.3612522482872009</v>
+        <v>0.3638312220573425</v>
       </c>
       <c r="HO4" t="n">
-        <v>0.37541663646698</v>
+        <v>0.3780695796012878</v>
       </c>
       <c r="HP4" t="n">
-        <v>0.3558698296546936</v>
+        <v>0.3578898012638092</v>
       </c>
       <c r="HQ4" t="n">
-        <v>0.3447541892528534</v>
+        <v>0.3463295698165894</v>
       </c>
       <c r="HR4" t="inlineStr">
         <is>
@@ -3607,676 +3607,676 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02428161539137363</v>
+        <v>0.02473416738212109</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03307140618562698</v>
+        <v>0.03344912454485893</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03513837233185768</v>
+        <v>0.03554841503500938</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03668710589408875</v>
+        <v>0.03709152340888977</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0371687114238739</v>
+        <v>0.0375659316778183</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0363958515226841</v>
+        <v>0.03685624152421951</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03586520254611969</v>
+        <v>0.03627607971429825</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03546717762947083</v>
+        <v>0.0359247662127018</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03567960485816002</v>
+        <v>0.0361330658197403</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03501757234334946</v>
+        <v>0.03544800356030464</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03403256461024284</v>
+        <v>0.03440780192613602</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03302906081080437</v>
+        <v>0.03338329493999481</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0329495370388031</v>
+        <v>0.03330028429627419</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03349742293357849</v>
+        <v>0.03387780487537384</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04932667687535286</v>
+        <v>0.04992398992180824</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06069430708885193</v>
+        <v>0.06129185110330582</v>
       </c>
       <c r="R5" t="n">
-        <v>0.06343423575162888</v>
+        <v>0.06404826045036316</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06439146399497986</v>
+        <v>0.06500336527824402</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06552542001008987</v>
+        <v>0.06623104214668274</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06314390897750854</v>
+        <v>0.06387736648321152</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06401883810758591</v>
+        <v>0.06469281017780304</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06360320001840591</v>
+        <v>0.06422294676303864</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06304826587438583</v>
+        <v>0.06367694586515427</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06258271634578705</v>
+        <v>0.06324388086795807</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05955564230680466</v>
+        <v>0.06013048067688942</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05724482238292694</v>
+        <v>0.05783383920788765</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.05709048360586166</v>
+        <v>0.05766372010111809</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.05845773220062256</v>
+        <v>0.05907176062464714</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0809459388256073</v>
+        <v>0.08157885819673538</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.09276671707630157</v>
+        <v>0.09353896230459213</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.09275485575199127</v>
+        <v>0.09358442574739456</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.09464776515960693</v>
+        <v>0.09555031359195709</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.09488420933485031</v>
+        <v>0.09577368199825287</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.09408487379550934</v>
+        <v>0.09507549554109573</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.09107310324907303</v>
+        <v>0.09190917015075684</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.09008074551820755</v>
+        <v>0.09091836214065552</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.09032281488180161</v>
+        <v>0.09118611365556717</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0873359814286232</v>
+        <v>0.08816232532262802</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.08314549922943115</v>
+        <v>0.08389639854431152</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.08120071142911911</v>
+        <v>0.08190590888261795</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.08331596851348877</v>
+        <v>0.08408883213996887</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.08399307727813721</v>
+        <v>0.0847870409488678</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.1099630072712898</v>
+        <v>0.1107722297310829</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.1170190721750259</v>
+        <v>0.1179482862353325</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.1176512986421585</v>
+        <v>0.1186547875404358</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1193445920944214</v>
+        <v>0.1202028170228004</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.1172000244259834</v>
+        <v>0.1182567328214645</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1130488738417625</v>
+        <v>0.113974504172802</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1134415939450264</v>
+        <v>0.1144487261772156</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.112589955329895</v>
+        <v>0.113565981388092</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.1110932901501656</v>
+        <v>0.1121683791279793</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.1075406447052956</v>
+        <v>0.1084655001759529</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.1029949709773064</v>
+        <v>0.1037489995360374</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.1011980846524239</v>
+        <v>0.1020455956459045</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0999150350689888</v>
+        <v>0.1007595285773277</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.1029106825590134</v>
+        <v>0.103792130947113</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.1383553892374039</v>
+        <v>0.1391679793596268</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.1403771340847015</v>
+        <v>0.141414687037468</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.1396708339452744</v>
+        <v>0.1407982409000397</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.1361535936594009</v>
+        <v>0.1373686343431473</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.1363601386547089</v>
+        <v>0.1374889612197876</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.1301098018884659</v>
+        <v>0.1312342286109924</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.1296607255935669</v>
+        <v>0.1306593120098114</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1271238178014755</v>
+        <v>0.1281212717294693</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.1250986009836197</v>
+        <v>0.1262461990118027</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.1264154464006424</v>
+        <v>0.1274926364421844</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1183575242757797</v>
+        <v>0.1192925646901131</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.1178278401494026</v>
+        <v>0.1186501309275627</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.1170707494020462</v>
+        <v>0.1180192083120346</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.1169656589627266</v>
+        <v>0.117886133491993</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.1726778298616409</v>
+        <v>0.1741604059934616</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.1707437783479691</v>
+        <v>0.1722528636455536</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1665240079164505</v>
+        <v>0.1681053787469864</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.1663969457149506</v>
+        <v>0.1679314523935318</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.1646133363246918</v>
+        <v>0.1660197824239731</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.1605410128831863</v>
+        <v>0.161988765001297</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.1566629558801651</v>
+        <v>0.1580227315425873</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.1537734568119049</v>
+        <v>0.1551034599542618</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.1517744362354279</v>
+        <v>0.1530550420284271</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.1478072702884674</v>
+        <v>0.1488942056894302</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.1441709250211716</v>
+        <v>0.1451496332883835</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1373832821846008</v>
+        <v>0.1384663432836533</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.1376007348299026</v>
+        <v>0.1385905742645264</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.1407306045293808</v>
+        <v>0.1418365836143494</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.1985745280981064</v>
+        <v>0.2001295834779739</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.1962727010250092</v>
+        <v>0.1981050968170166</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.1933558136224747</v>
+        <v>0.1952085345983505</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.189483255147934</v>
+        <v>0.1910886317491531</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.1859126538038254</v>
+        <v>0.187435582280159</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.1789685189723969</v>
+        <v>0.1807045042514801</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.17976213991642</v>
+        <v>0.1812525242567062</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.1733727753162384</v>
+        <v>0.1748516857624054</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.1718649864196777</v>
+        <v>0.1732723116874695</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.1727131605148315</v>
+        <v>0.173972561955452</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.1600938737392426</v>
+        <v>0.161129042506218</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.1575878858566284</v>
+        <v>0.1585945039987564</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.1575438380241394</v>
+        <v>0.1585931330919266</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.1636014878749847</v>
+        <v>0.164780855178833</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.2338492423295975</v>
+        <v>0.2357019484043121</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.2211229056119919</v>
+        <v>0.2231611460447311</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.2211014330387115</v>
+        <v>0.2229320853948593</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.2193984985351562</v>
+        <v>0.2212783396244049</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.2101068645715714</v>
+        <v>0.2119531631469727</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.2066126614809036</v>
+        <v>0.2084413319826126</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.2072108387947083</v>
+        <v>0.2088407427072525</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.202703669667244</v>
+        <v>0.2042566388845444</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.2024746686220169</v>
+        <v>0.2037457376718521</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.1968444734811783</v>
+        <v>0.1981510818004608</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.1912022680044174</v>
+        <v>0.192267507314682</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.1880062073469162</v>
+        <v>0.1891844570636749</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.1869572550058365</v>
+        <v>0.1880124807357788</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1894911229610443</v>
+        <v>0.1906141638755798</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.2498011738061905</v>
+        <v>0.252103328704834</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.2464492917060852</v>
+        <v>0.2487515360116959</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.2385351806879044</v>
+        <v>0.2405418306589127</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.2369461953639984</v>
+        <v>0.2388899475336075</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.2301236838102341</v>
+        <v>0.2318812757730484</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.2312591820955276</v>
+        <v>0.2327946871519089</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.2255589216947556</v>
+        <v>0.2269324511289597</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.2193460911512375</v>
+        <v>0.2209241986274719</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.2181019186973572</v>
+        <v>0.2194149494171143</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.2151637375354767</v>
+        <v>0.2164526730775833</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.2106511145830154</v>
+        <v>0.2117479145526886</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.2091563940048218</v>
+        <v>0.2102702707052231</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.2115691900253296</v>
+        <v>0.212636724114418</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.2136063575744629</v>
+        <v>0.2147048860788345</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.2665410339832306</v>
+        <v>0.2687053978443146</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.2565713822841644</v>
+        <v>0.2586471438407898</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.2551817297935486</v>
+        <v>0.2571910321712494</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.2479544281959534</v>
+        <v>0.249737948179245</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.247359499335289</v>
+        <v>0.2489961385726929</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.2414768934249878</v>
+        <v>0.2430773675441742</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.2388252913951874</v>
+        <v>0.2403547018766403</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.2374171614646912</v>
+        <v>0.2388584613800049</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.235098123550415</v>
+        <v>0.2365140914916992</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.2332528680562973</v>
+        <v>0.2344180643558502</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.2211922109127045</v>
+        <v>0.2224546819925308</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.2249737977981567</v>
+        <v>0.2260747849941254</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.2260561138391495</v>
+        <v>0.2271648645401001</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.2276663184165955</v>
+        <v>0.2287115007638931</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.2769182026386261</v>
+        <v>0.2787213325500488</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.2736349999904633</v>
+        <v>0.2754302620887756</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.2696051299571991</v>
+        <v>0.2711918652057648</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.2628173530101776</v>
+        <v>0.2643576860427856</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.2661106884479523</v>
+        <v>0.2675284445285797</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.2554362416267395</v>
+        <v>0.25661501288414</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.2550332844257355</v>
+        <v>0.2562940120697021</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.2489573508501053</v>
+        <v>0.2502081990242004</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.2518178522586823</v>
+        <v>0.2530697584152222</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.2510943710803986</v>
+        <v>0.2522704601287842</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.2476777136325836</v>
+        <v>0.2487702369689941</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.2475534528493881</v>
+        <v>0.248612642288208</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.2473466992378235</v>
+        <v>0.2484367936849594</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.2588701546192169</v>
+        <v>0.2600228786468506</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.2837186455726624</v>
+        <v>0.2849516868591309</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.2842648327350616</v>
+        <v>0.2854773104190826</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.2737100720405579</v>
+        <v>0.2748509645462036</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.2761415243148804</v>
+        <v>0.277224063873291</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.2665295302867889</v>
+        <v>0.267656534910202</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.2680985033512115</v>
+        <v>0.269146203994751</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.2676447033882141</v>
+        <v>0.2688190042972565</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.2643986940383911</v>
+        <v>0.2655416429042816</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.2599974274635315</v>
+        <v>0.261031299829483</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.2586829960346222</v>
+        <v>0.259748786687851</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.2609168589115143</v>
+        <v>0.2619999051094055</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.2629130184650421</v>
+        <v>0.263938695192337</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.2724821269512177</v>
+        <v>0.273695319890976</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.2828178703784943</v>
+        <v>0.283971756696701</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.2878608405590057</v>
+        <v>0.2891016602516174</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.2881698906421661</v>
+        <v>0.2893572449684143</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.2801757156848907</v>
+        <v>0.2813360989093781</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.2781451940536499</v>
+        <v>0.2794694304466248</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.2836282849311829</v>
+        <v>0.2847943305969238</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.2812299728393555</v>
+        <v>0.2825057208538055</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.2814462780952454</v>
+        <v>0.2826947569847107</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.2794629037380219</v>
+        <v>0.2807413041591644</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.2811989486217499</v>
+        <v>0.2825755774974823</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.2816669344902039</v>
+        <v>0.2829520404338837</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.2808065116405487</v>
+        <v>0.2821106910705566</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.2912438213825226</v>
+        <v>0.2927423715591431</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.29566890001297</v>
+        <v>0.2971332669258118</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.3101947009563446</v>
+        <v>0.3117667734622955</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.3037173748016357</v>
+        <v>0.3053008317947388</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.3042398691177368</v>
+        <v>0.3060196936130524</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.3054376542568207</v>
+        <v>0.3071396350860596</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.3053730428218842</v>
+        <v>0.3071007132530212</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.3034473061561584</v>
+        <v>0.3051992356777191</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.3019521534442902</v>
+        <v>0.3035702705383301</v>
       </c>
       <c r="GH5" t="n">
-        <v>0.2981713116168976</v>
+        <v>0.2998573482036591</v>
       </c>
       <c r="GI5" t="n">
-        <v>0.2988467812538147</v>
+        <v>0.3005275130271912</v>
       </c>
       <c r="GJ5" t="n">
-        <v>0.2992630898952484</v>
+        <v>0.3009275496006012</v>
       </c>
       <c r="GK5" t="n">
-        <v>0.3030703365802765</v>
+        <v>0.3047831356525421</v>
       </c>
       <c r="GL5" t="n">
-        <v>0.3093530833721161</v>
+        <v>0.3113350868225098</v>
       </c>
       <c r="GM5" t="n">
-        <v>0.3157668113708496</v>
+        <v>0.3177025020122528</v>
       </c>
       <c r="GN5" t="n">
-        <v>0.3310856819152832</v>
+        <v>0.333007425069809</v>
       </c>
       <c r="GO5" t="n">
-        <v>0.3388350903987885</v>
+        <v>0.3408304154872894</v>
       </c>
       <c r="GP5" t="n">
-        <v>0.3319146335124969</v>
+        <v>0.3337565362453461</v>
       </c>
       <c r="GQ5" t="n">
-        <v>0.3290154039859772</v>
+        <v>0.3307534456253052</v>
       </c>
       <c r="GR5" t="n">
-        <v>0.3279182314872742</v>
+        <v>0.3297140300273895</v>
       </c>
       <c r="GS5" t="n">
-        <v>0.3262442946434021</v>
+        <v>0.3281110823154449</v>
       </c>
       <c r="GT5" t="n">
-        <v>0.3277364075183868</v>
+        <v>0.3294674456119537</v>
       </c>
       <c r="GU5" t="n">
-        <v>0.3219917118549347</v>
+        <v>0.3237526416778564</v>
       </c>
       <c r="GV5" t="n">
-        <v>0.3270249664783478</v>
+        <v>0.3289768099784851</v>
       </c>
       <c r="GW5" t="n">
-        <v>0.3221427798271179</v>
+        <v>0.324056476354599</v>
       </c>
       <c r="GX5" t="n">
-        <v>0.3232372105121613</v>
+        <v>0.3251681327819824</v>
       </c>
       <c r="GY5" t="n">
-        <v>0.323392391204834</v>
+        <v>0.3254671990871429</v>
       </c>
       <c r="GZ5" t="n">
-        <v>0.3366337716579437</v>
+        <v>0.3386397957801819</v>
       </c>
       <c r="HA5" t="n">
-        <v>0.3496101498603821</v>
+        <v>0.3515212833881378</v>
       </c>
       <c r="HB5" t="n">
-        <v>0.3619756400585175</v>
+        <v>0.3640884757041931</v>
       </c>
       <c r="HC5" t="n">
-        <v>0.3563317656517029</v>
+        <v>0.3581221997737885</v>
       </c>
       <c r="HD5" t="n">
-        <v>0.3440744280815125</v>
+        <v>0.346624881029129</v>
       </c>
       <c r="HE5" t="n">
-        <v>0.3390648066997528</v>
+        <v>0.3417508900165558</v>
       </c>
       <c r="HF5" t="n">
-        <v>0.3406940400600433</v>
+        <v>0.3433244228363037</v>
       </c>
       <c r="HG5" t="n">
-        <v>0.3473596572875977</v>
+        <v>0.3499058187007904</v>
       </c>
       <c r="HH5" t="n">
-        <v>0.3460998237133026</v>
+        <v>0.348772406578064</v>
       </c>
       <c r="HI5" t="n">
-        <v>0.3446686565876007</v>
+        <v>0.3471459448337555</v>
       </c>
       <c r="HJ5" t="n">
-        <v>0.3469666540622711</v>
+        <v>0.3497397899627686</v>
       </c>
       <c r="HK5" t="n">
-        <v>0.3408218026161194</v>
+        <v>0.3434745967388153</v>
       </c>
       <c r="HL5" t="n">
-        <v>0.3425973057746887</v>
+        <v>0.345231294631958</v>
       </c>
       <c r="HM5" t="n">
-        <v>0.3394147753715515</v>
+        <v>0.3422352373600006</v>
       </c>
       <c r="HN5" t="n">
-        <v>0.3627010583877563</v>
+        <v>0.3654313385486603</v>
       </c>
       <c r="HO5" t="n">
-        <v>0.3768674433231354</v>
+        <v>0.3796762526035309</v>
       </c>
       <c r="HP5" t="n">
-        <v>0.3569578528404236</v>
+        <v>0.3590726554393768</v>
       </c>
       <c r="HQ5" t="n">
-        <v>0.3455815315246582</v>
+        <v>0.3472073376178741</v>
       </c>
       <c r="HR5" t="inlineStr">
         <is>
@@ -4291,676 +4291,676 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02460830099880695</v>
+        <v>0.02517016418278217</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03341932967305183</v>
+        <v>0.03390558436512947</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03547793254256248</v>
+        <v>0.03599368408322334</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03701359033584595</v>
+        <v>0.03752031922340393</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03747750818729401</v>
+        <v>0.03797036409378052</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03668248280882835</v>
+        <v>0.03723613545298576</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03613289818167686</v>
+        <v>0.03663570806384087</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03572870045900345</v>
+        <v>0.03628024458885193</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03593254834413528</v>
+        <v>0.03648054972290993</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03525543957948685</v>
+        <v>0.03578010573983192</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03424514457583427</v>
+        <v>0.03471121564507484</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0332060419023037</v>
+        <v>0.03364787623286247</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03312124684453011</v>
+        <v>0.03356094658374786</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03365932404994965</v>
+        <v>0.03413160145282745</v>
       </c>
       <c r="P6" t="n">
-        <v>0.04981780797243118</v>
+        <v>0.05059100314974785</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.06123539432883263</v>
+        <v>0.06199342012405396</v>
       </c>
       <c r="R6" t="n">
-        <v>0.06398546695709229</v>
+        <v>0.06476205587387085</v>
       </c>
       <c r="S6" t="n">
-        <v>0.06489376723766327</v>
+        <v>0.06565424054861069</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06601506471633911</v>
+        <v>0.06687222421169281</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06357222050428391</v>
+        <v>0.06445269286632538</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06443902105093002</v>
+        <v>0.06525736302137375</v>
       </c>
       <c r="W6" t="n">
-        <v>0.06398611515760422</v>
+        <v>0.06475250422954559</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06343159079551697</v>
+        <v>0.06420790404081345</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0629454180598259</v>
+        <v>0.0637521892786026</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.05987302586436272</v>
+        <v>0.0605868436396122</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.05751315876841545</v>
+        <v>0.05824298411607742</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.05735813826322556</v>
+        <v>0.05807644501328468</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0587100088596344</v>
+        <v>0.05947060510516167</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.08159765601158142</v>
+        <v>0.08242927491664886</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.09348231554031372</v>
+        <v>0.09444023668766022</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0934726893901825</v>
+        <v>0.09449491649866104</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.09528716653585434</v>
+        <v>0.09636606276035309</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.09549286961555481</v>
+        <v>0.09656601399183273</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.09465458989143372</v>
+        <v>0.09583082795143127</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.09159407019615173</v>
+        <v>0.09261065721511841</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.09055422246456146</v>
+        <v>0.09157418459653854</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.09080562740564346</v>
+        <v>0.09185347706079483</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.08778002858161926</v>
+        <v>0.08878914266824722</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.08351228386163712</v>
+        <v>0.08443298190832138</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.08152683079242706</v>
+        <v>0.08240904659032822</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.08365027606487274</v>
+        <v>0.08461112529039383</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.08430801331996918</v>
+        <v>0.08528981357812881</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.1107395812869072</v>
+        <v>0.1117576509714127</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.1179121434688568</v>
+        <v>0.1190429255366325</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.1184844151139259</v>
+        <v>0.1196847930550575</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1200622543692589</v>
+        <v>0.1210981607437134</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.117921844124794</v>
+        <v>0.1192080825567245</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.1136724352836609</v>
+        <v>0.1147996187210083</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1140382662415504</v>
+        <v>0.1152569204568863</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.1131350547075272</v>
+        <v>0.1143244728446007</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.1116382256150246</v>
+        <v>0.1129267066717148</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.1080292835831642</v>
+        <v>0.1091613844037056</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.1034002304077148</v>
+        <v>0.1043474525213242</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.1015660613775253</v>
+        <v>0.1026197075843811</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.1002735570073128</v>
+        <v>0.1013306602835655</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.1032581627368927</v>
+        <v>0.1043567731976509</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.1392768770456314</v>
+        <v>0.1402752846479416</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.1413277089595795</v>
+        <v>0.1425856351852417</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.1405391544103622</v>
+        <v>0.1418837308883667</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.1369635313749313</v>
+        <v>0.138389527797699</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.137127548456192</v>
+        <v>0.1385085731744766</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.1307879239320755</v>
+        <v>0.1321480125188828</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.1302807629108429</v>
+        <v>0.1315048038959503</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.127699613571167</v>
+        <v>0.1289337575435638</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.1256693005561829</v>
+        <v>0.1270499378442764</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.1269500404596329</v>
+        <v>0.1282547265291214</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.1187890470027924</v>
+        <v>0.1199386492371559</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.1182136759161949</v>
+        <v>0.1192644760012627</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.1174491345882416</v>
+        <v>0.1186322495341301</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.1173203960061073</v>
+        <v>0.1184756904840469</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.1739064753055573</v>
+        <v>0.1756865084171295</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.1718955934047699</v>
+        <v>0.1737146973609924</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1676251292228699</v>
+        <v>0.1695342510938644</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.1674039512872696</v>
+        <v>0.1692361980676651</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.1654671132564545</v>
+        <v>0.1671718657016754</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.1613375097513199</v>
+        <v>0.1630954295396805</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.1573990434408188</v>
+        <v>0.1590450257062912</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.1544530987739563</v>
+        <v>0.1560738831758499</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.1524064391851425</v>
+        <v>0.1539661288261414</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.1483860462903976</v>
+        <v>0.1497348845005035</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.144659623503685</v>
+        <v>0.145894467830658</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.1377941071987152</v>
+        <v>0.1391336917877197</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.1380038559436798</v>
+        <v>0.1392530053853989</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.1411163508892059</v>
+        <v>0.1424946784973145</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.1997932642698288</v>
+        <v>0.2016998380422592</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.1975423246622086</v>
+        <v>0.1997589468955994</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.194489374756813</v>
+        <v>0.196725144982338</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.1904725432395935</v>
+        <v>0.1924317181110382</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.1868435591459274</v>
+        <v>0.1887277960777283</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.1797984689474106</v>
+        <v>0.1818866580724716</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.1805299073457718</v>
+        <v>0.1823594123125076</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.1740788072347641</v>
+        <v>0.1758837401866913</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.1725350469350815</v>
+        <v>0.1742531806230545</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.1733337044715881</v>
+        <v>0.1748862564563751</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.160577192902565</v>
+        <v>0.1618903279304504</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.1580032855272293</v>
+        <v>0.1592940092086792</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.1579334735870361</v>
+        <v>0.1592652797698975</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.164006382226944</v>
+        <v>0.1654877811670303</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.2350495010614395</v>
+        <v>0.2373223006725311</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.2223486304283142</v>
+        <v>0.2248374968767166</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.2221644073724747</v>
+        <v>0.22441565990448</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.2203904986381531</v>
+        <v>0.2227082699537277</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.2110083997249603</v>
+        <v>0.2132617235183716</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.207451656460762</v>
+        <v>0.2096735090017319</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.2079890966415405</v>
+        <v>0.2099950909614563</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.2033936530351639</v>
+        <v>0.2052871733903885</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.2031059414148331</v>
+        <v>0.2047177404165268</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.1974244564771652</v>
+        <v>0.1990572959184647</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.1916718184947968</v>
+        <v>0.1930468827486038</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.1884379237890244</v>
+        <v>0.1899200081825256</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.1873471587896347</v>
+        <v>0.188700869679451</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1898567527532578</v>
+        <v>0.1912970393896103</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.2510426938533783</v>
+        <v>0.2538778185844421</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.2475395053625107</v>
+        <v>0.2503501772880554</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.2395381480455399</v>
+        <v>0.2419982701539993</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.2378909885883331</v>
+        <v>0.2402799725532532</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.230979710817337</v>
+        <v>0.2331686913967133</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.2320206016302109</v>
+        <v>0.2339462041854858</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.2262305170297623</v>
+        <v>0.2279721796512604</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.2199688404798508</v>
+        <v>0.2219014316797256</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.2186679244041443</v>
+        <v>0.2203274220228195</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.2156730145215988</v>
+        <v>0.2172944396734238</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.2110899090766907</v>
+        <v>0.2125003635883331</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.2095052450895309</v>
+        <v>0.2109064310789108</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.2119248360395432</v>
+        <v>0.2133038938045502</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.2139346897602081</v>
+        <v>0.2153543829917908</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.267612636089325</v>
+        <v>0.2702867388725281</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.257557600736618</v>
+        <v>0.2601114511489868</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.2561226189136505</v>
+        <v>0.2586124241352081</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.2487638294696808</v>
+        <v>0.2509621679782867</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.2480778098106384</v>
+        <v>0.2501130104064941</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.2421437501907349</v>
+        <v>0.2441292405128479</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.2394320964813232</v>
+        <v>0.2413289546966553</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.2379635870456696</v>
+        <v>0.2397627085447311</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.2356166243553162</v>
+        <v>0.2373688369989395</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.233735665678978</v>
+        <v>0.2352264076471329</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.2215907275676727</v>
+        <v>0.2231782227754593</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.2253143787384033</v>
+        <v>0.2267202585935593</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.2263280600309372</v>
+        <v>0.2277390211820602</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.2279582619667053</v>
+        <v>0.2293209433555603</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.2777406871318817</v>
+        <v>0.2800043821334839</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.274332195520401</v>
+        <v>0.2765668332576752</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.2702383100986481</v>
+        <v>0.2722377479076385</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.2633747458457947</v>
+        <v>0.2652983069419861</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.2666437923908234</v>
+        <v>0.2684288322925568</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.2559087574481964</v>
+        <v>0.2574323415756226</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.2555429637432098</v>
+        <v>0.2571604251861572</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.2493809461593628</v>
+        <v>0.2509784996509552</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.2522265017032623</v>
+        <v>0.2538008987903595</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.2514496147632599</v>
+        <v>0.2529424130916595</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.2479947507381439</v>
+        <v>0.2494071573019028</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.2478159070014954</v>
+        <v>0.2491773813962936</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.2475627362728119</v>
+        <v>0.248955175280571</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.2591266930103302</v>
+        <v>0.2606181800365448</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.2841159999370575</v>
+        <v>0.285676509141922</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.2846574485301971</v>
+        <v>0.286200076341629</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.2740708887577057</v>
+        <v>0.2755210995674133</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.2764819860458374</v>
+        <v>0.2778788208961487</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.2668426632881165</v>
+        <v>0.2682742774486542</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.2683984935283661</v>
+        <v>0.2697587907314301</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.2679448127746582</v>
+        <v>0.269427090883255</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.2646893858909607</v>
+        <v>0.2661425471305847</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.2602839171886444</v>
+        <v>0.2616211473941803</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.2589669823646545</v>
+        <v>0.2603334784507751</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.2611753046512604</v>
+        <v>0.2625717520713806</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.2631058096885681</v>
+        <v>0.2644355893135071</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.2726595103740692</v>
+        <v>0.2741954624652863</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.2829955518245697</v>
+        <v>0.2844903469085693</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.2882128357887268</v>
+        <v>0.2898115217685699</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.2884922325611115</v>
+        <v>0.2900263667106628</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.2804787755012512</v>
+        <v>0.2819751799106598</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.2784338891506195</v>
+        <v>0.2801010310649872</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.2839498817920685</v>
+        <v>0.2854616045951843</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.2815316021442413</v>
+        <v>0.2831636667251587</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.2817619740962982</v>
+        <v>0.2833709716796875</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.2797780930995941</v>
+        <v>0.2814218997955322</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.2815043926239014</v>
+        <v>0.2832595407962799</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.2819756865501404</v>
+        <v>0.2836438119411469</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.2810534536838531</v>
+        <v>0.282742977142334</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.2914471626281738</v>
+        <v>0.293339878320694</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.2958965003490448</v>
+        <v>0.2977727651596069</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.310440868139267</v>
+        <v>0.3124331831932068</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.3041685521602631</v>
+        <v>0.3062098324298859</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.3046949803829193</v>
+        <v>0.30694580078125</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.305920273065567</v>
+        <v>0.3081099689006805</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.3058610558509827</v>
+        <v>0.3080827593803406</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.3039098978042603</v>
+        <v>0.306151956319809</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.3023984432220459</v>
+        <v>0.3045004308223724</v>
       </c>
       <c r="GH6" t="n">
-        <v>0.2985987961292267</v>
+        <v>0.3007713854312897</v>
       </c>
       <c r="GI6" t="n">
-        <v>0.2992011308670044</v>
+        <v>0.30138298869133</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.2996741235256195</v>
+        <v>0.3018361926078796</v>
       </c>
       <c r="GK6" t="n">
-        <v>0.3034732341766357</v>
+        <v>0.3056974112987518</v>
       </c>
       <c r="GL6" t="n">
-        <v>0.3096971213817596</v>
+        <v>0.3121927380561829</v>
       </c>
       <c r="GM6" t="n">
-        <v>0.3160622119903564</v>
+        <v>0.3185139298439026</v>
       </c>
       <c r="GN6" t="n">
-        <v>0.3313938677310944</v>
+        <v>0.3338444828987122</v>
       </c>
       <c r="GO6" t="n">
-        <v>0.339202880859375</v>
+        <v>0.3417541086673737</v>
       </c>
       <c r="GP6" t="n">
-        <v>0.3323378264904022</v>
+        <v>0.3346989154815674</v>
       </c>
       <c r="GQ6" t="n">
-        <v>0.329377681016922</v>
+        <v>0.3316204845905304</v>
       </c>
       <c r="GR6" t="n">
-        <v>0.3283064067363739</v>
+        <v>0.330598384141922</v>
       </c>
       <c r="GS6" t="n">
-        <v>0.3266223073005676</v>
+        <v>0.3289921581745148</v>
       </c>
       <c r="GT6" t="n">
-        <v>0.3281302750110626</v>
+        <v>0.3303806781768799</v>
       </c>
       <c r="GU6" t="n">
-        <v>0.3223749101161957</v>
+        <v>0.3246597051620483</v>
       </c>
       <c r="GV6" t="n">
-        <v>0.3274253010749817</v>
+        <v>0.3299203217029572</v>
       </c>
       <c r="GW6" t="n">
-        <v>0.3225300312042236</v>
+        <v>0.3249919414520264</v>
       </c>
       <c r="GX6" t="n">
-        <v>0.3236373662948608</v>
+        <v>0.326132744550705</v>
       </c>
       <c r="GY6" t="n">
-        <v>0.3237972557544708</v>
+        <v>0.3264530599117279</v>
       </c>
       <c r="GZ6" t="n">
-        <v>0.3370093703269958</v>
+        <v>0.3395973742008209</v>
       </c>
       <c r="HA6" t="n">
-        <v>0.3499701321125031</v>
+        <v>0.3524373769760132</v>
       </c>
       <c r="HB6" t="n">
-        <v>0.3623749613761902</v>
+        <v>0.3650980889797211</v>
       </c>
       <c r="HC6" t="n">
-        <v>0.3566241860389709</v>
+        <v>0.3589120507240295</v>
       </c>
       <c r="HD6" t="n">
-        <v>0.3445243537425995</v>
+        <v>0.3477976322174072</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.3394887745380402</v>
+        <v>0.3428674936294556</v>
       </c>
       <c r="HF6" t="n">
-        <v>0.3411369025707245</v>
+        <v>0.3444588184356689</v>
       </c>
       <c r="HG6" t="n">
-        <v>0.3478296995162964</v>
+        <v>0.3510854542255402</v>
       </c>
       <c r="HH6" t="n">
-        <v>0.3465990424156189</v>
+        <v>0.3499990999698639</v>
       </c>
       <c r="HI6" t="n">
-        <v>0.3451824188232422</v>
+        <v>0.3483980298042297</v>
       </c>
       <c r="HJ6" t="n">
-        <v>0.3475129306316376</v>
+        <v>0.3510384261608124</v>
       </c>
       <c r="HK6" t="n">
-        <v>0.3413792252540588</v>
+        <v>0.3447870314121246</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.3431896269321442</v>
+        <v>0.3465872704982758</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.3400400578975677</v>
+        <v>0.3436257839202881</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.3632923364639282</v>
+        <v>0.3667937219142914</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.3774318993091583</v>
+        <v>0.3810317516326904</v>
       </c>
       <c r="HP6" t="n">
-        <v>0.3573610782623291</v>
+        <v>0.360063225030899</v>
       </c>
       <c r="HQ6" t="n">
-        <v>0.3458366692066193</v>
+        <v>0.3479192554950714</v>
       </c>
       <c r="HR6" t="inlineStr">
         <is>
@@ -4975,676 +4975,676 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02491302788257599</v>
+        <v>0.02555966190993786</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0337434858083725</v>
+        <v>0.03430430591106415</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03579605370759964</v>
+        <v>0.03638429939746857</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03731916099786758</v>
+        <v>0.03789743036031723</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03776314854621887</v>
+        <v>0.03832289576530457</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0369475819170475</v>
+        <v>0.03756701201200485</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03637934848666191</v>
+        <v>0.03694743290543556</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03596951439976692</v>
+        <v>0.03658725693821907</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03616558387875557</v>
+        <v>0.03678048029541969</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03547583147883415</v>
+        <v>0.03606660291552544</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03444110602140427</v>
+        <v>0.03497054800391197</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03337658196687698</v>
+        <v>0.03387969732284546</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03328792750835419</v>
+        <v>0.03378965333104134</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03382018581032753</v>
+        <v>0.03435652330517769</v>
       </c>
       <c r="P7" t="n">
-        <v>0.05029862746596336</v>
+        <v>0.05119465664029121</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.06174049898982048</v>
+        <v>0.06260639429092407</v>
       </c>
       <c r="R7" t="n">
-        <v>0.06449510902166367</v>
+        <v>0.06538324058055878</v>
       </c>
       <c r="S7" t="n">
-        <v>0.06535394489765167</v>
+        <v>0.06621860712766647</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06646320968866348</v>
+        <v>0.06742673367261887</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06397023797035217</v>
+        <v>0.06495321542024612</v>
       </c>
       <c r="V7" t="n">
-        <v>0.06482165306806564</v>
+        <v>0.0657414123415947</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06433954834938049</v>
+        <v>0.06520853191614151</v>
       </c>
       <c r="X7" t="n">
-        <v>0.06377924978733063</v>
+        <v>0.06465836614370346</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.06327381730079651</v>
+        <v>0.06418103724718094</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.06016005575656891</v>
+        <v>0.06096883863210678</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.05777007713913918</v>
+        <v>0.05859604477882385</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.05761370435357094</v>
+        <v>0.05843092873692513</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.05895696952939034</v>
+        <v>0.05981742963194847</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.08221755176782608</v>
+        <v>0.08317727595567703</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.09413620829582214</v>
+        <v>0.0952187106013298</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.09411920607089996</v>
+        <v>0.09527371823787689</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.09585623443126678</v>
+        <v>0.09705741703510284</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.09603569656610489</v>
+        <v>0.09723764657974243</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.09516448527574539</v>
+        <v>0.09646961838006973</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09205745160579681</v>
+        <v>0.09319928288459778</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.0909813866019249</v>
+        <v>0.09212687611579895</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.09123264998197556</v>
+        <v>0.09240712225437164</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0881766676902771</v>
+        <v>0.08931015431880951</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.08384855091571808</v>
+        <v>0.08488446474075317</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.08183448761701584</v>
+        <v>0.08283604681491852</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.08396614342927933</v>
+        <v>0.08505344390869141</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0846082791686058</v>
+        <v>0.08571616560220718</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.1114709973335266</v>
+        <v>0.1126212328672409</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.1186909973621368</v>
+        <v>0.1199614703655243</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.1192024126648903</v>
+        <v>0.1205417662858963</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1206746175885201</v>
+        <v>0.1218364909291267</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.118562325835228</v>
+        <v>0.120008572936058</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.1142162829637527</v>
+        <v>0.1154843866825104</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.114562600851059</v>
+        <v>0.1159280985593796</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.113620214164257</v>
+        <v>0.1149563118815422</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.1121149584650993</v>
+        <v>0.1135492101311684</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.1084648296236992</v>
+        <v>0.1097381561994553</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.1037653163075447</v>
+        <v>0.1048421710729599</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.1019096374511719</v>
+        <v>0.1031010076403618</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.1006163284182549</v>
+        <v>0.101815439760685</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.1035910025238991</v>
+        <v>0.1048342287540436</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.1400920897722244</v>
+        <v>0.1412138342857361</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.1421492695808411</v>
+        <v>0.1435614675283432</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.141279399394989</v>
+        <v>0.1427788883447647</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.1376321911811829</v>
+        <v>0.1392088681459427</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.1377930045127869</v>
+        <v>0.1393492966890335</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.131375327706337</v>
+        <v>0.1328990012407303</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.1308140307664871</v>
+        <v>0.1321932524442673</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.1282083541154861</v>
+        <v>0.1296034753322601</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.1261641085147858</v>
+        <v>0.1277025938034058</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.1274127662181854</v>
+        <v>0.1288702934980392</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1191757991909981</v>
+        <v>0.1204679906368256</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.1185775101184845</v>
+        <v>0.1197800189256668</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.1178122088313103</v>
+        <v>0.1191519051790237</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.1176678836345673</v>
+        <v>0.1189799383282661</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.1749810129404068</v>
+        <v>0.1769676357507706</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.1728684306144714</v>
+        <v>0.1749031692743301</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1685534715652466</v>
+        <v>0.1706938296556473</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.1682211607694626</v>
+        <v>0.1702644973993301</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.166194424033165</v>
+        <v>0.1681049317121506</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1620322167873383</v>
+        <v>0.1640018224716187</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.1580256223678589</v>
+        <v>0.1598677337169647</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.1550446003675461</v>
+        <v>0.1568611413240433</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.1529584378004074</v>
+        <v>0.1547058373689651</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.1488924473524094</v>
+        <v>0.1504175066947937</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.1450990587472916</v>
+        <v>0.1465038806200027</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.1381876468658447</v>
+        <v>0.1396975964307785</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.138394758105278</v>
+        <v>0.1398171931505203</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.141500398516655</v>
+        <v>0.1430598944425583</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.2008271366357803</v>
+        <v>0.2029811143875122</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.1985807716846466</v>
+        <v>0.2010700851678848</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.1954381465911865</v>
+        <v>0.1979428827762604</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.1912948787212372</v>
+        <v>0.1935014277696609</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.1876324117183685</v>
+        <v>0.1897662580013275</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.1805183589458466</v>
+        <v>0.1828470379114151</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.1811987459659576</v>
+        <v>0.1832571178674698</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.1746965199708939</v>
+        <v>0.1767198592424393</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.1731146425008774</v>
+        <v>0.1750420928001404</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.173866868019104</v>
+        <v>0.1756152808666229</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.1610256135463715</v>
+        <v>0.1625232994556427</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.1584117263555527</v>
+        <v>0.1598909646272659</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.1583289951086044</v>
+        <v>0.1598489731550217</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.1644178479909897</v>
+        <v>0.1661002635955811</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.2360334545373917</v>
+        <v>0.238604262471199</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.2233593314886093</v>
+        <v>0.226166695356369</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.2230610698461533</v>
+        <v>0.2256029695272446</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.2212566435337067</v>
+        <v>0.2238726913928986</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.2117855995893478</v>
+        <v>0.2143155187368393</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.2081783264875412</v>
+        <v>0.2106657922267914</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.2086696028709412</v>
+        <v>0.2109282314777374</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.203993022441864</v>
+        <v>0.2061149328947067</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.2036846876144409</v>
+        <v>0.2055249810218811</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1979604959487915</v>
+        <v>0.1998102813959122</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.1921262443065643</v>
+        <v>0.1937062591314316</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.1888589262962341</v>
+        <v>0.1905430853366852</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.1877443343400955</v>
+        <v>0.1892965883016586</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.190252274274826</v>
+        <v>0.191903680562973</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.2521146237850189</v>
+        <v>0.2553177177906036</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.2485072761774063</v>
+        <v>0.2516640424728394</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.2404009103775024</v>
+        <v>0.2431709915399551</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.2387133091688156</v>
+        <v>0.2414033859968185</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.2317368239164352</v>
+        <v>0.2342162579298019</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.2326855212450027</v>
+        <v>0.234872505068779</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.2268405705690384</v>
+        <v>0.2288289368152618</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.2205439507961273</v>
+        <v>0.2227123826742172</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.2192106992006302</v>
+        <v>0.2211010754108429</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.2161784619092941</v>
+        <v>0.2180220782756805</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.2115311324596405</v>
+        <v>0.213150218129158</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.2098664492368698</v>
+        <v>0.2114569991827011</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.2123114168643951</v>
+        <v>0.213897779583931</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.2143089473247528</v>
+        <v>0.2159418314695358</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.2685570120811462</v>
+        <v>0.2715796232223511</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.2584259212017059</v>
+        <v>0.2613034546375275</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.2569670081138611</v>
+        <v>0.2597808241844177</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.2494791746139526</v>
+        <v>0.2519568800926208</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.2487384974956512</v>
+        <v>0.2510427236557007</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.24276402592659</v>
+        <v>0.2450067102909088</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.2400128990411758</v>
+        <v>0.2421557307243347</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.2385061979293823</v>
+        <v>0.2405447959899902</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.2361221015453339</v>
+        <v>0.2380969077348709</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.234211802482605</v>
+        <v>0.2359194308519363</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.222019761800766</v>
+        <v>0.2238253802061081</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.2256982028484344</v>
+        <v>0.2273086756467819</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.2266673743724823</v>
+        <v>0.2282792627811432</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.2283143699169159</v>
+        <v>0.2298876494169235</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.2784887850284576</v>
+        <v>0.281062513589859</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.2750038504600525</v>
+        <v>0.2775323092937469</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.2708629667758942</v>
+        <v>0.2731387317180634</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.2639358043670654</v>
+        <v>0.2661146521568298</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.2671792209148407</v>
+        <v>0.2692090272903442</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.2563960254192352</v>
+        <v>0.2581497728824615</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.2560731172561646</v>
+        <v>0.2579318284988403</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.2498556673526764</v>
+        <v>0.2516874969005585</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.2526758313179016</v>
+        <v>0.2544668316841125</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.2518561482429504</v>
+        <v>0.2535609602928162</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.248377799987793</v>
+        <v>0.250002920627594</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.2481588423252106</v>
+        <v>0.249719649553299</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.2478750348091125</v>
+        <v>0.2494658380746841</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.2594949901103973</v>
+        <v>0.2612123191356659</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.2845499813556671</v>
+        <v>0.2863284945487976</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.2850992381572723</v>
+        <v>0.2868634462356567</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.2744861841201782</v>
+        <v>0.2761425077915192</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.2768921852111816</v>
+        <v>0.2784976065158844</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.2672316133975983</v>
+        <v>0.268865168094635</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.2687821686267853</v>
+        <v>0.2703492939472198</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.2683305740356445</v>
+        <v>0.2700158953666687</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.2650682330131531</v>
+        <v>0.2667263150215149</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.2606555819511414</v>
+        <v>0.2621933221817017</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.2593347132205963</v>
+        <v>0.2609007358551025</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.2615315616130829</v>
+        <v>0.2631352245807648</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.2634136974811554</v>
+        <v>0.2649427056312561</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.2729765176773071</v>
+        <v>0.2747219502925873</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.2833227515220642</v>
+        <v>0.2850388288497925</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.2886720597743988</v>
+        <v>0.2905089557170868</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.2889235317707062</v>
+        <v>0.2906878888607025</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.280888170003891</v>
+        <v>0.2826074063777924</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.2788376212120056</v>
+        <v>0.2807303965091705</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.2843760848045349</v>
+        <v>0.2861180901527405</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.2819477021694183</v>
+        <v>0.283814549446106</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.2821863293647766</v>
+        <v>0.2840344905853271</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.2802032828330994</v>
+        <v>0.2820897996425629</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.2819274961948395</v>
+        <v>0.2839334607124329</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.282402515411377</v>
+        <v>0.2843250334262848</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.2814392447471619</v>
+        <v>0.2833821177482605</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.2918093800544739</v>
+        <v>0.2939600348472595</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.2962910234928131</v>
+        <v>0.2984374761581421</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.310855507850647</v>
+        <v>0.3131246268749237</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.3047233521938324</v>
+        <v>0.3070703446865082</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.3052563369274139</v>
+        <v>0.3078203201293945</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.3065075576305389</v>
+        <v>0.3090237379074097</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.3064546287059784</v>
+        <v>0.309006929397583</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.3044816851615906</v>
+        <v>0.307050347328186</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.3029563128948212</v>
+        <v>0.3053803443908691</v>
       </c>
       <c r="GH7" t="n">
-        <v>0.2991357147693634</v>
+        <v>0.3016310632228851</v>
       </c>
       <c r="GI7" t="n">
-        <v>0.299690306186676</v>
+        <v>0.3022024631500244</v>
       </c>
       <c r="GJ7" t="n">
-        <v>0.3002147972583771</v>
+        <v>0.3027072548866272</v>
       </c>
       <c r="GK7" t="n">
-        <v>0.3040158748626709</v>
+        <v>0.3065799474716187</v>
       </c>
       <c r="GL7" t="n">
-        <v>0.3102082312107086</v>
+        <v>0.3130443096160889</v>
       </c>
       <c r="GM7" t="n">
-        <v>0.3165533244609833</v>
+        <v>0.319346159696579</v>
       </c>
       <c r="GN7" t="n">
-        <v>0.3319080770015717</v>
+        <v>0.3347063660621643</v>
       </c>
       <c r="GO7" t="n">
-        <v>0.3397673368453979</v>
+        <v>0.342685341835022</v>
       </c>
       <c r="GP7" t="n">
-        <v>0.3329037129878998</v>
+        <v>0.3356069922447205</v>
       </c>
       <c r="GQ7" t="n">
-        <v>0.3299024701118469</v>
+        <v>0.3324770033359528</v>
       </c>
       <c r="GR7" t="n">
-        <v>0.3288291692733765</v>
+        <v>0.3314462006092072</v>
       </c>
       <c r="GS7" t="n">
-        <v>0.3271486759185791</v>
+        <v>0.3298485279083252</v>
       </c>
       <c r="GT7" t="n">
-        <v>0.3286767899990082</v>
+        <v>0.3312697410583496</v>
       </c>
       <c r="GU7" t="n">
-        <v>0.3229175209999084</v>
+        <v>0.3255482316017151</v>
       </c>
       <c r="GV7" t="n">
-        <v>0.3279925286769867</v>
+        <v>0.3308454155921936</v>
       </c>
       <c r="GW7" t="n">
-        <v>0.3230977356433868</v>
+        <v>0.3259221911430359</v>
       </c>
       <c r="GX7" t="n">
-        <v>0.3242245018482208</v>
+        <v>0.3270941376686096</v>
       </c>
       <c r="GY7" t="n">
-        <v>0.3243957757949829</v>
+        <v>0.3274358510971069</v>
       </c>
       <c r="GZ7" t="n">
-        <v>0.3376069962978363</v>
+        <v>0.3405775129795074</v>
       </c>
       <c r="HA7" t="n">
-        <v>0.3505263924598694</v>
+        <v>0.3533594608306885</v>
       </c>
       <c r="HB7" t="n">
-        <v>0.3629983961582184</v>
+        <v>0.3661185503005981</v>
       </c>
       <c r="HC7" t="n">
-        <v>0.357110321521759</v>
+        <v>0.3597222864627838</v>
       </c>
       <c r="HD7" t="n">
-        <v>0.3452581167221069</v>
+        <v>0.3490028083324432</v>
       </c>
       <c r="HE7" t="n">
-        <v>0.3402059674263</v>
+        <v>0.3440355062484741</v>
       </c>
       <c r="HF7" t="n">
-        <v>0.3418543934822083</v>
+        <v>0.3456274271011353</v>
       </c>
       <c r="HG7" t="n">
-        <v>0.348565548658371</v>
+        <v>0.3522837162017822</v>
       </c>
       <c r="HH7" t="n">
-        <v>0.3473632335662842</v>
+        <v>0.3512374460697174</v>
       </c>
       <c r="HI7" t="n">
-        <v>0.3459617793560028</v>
+        <v>0.3496586382389069</v>
       </c>
       <c r="HJ7" t="n">
-        <v>0.348316490650177</v>
+        <v>0.3523313999176025</v>
       </c>
       <c r="HK7" t="n">
-        <v>0.3421920537948608</v>
+        <v>0.3460932374000549</v>
       </c>
       <c r="HL7" t="n">
-        <v>0.3440219461917877</v>
+        <v>0.3479198515415192</v>
       </c>
       <c r="HM7" t="n">
-        <v>0.3408894836902618</v>
+        <v>0.3449772298336029</v>
       </c>
       <c r="HN7" t="n">
-        <v>0.3641273975372314</v>
+        <v>0.3681218028068542</v>
       </c>
       <c r="HO7" t="n">
-        <v>0.3782435059547424</v>
+        <v>0.3823418319225311</v>
       </c>
       <c r="HP7" t="n">
-        <v>0.357998251914978</v>
+        <v>0.3610776662826538</v>
       </c>
       <c r="HQ7" t="n">
-        <v>0.34629887342453</v>
+        <v>0.3486772179603577</v>
       </c>
       <c r="HR7" t="inlineStr">
         <is>

--- a/results/submission_predictions.xlsx
+++ b/results/submission_predictions.xlsx
@@ -1576,7 +1576,7 @@
         <v>0.03495080769062042</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03461355343461037</v>
+        <v>0.03461355715990067</v>
       </c>
       <c r="J2" t="n">
         <v>0.0348496101796627</v>
@@ -1630,7 +1630,7 @@
         <v>0.05845443159341812</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05631149187684059</v>
+        <v>0.05631149560213089</v>
       </c>
       <c r="AB2" t="n">
         <v>0.05613158643245697</v>
@@ -1639,7 +1639,7 @@
         <v>0.05758491903543472</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.07858073711395264</v>
+        <v>0.07858074456453323</v>
       </c>
       <c r="AE2" t="n">
         <v>0.09026511758565903</v>
@@ -1687,7 +1687,7 @@
         <v>0.1139610186219215</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.1148864105343819</v>
+        <v>0.1148864179849625</v>
       </c>
       <c r="AU2" t="n">
         <v>0.116911418735981</v>
@@ -1702,7 +1702,7 @@
         <v>0.1114782765507698</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.1107744351029396</v>
+        <v>0.1107744425535202</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.1093958616256714</v>
@@ -1765,7 +1765,7 @@
         <v>0.1157198846340179</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.1684930026531219</v>
+        <v>0.1684930175542831</v>
       </c>
       <c r="BU2" t="n">
         <v>0.1668724417686462</v>
@@ -1777,7 +1777,7 @@
         <v>0.16323022544384</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.1618122160434723</v>
+        <v>0.1618122309446335</v>
       </c>
       <c r="BY2" t="n">
         <v>0.1579392850399017</v>
@@ -1873,7 +1873,7 @@
         <v>0.2005384266376495</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.2001926302909851</v>
+        <v>0.2001926451921463</v>
       </c>
       <c r="DE2" t="n">
         <v>0.1948353499174118</v>
@@ -1936,7 +1936,7 @@
         <v>0.2629711925983429</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.2533411681652069</v>
+        <v>0.2533411979675293</v>
       </c>
       <c r="DZ2" t="n">
         <v>0.2520175874233246</v>
@@ -2017,7 +2017,7 @@
         <v>0.2578244805335999</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.2822791934013367</v>
+        <v>0.2822792232036591</v>
       </c>
       <c r="FA2" t="n">
         <v>0.2827942967414856</v>
@@ -2047,10 +2047,10 @@
         <v>0.2575487494468689</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.2598561346530914</v>
+        <v>0.2598561644554138</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.2620879709720612</v>
+        <v>0.2620880007743835</v>
       </c>
       <c r="FL2" t="n">
         <v>0.2718250751495361</v>
@@ -2113,7 +2113,7 @@
         <v>0.3034467995166779</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.3016608953475952</v>
+        <v>0.3016609251499176</v>
       </c>
       <c r="GG2" t="n">
         <v>0.3001139461994171</v>
@@ -2158,13 +2158,13 @@
         <v>0.326114296913147</v>
       </c>
       <c r="GU2" t="n">
-        <v>0.3204239010810852</v>
+        <v>0.3204239308834076</v>
       </c>
       <c r="GV2" t="n">
         <v>0.3255016207695007</v>
       </c>
       <c r="GW2" t="n">
-        <v>0.3206013739109039</v>
+        <v>0.3206014037132263</v>
       </c>
       <c r="GX2" t="n">
         <v>0.3215973079204559</v>
@@ -2188,7 +2188,7 @@
         <v>0.342313289642334</v>
       </c>
       <c r="HE2" t="n">
-        <v>0.3376103043556213</v>
+        <v>0.3376103341579437</v>
       </c>
       <c r="HF2" t="n">
         <v>0.3391501903533936</v>
@@ -2200,7 +2200,7 @@
         <v>0.3442666828632355</v>
       </c>
       <c r="HI2" t="n">
-        <v>0.3425435125827789</v>
+        <v>0.3425435423851013</v>
       </c>
       <c r="HJ2" t="n">
         <v>0.3449710607528687</v>
@@ -2269,10 +2269,10 @@
         <v>0.03482587262988091</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03383027389645576</v>
+        <v>0.03383027762174606</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03286043927073479</v>
+        <v>0.03286044299602509</v>
       </c>
       <c r="N3" t="n">
         <v>0.0327799879014492</v>
@@ -2290,7 +2290,7 @@
         <v>0.06281717866659164</v>
       </c>
       <c r="S3" t="n">
-        <v>0.06386222690343857</v>
+        <v>0.06386223435401917</v>
       </c>
       <c r="T3" t="n">
         <v>0.06508798897266388</v>
@@ -2311,7 +2311,7 @@
         <v>0.06229023635387421</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.05926084145903587</v>
+        <v>0.05926084890961647</v>
       </c>
       <c r="AA3" t="n">
         <v>0.05701804533600807</v>
@@ -2371,13 +2371,13 @@
         <v>0.1161142066121101</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.1169030070304871</v>
+        <v>0.1169030144810677</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.1186547726392746</v>
+        <v>0.1186547800898552</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1165369302034378</v>
+        <v>0.116536945104599</v>
       </c>
       <c r="AW3" t="n">
         <v>0.1124852672219276</v>
@@ -2422,7 +2422,7 @@
         <v>0.1356372237205505</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.1295625865459442</v>
+        <v>0.1295626014471054</v>
       </c>
       <c r="BL3" t="n">
         <v>0.1291055381298065</v>
@@ -2431,7 +2431,7 @@
         <v>0.1265901476144791</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.1247411295771599</v>
+        <v>0.1247411370277405</v>
       </c>
       <c r="BO3" t="n">
         <v>0.1260560601949692</v>
@@ -2443,10 +2443,10 @@
         <v>0.1174057275056839</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1167658567428589</v>
+        <v>0.1167658641934395</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.1166694164276123</v>
+        <v>0.1166694313287735</v>
       </c>
       <c r="BT3" t="n">
         <v>0.1715075224637985</v>
@@ -2503,7 +2503,7 @@
         <v>0.1886332482099533</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.1850346624851227</v>
+        <v>0.1850346773862839</v>
       </c>
       <c r="CM3" t="n">
         <v>0.1784699261188507</v>
@@ -2515,10 +2515,10 @@
         <v>0.1728760898113251</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.1713965833187103</v>
+        <v>0.1713965982198715</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.1722226589918137</v>
+        <v>0.1722226738929749</v>
       </c>
       <c r="CR3" t="n">
         <v>0.1595985144376755</v>
@@ -2590,7 +2590,7 @@
         <v>0.2293724566698074</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.2305524498224258</v>
+        <v>0.230552464723587</v>
       </c>
       <c r="DP3" t="n">
         <v>0.2248707562685013</v>
@@ -2605,7 +2605,7 @@
         <v>0.2147173285484314</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.2101764231920242</v>
+        <v>0.2101764380931854</v>
       </c>
       <c r="DU3" t="n">
         <v>0.2089126855134964</v>
@@ -2614,7 +2614,7 @@
         <v>0.2111962735652924</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.2132936418056488</v>
+        <v>0.21329365670681</v>
       </c>
       <c r="DX3" t="n">
         <v>0.2656556963920593</v>
@@ -2692,7 +2692,7 @@
         <v>0.2473685592412949</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.2473494112491608</v>
+        <v>0.247349426150322</v>
       </c>
       <c r="EX3" t="n">
         <v>0.2472548186779022</v>
@@ -2752,7 +2752,7 @@
         <v>0.2799128293991089</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.2780460119247437</v>
+        <v>0.278046041727066</v>
       </c>
       <c r="FR3" t="n">
         <v>0.2833132743835449</v>
@@ -2773,7 +2773,7 @@
         <v>0.2813920676708221</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.2806528806686401</v>
+        <v>0.2806529104709625</v>
       </c>
       <c r="FY3" t="n">
         <v>0.2913435101509094</v>
@@ -2836,7 +2836,7 @@
         <v>0.3277302086353302</v>
       </c>
       <c r="GS3" t="n">
-        <v>0.3261200785636902</v>
+        <v>0.3261201083660126</v>
       </c>
       <c r="GT3" t="n">
         <v>0.3274120986461639</v>
@@ -2872,7 +2872,7 @@
         <v>0.3439421355724335</v>
       </c>
       <c r="HE3" t="n">
-        <v>0.3391879796981812</v>
+        <v>0.3391880095005035</v>
       </c>
       <c r="HF3" t="n">
         <v>0.3407431840896606</v>
@@ -2881,7 +2881,7 @@
         <v>0.3472293019294739</v>
       </c>
       <c r="HH3" t="n">
-        <v>0.3459927439689636</v>
+        <v>0.3459928035736084</v>
       </c>
       <c r="HI3" t="n">
         <v>0.3443102836608887</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02437747269868851</v>
+        <v>0.02437747456133366</v>
       </c>
       <c r="C4" t="n">
         <v>0.03307125717401505</v>
@@ -2935,7 +2935,7 @@
         <v>0.03673110157251358</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03722700849175453</v>
+        <v>0.03722701221704483</v>
       </c>
       <c r="G4" t="n">
         <v>0.0365341454744339</v>
@@ -2971,10 +2971,10 @@
         <v>0.06071498245000839</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0634593740105629</v>
+        <v>0.06345938146114349</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06446421146392822</v>
+        <v>0.06446421891450882</v>
       </c>
       <c r="T4" t="n">
         <v>0.06569310277700424</v>
@@ -2992,16 +2992,16 @@
         <v>0.06320900470018387</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06279194355010986</v>
+        <v>0.06279195100069046</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0597161203622818</v>
+        <v>0.0597161278128624</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0574403740465641</v>
+        <v>0.0574403777718544</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0572635792195797</v>
+        <v>0.05726358667016029</v>
       </c>
       <c r="AC4" t="n">
         <v>0.05867672339081764</v>
@@ -3019,7 +3019,7 @@
         <v>0.09488745033740997</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.09511441737413406</v>
+        <v>0.09511442482471466</v>
       </c>
       <c r="AI4" t="n">
         <v>0.09443804621696472</v>
@@ -3049,7 +3049,7 @@
         <v>0.08428891003131866</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.1099750846624374</v>
+        <v>0.109975092113018</v>
       </c>
       <c r="AS4" t="n">
         <v>0.1170998513698578</v>
@@ -3073,7 +3073,7 @@
         <v>0.1128963157534599</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.1115022897720337</v>
+        <v>0.1115022972226143</v>
       </c>
       <c r="BA4" t="n">
         <v>0.1078397408127785</v>
@@ -3082,10 +3082,10 @@
         <v>0.1031942218542099</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.101487822830677</v>
+        <v>0.1014878302812576</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.1001950055360794</v>
+        <v>0.10019501298666</v>
       </c>
       <c r="BE4" t="n">
         <v>0.1032266840338707</v>
@@ -3103,7 +3103,7 @@
         <v>0.1365563720464706</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.1366278380155563</v>
+        <v>0.1366278529167175</v>
       </c>
       <c r="BK4" t="n">
         <v>0.1304530501365662</v>
@@ -3139,7 +3139,7 @@
         <v>0.1710714995861053</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1669260263442993</v>
+        <v>0.1669260412454605</v>
       </c>
       <c r="BW4" t="n">
         <v>0.1668651849031448</v>
@@ -3172,7 +3172,7 @@
         <v>0.1379229873418808</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.1411560922861099</v>
+        <v>0.1411561071872711</v>
       </c>
       <c r="CH4" t="n">
         <v>0.1988352686166763</v>
@@ -3181,7 +3181,7 @@
         <v>0.1967368870973587</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.1939200311899185</v>
+        <v>0.1939200162887573</v>
       </c>
       <c r="CK4" t="n">
         <v>0.1899362653493881</v>
@@ -3250,7 +3250,7 @@
         <v>0.1914772838354111</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.188427746295929</v>
+        <v>0.1884277611970901</v>
       </c>
       <c r="DH4" t="n">
         <v>0.1872883886098862</v>
@@ -3328,10 +3328,10 @@
         <v>0.2356540709733963</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.2335969805717468</v>
+        <v>0.233596995472908</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.2216816991567612</v>
+        <v>0.2216817289590836</v>
       </c>
       <c r="EI4" t="n">
         <v>0.2253722250461578</v>
@@ -3340,7 +3340,7 @@
         <v>0.2265103459358215</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.2280198335647583</v>
+        <v>0.2280198484659195</v>
       </c>
       <c r="EL4" t="n">
         <v>0.2774821817874908</v>
@@ -3382,7 +3382,7 @@
         <v>0.2478193044662476</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.259325236082077</v>
+        <v>0.2593252658843994</v>
       </c>
       <c r="EZ4" t="n">
         <v>0.2841792404651642</v>
@@ -3415,7 +3415,7 @@
         <v>0.2590891718864441</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.2613368332386017</v>
+        <v>0.2613368630409241</v>
       </c>
       <c r="FK4" t="n">
         <v>0.2633356750011444</v>
@@ -3430,7 +3430,7 @@
         <v>0.288307398557663</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.2886003851890564</v>
+        <v>0.2886004149913788</v>
       </c>
       <c r="FP4" t="n">
         <v>0.2806093692779541</v>
@@ -3442,7 +3442,7 @@
         <v>0.2840398848056793</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.2817472517490387</v>
+        <v>0.2817472815513611</v>
       </c>
       <c r="FT4" t="n">
         <v>0.2819203734397888</v>
@@ -3466,7 +3466,7 @@
         <v>0.2963405251502991</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.3109511435031891</v>
+        <v>0.3109511733055115</v>
       </c>
       <c r="GB4" t="n">
         <v>0.3042809069156647</v>
@@ -3511,7 +3511,7 @@
         <v>0.3397187888622284</v>
       </c>
       <c r="GP4" t="n">
-        <v>0.3326640129089355</v>
+        <v>0.3326640427112579</v>
       </c>
       <c r="GQ4" t="n">
         <v>0.3297248184680939</v>
@@ -3529,10 +3529,10 @@
         <v>0.3226777613162994</v>
       </c>
       <c r="GV4" t="n">
-        <v>0.3278586566448212</v>
+        <v>0.3278586864471436</v>
       </c>
       <c r="GW4" t="n">
-        <v>0.3229389488697052</v>
+        <v>0.3229389786720276</v>
       </c>
       <c r="GX4" t="n">
         <v>0.3240161538124084</v>
@@ -3556,7 +3556,7 @@
         <v>0.3451950252056122</v>
       </c>
       <c r="HE4" t="n">
-        <v>0.3403863608837128</v>
+        <v>0.3403863906860352</v>
       </c>
       <c r="HF4" t="n">
         <v>0.3419497311115265</v>
@@ -3586,7 +3586,7 @@
         <v>0.3638312220573425</v>
       </c>
       <c r="HO4" t="n">
-        <v>0.3780695796012878</v>
+        <v>0.3780696392059326</v>
       </c>
       <c r="HP4" t="n">
         <v>0.3578898012638092</v>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02473416738212109</v>
+        <v>0.02473416924476624</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03344912454485893</v>
+        <v>0.03344912827014923</v>
       </c>
       <c r="D5" t="n">
         <v>0.03554841503500938</v>
@@ -3628,7 +3628,7 @@
         <v>0.03627607971429825</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0359247662127018</v>
+        <v>0.0359247699379921</v>
       </c>
       <c r="J5" t="n">
         <v>0.0361330658197403</v>
@@ -3643,13 +3643,13 @@
         <v>0.03338329493999481</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03330028429627419</v>
+        <v>0.03330028802156448</v>
       </c>
       <c r="O5" t="n">
         <v>0.03387780487537384</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04992398992180824</v>
+        <v>0.04992399364709854</v>
       </c>
       <c r="Q5" t="n">
         <v>0.06129185110330582</v>
@@ -3661,10 +3661,10 @@
         <v>0.06500336527824402</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06623104214668274</v>
+        <v>0.06623104959726334</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06387736648321152</v>
+        <v>0.06387737393379211</v>
       </c>
       <c r="V5" t="n">
         <v>0.06469281017780304</v>
@@ -3679,16 +3679,16 @@
         <v>0.06324388086795807</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.06013048067688942</v>
+        <v>0.06013048440217972</v>
       </c>
       <c r="AA5" t="n">
         <v>0.05783383920788765</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.05766372010111809</v>
+        <v>0.05766372755169868</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.05907176062464714</v>
+        <v>0.05907176434993744</v>
       </c>
       <c r="AD5" t="n">
         <v>0.08157885819673538</v>
@@ -3700,37 +3700,37 @@
         <v>0.09358442574739456</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.09555031359195709</v>
+        <v>0.09555032104253769</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.09577368199825287</v>
+        <v>0.09577368944883347</v>
       </c>
       <c r="AI5" t="n">
         <v>0.09507549554109573</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.09190917015075684</v>
+        <v>0.09190917760133743</v>
       </c>
       <c r="AK5" t="n">
         <v>0.09091836214065552</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.09118611365556717</v>
+        <v>0.09118612110614777</v>
       </c>
       <c r="AM5" t="n">
         <v>0.08816232532262802</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.08389639854431152</v>
+        <v>0.08389640599489212</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.08190590888261795</v>
+        <v>0.08190591633319855</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.08408883213996887</v>
+        <v>0.08408883959054947</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0847870409488678</v>
+        <v>0.08478704839944839</v>
       </c>
       <c r="AR5" t="n">
         <v>0.1107722297310829</v>
@@ -3742,7 +3742,7 @@
         <v>0.1186547875404358</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1202028170228004</v>
+        <v>0.120202824473381</v>
       </c>
       <c r="AV5" t="n">
         <v>0.1182567328214645</v>
@@ -3754,10 +3754,10 @@
         <v>0.1144487261772156</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.113565981388092</v>
+        <v>0.1135659962892532</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.1121683791279793</v>
+        <v>0.1121683865785599</v>
       </c>
       <c r="BA5" t="n">
         <v>0.1084655001759529</v>
@@ -3769,16 +3769,16 @@
         <v>0.1020455956459045</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.1007595285773277</v>
+        <v>0.1007595360279083</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.103792130947113</v>
+        <v>0.1037921458482742</v>
       </c>
       <c r="BF5" t="n">
         <v>0.1391679793596268</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.141414687037468</v>
+        <v>0.1414147019386292</v>
       </c>
       <c r="BH5" t="n">
         <v>0.1407982409000397</v>
@@ -3796,7 +3796,7 @@
         <v>0.1306593120098114</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1281212717294693</v>
+        <v>0.1281212866306305</v>
       </c>
       <c r="BN5" t="n">
         <v>0.1262461990118027</v>
@@ -3811,10 +3811,10 @@
         <v>0.1186501309275627</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.1180192083120346</v>
+        <v>0.1180192157626152</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.117886133491993</v>
+        <v>0.1178861409425735</v>
       </c>
       <c r="BT5" t="n">
         <v>0.1741604059934616</v>
@@ -3823,10 +3823,10 @@
         <v>0.1722528636455536</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1681053787469864</v>
+        <v>0.1681053936481476</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.1679314523935318</v>
+        <v>0.167931467294693</v>
       </c>
       <c r="BX5" t="n">
         <v>0.1660197824239731</v>
@@ -3853,16 +3853,16 @@
         <v>0.1384663432836533</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.1385905742645264</v>
+        <v>0.1385905891656876</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.1418365836143494</v>
+        <v>0.1418365985155106</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.2001295834779739</v>
+        <v>0.2001295983791351</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.1981050968170166</v>
+        <v>0.1981051117181778</v>
       </c>
       <c r="CJ5" t="n">
         <v>0.1952085345983505</v>
@@ -3874,7 +3874,7 @@
         <v>0.187435582280159</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.1807045042514801</v>
+        <v>0.1807045191526413</v>
       </c>
       <c r="CN5" t="n">
         <v>0.1812525242567062</v>
@@ -3883,13 +3883,13 @@
         <v>0.1748516857624054</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.1732723116874695</v>
+        <v>0.1732723265886307</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.173972561955452</v>
+        <v>0.1739725768566132</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.161129042506218</v>
+        <v>0.1611290574073792</v>
       </c>
       <c r="CS5" t="n">
         <v>0.1585945039987564</v>
@@ -3907,7 +3907,7 @@
         <v>0.2231611460447311</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.2229320853948593</v>
+        <v>0.2229321002960205</v>
       </c>
       <c r="CY5" t="n">
         <v>0.2212783396244049</v>
@@ -3922,13 +3922,13 @@
         <v>0.2088407427072525</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.2042566388845444</v>
+        <v>0.2042566537857056</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.2037457376718521</v>
+        <v>0.2037457525730133</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.1981510818004608</v>
+        <v>0.198151096701622</v>
       </c>
       <c r="DF5" t="n">
         <v>0.192267507314682</v>
@@ -3937,7 +3937,7 @@
         <v>0.1891844570636749</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.1880124807357788</v>
+        <v>0.1880125105381012</v>
       </c>
       <c r="DI5" t="n">
         <v>0.1906141638755798</v>
@@ -3946,7 +3946,7 @@
         <v>0.252103328704834</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.2487515360116959</v>
+        <v>0.2487515658140182</v>
       </c>
       <c r="DL5" t="n">
         <v>0.2405418306589127</v>
@@ -3958,7 +3958,7 @@
         <v>0.2318812757730484</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.2327946871519089</v>
+        <v>0.2327947169542313</v>
       </c>
       <c r="DP5" t="n">
         <v>0.2269324511289597</v>
@@ -3982,7 +3982,7 @@
         <v>0.212636724114418</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.2147048860788345</v>
+        <v>0.2147049158811569</v>
       </c>
       <c r="DX5" t="n">
         <v>0.2687053978443146</v>
@@ -4012,13 +4012,13 @@
         <v>0.2365140914916992</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.2344180643558502</v>
+        <v>0.2344180792570114</v>
       </c>
       <c r="EH5" t="n">
         <v>0.2224546819925308</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.2260747849941254</v>
+        <v>0.2260747998952866</v>
       </c>
       <c r="EJ5" t="n">
         <v>0.2271648645401001</v>
@@ -4036,7 +4036,7 @@
         <v>0.2711918652057648</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.2643576860427856</v>
+        <v>0.264357715845108</v>
       </c>
       <c r="EP5" t="n">
         <v>0.2675284445285797</v>
@@ -4048,7 +4048,7 @@
         <v>0.2562940120697021</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.2502081990242004</v>
+        <v>0.2502082288265228</v>
       </c>
       <c r="ET5" t="n">
         <v>0.2530697584152222</v>
@@ -4066,25 +4066,25 @@
         <v>0.2484367936849594</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.2600228786468506</v>
+        <v>0.260022908449173</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.2849516868591309</v>
+        <v>0.2849517166614532</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.2854773104190826</v>
+        <v>0.285477340221405</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.2748509645462036</v>
+        <v>0.274850994348526</v>
       </c>
       <c r="FC5" t="n">
         <v>0.277224063873291</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.267656534910202</v>
+        <v>0.2676565647125244</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.269146203994751</v>
+        <v>0.2691462337970734</v>
       </c>
       <c r="FF5" t="n">
         <v>0.2688190042972565</v>
@@ -4093,7 +4093,7 @@
         <v>0.2655416429042816</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.261031299829483</v>
+        <v>0.2610313296318054</v>
       </c>
       <c r="FI5" t="n">
         <v>0.259748786687851</v>
@@ -4114,7 +4114,7 @@
         <v>0.2891016602516174</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.2893572449684143</v>
+        <v>0.2893572747707367</v>
       </c>
       <c r="FP5" t="n">
         <v>0.2813360989093781</v>
@@ -4129,10 +4129,10 @@
         <v>0.2825057208538055</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.2826947569847107</v>
+        <v>0.2826947867870331</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.2807413041591644</v>
+        <v>0.2807413339614868</v>
       </c>
       <c r="FV5" t="n">
         <v>0.2825755774974823</v>
@@ -4144,19 +4144,19 @@
         <v>0.2821106910705566</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.2927423715591431</v>
+        <v>0.2927424013614655</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.2971332669258118</v>
+        <v>0.2971332967281342</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.3117667734622955</v>
+        <v>0.3117668032646179</v>
       </c>
       <c r="GB5" t="n">
         <v>0.3053008317947388</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.3060196936130524</v>
+        <v>0.3060197234153748</v>
       </c>
       <c r="GD5" t="n">
         <v>0.3071396350860596</v>
@@ -4174,10 +4174,10 @@
         <v>0.2998573482036591</v>
       </c>
       <c r="GI5" t="n">
-        <v>0.3005275130271912</v>
+        <v>0.3005275428295135</v>
       </c>
       <c r="GJ5" t="n">
-        <v>0.3009275496006012</v>
+        <v>0.3009275794029236</v>
       </c>
       <c r="GK5" t="n">
         <v>0.3047831356525421</v>
@@ -4192,7 +4192,7 @@
         <v>0.333007425069809</v>
       </c>
       <c r="GO5" t="n">
-        <v>0.3408304154872894</v>
+        <v>0.3408304452896118</v>
       </c>
       <c r="GP5" t="n">
         <v>0.3337565362453461</v>
@@ -4210,7 +4210,7 @@
         <v>0.3294674456119537</v>
       </c>
       <c r="GU5" t="n">
-        <v>0.3237526416778564</v>
+        <v>0.3237526714801788</v>
       </c>
       <c r="GV5" t="n">
         <v>0.3289768099784851</v>
@@ -4225,10 +4225,10 @@
         <v>0.3254671990871429</v>
       </c>
       <c r="GZ5" t="n">
-        <v>0.3386397957801819</v>
+        <v>0.3386398255825043</v>
       </c>
       <c r="HA5" t="n">
-        <v>0.3515212833881378</v>
+        <v>0.3515213131904602</v>
       </c>
       <c r="HB5" t="n">
         <v>0.3640884757041931</v>
@@ -4240,13 +4240,13 @@
         <v>0.346624881029129</v>
       </c>
       <c r="HE5" t="n">
-        <v>0.3417508900165558</v>
+        <v>0.3417509198188782</v>
       </c>
       <c r="HF5" t="n">
         <v>0.3433244228363037</v>
       </c>
       <c r="HG5" t="n">
-        <v>0.3499058187007904</v>
+        <v>0.3499058485031128</v>
       </c>
       <c r="HH5" t="n">
         <v>0.348772406578064</v>
@@ -4264,13 +4264,13 @@
         <v>0.345231294631958</v>
       </c>
       <c r="HM5" t="n">
-        <v>0.3422352373600006</v>
+        <v>0.342235267162323</v>
       </c>
       <c r="HN5" t="n">
         <v>0.3654313385486603</v>
       </c>
       <c r="HO5" t="n">
-        <v>0.3796762526035309</v>
+        <v>0.3796762824058533</v>
       </c>
       <c r="HP5" t="n">
         <v>0.3590726554393768</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02517016418278217</v>
+        <v>0.02517016604542732</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03390558436512947</v>
+        <v>0.03390558809041977</v>
       </c>
       <c r="D6" t="n">
         <v>0.03599368408322334</v>
@@ -4315,7 +4315,7 @@
         <v>0.03628024458885193</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03648054972290993</v>
+        <v>0.03648055344820023</v>
       </c>
       <c r="K6" t="n">
         <v>0.03578010573983192</v>
@@ -4330,10 +4330,10 @@
         <v>0.03356094658374786</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03413160145282745</v>
+        <v>0.03413160517811775</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05059100314974785</v>
+        <v>0.05059100687503815</v>
       </c>
       <c r="Q6" t="n">
         <v>0.06199342012405396</v>
@@ -4354,7 +4354,7 @@
         <v>0.06525736302137375</v>
       </c>
       <c r="W6" t="n">
-        <v>0.06475250422954559</v>
+        <v>0.06475251168012619</v>
       </c>
       <c r="X6" t="n">
         <v>0.06420790404081345</v>
@@ -4363,13 +4363,13 @@
         <v>0.0637521892786026</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0605868436396122</v>
+        <v>0.0605868473649025</v>
       </c>
       <c r="AA6" t="n">
         <v>0.05824298411607742</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.05807644501328468</v>
+        <v>0.05807644873857498</v>
       </c>
       <c r="AC6" t="n">
         <v>0.05947060510516167</v>
@@ -4393,7 +4393,7 @@
         <v>0.09583082795143127</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.09261065721511841</v>
+        <v>0.09261066466569901</v>
       </c>
       <c r="AK6" t="n">
         <v>0.09157418459653854</v>
@@ -4405,7 +4405,7 @@
         <v>0.08878914266824722</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.08443298190832138</v>
+        <v>0.08443297445774078</v>
       </c>
       <c r="AO6" t="n">
         <v>0.08240904659032822</v>
@@ -4417,7 +4417,7 @@
         <v>0.08528981357812881</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.1117576509714127</v>
+        <v>0.1117576584219933</v>
       </c>
       <c r="AS6" t="n">
         <v>0.1190429255366325</v>
@@ -4444,13 +4444,13 @@
         <v>0.1129267066717148</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.1091613844037056</v>
+        <v>0.1091613918542862</v>
       </c>
       <c r="BB6" t="n">
         <v>0.1043474525213242</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.1026197075843811</v>
+        <v>0.1026197150349617</v>
       </c>
       <c r="BD6" t="n">
         <v>0.1013306602835655</v>
@@ -4510,13 +4510,13 @@
         <v>0.1695342510938644</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.1692361980676651</v>
+        <v>0.1692362129688263</v>
       </c>
       <c r="BX6" t="n">
         <v>0.1671718657016754</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.1630954295396805</v>
+        <v>0.1630954146385193</v>
       </c>
       <c r="BZ6" t="n">
         <v>0.1590450257062912</v>
@@ -4564,7 +4564,7 @@
         <v>0.1823594123125076</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.1758837401866913</v>
+        <v>0.1758837252855301</v>
       </c>
       <c r="CP6" t="n">
         <v>0.1742531806230545</v>
@@ -4576,7 +4576,7 @@
         <v>0.1618903279304504</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.1592940092086792</v>
+        <v>0.1592940241098404</v>
       </c>
       <c r="CT6" t="n">
         <v>0.1592652797698975</v>
@@ -4585,13 +4585,13 @@
         <v>0.1654877811670303</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.2373223006725311</v>
+        <v>0.2373222857713699</v>
       </c>
       <c r="CW6" t="n">
         <v>0.2248374968767166</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.22441565990448</v>
+        <v>0.2244156897068024</v>
       </c>
       <c r="CY6" t="n">
         <v>0.2227082699537277</v>
@@ -4600,7 +4600,7 @@
         <v>0.2132617235183716</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.2096735090017319</v>
+        <v>0.2096735239028931</v>
       </c>
       <c r="DB6" t="n">
         <v>0.2099950909614563</v>
@@ -4612,7 +4612,7 @@
         <v>0.2047177404165268</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.1990572959184647</v>
+        <v>0.1990573108196259</v>
       </c>
       <c r="DF6" t="n">
         <v>0.1930468827486038</v>
@@ -4621,13 +4621,13 @@
         <v>0.1899200081825256</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.188700869679451</v>
+        <v>0.1887008845806122</v>
       </c>
       <c r="DI6" t="n">
         <v>0.1912970393896103</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.2538778185844421</v>
+        <v>0.2538777887821198</v>
       </c>
       <c r="DK6" t="n">
         <v>0.2503501772880554</v>
@@ -4705,7 +4705,7 @@
         <v>0.2267202585935593</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.2277390211820602</v>
+        <v>0.2277390360832214</v>
       </c>
       <c r="EK6" t="n">
         <v>0.2293209433555603</v>
@@ -4732,10 +4732,10 @@
         <v>0.2571604251861572</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.2509784996509552</v>
+        <v>0.2509785294532776</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.2538008987903595</v>
+        <v>0.2538009285926819</v>
       </c>
       <c r="EU6" t="n">
         <v>0.2529424130916595</v>
@@ -4744,16 +4744,16 @@
         <v>0.2494071573019028</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.2491773813962936</v>
+        <v>0.2491773962974548</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.248955175280571</v>
+        <v>0.2489552050828934</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.2606181800365448</v>
+        <v>0.2606182098388672</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.285676509141922</v>
+        <v>0.2856765389442444</v>
       </c>
       <c r="FA6" t="n">
         <v>0.286200076341629</v>
@@ -4762,7 +4762,7 @@
         <v>0.2755210995674133</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.2778788208961487</v>
+        <v>0.2778788506984711</v>
       </c>
       <c r="FD6" t="n">
         <v>0.2682742774486542</v>
@@ -4771,7 +4771,7 @@
         <v>0.2697587907314301</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.269427090883255</v>
+        <v>0.2694271206855774</v>
       </c>
       <c r="FG6" t="n">
         <v>0.2661425471305847</v>
@@ -4801,7 +4801,7 @@
         <v>0.2900263667106628</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.2819751799106598</v>
+        <v>0.2819752097129822</v>
       </c>
       <c r="FQ6" t="n">
         <v>0.2801010310649872</v>
@@ -4819,28 +4819,28 @@
         <v>0.2814218997955322</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.2832595407962799</v>
+        <v>0.2832595705986023</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.2836438119411469</v>
+        <v>0.2836438417434692</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.282742977142334</v>
+        <v>0.2827430069446564</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.293339878320694</v>
+        <v>0.2933399081230164</v>
       </c>
       <c r="FZ6" t="n">
         <v>0.2977727651596069</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.3124331831932068</v>
+        <v>0.3124332129955292</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.3062098324298859</v>
+        <v>0.3062098622322083</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.30694580078125</v>
+        <v>0.3069458305835724</v>
       </c>
       <c r="GD6" t="n">
         <v>0.3081099689006805</v>
@@ -4852,13 +4852,13 @@
         <v>0.306151956319809</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.3045004308223724</v>
+        <v>0.3045004606246948</v>
       </c>
       <c r="GH6" t="n">
         <v>0.3007713854312897</v>
       </c>
       <c r="GI6" t="n">
-        <v>0.30138298869133</v>
+        <v>0.3013830184936523</v>
       </c>
       <c r="GJ6" t="n">
         <v>0.3018361926078796</v>
@@ -4894,7 +4894,7 @@
         <v>0.3303806781768799</v>
       </c>
       <c r="GU6" t="n">
-        <v>0.3246597051620483</v>
+        <v>0.3246597349643707</v>
       </c>
       <c r="GV6" t="n">
         <v>0.3299203217029572</v>
@@ -4903,25 +4903,25 @@
         <v>0.3249919414520264</v>
       </c>
       <c r="GX6" t="n">
-        <v>0.326132744550705</v>
+        <v>0.3261327743530273</v>
       </c>
       <c r="GY6" t="n">
         <v>0.3264530599117279</v>
       </c>
       <c r="GZ6" t="n">
-        <v>0.3395973742008209</v>
+        <v>0.3395974040031433</v>
       </c>
       <c r="HA6" t="n">
         <v>0.3524373769760132</v>
       </c>
       <c r="HB6" t="n">
-        <v>0.3650980889797211</v>
+        <v>0.3650981187820435</v>
       </c>
       <c r="HC6" t="n">
-        <v>0.3589120507240295</v>
+        <v>0.3589120805263519</v>
       </c>
       <c r="HD6" t="n">
-        <v>0.3477976322174072</v>
+        <v>0.3477976620197296</v>
       </c>
       <c r="HE6" t="n">
         <v>0.3428674936294556</v>
@@ -4930,22 +4930,22 @@
         <v>0.3444588184356689</v>
       </c>
       <c r="HG6" t="n">
-        <v>0.3510854542255402</v>
+        <v>0.3510854840278625</v>
       </c>
       <c r="HH6" t="n">
         <v>0.3499990999698639</v>
       </c>
       <c r="HI6" t="n">
-        <v>0.3483980298042297</v>
+        <v>0.3483980596065521</v>
       </c>
       <c r="HJ6" t="n">
         <v>0.3510384261608124</v>
       </c>
       <c r="HK6" t="n">
-        <v>0.3447870314121246</v>
+        <v>0.344787061214447</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.3465872704982758</v>
+        <v>0.3465873301029205</v>
       </c>
       <c r="HM6" t="n">
         <v>0.3436257839202881</v>
@@ -4954,13 +4954,13 @@
         <v>0.3667937219142914</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.3810317516326904</v>
+        <v>0.3810317814350128</v>
       </c>
       <c r="HP6" t="n">
-        <v>0.360063225030899</v>
+        <v>0.3600632548332214</v>
       </c>
       <c r="HQ6" t="n">
-        <v>0.3479192554950714</v>
+        <v>0.3479192852973938</v>
       </c>
       <c r="HR6" t="inlineStr">
         <is>
@@ -4975,28 +4975,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02555966190993786</v>
+        <v>0.02555966377258301</v>
       </c>
       <c r="C7" t="n">
         <v>0.03430430591106415</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03638429939746857</v>
+        <v>0.03638430312275887</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03789743036031723</v>
+        <v>0.03789743408560753</v>
       </c>
       <c r="F7" t="n">
         <v>0.03832289576530457</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03756701201200485</v>
+        <v>0.03756701573729515</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03694743290543556</v>
+        <v>0.03694743663072586</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03658725693821907</v>
+        <v>0.03658726066350937</v>
       </c>
       <c r="J7" t="n">
         <v>0.03678048029541969</v>
@@ -5005,34 +5005,34 @@
         <v>0.03606660291552544</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03497054800391197</v>
+        <v>0.03497055172920227</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03387969732284546</v>
+        <v>0.03387970104813576</v>
       </c>
       <c r="N7" t="n">
         <v>0.03378965333104134</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03435652330517769</v>
+        <v>0.03435652703046799</v>
       </c>
       <c r="P7" t="n">
-        <v>0.05119465664029121</v>
+        <v>0.05119466409087181</v>
       </c>
       <c r="Q7" t="n">
         <v>0.06260639429092407</v>
       </c>
       <c r="R7" t="n">
-        <v>0.06538324058055878</v>
+        <v>0.06538324803113937</v>
       </c>
       <c r="S7" t="n">
-        <v>0.06621860712766647</v>
+        <v>0.06621861457824707</v>
       </c>
       <c r="T7" t="n">
         <v>0.06742673367261887</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06495321542024612</v>
+        <v>0.06495322287082672</v>
       </c>
       <c r="V7" t="n">
         <v>0.0657414123415947</v>
@@ -5047,16 +5047,16 @@
         <v>0.06418103724718094</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.06096883863210678</v>
+        <v>0.06096884235739708</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.05859604477882385</v>
+        <v>0.05859604850411415</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.05843092873692513</v>
+        <v>0.05843093246221542</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.05981742963194847</v>
+        <v>0.05981743335723877</v>
       </c>
       <c r="AD7" t="n">
         <v>0.08317727595567703</v>
@@ -5065,16 +5065,16 @@
         <v>0.0952187106013298</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.09527371823787689</v>
+        <v>0.09527372568845749</v>
       </c>
       <c r="AG7" t="n">
         <v>0.09705741703510284</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.09723764657974243</v>
+        <v>0.09723765403032303</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.09646961838006973</v>
+        <v>0.09646962583065033</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.09319928288459778</v>
@@ -5083,7 +5083,7 @@
         <v>0.09212687611579895</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.09240712225437164</v>
+        <v>0.09240712970495224</v>
       </c>
       <c r="AM7" t="n">
         <v>0.08931015431880951</v>
@@ -5092,10 +5092,10 @@
         <v>0.08488446474075317</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.08283604681491852</v>
+        <v>0.08283605426549911</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.08505344390869141</v>
+        <v>0.085053451359272</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.08571616560220718</v>
@@ -5110,40 +5110,40 @@
         <v>0.1205417662858963</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1218364909291267</v>
+        <v>0.1218364983797073</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.120008572936058</v>
+        <v>0.1200085803866386</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.1154843866825104</v>
+        <v>0.115484394133091</v>
       </c>
       <c r="AX7" t="n">
         <v>0.1159280985593796</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.1149563118815422</v>
+        <v>0.1149563193321228</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.1135492101311684</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.1097381561994553</v>
+        <v>0.1097381636500359</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.1048421710729599</v>
+        <v>0.1048421785235405</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.1031010076403618</v>
+        <v>0.1031010150909424</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.101815439760685</v>
+        <v>0.1018154472112656</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.1048342287540436</v>
+        <v>0.1048342362046242</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.1412138342857361</v>
+        <v>0.1412138491868973</v>
       </c>
       <c r="BG7" t="n">
         <v>0.1435614675283432</v>
@@ -5152,10 +5152,10 @@
         <v>0.1427788883447647</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.1392088681459427</v>
+        <v>0.1392088830471039</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.1393492966890335</v>
+        <v>0.1393493115901947</v>
       </c>
       <c r="BK7" t="n">
         <v>0.1328990012407303</v>
@@ -5167,16 +5167,16 @@
         <v>0.1296034753322601</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.1277025938034058</v>
+        <v>0.127702608704567</v>
       </c>
       <c r="BO7" t="n">
         <v>0.1288702934980392</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1204679906368256</v>
+        <v>0.1204679980874062</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.1197800189256668</v>
+        <v>0.1197800263762474</v>
       </c>
       <c r="BR7" t="n">
         <v>0.1191519051790237</v>
@@ -5185,7 +5185,7 @@
         <v>0.1189799383282661</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.1769676357507706</v>
+        <v>0.1769676506519318</v>
       </c>
       <c r="BU7" t="n">
         <v>0.1749031692743301</v>
@@ -5194,13 +5194,13 @@
         <v>0.1706938296556473</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.1702644973993301</v>
+        <v>0.1702645123004913</v>
       </c>
       <c r="BX7" t="n">
         <v>0.1681049317121506</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1640018224716187</v>
+        <v>0.1640018373727798</v>
       </c>
       <c r="BZ7" t="n">
         <v>0.1598677337169647</v>
@@ -5212,10 +5212,10 @@
         <v>0.1547058373689651</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.1504175066947937</v>
+        <v>0.1504175215959549</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.1465038806200027</v>
+        <v>0.1465038955211639</v>
       </c>
       <c r="CE7" t="n">
         <v>0.1396975964307785</v>
@@ -5227,13 +5227,13 @@
         <v>0.1430598944425583</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.2029811143875122</v>
+        <v>0.2029811292886734</v>
       </c>
       <c r="CI7" t="n">
         <v>0.2010700851678848</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.1979428827762604</v>
+        <v>0.1979428976774216</v>
       </c>
       <c r="CK7" t="n">
         <v>0.1935014277696609</v>
@@ -5245,10 +5245,10 @@
         <v>0.1828470379114151</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.1832571178674698</v>
+        <v>0.183257132768631</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.1767198592424393</v>
+        <v>0.1767198741436005</v>
       </c>
       <c r="CP7" t="n">
         <v>0.1750420928001404</v>
@@ -5257,7 +5257,7 @@
         <v>0.1756152808666229</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.1625232994556427</v>
+        <v>0.1625233143568039</v>
       </c>
       <c r="CS7" t="n">
         <v>0.1598909646272659</v>
@@ -5269,13 +5269,13 @@
         <v>0.1661002635955811</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.238604262471199</v>
+        <v>0.2386042922735214</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.226166695356369</v>
+        <v>0.2261667102575302</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.2256029695272446</v>
+        <v>0.2256029844284058</v>
       </c>
       <c r="CY7" t="n">
         <v>0.2238726913928986</v>
@@ -5287,7 +5287,7 @@
         <v>0.2106657922267914</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.2109282314777374</v>
+        <v>0.2109282463788986</v>
       </c>
       <c r="DC7" t="n">
         <v>0.2061149328947067</v>
@@ -5302,7 +5302,7 @@
         <v>0.1937062591314316</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.1905430853366852</v>
+        <v>0.1905431002378464</v>
       </c>
       <c r="DH7" t="n">
         <v>0.1892965883016586</v>
@@ -5320,22 +5320,22 @@
         <v>0.2431709915399551</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.2414033859968185</v>
+        <v>0.2414034008979797</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.2342162579298019</v>
+        <v>0.2342162728309631</v>
       </c>
       <c r="DO7" t="n">
         <v>0.234872505068779</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.2288289368152618</v>
+        <v>0.228828951716423</v>
       </c>
       <c r="DQ7" t="n">
         <v>0.2227123826742172</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.2211010754108429</v>
+        <v>0.2211010903120041</v>
       </c>
       <c r="DS7" t="n">
         <v>0.2180220782756805</v>
@@ -5344,22 +5344,22 @@
         <v>0.213150218129158</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.2114569991827011</v>
+        <v>0.2114570140838623</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.213897779583931</v>
+        <v>0.2138978093862534</v>
       </c>
       <c r="DW7" t="n">
         <v>0.2159418314695358</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.2715796232223511</v>
+        <v>0.2715796530246735</v>
       </c>
       <c r="DY7" t="n">
         <v>0.2613034546375275</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.2597808241844177</v>
+        <v>0.2597808539867401</v>
       </c>
       <c r="EA7" t="n">
         <v>0.2519568800926208</v>
@@ -5398,7 +5398,7 @@
         <v>0.281062513589859</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.2775323092937469</v>
+        <v>0.2775323390960693</v>
       </c>
       <c r="EN7" t="n">
         <v>0.2731387317180634</v>
@@ -5407,7 +5407,7 @@
         <v>0.2661146521568298</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.2692090272903442</v>
+        <v>0.2692090570926666</v>
       </c>
       <c r="EQ7" t="n">
         <v>0.2581497728824615</v>
@@ -5452,13 +5452,13 @@
         <v>0.268865168094635</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.2703492939472198</v>
+        <v>0.2703493237495422</v>
       </c>
       <c r="FF7" t="n">
         <v>0.2700158953666687</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.2667263150215149</v>
+        <v>0.2667263448238373</v>
       </c>
       <c r="FH7" t="n">
         <v>0.2621933221817017</v>
@@ -5485,13 +5485,13 @@
         <v>0.2906878888607025</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.2826074063777924</v>
+        <v>0.2826074361801147</v>
       </c>
       <c r="FQ7" t="n">
         <v>0.2807303965091705</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.2861180901527405</v>
+        <v>0.2861181199550629</v>
       </c>
       <c r="FS7" t="n">
         <v>0.283814549446106</v>
@@ -5509,34 +5509,34 @@
         <v>0.2843250334262848</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.2833821177482605</v>
+        <v>0.2833821475505829</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.2939600348472595</v>
+        <v>0.2939600646495819</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.2984374761581421</v>
+        <v>0.2984375059604645</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.3131246268749237</v>
+        <v>0.3131246566772461</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.3070703446865082</v>
+        <v>0.3070703744888306</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.3078203201293945</v>
+        <v>0.3078203499317169</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.3090237379074097</v>
+        <v>0.3090237677097321</v>
       </c>
       <c r="GE7" t="n">
         <v>0.309006929397583</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.307050347328186</v>
+        <v>0.3070503771305084</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.3053803443908691</v>
+        <v>0.3053803741931915</v>
       </c>
       <c r="GH7" t="n">
         <v>0.3016310632228851</v>
@@ -5551,7 +5551,7 @@
         <v>0.3065799474716187</v>
       </c>
       <c r="GL7" t="n">
-        <v>0.3130443096160889</v>
+        <v>0.3130443394184113</v>
       </c>
       <c r="GM7" t="n">
         <v>0.319346159696579</v>
@@ -5569,7 +5569,7 @@
         <v>0.3324770033359528</v>
       </c>
       <c r="GR7" t="n">
-        <v>0.3314462006092072</v>
+        <v>0.3314462304115295</v>
       </c>
       <c r="GS7" t="n">
         <v>0.3298485279083252</v>
@@ -5578,40 +5578,40 @@
         <v>0.3312697410583496</v>
       </c>
       <c r="GU7" t="n">
-        <v>0.3255482316017151</v>
+        <v>0.3255482614040375</v>
       </c>
       <c r="GV7" t="n">
         <v>0.3308454155921936</v>
       </c>
       <c r="GW7" t="n">
-        <v>0.3259221911430359</v>
+        <v>0.3259222209453583</v>
       </c>
       <c r="GX7" t="n">
-        <v>0.3270941376686096</v>
+        <v>0.327094167470932</v>
       </c>
       <c r="GY7" t="n">
-        <v>0.3274358510971069</v>
+        <v>0.3274358808994293</v>
       </c>
       <c r="GZ7" t="n">
         <v>0.3405775129795074</v>
       </c>
       <c r="HA7" t="n">
-        <v>0.3533594608306885</v>
+        <v>0.3533594906330109</v>
       </c>
       <c r="HB7" t="n">
-        <v>0.3661185503005981</v>
+        <v>0.3661185801029205</v>
       </c>
       <c r="HC7" t="n">
         <v>0.3597222864627838</v>
       </c>
       <c r="HD7" t="n">
-        <v>0.3490028083324432</v>
+        <v>0.3490028381347656</v>
       </c>
       <c r="HE7" t="n">
-        <v>0.3440355062484741</v>
+        <v>0.3440355360507965</v>
       </c>
       <c r="HF7" t="n">
-        <v>0.3456274271011353</v>
+        <v>0.3456274569034576</v>
       </c>
       <c r="HG7" t="n">
         <v>0.3522837162017822</v>
@@ -5632,7 +5632,7 @@
         <v>0.3479198515415192</v>
       </c>
       <c r="HM7" t="n">
-        <v>0.3449772298336029</v>
+        <v>0.3449772596359253</v>
       </c>
       <c r="HN7" t="n">
         <v>0.3681218028068542</v>
@@ -5644,7 +5644,7 @@
         <v>0.3610776662826538</v>
       </c>
       <c r="HQ7" t="n">
-        <v>0.3486772179603577</v>
+        <v>0.3486772477626801</v>
       </c>
       <c r="HR7" t="inlineStr">
         <is>

--- a/results/submission_predictions.xlsx
+++ b/results/submission_predictions.xlsx
@@ -1555,676 +1555,676 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02326624281704426</v>
+        <v>0.02326625399291515</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03184730932116508</v>
+        <v>0.03184733167290688</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03395084664225578</v>
+        <v>0.03395086899399757</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03552864119410515</v>
+        <v>0.03552865609526634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03608324378728867</v>
+        <v>0.03608325868844986</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03545859828591347</v>
+        <v>0.03545861318707466</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03495080769062042</v>
+        <v>0.03495082259178162</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03461355715990067</v>
+        <v>0.03461356461048126</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0348496101796627</v>
+        <v>0.0348496250808239</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03421995788812637</v>
+        <v>0.03421996906399727</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03328651562333107</v>
+        <v>0.03328653424978256</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03239406272768974</v>
+        <v>0.03239406645298004</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03232501447200775</v>
+        <v>0.03232502192258835</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03292563557624817</v>
+        <v>0.03292563930153847</v>
       </c>
       <c r="P2" t="n">
-        <v>0.04760322719812393</v>
+        <v>0.04760325700044632</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0587894506752491</v>
+        <v>0.05878948420286179</v>
       </c>
       <c r="R2" t="n">
-        <v>0.06146266311407089</v>
+        <v>0.06146269664168358</v>
       </c>
       <c r="S2" t="n">
-        <v>0.06261803209781647</v>
+        <v>0.06261806935071945</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06386690586805344</v>
+        <v>0.06386692821979523</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06174226850271225</v>
+        <v>0.06174229457974434</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06260816752910614</v>
+        <v>0.06260819733142853</v>
       </c>
       <c r="W2" t="n">
-        <v>0.06225843727588654</v>
+        <v>0.06225846707820892</v>
       </c>
       <c r="X2" t="n">
-        <v>0.06171950697898865</v>
+        <v>0.06171952933073044</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.06137225776910782</v>
+        <v>0.06137227639555931</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.05845443159341812</v>
+        <v>0.05845445021986961</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05631149560213089</v>
+        <v>0.05631150677800179</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05613158643245697</v>
+        <v>0.05613159388303757</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.05758491903543472</v>
+        <v>0.05758493393659592</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.07858074456453323</v>
+        <v>0.07858078926801682</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.09026511758565903</v>
+        <v>0.09026516973972321</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.09025271236896515</v>
+        <v>0.09025275707244873</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.09254395216703415</v>
+        <v>0.09254399687051773</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.09284490346908569</v>
+        <v>0.09284494817256927</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.09228673577308655</v>
+        <v>0.09228677302598953</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.08932638168334961</v>
+        <v>0.08932642638683319</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0884973406791687</v>
+        <v>0.08849737793207169</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.08873913437128067</v>
+        <v>0.08873917162418365</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.08585983514785767</v>
+        <v>0.08585985749959946</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.08191733062267303</v>
+        <v>0.08191736042499542</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.08004793524742126</v>
+        <v>0.08004794269800186</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.08216208219528198</v>
+        <v>0.08216211199760437</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.0829370841383934</v>
+        <v>0.082937091588974</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.1072095707058907</v>
+        <v>0.1072096303105354</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.1139610186219215</v>
+        <v>0.1139610856771469</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.1148864179849625</v>
+        <v>0.1148864701390266</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.116911418735981</v>
+        <v>0.1169114783406258</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.1147406846284866</v>
+        <v>0.1147407367825508</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.1109433472156525</v>
+        <v>0.110943391919136</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1114782765507698</v>
+        <v>0.1114783138036728</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.1107744425535202</v>
+        <v>0.1107744798064232</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1093958616256714</v>
+        <v>0.1093958765268326</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.1059109047055244</v>
+        <v>0.1059109345078468</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.1015538275241852</v>
+        <v>0.1015538573265076</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.09993546456098557</v>
+        <v>0.09993547946214676</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.09865272045135498</v>
+        <v>0.09865274280309677</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.1017197370529175</v>
+        <v>0.1017197594046593</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.1351003646850586</v>
+        <v>0.1351004391908646</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.1370925307273865</v>
+        <v>0.1370926201343536</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.136800229549408</v>
+        <v>0.1368002742528915</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.1336499750614166</v>
+        <v>0.1336500346660614</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.1337406486272812</v>
+        <v>0.133740708231926</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.1278858780860901</v>
+        <v>0.1278859227895737</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.1275735795497894</v>
+        <v>0.127573624253273</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.1251439899206161</v>
+        <v>0.1251440197229385</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.1233212053775787</v>
+        <v>0.1233212500810623</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.1247251257300377</v>
+        <v>0.1247251555323601</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1169379726052284</v>
+        <v>0.1169379949569702</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.1163929328322411</v>
+        <v>0.1163929477334023</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.1157632023096085</v>
+        <v>0.1157632172107697</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.1157198846340179</v>
+        <v>0.1157199069857597</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.1684930175542831</v>
+        <v>0.1684931069612503</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.1668724417686462</v>
+        <v>0.1668725162744522</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.1628893613815308</v>
+        <v>0.1628894358873367</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.16323022544384</v>
+        <v>0.163230299949646</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.1618122309446335</v>
+        <v>0.1618122905492783</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.1579392850399017</v>
+        <v>0.1579393446445465</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.1543184369802475</v>
+        <v>0.1543184667825699</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.1515738219022751</v>
+        <v>0.1515738666057587</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.1497409492731094</v>
+        <v>0.1497409790754318</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.1458337157964706</v>
+        <v>0.1458337306976318</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.1424359530210495</v>
+        <v>0.1424359828233719</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.1360165029764175</v>
+        <v>0.1360165327787399</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.1361581981182098</v>
+        <v>0.136158213019371</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.1394180804491043</v>
+        <v>0.1394181102514267</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.1943377554416656</v>
+        <v>0.194337859749794</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.1921221911907196</v>
+        <v>0.1921222805976868</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.1897089034318924</v>
+        <v>0.1897089779376984</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.1862373948097229</v>
+        <v>0.1862374395132065</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.1827536672353745</v>
+        <v>0.1827537268400192</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.1764062792062759</v>
+        <v>0.1764063388109207</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.1772307753562927</v>
+        <v>0.1772308200597763</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.1711097806692123</v>
+        <v>0.1711098253726959</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.1697260737419128</v>
+        <v>0.169726088643074</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.1706794202327728</v>
+        <v>0.1706794798374176</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.1583408862352371</v>
+        <v>0.1583409160375595</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.1560250073671341</v>
+        <v>0.1560250371694565</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.1561156660318375</v>
+        <v>0.1561156958341599</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.1621867418289185</v>
+        <v>0.1621867716312408</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.2298654615879059</v>
+        <v>0.2298655360937119</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.2171444743871689</v>
+        <v>0.2171445488929749</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.217566192150116</v>
+        <v>0.2175662666559219</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.2160788029432297</v>
+        <v>0.2160788774490356</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.2072250545024872</v>
+        <v>0.2072250992059708</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.2039920687675476</v>
+        <v>0.2039921134710312</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.2046655565500259</v>
+        <v>0.2046656012535095</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.2005384266376495</v>
+        <v>0.2005384713411331</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.2001926451921463</v>
+        <v>0.2001926749944687</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.1948353499174118</v>
+        <v>0.1948353797197342</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.1894027441740036</v>
+        <v>0.1894027888774872</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.1865027993917465</v>
+        <v>0.1865028440952301</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.1854919940233231</v>
+        <v>0.1854920387268066</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.1881078332662582</v>
+        <v>0.1881078630685806</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.2456706762313843</v>
+        <v>0.2456707805395126</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.2429290115833282</v>
+        <v>0.2429291009902954</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.235290914773941</v>
+        <v>0.2352909743785858</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.2338629513978958</v>
+        <v>0.2338630259037018</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.2272153496742249</v>
+        <v>0.2272153943777084</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.2286425828933716</v>
+        <v>0.228642612695694</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.223147913813591</v>
+        <v>0.2231479436159134</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.2173605859279633</v>
+        <v>0.2173606306314468</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.216062068939209</v>
+        <v>0.2160621136426926</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.21334208548069</v>
+        <v>0.2133421301841736</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.2089819759130478</v>
+        <v>0.2089820057153702</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.2079463750123978</v>
+        <v>0.2079464197158813</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.2101826518774033</v>
+        <v>0.210182711482048</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2123355269432068</v>
+        <v>0.2123355716466904</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.2629711925983429</v>
+        <v>0.2629712522029877</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.2533411979675293</v>
+        <v>0.2533412277698517</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.2520175874233246</v>
+        <v>0.2520176470279694</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.2453045099973679</v>
+        <v>0.2453045696020126</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.2449192851781845</v>
+        <v>0.2449193298816681</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.2392342835664749</v>
+        <v>0.2392343431711197</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.2367788702249527</v>
+        <v>0.2367789298295975</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.2355187833309174</v>
+        <v>0.2355188131332397</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.2333745062351227</v>
+        <v>0.2333745509386063</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.2314516752958298</v>
+        <v>0.2314517050981522</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.2197874039411545</v>
+        <v>0.2197874486446381</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.2237004488706589</v>
+        <v>0.2237004935741425</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.2250558584928513</v>
+        <v>0.2250559031963348</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.2264781594276428</v>
+        <v>0.2264781892299652</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.2740674316883087</v>
+        <v>0.2740674614906311</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.2712678015232086</v>
+        <v>0.2712678611278534</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.2673355340957642</v>
+        <v>0.2673355937004089</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.2608833014965057</v>
+        <v>0.2608833312988281</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.264211118221283</v>
+        <v>0.2642111480236053</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.2535957992076874</v>
+        <v>0.2535958588123322</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.2530747056007385</v>
+        <v>0.2530747354030609</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.2473413497209549</v>
+        <v>0.2473413944244385</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.2503487765789032</v>
+        <v>0.2503488063812256</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.2497831881046295</v>
+        <v>0.2497832328081131</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.2464046031236649</v>
+        <v>0.2464046478271484</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.2465107887983322</v>
+        <v>0.246510848402977</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.2465187460184097</v>
+        <v>0.2465188056230545</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.2578244805335999</v>
+        <v>0.2578245103359222</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.2822792232036591</v>
+        <v>0.2822792530059814</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.2827942967414856</v>
+        <v>0.282794326543808</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.2723480761051178</v>
+        <v>0.2723481357097626</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.2747620940208435</v>
+        <v>0.2747621536254883</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.2653318643569946</v>
+        <v>0.2653319239616394</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.2668420374393463</v>
+        <v>0.2668420970439911</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.2665213644504547</v>
+        <v>0.2665213942527771</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.2632776200771332</v>
+        <v>0.263277679681778</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.2588111758232117</v>
+        <v>0.2588112354278564</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.2575487494468689</v>
+        <v>0.2575488090515137</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.2598561644554138</v>
+        <v>0.2598561942577362</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.2620880007743835</v>
+        <v>0.2620880603790283</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.2718250751495361</v>
+        <v>0.2718251943588257</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.2820399403572083</v>
+        <v>0.2820400595664978</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.2864048779010773</v>
+        <v>0.286404937505722</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.2868222296237946</v>
+        <v>0.2868222892284393</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.2789211869239807</v>
+        <v>0.2789212465286255</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.2770764231681824</v>
+        <v>0.2770764827728271</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.2822731733322144</v>
+        <v>0.2822732031345367</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.2800259590148926</v>
+        <v>0.2800260484218597</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.2801548540592194</v>
+        <v>0.2801549136638641</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.2781893610954285</v>
+        <v>0.2781893908977509</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.2800170183181763</v>
+        <v>0.280017077922821</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.280366837978363</v>
+        <v>0.2803669273853302</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.2797637581825256</v>
+        <v>0.2797638475894928</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.2905438244342804</v>
+        <v>0.2905439138412476</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.294764518737793</v>
+        <v>0.2947646379470825</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.3093151450157166</v>
+        <v>0.3093152642250061</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.3019087016582489</v>
+        <v>0.3019087612628937</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.3025695085525513</v>
+        <v>0.3025695979595184</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.3035298585891724</v>
+        <v>0.3035299479961395</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.3034467995166779</v>
+        <v>0.303446888923645</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.3016609251499176</v>
+        <v>0.3016610145568848</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.3001139461994171</v>
+        <v>0.3001140356063843</v>
       </c>
       <c r="GH2" t="n">
-        <v>0.2964869439601898</v>
+        <v>0.2964870035648346</v>
       </c>
       <c r="GI2" t="n">
-        <v>0.2974066734313965</v>
+        <v>0.2974067628383636</v>
       </c>
       <c r="GJ2" t="n">
-        <v>0.2975610792636871</v>
+        <v>0.2975611686706543</v>
       </c>
       <c r="GK2" t="n">
-        <v>0.3014009296894073</v>
+        <v>0.3014009892940521</v>
       </c>
       <c r="GL2" t="n">
-        <v>0.3081745505332947</v>
+        <v>0.3081746697425842</v>
       </c>
       <c r="GM2" t="n">
-        <v>0.3147276937961578</v>
+        <v>0.3147278130054474</v>
       </c>
       <c r="GN2" t="n">
-        <v>0.3299196660518646</v>
+        <v>0.3299198150634766</v>
       </c>
       <c r="GO2" t="n">
-        <v>0.3374396860599518</v>
+        <v>0.3374398052692413</v>
       </c>
       <c r="GP2" t="n">
-        <v>0.3302976787090302</v>
+        <v>0.3302977681159973</v>
       </c>
       <c r="GQ2" t="n">
-        <v>0.327569454908371</v>
+        <v>0.3275695443153381</v>
       </c>
       <c r="GR2" t="n">
-        <v>0.3264769613742828</v>
+        <v>0.3264770209789276</v>
       </c>
       <c r="GS2" t="n">
-        <v>0.324869692325592</v>
+        <v>0.3248697817325592</v>
       </c>
       <c r="GT2" t="n">
-        <v>0.326114296913147</v>
+        <v>0.3261143565177917</v>
       </c>
       <c r="GU2" t="n">
-        <v>0.3204239308834076</v>
+        <v>0.3204240202903748</v>
       </c>
       <c r="GV2" t="n">
-        <v>0.3255016207695007</v>
+        <v>0.3255017399787903</v>
       </c>
       <c r="GW2" t="n">
-        <v>0.3206014037132263</v>
+        <v>0.3206014931201935</v>
       </c>
       <c r="GX2" t="n">
-        <v>0.3215973079204559</v>
+        <v>0.3215974271297455</v>
       </c>
       <c r="GY2" t="n">
-        <v>0.3218244016170502</v>
+        <v>0.3218245208263397</v>
       </c>
       <c r="GZ2" t="n">
-        <v>0.3350946605205536</v>
+        <v>0.3350948095321655</v>
       </c>
       <c r="HA2" t="n">
-        <v>0.348188579082489</v>
+        <v>0.348188728094101</v>
       </c>
       <c r="HB2" t="n">
-        <v>0.3604069948196411</v>
+        <v>0.3604071736335754</v>
       </c>
       <c r="HC2" t="n">
-        <v>0.3552491068840027</v>
+        <v>0.3552492260932922</v>
       </c>
       <c r="HD2" t="n">
-        <v>0.342313289642334</v>
+        <v>0.3423134684562683</v>
       </c>
       <c r="HE2" t="n">
-        <v>0.3376103341579437</v>
+        <v>0.3376105129718781</v>
       </c>
       <c r="HF2" t="n">
-        <v>0.3391501903533936</v>
+        <v>0.3391503691673279</v>
       </c>
       <c r="HG2" t="n">
-        <v>0.3455820679664612</v>
+        <v>0.3455822467803955</v>
       </c>
       <c r="HH2" t="n">
-        <v>0.3442666828632355</v>
+        <v>0.3442668318748474</v>
       </c>
       <c r="HI2" t="n">
-        <v>0.3425435423851013</v>
+        <v>0.342543751001358</v>
       </c>
       <c r="HJ2" t="n">
-        <v>0.3449710607528687</v>
+        <v>0.3449712693691254</v>
       </c>
       <c r="HK2" t="n">
-        <v>0.3386457860469818</v>
+        <v>0.3386459350585938</v>
       </c>
       <c r="HL2" t="n">
-        <v>0.3402526676654816</v>
+        <v>0.3402528762817383</v>
       </c>
       <c r="HM2" t="n">
-        <v>0.3371363580226898</v>
+        <v>0.3371365070343018</v>
       </c>
       <c r="HN2" t="n">
-        <v>0.360469788312912</v>
+        <v>0.3604699671268463</v>
       </c>
       <c r="HO2" t="n">
-        <v>0.3748536705970764</v>
+        <v>0.3748538792133331</v>
       </c>
       <c r="HP2" t="n">
-        <v>0.3554169535636902</v>
+        <v>0.3554171025753021</v>
       </c>
       <c r="HQ2" t="n">
-        <v>0.3445872962474823</v>
+        <v>0.3445874750614166</v>
       </c>
       <c r="HR2" t="inlineStr">
         <is>
@@ -2239,676 +2239,676 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02403732948005199</v>
+        <v>0.02403736300766468</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03268427401781082</v>
+        <v>0.03268431127071381</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03478318825364113</v>
+        <v>0.03478322550654411</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0363391749560833</v>
+        <v>0.03633921220898628</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0368516631424427</v>
+        <v>0.03685170039534569</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03617646172642708</v>
+        <v>0.03617649525403976</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03562355414032936</v>
+        <v>0.03562358394265175</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03527325391769409</v>
+        <v>0.03527328372001648</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03548981249332428</v>
+        <v>0.03548984602093697</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03482587262988091</v>
+        <v>0.03482589870691299</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03383027762174606</v>
+        <v>0.03383029997348785</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03286044299602509</v>
+        <v>0.03286046162247658</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0327799879014492</v>
+        <v>0.03278001397848129</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03336161747574806</v>
+        <v>0.03336164355278015</v>
       </c>
       <c r="P3" t="n">
-        <v>0.04881107434630394</v>
+        <v>0.04881113022565842</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.06010539084672928</v>
+        <v>0.06010545417666435</v>
       </c>
       <c r="R3" t="n">
-        <v>0.06281717866659164</v>
+        <v>0.06281723827123642</v>
       </c>
       <c r="S3" t="n">
-        <v>0.06386223435401917</v>
+        <v>0.06386229395866394</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06508798897266388</v>
+        <v>0.06508804112672806</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06282736361026764</v>
+        <v>0.06282741576433182</v>
       </c>
       <c r="V3" t="n">
-        <v>0.06366428732872009</v>
+        <v>0.06366434693336487</v>
       </c>
       <c r="W3" t="n">
-        <v>0.06323368847370148</v>
+        <v>0.06323374062776566</v>
       </c>
       <c r="X3" t="n">
-        <v>0.06268788874149323</v>
+        <v>0.0626879408955574</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06229023635387421</v>
+        <v>0.06229028478264809</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.05926084890961647</v>
+        <v>0.05926088243722916</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.05701804533600807</v>
+        <v>0.05701807886362076</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.05683641880750656</v>
+        <v>0.05683645606040955</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.05825904756784439</v>
+        <v>0.05825908482074738</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.08016257733106613</v>
+        <v>0.0801626592874527</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.09201079607009888</v>
+        <v>0.09201088547706604</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0920148566365242</v>
+        <v>0.09201493859291077</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.09412144124507904</v>
+        <v>0.09412152320146561</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.09435664117336273</v>
+        <v>0.0943567231297493</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.09371016174554825</v>
+        <v>0.09371022880077362</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.09062831103801727</v>
+        <v>0.09062837809324265</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.08969339728355408</v>
+        <v>0.08969345688819885</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.08994727581739426</v>
+        <v>0.08994735032320023</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.08697980642318726</v>
+        <v>0.08697987347841263</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.08285895735025406</v>
+        <v>0.08285900950431824</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.08090165257453918</v>
+        <v>0.08090169727802277</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.08303867280483246</v>
+        <v>0.08303873240947723</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.08376628160476685</v>
+        <v>0.08376631885766983</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.1091116219758987</v>
+        <v>0.1091117188334465</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.1161142066121101</v>
+        <v>0.1161143183708191</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.1169030144810677</v>
+        <v>0.1169031038880348</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.1186547800898552</v>
+        <v>0.1186548694968224</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.116536945104599</v>
+        <v>0.1165370345115662</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1124852672219276</v>
+        <v>0.1124853417277336</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1129644364118576</v>
+        <v>0.1129645109176636</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.1121451631188393</v>
+        <v>0.1121452376246452</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.110755480825901</v>
+        <v>0.1107555404305458</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1071450784802437</v>
+        <v>0.1071451455354691</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.1025877892971039</v>
+        <v>0.1025878489017487</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1008946225047112</v>
+        <v>0.1008946746587753</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.09959989041090012</v>
+        <v>0.0995999351143837</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1026377305388451</v>
+        <v>0.1026377826929092</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1373291611671448</v>
+        <v>0.1373292803764343</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.1394053548574448</v>
+        <v>0.1394054740667343</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.138910710811615</v>
+        <v>0.1389108151197433</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.1355936676263809</v>
+        <v>0.1355937570333481</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.1356372237205505</v>
+        <v>0.1356373429298401</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.1295626014471054</v>
+        <v>0.1295626759529114</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.1291055381298065</v>
+        <v>0.1291056126356125</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.1265901476144791</v>
+        <v>0.126590222120285</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.1247411370277405</v>
+        <v>0.124741218984127</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.1260560601949692</v>
+        <v>0.126056119799614</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1180353760719299</v>
+        <v>0.1180354431271553</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.1174057275056839</v>
+        <v>0.1174057796597481</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1167658641934395</v>
+        <v>0.1167659237980843</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.1166694313287735</v>
+        <v>0.1166694834828377</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.1715075224637985</v>
+        <v>0.1715077012777328</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.1696704924106598</v>
+        <v>0.1696706265211105</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.1655588746070862</v>
+        <v>0.1655589938163757</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1656283438205719</v>
+        <v>0.1656284779310226</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.1639087051153183</v>
+        <v>0.1639088243246078</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.1599232852458954</v>
+        <v>0.1599233895540237</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.1561277061700821</v>
+        <v>0.1561277806758881</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.153268963098526</v>
+        <v>0.1532690525054932</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.1513223052024841</v>
+        <v>0.1513223797082901</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.1472853720188141</v>
+        <v>0.1472854316234589</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.1436840444803238</v>
+        <v>0.1436841189861298</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.1371039152145386</v>
+        <v>0.1371039748191833</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.1372312754392624</v>
+        <v>0.1372313499450684</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.1404612213373184</v>
+        <v>0.1404612958431244</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.1973127871751785</v>
+        <v>0.1973129361867905</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.1951549202203751</v>
+        <v>0.195155069231987</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.1924537122249603</v>
+        <v>0.1924538314342499</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.1886332482099533</v>
+        <v>0.1886333674192429</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.1850346773862839</v>
+        <v>0.1850348114967346</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.1784699261188507</v>
+        <v>0.1784700453281403</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.1791473031044006</v>
+        <v>0.1791474223136902</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1728760898113251</v>
+        <v>0.1728761941194534</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.1713965982198715</v>
+        <v>0.1713966578245163</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.1722226738929749</v>
+        <v>0.172222763299942</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.1595985144376755</v>
+        <v>0.1595985889434814</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.1571419835090637</v>
+        <v>0.1571420580148697</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.1571822315454483</v>
+        <v>0.1571823060512543</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.1632937341928482</v>
+        <v>0.1632938235998154</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.2327416390180588</v>
+        <v>0.2327418029308319</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.2200867235660553</v>
+        <v>0.2200868725776672</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.2201635837554932</v>
+        <v>0.2201637327671051</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.2185530960559845</v>
+        <v>0.2185532450675964</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.2094584554433823</v>
+        <v>0.2094585597515106</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.2060793787240982</v>
+        <v>0.2060794830322266</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.2066149264574051</v>
+        <v>0.2066150158643723</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.2022633105516434</v>
+        <v>0.2022633999586105</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.2018202096223831</v>
+        <v>0.2018202990293503</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.1963387727737427</v>
+        <v>0.1963388621807098</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.190655991435051</v>
+        <v>0.1906560808420181</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.1876568645238876</v>
+        <v>0.1876569390296936</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.1865604370832443</v>
+        <v>0.1865605115890503</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.1891448944807053</v>
+        <v>0.1891449987888336</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.2487358301877975</v>
+        <v>0.2487360090017319</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.245670422911644</v>
+        <v>0.2456705719232559</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.2377710342407227</v>
+        <v>0.2377711832523346</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.2362193316221237</v>
+        <v>0.2362194508314133</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.2293724566698074</v>
+        <v>0.229372575879097</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.230552464723587</v>
+        <v>0.2305525541305542</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.2248707562685013</v>
+        <v>0.2248708456754684</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.2189717888832092</v>
+        <v>0.2189718931913376</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.2175602465867996</v>
+        <v>0.217560350894928</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.2147173285484314</v>
+        <v>0.2147174328565598</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.2101764380931854</v>
+        <v>0.2101765125989914</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.2089126855134964</v>
+        <v>0.2089127749204636</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.2111962735652924</v>
+        <v>0.2111963778734207</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.21329365670681</v>
+        <v>0.213293731212616</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.2656556963920593</v>
+        <v>0.2656558454036713</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.2558151483535767</v>
+        <v>0.2558152675628662</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.2544072270393372</v>
+        <v>0.2544073462486267</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.2473454922437668</v>
+        <v>0.2473456114530563</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.2467721253633499</v>
+        <v>0.2467722445726395</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.2409675717353821</v>
+        <v>0.2409676760435104</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.2383812963962555</v>
+        <v>0.2383814007043839</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.2369942218065262</v>
+        <v>0.2369943410158157</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.2347601056098938</v>
+        <v>0.234760195016861</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.2327508181333542</v>
+        <v>0.2327509075403214</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.220913365483284</v>
+        <v>0.22091343998909</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.2246875315904617</v>
+        <v>0.2246876209974289</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.225895032286644</v>
+        <v>0.2258951216936111</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.2273672521114349</v>
+        <v>0.2273673415184021</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.2761739790439606</v>
+        <v>0.2761740684509277</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.2731141149997711</v>
+        <v>0.2731142342090607</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.2690387070178986</v>
+        <v>0.2690387964248657</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.2624012231826782</v>
+        <v>0.2624013423919678</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.2656601071357727</v>
+        <v>0.2656601965427399</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.2549009025096893</v>
+        <v>0.2549009919166565</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.2544876039028168</v>
+        <v>0.2544876933097839</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.2485671937465668</v>
+        <v>0.2485672831535339</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.2515192925930023</v>
+        <v>0.2515194118022919</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.2508253455162048</v>
+        <v>0.250825434923172</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.2473685592412949</v>
+        <v>0.2473686635494232</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.247349426150322</v>
+        <v>0.2473495155572891</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.2472548186779022</v>
+        <v>0.2472549229860306</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.258689671754837</v>
+        <v>0.2586897909641266</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.2834113538265228</v>
+        <v>0.28341144323349</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.2839338481426239</v>
+        <v>0.2839339673519135</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.2734110951423645</v>
+        <v>0.2734111845493317</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.2757968902587891</v>
+        <v>0.2757969796657562</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.2663017809391022</v>
+        <v>0.2663018703460693</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.2677897810935974</v>
+        <v>0.2677898705005646</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.267472892999649</v>
+        <v>0.2674729824066162</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.2642071545124054</v>
+        <v>0.2642072439193726</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.2597238719463348</v>
+        <v>0.259723961353302</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.2584528923034668</v>
+        <v>0.258452981710434</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.2607125043869019</v>
+        <v>0.260712593793869</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.2627922892570496</v>
+        <v>0.2627924084663391</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.2725261151790619</v>
+        <v>0.2725262641906738</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.2827572822570801</v>
+        <v>0.282757431268692</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.2875323891639709</v>
+        <v>0.2875325083732605</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.2878704071044922</v>
+        <v>0.2878704965114594</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.2799128293991089</v>
+        <v>0.2799129486083984</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.278046041727066</v>
+        <v>0.2780461311340332</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.2833132743835449</v>
+        <v>0.2833133935928345</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.2810271382331848</v>
+        <v>0.2810272574424744</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.2811840176582336</v>
+        <v>0.2811841368675232</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.2792185544967651</v>
+        <v>0.2792186737060547</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.2810328602790833</v>
+        <v>0.2810329794883728</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.2813920676708221</v>
+        <v>0.2813921868801117</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.2806529104709625</v>
+        <v>0.2806530594825745</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.2913435101509094</v>
+        <v>0.2913436591625214</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.2956438660621643</v>
+        <v>0.2956440448760986</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.3102382123470306</v>
+        <v>0.310238391160965</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.3032962381839752</v>
+        <v>0.3032963871955872</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.3039712309837341</v>
+        <v>0.3039713501930237</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.3050023913383484</v>
+        <v>0.3050025403499603</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.3049361705780029</v>
+        <v>0.3049362897872925</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.3030866086483002</v>
+        <v>0.3030867576599121</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.3015004396438599</v>
+        <v>0.3015005886554718</v>
       </c>
       <c r="GH3" t="n">
-        <v>0.2978169918060303</v>
+        <v>0.2978171408176422</v>
       </c>
       <c r="GI3" t="n">
-        <v>0.2985759675502777</v>
+        <v>0.2985761165618896</v>
       </c>
       <c r="GJ3" t="n">
-        <v>0.2988802492618561</v>
+        <v>0.298880398273468</v>
       </c>
       <c r="GK3" t="n">
-        <v>0.3027134835720062</v>
+        <v>0.3027136325836182</v>
       </c>
       <c r="GL3" t="n">
-        <v>0.3093658983707428</v>
+        <v>0.3093660771846771</v>
       </c>
       <c r="GM3" t="n">
-        <v>0.3158291876316071</v>
+        <v>0.3158293962478638</v>
       </c>
       <c r="GN3" t="n">
-        <v>0.3310709893703461</v>
+        <v>0.3310711979866028</v>
       </c>
       <c r="GO3" t="n">
-        <v>0.3387305736541748</v>
+        <v>0.3387307524681091</v>
       </c>
       <c r="GP3" t="n">
-        <v>0.3316564857959747</v>
+        <v>0.3316566348075867</v>
       </c>
       <c r="GQ3" t="n">
-        <v>0.3287949860095978</v>
+        <v>0.3287951648235321</v>
       </c>
       <c r="GR3" t="n">
-        <v>0.3277302086353302</v>
+        <v>0.3277303576469421</v>
       </c>
       <c r="GS3" t="n">
-        <v>0.3261201083660126</v>
+        <v>0.3261202573776245</v>
       </c>
       <c r="GT3" t="n">
-        <v>0.3274120986461639</v>
+        <v>0.3274122476577759</v>
       </c>
       <c r="GU3" t="n">
-        <v>0.3217029869556427</v>
+        <v>0.321703165769577</v>
       </c>
       <c r="GV3" t="n">
-        <v>0.3268396556377411</v>
+        <v>0.3268398344516754</v>
       </c>
       <c r="GW3" t="n">
-        <v>0.3219266533851624</v>
+        <v>0.3219268321990967</v>
       </c>
       <c r="GX3" t="n">
-        <v>0.3229702711105347</v>
+        <v>0.3229704797267914</v>
       </c>
       <c r="GY3" t="n">
-        <v>0.3232180774211884</v>
+        <v>0.3232182860374451</v>
       </c>
       <c r="GZ3" t="n">
-        <v>0.3364500999450684</v>
+        <v>0.3364503383636475</v>
       </c>
       <c r="HA3" t="n">
-        <v>0.3494464159011841</v>
+        <v>0.3494466245174408</v>
       </c>
       <c r="HB3" t="n">
-        <v>0.3618084788322449</v>
+        <v>0.3618087470531464</v>
       </c>
       <c r="HC3" t="n">
-        <v>0.3563204705715179</v>
+        <v>0.3563206791877747</v>
       </c>
       <c r="HD3" t="n">
-        <v>0.3439421355724335</v>
+        <v>0.3439424633979797</v>
       </c>
       <c r="HE3" t="n">
-        <v>0.3391880095005035</v>
+        <v>0.3391883373260498</v>
       </c>
       <c r="HF3" t="n">
-        <v>0.3407431840896606</v>
+        <v>0.3407434821128845</v>
       </c>
       <c r="HG3" t="n">
-        <v>0.3472293019294739</v>
+        <v>0.3472295999526978</v>
       </c>
       <c r="HH3" t="n">
-        <v>0.3459928035736084</v>
+        <v>0.3459930419921875</v>
       </c>
       <c r="HI3" t="n">
-        <v>0.3443102836608887</v>
+        <v>0.3443105816841125</v>
       </c>
       <c r="HJ3" t="n">
-        <v>0.3468121886253357</v>
+        <v>0.3468124866485596</v>
       </c>
       <c r="HK3" t="n">
-        <v>0.3405160307884216</v>
+        <v>0.3405162692070007</v>
       </c>
       <c r="HL3" t="n">
-        <v>0.342191606760025</v>
+        <v>0.3421918451786041</v>
       </c>
       <c r="HM3" t="n">
-        <v>0.3391364812850952</v>
+        <v>0.3391367197036743</v>
       </c>
       <c r="HN3" t="n">
-        <v>0.3623926937580109</v>
+        <v>0.3623929917812347</v>
       </c>
       <c r="HO3" t="n">
-        <v>0.3766745626926422</v>
+        <v>0.3766748607158661</v>
       </c>
       <c r="HP3" t="n">
-        <v>0.3568391799926758</v>
+        <v>0.3568394482135773</v>
       </c>
       <c r="HQ3" t="n">
-        <v>0.3455772697925568</v>
+        <v>0.3455774784088135</v>
       </c>
       <c r="HR3" t="inlineStr">
         <is>
@@ -2923,676 +2923,676 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02437747456133366</v>
+        <v>0.02437753230333328</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03307125717401505</v>
+        <v>0.03307131677865982</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03517702966928482</v>
+        <v>0.03517709299921989</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03673110157251358</v>
+        <v>0.03673115745186806</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03722701221704483</v>
+        <v>0.03722706437110901</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0365341454744339</v>
+        <v>0.03653419762849808</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03596702590584755</v>
+        <v>0.03596707805991173</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03561603650450706</v>
+        <v>0.03561608865857124</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03582786396145821</v>
+        <v>0.03582791611552238</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03515215590596199</v>
+        <v>0.03515220060944557</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03413248807191849</v>
+        <v>0.03413254022598267</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03313186764717102</v>
+        <v>0.0331319086253643</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03304930776357651</v>
+        <v>0.03304935246706009</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03362715616822243</v>
+        <v>0.03362719342112541</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04936326667666435</v>
+        <v>0.04936335980892181</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06071498245000839</v>
+        <v>0.06071508303284645</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06345938146114349</v>
+        <v>0.06345947831869125</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06446421891450882</v>
+        <v>0.06446430087089539</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06569310277700424</v>
+        <v>0.06569319218397141</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06338238716125488</v>
+        <v>0.06338246911764145</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06420854479074478</v>
+        <v>0.06420863419771194</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0637550950050354</v>
+        <v>0.06375516951084137</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06320900470018387</v>
+        <v>0.06320908665657043</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06279195100069046</v>
+        <v>0.06279201805591583</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0597161278128624</v>
+        <v>0.05971619486808777</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0574403777718544</v>
+        <v>0.05744044110178947</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05726358667016029</v>
+        <v>0.05726365000009537</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.05867672339081764</v>
+        <v>0.05867679044604301</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.08087998628616333</v>
+        <v>0.08088011294603348</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.09281545132398605</v>
+        <v>0.0928155779838562</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.09284943342208862</v>
+        <v>0.09284955263137817</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.09488745033740997</v>
+        <v>0.09488756954669952</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.09511442482471466</v>
+        <v>0.09511453658342361</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.09443804621696472</v>
+        <v>0.09443815052509308</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.09130918234586716</v>
+        <v>0.09130929410457611</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.09034091234207153</v>
+        <v>0.09034101665019989</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0906023234128952</v>
+        <v>0.09060243517160416</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.08760269731283188</v>
+        <v>0.08760279417037964</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.08340112864971161</v>
+        <v>0.08340121805667877</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.08142030239105225</v>
+        <v>0.08142037689685822</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.08357953280210495</v>
+        <v>0.08357962965965271</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.08428891003131866</v>
+        <v>0.08428898453712463</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.109975092113018</v>
+        <v>0.1099752336740494</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.1170998513698578</v>
+        <v>0.1171000152826309</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.1178495362401009</v>
+        <v>0.1178496778011322</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.1194950938224792</v>
+        <v>0.1194952204823494</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.1174563467502594</v>
+        <v>0.1174564957618713</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.1132811009883881</v>
+        <v>0.1132812276482582</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1137536913156509</v>
+        <v>0.1137538105249405</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.1128963157534599</v>
+        <v>0.1128964349627495</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.1115022972226143</v>
+        <v>0.111502394080162</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.1078397408127785</v>
+        <v>0.1078398525714874</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.1031942218542099</v>
+        <v>0.1031943187117577</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.1014878302812576</v>
+        <v>0.1014879196882248</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.10019501298666</v>
+        <v>0.1001951023936272</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.1032266840338707</v>
+        <v>0.1032267734408379</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.1383228600025177</v>
+        <v>0.1383230090141296</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.140497624874115</v>
+        <v>0.1404978185892105</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.1399353593587875</v>
+        <v>0.1399355083703995</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.1365563720464706</v>
+        <v>0.1365565061569214</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.1366278529167175</v>
+        <v>0.1366280168294907</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.1304530501365662</v>
+        <v>0.1304531842470169</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.1299313604831696</v>
+        <v>0.1299314796924591</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.1273974478244781</v>
+        <v>0.1273975670337677</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.1255345940589905</v>
+        <v>0.1255347281694412</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.1268115490674973</v>
+        <v>0.1268116533756256</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.1186889708042145</v>
+        <v>0.1186890825629234</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.1180447265505791</v>
+        <v>0.1180448308587074</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.1174065470695496</v>
+        <v>0.1174066588282585</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.1172870397567749</v>
+        <v>0.1172871515154839</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.1729487329721451</v>
+        <v>0.172948956489563</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.1710714995861053</v>
+        <v>0.1710716933012009</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1669260412454605</v>
+        <v>0.1669262498617172</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.1668651849031448</v>
+        <v>0.1668653786182404</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.1650345176458359</v>
+        <v>0.1650347113609314</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.1610164195299149</v>
+        <v>0.161016583442688</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.1571286767721176</v>
+        <v>0.1571288257837296</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.154232993721962</v>
+        <v>0.1542331427335739</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.1522310972213745</v>
+        <v>0.1522312313318253</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.148128017783165</v>
+        <v>0.1481281369924545</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.144443467259407</v>
+        <v>0.1444435715675354</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.1377998888492584</v>
+        <v>0.1377999931573868</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.1379229873418808</v>
+        <v>0.1379231065511703</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.1411561071872711</v>
+        <v>0.1411562263965607</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.1988352686166763</v>
+        <v>0.1988355070352554</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.1967368870973587</v>
+        <v>0.1967371255159378</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.1939200162887573</v>
+        <v>0.1939202398061752</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.1899362653493881</v>
+        <v>0.1899364441633224</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.1863023340702057</v>
+        <v>0.1863025426864624</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.1796433329582214</v>
+        <v>0.1796435117721558</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.1802505105733871</v>
+        <v>0.1802506893873215</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.1739073246717453</v>
+        <v>0.1739074885845184</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.1723753809928894</v>
+        <v>0.1723755151033401</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.1731348931789398</v>
+        <v>0.173135057091713</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.1603864133358002</v>
+        <v>0.1603865474462509</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.1578785181045532</v>
+        <v>0.157878652215004</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.1578940600156784</v>
+        <v>0.157894179224968</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.1640408039093018</v>
+        <v>0.1640409231185913</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.2343118190765381</v>
+        <v>0.2343120574951172</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.2217081487178802</v>
+        <v>0.2217084020376205</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.2216228991746902</v>
+        <v>0.2216231226921082</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.2199796438217163</v>
+        <v>0.2199798673391342</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.2107603996992111</v>
+        <v>0.2107605785131454</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.2073090225458145</v>
+        <v>0.20730921626091</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.2077720314264297</v>
+        <v>0.2077722102403641</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.2032981067895889</v>
+        <v>0.2032982856035233</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.2028147280216217</v>
+        <v>0.2028148919343948</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.1972729116678238</v>
+        <v>0.1972730606794357</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.1914772838354111</v>
+        <v>0.1914774179458618</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.1884277611970901</v>
+        <v>0.1884278953075409</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.1872883886098862</v>
+        <v>0.1872885227203369</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.1898732930421829</v>
+        <v>0.1898734569549561</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.2504976689815521</v>
+        <v>0.250497967004776</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.2472755759954453</v>
+        <v>0.2472758144140244</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.2392150163650513</v>
+        <v>0.2392152398824692</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.2376093864440918</v>
+        <v>0.2376096099615097</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.2306723296642303</v>
+        <v>0.2306725233793259</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.2317129075527191</v>
+        <v>0.2317130863666534</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.225933626294136</v>
+        <v>0.2259337902069092</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.2199755907058716</v>
+        <v>0.2199757397174835</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.2185096889734268</v>
+        <v>0.2185098528862</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2156016528606415</v>
+        <v>0.2156018018722534</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.2109702676534653</v>
+        <v>0.2109704166650772</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.209589958190918</v>
+        <v>0.2095901072025299</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.2119111269712448</v>
+        <v>0.2119113057851791</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.2139839679002762</v>
+        <v>0.2139841318130493</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.2672398686408997</v>
+        <v>0.2672401070594788</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.2572857141494751</v>
+        <v>0.2572859525680542</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.2558490335941315</v>
+        <v>0.2558492720127106</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.2485837787389755</v>
+        <v>0.248583972454071</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.2479168027639389</v>
+        <v>0.2479169964790344</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.2420514076948166</v>
+        <v>0.2420516014099121</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.2393912225961685</v>
+        <v>0.2393913716077805</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.2379436641931534</v>
+        <v>0.2379438281059265</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.2356540709733963</v>
+        <v>0.2356542199850082</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.233596995472908</v>
+        <v>0.23359714448452</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.2216817289590836</v>
+        <v>0.2216818630695343</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.2253722250461578</v>
+        <v>0.2253723740577698</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.2265103459358215</v>
+        <v>0.2265105098485947</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.2280198484659195</v>
+        <v>0.2280199974775314</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.2774821817874908</v>
+        <v>0.2774823904037476</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.2742945551872253</v>
+        <v>0.2742947638034821</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.2701353132724762</v>
+        <v>0.2701354920864105</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.2633942663669586</v>
+        <v>0.2633944451808929</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.2666073143482208</v>
+        <v>0.2666074931621552</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.2557661235332489</v>
+        <v>0.2557662725448608</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.2554018199443817</v>
+        <v>0.255401998758316</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.2493857145309448</v>
+        <v>0.249385878443718</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.2522963583469391</v>
+        <v>0.252296507358551</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.2515408992767334</v>
+        <v>0.2515410780906677</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.2480570822954178</v>
+        <v>0.2480572462081909</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.2479637265205383</v>
+        <v>0.2479638904333115</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.2478193044662476</v>
+        <v>0.2478194683790207</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.2593252658843994</v>
+        <v>0.2593254446983337</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.2841792404651642</v>
+        <v>0.2841794192790985</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.2847025394439697</v>
+        <v>0.2847026884555817</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.2741288244724274</v>
+        <v>0.2741290032863617</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.2765059769153595</v>
+        <v>0.2765061557292938</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.2669718265533447</v>
+        <v>0.2669719755649567</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.2684570848941803</v>
+        <v>0.2684572339057922</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.268137127161026</v>
+        <v>0.2681372761726379</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.2648625671863556</v>
+        <v>0.2648627460002899</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.2603660225868225</v>
+        <v>0.2603661715984344</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.2590891718864441</v>
+        <v>0.259089320898056</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.2613368630409241</v>
+        <v>0.261337012052536</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.2633356750011444</v>
+        <v>0.2633358240127563</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.2730752527713776</v>
+        <v>0.2730754613876343</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.2833245694637299</v>
+        <v>0.2833247780799866</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.288307398557663</v>
+        <v>0.2883075773715973</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.2886004149913788</v>
+        <v>0.2886005640029907</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.2806093692779541</v>
+        <v>0.280609518289566</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.2787407636642456</v>
+        <v>0.2787409424781799</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.2840398848056793</v>
+        <v>0.2840400338172913</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.2817472815513611</v>
+        <v>0.2817474603652954</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.2819203734397888</v>
+        <v>0.2819205522537231</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.2799591422080994</v>
+        <v>0.2799593508243561</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.2817789912223816</v>
+        <v>0.2817791998386383</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.2821460068225861</v>
+        <v>0.2821461856365204</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.2813436985015869</v>
+        <v>0.2813439071178436</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.2919933795928955</v>
+        <v>0.2919936180114746</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.2963405251502991</v>
+        <v>0.2963407933712006</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.3109511733055115</v>
+        <v>0.3109514117240906</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.3042809069156647</v>
+        <v>0.3042811155319214</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.3049757182598114</v>
+        <v>0.3049759268760681</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.3060508668422699</v>
+        <v>0.306051105260849</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.3059982061386108</v>
+        <v>0.3059984445571899</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.3041191399097443</v>
+        <v>0.3041193783283234</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.3025106489658356</v>
+        <v>0.3025108873844147</v>
       </c>
       <c r="GH4" t="n">
-        <v>0.2988065183162689</v>
+        <v>0.2988067269325256</v>
       </c>
       <c r="GI4" t="n">
-        <v>0.2995027899742126</v>
+        <v>0.2995030581951141</v>
       </c>
       <c r="GJ4" t="n">
-        <v>0.2998694479465485</v>
+        <v>0.29986971616745</v>
       </c>
       <c r="GK4" t="n">
-        <v>0.3037088513374329</v>
+        <v>0.303709089756012</v>
       </c>
       <c r="GL4" t="n">
-        <v>0.3102984130382538</v>
+        <v>0.3102986514568329</v>
       </c>
       <c r="GM4" t="n">
-        <v>0.316702276468277</v>
+        <v>0.3167025744915009</v>
       </c>
       <c r="GN4" t="n">
-        <v>0.3319770991802216</v>
+        <v>0.3319773972034454</v>
       </c>
       <c r="GO4" t="n">
-        <v>0.3397187888622284</v>
+        <v>0.3397191166877747</v>
       </c>
       <c r="GP4" t="n">
-        <v>0.3326640427112579</v>
+        <v>0.332664281129837</v>
       </c>
       <c r="GQ4" t="n">
-        <v>0.3297248184680939</v>
+        <v>0.329725056886673</v>
       </c>
       <c r="GR4" t="n">
-        <v>0.3286796808242798</v>
+        <v>0.3286799490451813</v>
       </c>
       <c r="GS4" t="n">
-        <v>0.3270716667175293</v>
+        <v>0.3270719051361084</v>
       </c>
       <c r="GT4" t="n">
-        <v>0.3283929824829102</v>
+        <v>0.3283932507038116</v>
       </c>
       <c r="GU4" t="n">
-        <v>0.3226777613162994</v>
+        <v>0.3226780295372009</v>
       </c>
       <c r="GV4" t="n">
-        <v>0.3278586864471436</v>
+        <v>0.327858954668045</v>
       </c>
       <c r="GW4" t="n">
-        <v>0.3229389786720276</v>
+        <v>0.3229392468929291</v>
       </c>
       <c r="GX4" t="n">
-        <v>0.3240161538124084</v>
+        <v>0.3240164816379547</v>
       </c>
       <c r="GY4" t="n">
-        <v>0.3242860436439514</v>
+        <v>0.3242863714694977</v>
       </c>
       <c r="GZ4" t="n">
-        <v>0.3374823331832886</v>
+        <v>0.3374826908111572</v>
       </c>
       <c r="HA4" t="n">
-        <v>0.3504157960414886</v>
+        <v>0.3504160940647125</v>
       </c>
       <c r="HB4" t="n">
-        <v>0.3628747165203094</v>
+        <v>0.3628751039505005</v>
       </c>
       <c r="HC4" t="n">
-        <v>0.3571552932262421</v>
+        <v>0.3571555912494659</v>
       </c>
       <c r="HD4" t="n">
-        <v>0.3451950252056122</v>
+        <v>0.3451954424381256</v>
       </c>
       <c r="HE4" t="n">
-        <v>0.3403863906860352</v>
+        <v>0.340386837720871</v>
       </c>
       <c r="HF4" t="n">
-        <v>0.3419497311115265</v>
+        <v>0.3419501781463623</v>
       </c>
       <c r="HG4" t="n">
-        <v>0.3484822511672974</v>
+        <v>0.3484826683998108</v>
       </c>
       <c r="HH4" t="n">
-        <v>0.3472996950149536</v>
+        <v>0.3473001420497894</v>
       </c>
       <c r="HI4" t="n">
-        <v>0.3456459045410156</v>
+        <v>0.3456463515758514</v>
       </c>
       <c r="HJ4" t="n">
-        <v>0.3481964766979218</v>
+        <v>0.3481968641281128</v>
       </c>
       <c r="HK4" t="n">
-        <v>0.3419178128242493</v>
+        <v>0.3419182002544403</v>
       </c>
       <c r="HL4" t="n">
-        <v>0.3436370193958282</v>
+        <v>0.3436374068260193</v>
       </c>
       <c r="HM4" t="n">
-        <v>0.3406157791614532</v>
+        <v>0.3406161963939667</v>
       </c>
       <c r="HN4" t="n">
-        <v>0.3638312220573425</v>
+        <v>0.3638316690921783</v>
       </c>
       <c r="HO4" t="n">
-        <v>0.3780696392059326</v>
+        <v>0.3780700266361237</v>
       </c>
       <c r="HP4" t="n">
-        <v>0.3578898012638092</v>
+        <v>0.3578901886940002</v>
       </c>
       <c r="HQ4" t="n">
-        <v>0.3463295698165894</v>
+        <v>0.3463298976421356</v>
       </c>
       <c r="HR4" t="inlineStr">
         <is>
@@ -3607,676 +3607,676 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02473416924476624</v>
+        <v>0.02473424561321735</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03344912827014923</v>
+        <v>0.0334492065012455</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03554841503500938</v>
+        <v>0.03554849326610565</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03709152340888977</v>
+        <v>0.03709160163998604</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0375659316778183</v>
+        <v>0.03756600618362427</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03685624152421951</v>
+        <v>0.03685631603002548</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03627607971429825</v>
+        <v>0.03627615049481392</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0359247699379921</v>
+        <v>0.03592483699321747</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0361330658197403</v>
+        <v>0.03613313660025597</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03544800356030464</v>
+        <v>0.03544807061553001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03440780192613602</v>
+        <v>0.03440786898136139</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03338329493999481</v>
+        <v>0.03338335454463959</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03330028802156448</v>
+        <v>0.03330034762620926</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03387780487537384</v>
+        <v>0.03387786448001862</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04992399364709854</v>
+        <v>0.04992411658167839</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06129185110330582</v>
+        <v>0.06129197776317596</v>
       </c>
       <c r="R5" t="n">
-        <v>0.06404826045036316</v>
+        <v>0.06404837965965271</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06500336527824402</v>
+        <v>0.06500349193811417</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06623104959726334</v>
+        <v>0.06623115390539169</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06387737393379211</v>
+        <v>0.06387748569250107</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06469281017780304</v>
+        <v>0.06469292193651199</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06422294676303864</v>
+        <v>0.06422305852174759</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06367694586515427</v>
+        <v>0.06367705762386322</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06324388086795807</v>
+        <v>0.06324398517608643</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.06013048440217972</v>
+        <v>0.06013057753443718</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05783383920788765</v>
+        <v>0.05783393606543541</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.05766372755169868</v>
+        <v>0.05766382068395615</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.05907176434993744</v>
+        <v>0.0590718612074852</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.08157885819673538</v>
+        <v>0.08157900720834732</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.09353896230459213</v>
+        <v>0.09353911876678467</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.09358442574739456</v>
+        <v>0.09358458966016769</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.09555032104253769</v>
+        <v>0.09555047005414963</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.09577368944883347</v>
+        <v>0.09577383100986481</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.09507549554109573</v>
+        <v>0.09507563710212708</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.09190917760133743</v>
+        <v>0.09190931916236877</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.09091836214065552</v>
+        <v>0.09091850370168686</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.09118612110614777</v>
+        <v>0.09118626266717911</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.08816232532262802</v>
+        <v>0.08816245943307877</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.08389640599489212</v>
+        <v>0.08389652520418167</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.08190591633319855</v>
+        <v>0.0819060280919075</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.08408883959054947</v>
+        <v>0.08408896625041962</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.08478704839944839</v>
+        <v>0.08478716015815735</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.1107722297310829</v>
+        <v>0.110772393643856</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.1179482862353325</v>
+        <v>0.117948479950428</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.1186547875404358</v>
+        <v>0.1186549663543701</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.120202824473381</v>
+        <v>0.1202029809355736</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.1182567328214645</v>
+        <v>0.1182569265365601</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.113974504172802</v>
+        <v>0.1139746606349945</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1144487261772156</v>
+        <v>0.1144488900899887</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.1135659962892532</v>
+        <v>0.1135661527514458</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.1121683865785599</v>
+        <v>0.1121685281395912</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.1084655001759529</v>
+        <v>0.1084656491875648</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.1037489995360374</v>
+        <v>0.1037491336464882</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.1020455956459045</v>
+        <v>0.1020457297563553</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.1007595360279083</v>
+        <v>0.1007596701383591</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.1037921458482742</v>
+        <v>0.103792279958725</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.1391679793596268</v>
+        <v>0.1391681581735611</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.1414147019386292</v>
+        <v>0.1414149105548859</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.1407982409000397</v>
+        <v>0.140798419713974</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.1373686343431473</v>
+        <v>0.1373688131570816</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.1374889612197876</v>
+        <v>0.1374891847372055</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.1312342286109924</v>
+        <v>0.1312344074249268</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.1306593120098114</v>
+        <v>0.1306594759225845</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1281212866306305</v>
+        <v>0.1281214356422424</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.1262461990118027</v>
+        <v>0.126246377825737</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.1274926364421844</v>
+        <v>0.1274928003549576</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1192925646901131</v>
+        <v>0.119292713701725</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.1186501309275627</v>
+        <v>0.1186502724885941</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.1180192157626152</v>
+        <v>0.1180193573236465</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.1178861409425735</v>
+        <v>0.1178862974047661</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.1741604059934616</v>
+        <v>0.1741607040166855</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.1722528636455536</v>
+        <v>0.1722531318664551</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1681053936481476</v>
+        <v>0.1681056618690491</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.167931467294693</v>
+        <v>0.1679317206144333</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.1660197824239731</v>
+        <v>0.1660200208425522</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.161988765001297</v>
+        <v>0.1619889885187149</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.1580227315425873</v>
+        <v>0.158022940158844</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.1551034599542618</v>
+        <v>0.1551036536693573</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.1530550420284271</v>
+        <v>0.1530552357435226</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.1488942056894302</v>
+        <v>0.1488943845033646</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.1451496332883835</v>
+        <v>0.1451498121023178</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1384663432836533</v>
+        <v>0.1384665071964264</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.1385905891656876</v>
+        <v>0.1385907381772995</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.1418365985155106</v>
+        <v>0.1418367773294449</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.2001295983791351</v>
+        <v>0.2001298815011978</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.1981051117181778</v>
+        <v>0.1981054395437241</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.1952085345983505</v>
+        <v>0.1952088326215744</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.1910886317491531</v>
+        <v>0.191088855266571</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.187435582280159</v>
+        <v>0.1874358505010605</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.1807045191526413</v>
+        <v>0.1807047575712204</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.1812525242567062</v>
+        <v>0.1812527626752853</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.1748516857624054</v>
+        <v>0.1748519092798233</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.1732723265886307</v>
+        <v>0.173272505402565</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.1739725768566132</v>
+        <v>0.1739727854728699</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.1611290574073792</v>
+        <v>0.1611292362213135</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.1585945039987564</v>
+        <v>0.1585946977138519</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.1585931330919266</v>
+        <v>0.1585933119058609</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.164780855178833</v>
+        <v>0.1647810488939285</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.2357019484043121</v>
+        <v>0.2357022762298584</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.2231611460447311</v>
+        <v>0.2231614738702774</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.2229321002960205</v>
+        <v>0.2229323983192444</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.2212783396244049</v>
+        <v>0.2212786376476288</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.2119531631469727</v>
+        <v>0.2119534313678741</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.2084413319826126</v>
+        <v>0.2084416151046753</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.2088407427072525</v>
+        <v>0.2088409811258316</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.2042566537857056</v>
+        <v>0.2042568773031235</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.2037457525730133</v>
+        <v>0.2037459760904312</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.198151096701622</v>
+        <v>0.1981513202190399</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.192267507314682</v>
+        <v>0.1922677010297775</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.1891844570636749</v>
+        <v>0.1891846507787704</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.1880125105381012</v>
+        <v>0.1880126893520355</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1906141638755798</v>
+        <v>0.1906143873929977</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.252103328704834</v>
+        <v>0.252103716135025</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.2487515658140182</v>
+        <v>0.2487518936395645</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.2405418306589127</v>
+        <v>0.2405421286821365</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.2388899475336075</v>
+        <v>0.2388902604579926</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.2318812757730484</v>
+        <v>0.2318815588951111</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.2327947169542313</v>
+        <v>0.2327949702739716</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.2269324511289597</v>
+        <v>0.2269326895475388</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.2209241986274719</v>
+        <v>0.2209244221448898</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.2194149494171143</v>
+        <v>0.2194151878356934</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.2164526730775833</v>
+        <v>0.2164528965950012</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.2117479145526886</v>
+        <v>0.2117480933666229</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.2102702707052231</v>
+        <v>0.2102704793214798</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.212636724114418</v>
+        <v>0.2126369625329971</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.2147049158811569</v>
+        <v>0.2147051244974136</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.2687053978443146</v>
+        <v>0.2687057256698608</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.2586471438407898</v>
+        <v>0.2586474418640137</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.2571910321712494</v>
+        <v>0.2571913301944733</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.249737948179245</v>
+        <v>0.2497382313013077</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.2489961385726929</v>
+        <v>0.2489964067935944</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.2430773675441742</v>
+        <v>0.2430776208639145</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.2403547018766403</v>
+        <v>0.2403549551963806</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.2388584613800049</v>
+        <v>0.2388586848974228</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.2365140914916992</v>
+        <v>0.2365143150091171</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.2344180792570114</v>
+        <v>0.2344182729721069</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.2224546819925308</v>
+        <v>0.2224549055099487</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.2260747998952866</v>
+        <v>0.2260749936103821</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.2271648645401001</v>
+        <v>0.2271650731563568</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.2287115007638931</v>
+        <v>0.2287117093801498</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.2787213325500488</v>
+        <v>0.2787216305732727</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.2754302620887756</v>
+        <v>0.2754305601119995</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.2711918652057648</v>
+        <v>0.2711921334266663</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.264357715845108</v>
+        <v>0.2643579542636871</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.2675284445285797</v>
+        <v>0.2675286829471588</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.25661501288414</v>
+        <v>0.2566152513027191</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.2562940120697021</v>
+        <v>0.2562942504882812</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.2502082288265228</v>
+        <v>0.2502084374427795</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.2530697584152222</v>
+        <v>0.2530699670314789</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.2522704601287842</v>
+        <v>0.2522706687450409</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.2487702369689941</v>
+        <v>0.248770460486412</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.248612642288208</v>
+        <v>0.2486128658056259</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.2484367936849594</v>
+        <v>0.2484370023012161</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.260022908449173</v>
+        <v>0.2600231468677521</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.2849517166614532</v>
+        <v>0.28495192527771</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.285477340221405</v>
+        <v>0.2854775488376617</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.274850994348526</v>
+        <v>0.2748512029647827</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.277224063873291</v>
+        <v>0.2772242724895477</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.2676565647125244</v>
+        <v>0.2676567435264587</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.2691462337970734</v>
+        <v>0.2691464424133301</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.2688190042972565</v>
+        <v>0.2688192129135132</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.2655416429042816</v>
+        <v>0.2655418515205383</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.2610313296318054</v>
+        <v>0.2610315382480621</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.259748786687851</v>
+        <v>0.2597489953041077</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.2619999051094055</v>
+        <v>0.2620001137256622</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.263938695192337</v>
+        <v>0.2639389336109161</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.273695319890976</v>
+        <v>0.2736955881118774</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.283971756696701</v>
+        <v>0.2839720249176025</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.2891016602516174</v>
+        <v>0.2891019284725189</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.2893572747707367</v>
+        <v>0.2893575131893158</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.2813360989093781</v>
+        <v>0.2813363671302795</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.2794694304466248</v>
+        <v>0.2794696688652039</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.2847943305969238</v>
+        <v>0.2847945988178253</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.2825057208538055</v>
+        <v>0.282505989074707</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.2826947867870331</v>
+        <v>0.2826950252056122</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.2807413339614868</v>
+        <v>0.2807415723800659</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.2825755774974823</v>
+        <v>0.2825758457183838</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.2829520404338837</v>
+        <v>0.2829523086547852</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.2821106910705566</v>
+        <v>0.2821109592914581</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.2927424013614655</v>
+        <v>0.2927426993846893</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.2971332967281342</v>
+        <v>0.2971336245536804</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.3117668032646179</v>
+        <v>0.3117671310901642</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.3053008317947388</v>
+        <v>0.305301159620285</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.3060197234153748</v>
+        <v>0.306020051240921</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.3071396350860596</v>
+        <v>0.3071399629116058</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.3071007132530212</v>
+        <v>0.3071010708808899</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.3051992356777191</v>
+        <v>0.3051995635032654</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.3035702705383301</v>
+        <v>0.3035706281661987</v>
       </c>
       <c r="GH5" t="n">
-        <v>0.2998573482036591</v>
+        <v>0.2998576760292053</v>
       </c>
       <c r="GI5" t="n">
-        <v>0.3005275428295135</v>
+        <v>0.3005278408527374</v>
       </c>
       <c r="GJ5" t="n">
-        <v>0.3009275794029236</v>
+        <v>0.3009279072284698</v>
       </c>
       <c r="GK5" t="n">
-        <v>0.3047831356525421</v>
+        <v>0.3047835230827332</v>
       </c>
       <c r="GL5" t="n">
-        <v>0.3113350868225098</v>
+        <v>0.3113354742527008</v>
       </c>
       <c r="GM5" t="n">
-        <v>0.3177025020122528</v>
+        <v>0.3177029192447662</v>
       </c>
       <c r="GN5" t="n">
-        <v>0.333007425069809</v>
+        <v>0.3330078125</v>
       </c>
       <c r="GO5" t="n">
-        <v>0.3408304452896118</v>
+        <v>0.3408308327198029</v>
       </c>
       <c r="GP5" t="n">
-        <v>0.3337565362453461</v>
+        <v>0.3337568938732147</v>
       </c>
       <c r="GQ5" t="n">
-        <v>0.3307534456253052</v>
+        <v>0.3307538330554962</v>
       </c>
       <c r="GR5" t="n">
-        <v>0.3297140300273895</v>
+        <v>0.3297143876552582</v>
       </c>
       <c r="GS5" t="n">
-        <v>0.3281110823154449</v>
+        <v>0.3281114101409912</v>
       </c>
       <c r="GT5" t="n">
-        <v>0.3294674456119537</v>
+        <v>0.3294678032398224</v>
       </c>
       <c r="GU5" t="n">
-        <v>0.3237526714801788</v>
+        <v>0.3237530291080475</v>
       </c>
       <c r="GV5" t="n">
-        <v>0.3289768099784851</v>
+        <v>0.3289771974086761</v>
       </c>
       <c r="GW5" t="n">
-        <v>0.324056476354599</v>
+        <v>0.3240568935871124</v>
       </c>
       <c r="GX5" t="n">
-        <v>0.3251681327819824</v>
+        <v>0.3251685798168182</v>
       </c>
       <c r="GY5" t="n">
-        <v>0.3254671990871429</v>
+        <v>0.3254676163196564</v>
       </c>
       <c r="GZ5" t="n">
-        <v>0.3386398255825043</v>
+        <v>0.3386402726173401</v>
       </c>
       <c r="HA5" t="n">
-        <v>0.3515213131904602</v>
+        <v>0.3515217304229736</v>
       </c>
       <c r="HB5" t="n">
-        <v>0.3640884757041931</v>
+        <v>0.3640889823436737</v>
       </c>
       <c r="HC5" t="n">
-        <v>0.3581221997737885</v>
+        <v>0.3581225872039795</v>
       </c>
       <c r="HD5" t="n">
-        <v>0.346624881029129</v>
+        <v>0.3466254472732544</v>
       </c>
       <c r="HE5" t="n">
-        <v>0.3417509198188782</v>
+        <v>0.3417514860630035</v>
       </c>
       <c r="HF5" t="n">
-        <v>0.3433244228363037</v>
+        <v>0.3433250188827515</v>
       </c>
       <c r="HG5" t="n">
-        <v>0.3499058485031128</v>
+        <v>0.3499063551425934</v>
       </c>
       <c r="HH5" t="n">
-        <v>0.348772406578064</v>
+        <v>0.3487730026245117</v>
       </c>
       <c r="HI5" t="n">
-        <v>0.3471459448337555</v>
+        <v>0.3471465706825256</v>
       </c>
       <c r="HJ5" t="n">
-        <v>0.3497397899627686</v>
+        <v>0.3497403860092163</v>
       </c>
       <c r="HK5" t="n">
-        <v>0.3434745967388153</v>
+        <v>0.3434751629829407</v>
       </c>
       <c r="HL5" t="n">
-        <v>0.345231294631958</v>
+        <v>0.3452318608760834</v>
       </c>
       <c r="HM5" t="n">
-        <v>0.342235267162323</v>
+        <v>0.3422358334064484</v>
       </c>
       <c r="HN5" t="n">
-        <v>0.3654313385486603</v>
+        <v>0.365431934595108</v>
       </c>
       <c r="HO5" t="n">
-        <v>0.3796762824058533</v>
+        <v>0.3796768486499786</v>
       </c>
       <c r="HP5" t="n">
-        <v>0.3590726554393768</v>
+        <v>0.3590731620788574</v>
       </c>
       <c r="HQ5" t="n">
-        <v>0.3472073376178741</v>
+        <v>0.3472077548503876</v>
       </c>
       <c r="HR5" t="inlineStr">
         <is>
@@ -4291,676 +4291,676 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02517016604542732</v>
+        <v>0.02517027035355568</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03390558809041977</v>
+        <v>0.03390568867325783</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03599368408322334</v>
+        <v>0.0359937883913517</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03752031922340393</v>
+        <v>0.03752041980624199</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03797036409378052</v>
+        <v>0.03797045722603798</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03723613545298576</v>
+        <v>0.03723622858524323</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03663570806384087</v>
+        <v>0.03663580119609833</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03628024458885193</v>
+        <v>0.03628033399581909</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03648055344820023</v>
+        <v>0.03648064285516739</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03578010573983192</v>
+        <v>0.03578019142150879</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03471121564507484</v>
+        <v>0.03471130132675171</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03364787623286247</v>
+        <v>0.03364795446395874</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03356094658374786</v>
+        <v>0.03356102854013443</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03413160517811775</v>
+        <v>0.03413168340921402</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05059100687503815</v>
+        <v>0.05059117078781128</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.06199342012405396</v>
+        <v>0.06199358031153679</v>
       </c>
       <c r="R6" t="n">
-        <v>0.06476205587387085</v>
+        <v>0.06476221978664398</v>
       </c>
       <c r="S6" t="n">
-        <v>0.06565424054861069</v>
+        <v>0.06565439701080322</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06687222421169281</v>
+        <v>0.06687237322330475</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06445269286632538</v>
+        <v>0.06445284187793732</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06525736302137375</v>
+        <v>0.06525750458240509</v>
       </c>
       <c r="W6" t="n">
-        <v>0.06475251168012619</v>
+        <v>0.06475265324115753</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06420790404081345</v>
+        <v>0.06420805305242538</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0637521892786026</v>
+        <v>0.06375232338905334</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0605868473649025</v>
+        <v>0.06058697402477264</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.05824298411607742</v>
+        <v>0.05824310705065727</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.05807644873857498</v>
+        <v>0.05807656794786453</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.05947060510516167</v>
+        <v>0.05947072803974152</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.08242927491664886</v>
+        <v>0.08242946863174438</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.09444023668766022</v>
+        <v>0.09444043785333633</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.09449491649866104</v>
+        <v>0.09449511021375656</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.09636606276035309</v>
+        <v>0.09636625647544861</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.09656601399183273</v>
+        <v>0.09656621515750885</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.09583082795143127</v>
+        <v>0.0958310142159462</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.09261066466569901</v>
+        <v>0.09261084347963333</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.09157418459653854</v>
+        <v>0.09157436341047287</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.09185347706079483</v>
+        <v>0.09185365587472916</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.08878914266824722</v>
+        <v>0.08878931403160095</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.08443297445774078</v>
+        <v>0.08443313837051392</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.08240904659032822</v>
+        <v>0.08240920305252075</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.08461112529039383</v>
+        <v>0.08461129665374756</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.08528981357812881</v>
+        <v>0.08528996258974075</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.1117576584219933</v>
+        <v>0.11175786703825</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.1190429255366325</v>
+        <v>0.1190431639552116</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.1196847930550575</v>
+        <v>0.1196850091218948</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1210981607437134</v>
+        <v>0.1210983693599701</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.1192080825567245</v>
+        <v>0.1192083284258842</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.1147996187210083</v>
+        <v>0.114799827337265</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1152569204568863</v>
+        <v>0.1152571365237236</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.1143244728446007</v>
+        <v>0.1143246814608574</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.1129267066717148</v>
+        <v>0.1129268929362297</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.1091613918542862</v>
+        <v>0.1091615855693817</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.1043474525213242</v>
+        <v>0.1043476313352585</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.1026197150349617</v>
+        <v>0.1026198863983154</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.1013306602835655</v>
+        <v>0.1013308465480804</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.1043567731976509</v>
+        <v>0.1043569594621658</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.1402752846479416</v>
+        <v>0.1402755081653595</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.1425856351852417</v>
+        <v>0.1425859034061432</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.1418837308883667</v>
+        <v>0.1418839693069458</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.138389527797699</v>
+        <v>0.1383897513151169</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.1385085731744766</v>
+        <v>0.1385088264942169</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.1321480125188828</v>
+        <v>0.1321482360363007</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.1315048038959503</v>
+        <v>0.131505012512207</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.1289337575435638</v>
+        <v>0.1289339661598206</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.1270499378442764</v>
+        <v>0.1270501613616943</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.1282547265291214</v>
+        <v>0.1282549202442169</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.1199386492371559</v>
+        <v>0.1199388429522514</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.1192644760012627</v>
+        <v>0.1192646697163582</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.1186322495341301</v>
+        <v>0.1186324432492256</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.1184756904840469</v>
+        <v>0.1184758916497231</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.1756865084171295</v>
+        <v>0.1756868660449982</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.1737146973609924</v>
+        <v>0.1737150251865387</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1695342510938644</v>
+        <v>0.1695346087217331</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.1692362129688263</v>
+        <v>0.1692365109920502</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.1671718657016754</v>
+        <v>0.1671721786260605</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.1630954146385193</v>
+        <v>0.1630957126617432</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.1590450257062912</v>
+        <v>0.1590452790260315</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.1560738831758499</v>
+        <v>0.1560741662979126</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.1539661288261414</v>
+        <v>0.1539663821458817</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.1497348845005035</v>
+        <v>0.1497351080179214</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.145894467830658</v>
+        <v>0.1458946913480759</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.1391336917877197</v>
+        <v>0.1391339004039764</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.1392530053853989</v>
+        <v>0.1392532140016556</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.1424946784973145</v>
+        <v>0.1424949169158936</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.2016998380422592</v>
+        <v>0.2017002254724503</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.1997589468955994</v>
+        <v>0.1997593492269516</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.196725144982338</v>
+        <v>0.196725532412529</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.1924317181110382</v>
+        <v>0.1924320310354233</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.1887277960777283</v>
+        <v>0.1887281537055969</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.1818866580724716</v>
+        <v>0.1818870007991791</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.1823594123125076</v>
+        <v>0.1823597401380539</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.1758837252855301</v>
+        <v>0.175884023308754</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.1742531806230545</v>
+        <v>0.1742534339427948</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.1748862564563751</v>
+        <v>0.1748865246772766</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.1618903279304504</v>
+        <v>0.1618905663490295</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.1592940241098404</v>
+        <v>0.1592942625284195</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.1592652797698975</v>
+        <v>0.1592655032873154</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.1654877811670303</v>
+        <v>0.1654880344867706</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.2373222857713699</v>
+        <v>0.2373227030038834</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.2248374968767166</v>
+        <v>0.2248379290103912</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.2244156897068024</v>
+        <v>0.2244160622358322</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.2227082699537277</v>
+        <v>0.22270867228508</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.2132617235183716</v>
+        <v>0.2132620811462402</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.2096735239028931</v>
+        <v>0.2096738666296005</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.2099950909614563</v>
+        <v>0.2099954038858414</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.2052871733903885</v>
+        <v>0.2052874714136124</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.2047177404165268</v>
+        <v>0.2047180384397507</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.1990573108196259</v>
+        <v>0.1990575939416885</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.1930468827486038</v>
+        <v>0.1930471360683441</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.1899200081825256</v>
+        <v>0.1899202615022659</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.1887008845806122</v>
+        <v>0.1887011229991913</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1912970393896103</v>
+        <v>0.1912973076105118</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.2538777887821198</v>
+        <v>0.2538783252239227</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.2503501772880554</v>
+        <v>0.2503506541252136</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.2419982701539993</v>
+        <v>0.2419986575841904</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.2402799725532532</v>
+        <v>0.2402803748846054</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.2331686913967133</v>
+        <v>0.2331690788269043</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.2339462041854858</v>
+        <v>0.2339465469121933</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.2279721796512604</v>
+        <v>0.2279724925756454</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.2219014316797256</v>
+        <v>0.2219017297029495</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.2203274220228195</v>
+        <v>0.2203277349472046</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.2172944396734238</v>
+        <v>0.2172947227954865</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.2125003635883331</v>
+        <v>0.2125006020069122</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.2109064310789108</v>
+        <v>0.2109066843986511</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.2133038938045502</v>
+        <v>0.2133041620254517</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.2153543829917908</v>
+        <v>0.2153546512126923</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.2702867388725281</v>
+        <v>0.2702871859073639</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.2601114511489868</v>
+        <v>0.2601118683815002</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.2586124241352081</v>
+        <v>0.2586128413677216</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.2509621679782867</v>
+        <v>0.2509625554084778</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.2501130104064941</v>
+        <v>0.2501133680343628</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.2441292405128479</v>
+        <v>0.2441295832395554</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.2413289546966553</v>
+        <v>0.2413292825222015</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.2397627085447311</v>
+        <v>0.2397630214691162</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.2373688369989395</v>
+        <v>0.2373691350221634</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.2352264076471329</v>
+        <v>0.2352266907691956</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.2231782227754593</v>
+        <v>0.223178505897522</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.2267202585935593</v>
+        <v>0.2267205268144608</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.2277390360832214</v>
+        <v>0.2277393043041229</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.2293209433555603</v>
+        <v>0.229321226477623</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.2800043821334839</v>
+        <v>0.2800047695636749</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.2765668332576752</v>
+        <v>0.2765672206878662</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.2722377479076385</v>
+        <v>0.2722381055355072</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.2652983069419861</v>
+        <v>0.2652986347675323</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.2684288322925568</v>
+        <v>0.2684291303157806</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.2574323415756226</v>
+        <v>0.2574326395988464</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.2571604251861572</v>
+        <v>0.2571607530117035</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.2509785294532776</v>
+        <v>0.2509787976741791</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.2538009285926819</v>
+        <v>0.2538011968135834</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.2529424130916595</v>
+        <v>0.252942681312561</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.2494071573019028</v>
+        <v>0.2494074404239655</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.2491773962974548</v>
+        <v>0.2491776496171951</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.2489552050828934</v>
+        <v>0.2489554733037949</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.2606182098388672</v>
+        <v>0.2606185078620911</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.2856765389442444</v>
+        <v>0.2856768071651459</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.286200076341629</v>
+        <v>0.2862003445625305</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.2755210995674133</v>
+        <v>0.2755213677883148</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.2778788506984711</v>
+        <v>0.2778791189193726</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.2682742774486542</v>
+        <v>0.2682745754718781</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.2697587907314301</v>
+        <v>0.2697590589523315</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.2694271206855774</v>
+        <v>0.2694273889064789</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.2661425471305847</v>
+        <v>0.2661428153514862</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.2616211473941803</v>
+        <v>0.2616214156150818</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.2603334784507751</v>
+        <v>0.2603337466716766</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.2625717520713806</v>
+        <v>0.2625720202922821</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.2644355893135071</v>
+        <v>0.264435887336731</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.2741954624652863</v>
+        <v>0.2741957902908325</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.2844903469085693</v>
+        <v>0.284490704536438</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.2898115217685699</v>
+        <v>0.2898118197917938</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.2900263667106628</v>
+        <v>0.2900266945362091</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.2819752097129822</v>
+        <v>0.2819755077362061</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.2801010310649872</v>
+        <v>0.2801013588905334</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.2854616045951843</v>
+        <v>0.2854619026184082</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.2831636667251587</v>
+        <v>0.283163994550705</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.2833709716796875</v>
+        <v>0.2833713293075562</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.2814218997955322</v>
+        <v>0.2814222276210785</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.2832595705986023</v>
+        <v>0.2832598984241486</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.2836438417434692</v>
+        <v>0.2836441695690155</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.2827430069446564</v>
+        <v>0.282743364572525</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.2933399081230164</v>
+        <v>0.293340265750885</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.2977727651596069</v>
+        <v>0.2977731823921204</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.3124332129955292</v>
+        <v>0.3124336302280426</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.3062098622322083</v>
+        <v>0.3062102794647217</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.3069458305835724</v>
+        <v>0.3069462180137634</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.3081099689006805</v>
+        <v>0.308110386133194</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.3080827593803406</v>
+        <v>0.3080832064151764</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.306151956319809</v>
+        <v>0.3061524033546448</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.3045004606246948</v>
+        <v>0.3045009076595306</v>
       </c>
       <c r="GH6" t="n">
-        <v>0.3007713854312897</v>
+        <v>0.3007718324661255</v>
       </c>
       <c r="GI6" t="n">
-        <v>0.3013830184936523</v>
+        <v>0.3013834655284882</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.3018361926078796</v>
+        <v>0.3018366396427155</v>
       </c>
       <c r="GK6" t="n">
-        <v>0.3056974112987518</v>
+        <v>0.3056978583335876</v>
       </c>
       <c r="GL6" t="n">
-        <v>0.3121927380561829</v>
+        <v>0.3121932148933411</v>
       </c>
       <c r="GM6" t="n">
-        <v>0.3185139298439026</v>
+        <v>0.3185144364833832</v>
       </c>
       <c r="GN6" t="n">
-        <v>0.3338444828987122</v>
+        <v>0.3338450193405151</v>
       </c>
       <c r="GO6" t="n">
-        <v>0.3417541086673737</v>
+        <v>0.3417546451091766</v>
       </c>
       <c r="GP6" t="n">
-        <v>0.3346989154815674</v>
+        <v>0.3346993625164032</v>
       </c>
       <c r="GQ6" t="n">
-        <v>0.3316204845905304</v>
+        <v>0.3316209614276886</v>
       </c>
       <c r="GR6" t="n">
-        <v>0.330598384141922</v>
+        <v>0.3305988609790802</v>
       </c>
       <c r="GS6" t="n">
-        <v>0.3289921581745148</v>
+        <v>0.3289926052093506</v>
       </c>
       <c r="GT6" t="n">
-        <v>0.3303806781768799</v>
+        <v>0.3303811550140381</v>
       </c>
       <c r="GU6" t="n">
-        <v>0.3246597349643707</v>
+        <v>0.3246602118015289</v>
       </c>
       <c r="GV6" t="n">
-        <v>0.3299203217029572</v>
+        <v>0.3299208283424377</v>
       </c>
       <c r="GW6" t="n">
-        <v>0.3249919414520264</v>
+        <v>0.3249924778938293</v>
       </c>
       <c r="GX6" t="n">
-        <v>0.3261327743530273</v>
+        <v>0.3261333107948303</v>
       </c>
       <c r="GY6" t="n">
-        <v>0.3264530599117279</v>
+        <v>0.3264535963535309</v>
       </c>
       <c r="GZ6" t="n">
-        <v>0.3395974040031433</v>
+        <v>0.3395979702472687</v>
       </c>
       <c r="HA6" t="n">
-        <v>0.3524373769760132</v>
+        <v>0.3524379134178162</v>
       </c>
       <c r="HB6" t="n">
-        <v>0.3650981187820435</v>
+        <v>0.3650987148284912</v>
       </c>
       <c r="HC6" t="n">
-        <v>0.3589120805263519</v>
+        <v>0.3589125573635101</v>
       </c>
       <c r="HD6" t="n">
-        <v>0.3477976620197296</v>
+        <v>0.3477983772754669</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.3428674936294556</v>
+        <v>0.3428682088851929</v>
       </c>
       <c r="HF6" t="n">
-        <v>0.3444588184356689</v>
+        <v>0.3444595336914062</v>
       </c>
       <c r="HG6" t="n">
-        <v>0.3510854840278625</v>
+        <v>0.3510861396789551</v>
       </c>
       <c r="HH6" t="n">
-        <v>0.3499990999698639</v>
+        <v>0.3499998152256012</v>
       </c>
       <c r="HI6" t="n">
-        <v>0.3483980596065521</v>
+        <v>0.3483987748622894</v>
       </c>
       <c r="HJ6" t="n">
-        <v>0.3510384261608124</v>
+        <v>0.3510391712188721</v>
       </c>
       <c r="HK6" t="n">
-        <v>0.344787061214447</v>
+        <v>0.3447877764701843</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.3465873301029205</v>
+        <v>0.3465880155563354</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.3436257839202881</v>
+        <v>0.343626469373703</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.3667937219142914</v>
+        <v>0.3667944371700287</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.3810317814350128</v>
+        <v>0.3810324966907501</v>
       </c>
       <c r="HP6" t="n">
-        <v>0.3600632548332214</v>
+        <v>0.3600638508796692</v>
       </c>
       <c r="HQ6" t="n">
-        <v>0.3479192852973938</v>
+        <v>0.347919762134552</v>
       </c>
       <c r="HR6" t="inlineStr">
         <is>
@@ -4975,676 +4975,676 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02555966377258301</v>
+        <v>0.0255597960203886</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03430430591106415</v>
+        <v>0.03430443629622459</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03638430312275887</v>
+        <v>0.03638442978262901</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03789743408560753</v>
+        <v>0.03789756074547768</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03832289576530457</v>
+        <v>0.03832301497459412</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03756701573729515</v>
+        <v>0.0375671312212944</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03694743663072586</v>
+        <v>0.03694754838943481</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03658726066350937</v>
+        <v>0.03658737242221832</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03678048029541969</v>
+        <v>0.03678059577941895</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03606660291552544</v>
+        <v>0.03606671467423439</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03497055172920227</v>
+        <v>0.03497065603733063</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03387970104813576</v>
+        <v>0.03387979790568352</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03378965333104134</v>
+        <v>0.03378975391387939</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03435652703046799</v>
+        <v>0.03435662761330605</v>
       </c>
       <c r="P7" t="n">
-        <v>0.05119466409087181</v>
+        <v>0.05119486525654793</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.06260639429092407</v>
+        <v>0.06260659545660019</v>
       </c>
       <c r="R7" t="n">
-        <v>0.06538324803113937</v>
+        <v>0.06538344919681549</v>
       </c>
       <c r="S7" t="n">
-        <v>0.06621861457824707</v>
+        <v>0.06621880084276199</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06742673367261887</v>
+        <v>0.06742691993713379</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06495322287082672</v>
+        <v>0.06495340168476105</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0657414123415947</v>
+        <v>0.06574159115552902</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06520853191614151</v>
+        <v>0.06520871073007584</v>
       </c>
       <c r="X7" t="n">
-        <v>0.06465836614370346</v>
+        <v>0.06465854495763779</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.06418103724718094</v>
+        <v>0.06418120861053467</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.06096884235739708</v>
+        <v>0.06096899881958961</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.05859604850411415</v>
+        <v>0.05859620124101639</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.05843093246221542</v>
+        <v>0.05843108519911766</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.05981743335723877</v>
+        <v>0.05981758609414101</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.08317727595567703</v>
+        <v>0.08317751437425613</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0952187106013298</v>
+        <v>0.09521894901990891</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.09527372568845749</v>
+        <v>0.09527397900819778</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.09705741703510284</v>
+        <v>0.09705764800310135</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.09723765403032303</v>
+        <v>0.09723789244890213</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.09646962583065033</v>
+        <v>0.09646984934806824</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09319928288459778</v>
+        <v>0.09319950640201569</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.09212687611579895</v>
+        <v>0.09212709218263626</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.09240712970495224</v>
+        <v>0.09240735322237015</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.08931015431880951</v>
+        <v>0.08931037038564682</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.08488446474075317</v>
+        <v>0.08488466590642929</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.08283605426549911</v>
+        <v>0.08283624053001404</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.085053451359272</v>
+        <v>0.08505365252494812</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.08571616560220718</v>
+        <v>0.0857163593173027</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.1126212328672409</v>
+        <v>0.1126214936375618</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.1199614703655243</v>
+        <v>0.1199617609381676</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.1205417662858963</v>
+        <v>0.1205420419573784</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1218364983797073</v>
+        <v>0.121836744248867</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.1200085803866386</v>
+        <v>0.1200088784098625</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.115484394133091</v>
+        <v>0.1154846474528313</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1159280985593796</v>
+        <v>0.1159283593297005</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.1149563193321228</v>
+        <v>0.1149565726518631</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.1135492101311684</v>
+        <v>0.1135494485497475</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.1097381636500359</v>
+        <v>0.1097384095191956</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.1048421785235405</v>
+        <v>0.1048423945903778</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.1031010150909424</v>
+        <v>0.1031012237071991</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.1018154472112656</v>
+        <v>0.1018156707286835</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.1048342362046242</v>
+        <v>0.1048344671726227</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.1412138491868973</v>
+        <v>0.1412141174077988</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.1435614675283432</v>
+        <v>0.1435617804527283</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.1427788883447647</v>
+        <v>0.1427791863679886</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.1392088830471039</v>
+        <v>0.1392091363668442</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.1393493115901947</v>
+        <v>0.139349639415741</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.1328990012407303</v>
+        <v>0.132899284362793</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.1321932524442673</v>
+        <v>0.1321935057640076</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.1296034753322601</v>
+        <v>0.1296037435531616</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.127702608704567</v>
+        <v>0.1277028769254684</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.1288702934980392</v>
+        <v>0.1288705468177795</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1204679980874062</v>
+        <v>0.1204682365059853</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.1197800263762474</v>
+        <v>0.1197802573442459</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.1191519051790237</v>
+        <v>0.1191521510481834</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.1189799383282661</v>
+        <v>0.1189801841974258</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.1769676506519318</v>
+        <v>0.1769680678844452</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.1749031692743301</v>
+        <v>0.1749035716056824</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1706938296556473</v>
+        <v>0.1706942468881607</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.1702645123004913</v>
+        <v>0.1702648997306824</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.1681049317121506</v>
+        <v>0.1681053042411804</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1640018373727798</v>
+        <v>0.1640021950006485</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.1598677337169647</v>
+        <v>0.159868061542511</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.1568611413240433</v>
+        <v>0.1568614840507507</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.1547058373689651</v>
+        <v>0.1547061502933502</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.1504175215959549</v>
+        <v>0.1504178047180176</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.1465038955211639</v>
+        <v>0.1465041637420654</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.1396975964307785</v>
+        <v>0.13969786465168</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.1398171931505203</v>
+        <v>0.1398174613714218</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.1430598944425583</v>
+        <v>0.1430601924657822</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.2029811292886734</v>
+        <v>0.2029815912246704</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.2010700851678848</v>
+        <v>0.2010705918073654</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.1979428976774216</v>
+        <v>0.1979433447122574</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.1935014277696609</v>
+        <v>0.1935018450021744</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.1897662580013275</v>
+        <v>0.1897666901350021</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.1828470379114151</v>
+        <v>0.1828474402427673</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.183257132768631</v>
+        <v>0.1832575052976608</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.1767198741436005</v>
+        <v>0.1767202168703079</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.1750420928001404</v>
+        <v>0.1750424206256866</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.1756152808666229</v>
+        <v>0.1756156086921692</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.1625233143568039</v>
+        <v>0.1625235974788666</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.1598909646272659</v>
+        <v>0.159891277551651</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.1598489731550217</v>
+        <v>0.1598492711782455</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.1661002635955811</v>
+        <v>0.1661005765199661</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.2386042922735214</v>
+        <v>0.2386047840118408</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.2261667102575302</v>
+        <v>0.226167231798172</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.2256029844284058</v>
+        <v>0.225603461265564</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.2238726913928986</v>
+        <v>0.2238731682300568</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.2143155187368393</v>
+        <v>0.2143159508705139</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.2106657922267914</v>
+        <v>0.210666224360466</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.2109282463788986</v>
+        <v>0.2109286338090897</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.2061149328947067</v>
+        <v>0.2061153054237366</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.2055249810218811</v>
+        <v>0.2055253535509109</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1998102813959122</v>
+        <v>0.1998106390237808</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.1937062591314316</v>
+        <v>0.1937065869569778</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.1905431002378464</v>
+        <v>0.1905433982610703</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.1892965883016586</v>
+        <v>0.1892968863248825</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.191903680562973</v>
+        <v>0.1919040083885193</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.2553177177906036</v>
+        <v>0.2553183436393738</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.2516640424728394</v>
+        <v>0.2516646087169647</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.2431709915399551</v>
+        <v>0.2431714832782745</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.2414034008979797</v>
+        <v>0.2414038926362991</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.2342162728309631</v>
+        <v>0.2342167347669601</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.234872505068779</v>
+        <v>0.2348729223012924</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.228828951716423</v>
+        <v>0.2288293242454529</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.2227123826742172</v>
+        <v>0.2227127552032471</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.2211010903120041</v>
+        <v>0.2211014628410339</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.2180220782756805</v>
+        <v>0.2180224508047104</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.213150218129158</v>
+        <v>0.2131505459547043</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.2114570140838623</v>
+        <v>0.2114573270082474</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.2138978093862534</v>
+        <v>0.2138981372117996</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.2159418314695358</v>
+        <v>0.2159421741962433</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.2715796530246735</v>
+        <v>0.2715802192687988</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.2613034546375275</v>
+        <v>0.2613039910793304</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.2597808539867401</v>
+        <v>0.2597813606262207</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.2519568800926208</v>
+        <v>0.2519573271274567</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.2510427236557007</v>
+        <v>0.2510431706905365</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.2450067102909088</v>
+        <v>0.245007112622261</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.2421557307243347</v>
+        <v>0.2421561181545258</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.2405447959899902</v>
+        <v>0.2405451834201813</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.2380969077348709</v>
+        <v>0.2380972802639008</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.2359194308519363</v>
+        <v>0.2359197735786438</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.2238253802061081</v>
+        <v>0.2238257378339767</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.2273086756467819</v>
+        <v>0.2273090183734894</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.2282792627811432</v>
+        <v>0.2282796055078506</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.2298876494169235</v>
+        <v>0.2298880070447922</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.281062513589859</v>
+        <v>0.2810629904270172</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.2775323390960693</v>
+        <v>0.2775327861309052</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.2731387317180634</v>
+        <v>0.2731391489505768</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.2661146521568298</v>
+        <v>0.2661150693893433</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.2692090570926666</v>
+        <v>0.2692094445228577</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.2581497728824615</v>
+        <v>0.2581501305103302</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.2579318284988403</v>
+        <v>0.2579322159290314</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.2516874969005585</v>
+        <v>0.2516878843307495</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.2544668316841125</v>
+        <v>0.2544671893119812</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.2535609602928162</v>
+        <v>0.2535612881183624</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.250002920627594</v>
+        <v>0.2500032782554626</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.249719649553299</v>
+        <v>0.2497199922800064</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.2494658380746841</v>
+        <v>0.2494661957025528</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.2612123191356659</v>
+        <v>0.2612127065658569</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.2863284945487976</v>
+        <v>0.2863288521766663</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.2868634462356567</v>
+        <v>0.2868638336658478</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.2761425077915192</v>
+        <v>0.2761428654193878</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.2784976065158844</v>
+        <v>0.2784979641437531</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.268865168094635</v>
+        <v>0.2688654959201813</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.2703493237495422</v>
+        <v>0.2703496515750885</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.2700158953666687</v>
+        <v>0.2700162529945374</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.2667263448238373</v>
+        <v>0.2667267024517059</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.2621933221817017</v>
+        <v>0.2621936500072479</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.2609007358551025</v>
+        <v>0.2609010636806488</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.2631352245807648</v>
+        <v>0.263135552406311</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.2649427056312561</v>
+        <v>0.2649430930614471</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.2747219502925873</v>
+        <v>0.2747223377227783</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.2850388288497925</v>
+        <v>0.2850392758846283</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.2905089557170868</v>
+        <v>0.2905093431472778</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.2906878888607025</v>
+        <v>0.2906882762908936</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.2826074361801147</v>
+        <v>0.2826077938079834</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.2807303965091705</v>
+        <v>0.2807307839393616</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.2861181199550629</v>
+        <v>0.2861185073852539</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.283814549446106</v>
+        <v>0.2838149666786194</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.2840344905853271</v>
+        <v>0.2840349078178406</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.2820897996425629</v>
+        <v>0.2820902168750763</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.2839334607124329</v>
+        <v>0.2839339077472687</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.2843250334262848</v>
+        <v>0.2843254506587982</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.2833821475505829</v>
+        <v>0.2833825647830963</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.2939600646495819</v>
+        <v>0.2939605116844177</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.2984375059604645</v>
+        <v>0.2984379827976227</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.3131246566772461</v>
+        <v>0.3131251633167267</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.3070703744888306</v>
+        <v>0.3070708811283112</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.3078203499317169</v>
+        <v>0.3078208863735199</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.3090237677097321</v>
+        <v>0.309024304151535</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.309006929397583</v>
+        <v>0.3090074956417084</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.3070503771305084</v>
+        <v>0.307050883769989</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.3053803741931915</v>
+        <v>0.3053809106349945</v>
       </c>
       <c r="GH7" t="n">
-        <v>0.3016310632228851</v>
+        <v>0.3016315996646881</v>
       </c>
       <c r="GI7" t="n">
-        <v>0.3022024631500244</v>
+        <v>0.3022029995918274</v>
       </c>
       <c r="GJ7" t="n">
-        <v>0.3027072548866272</v>
+        <v>0.3027077913284302</v>
       </c>
       <c r="GK7" t="n">
-        <v>0.3065799474716187</v>
+        <v>0.306580513715744</v>
       </c>
       <c r="GL7" t="n">
-        <v>0.3130443394184113</v>
+        <v>0.3130449056625366</v>
       </c>
       <c r="GM7" t="n">
-        <v>0.319346159696579</v>
+        <v>0.3193467855453491</v>
       </c>
       <c r="GN7" t="n">
-        <v>0.3347063660621643</v>
+        <v>0.3347069919109344</v>
       </c>
       <c r="GO7" t="n">
-        <v>0.342685341835022</v>
+        <v>0.3426859676837921</v>
       </c>
       <c r="GP7" t="n">
-        <v>0.3356069922447205</v>
+        <v>0.3356075584888458</v>
       </c>
       <c r="GQ7" t="n">
-        <v>0.3324770033359528</v>
+        <v>0.3324775695800781</v>
       </c>
       <c r="GR7" t="n">
-        <v>0.3314462304115295</v>
+        <v>0.3314467966556549</v>
       </c>
       <c r="GS7" t="n">
-        <v>0.3298485279083252</v>
+        <v>0.3298490941524506</v>
       </c>
       <c r="GT7" t="n">
-        <v>0.3312697410583496</v>
+        <v>0.331270307302475</v>
       </c>
       <c r="GU7" t="n">
-        <v>0.3255482614040375</v>
+        <v>0.3255488574504852</v>
       </c>
       <c r="GV7" t="n">
-        <v>0.3308454155921936</v>
+        <v>0.3308460116386414</v>
       </c>
       <c r="GW7" t="n">
-        <v>0.3259222209453583</v>
+        <v>0.325922816991806</v>
       </c>
       <c r="GX7" t="n">
-        <v>0.327094167470932</v>
+        <v>0.3270948231220245</v>
       </c>
       <c r="GY7" t="n">
-        <v>0.3274358808994293</v>
+        <v>0.3274365365505219</v>
       </c>
       <c r="GZ7" t="n">
-        <v>0.3405775129795074</v>
+        <v>0.3405782580375671</v>
       </c>
       <c r="HA7" t="n">
-        <v>0.3533594906330109</v>
+        <v>0.353360116481781</v>
       </c>
       <c r="HB7" t="n">
-        <v>0.3661185801029205</v>
+        <v>0.3661192953586578</v>
       </c>
       <c r="HC7" t="n">
-        <v>0.3597222864627838</v>
+        <v>0.3597228825092316</v>
       </c>
       <c r="HD7" t="n">
-        <v>0.3490028381347656</v>
+        <v>0.3490037024021149</v>
       </c>
       <c r="HE7" t="n">
-        <v>0.3440355360507965</v>
+        <v>0.3440364003181458</v>
       </c>
       <c r="HF7" t="n">
-        <v>0.3456274569034576</v>
+        <v>0.3456283211708069</v>
       </c>
       <c r="HG7" t="n">
-        <v>0.3522837162017822</v>
+        <v>0.3522845506668091</v>
       </c>
       <c r="HH7" t="n">
-        <v>0.3512374460697174</v>
+        <v>0.351238340139389</v>
       </c>
       <c r="HI7" t="n">
-        <v>0.3496586382389069</v>
+        <v>0.3496595621109009</v>
       </c>
       <c r="HJ7" t="n">
-        <v>0.3523313999176025</v>
+        <v>0.3523322939872742</v>
       </c>
       <c r="HK7" t="n">
-        <v>0.3460932374000549</v>
+        <v>0.346094161272049</v>
       </c>
       <c r="HL7" t="n">
-        <v>0.3479198515415192</v>
+        <v>0.3479207456111908</v>
       </c>
       <c r="HM7" t="n">
-        <v>0.3449772596359253</v>
+        <v>0.3449780941009521</v>
       </c>
       <c r="HN7" t="n">
-        <v>0.3681218028068542</v>
+        <v>0.3681227266788483</v>
       </c>
       <c r="HO7" t="n">
-        <v>0.3823418319225311</v>
+        <v>0.3823427259922028</v>
       </c>
       <c r="HP7" t="n">
-        <v>0.3610776662826538</v>
+        <v>0.3610783815383911</v>
       </c>
       <c r="HQ7" t="n">
-        <v>0.3486772477626801</v>
+        <v>0.3486778438091278</v>
       </c>
       <c r="HR7" t="inlineStr">
         <is>

--- a/results/submission_predictions.xlsx
+++ b/results/submission_predictions.xlsx
@@ -1555,676 +1555,676 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02326625399291515</v>
+        <v>0.02327178977429867</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03184733167290688</v>
+        <v>0.03185594826936722</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03395086899399757</v>
+        <v>0.03395998477935791</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03552865609526634</v>
+        <v>0.03553741797804832</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03608325868844986</v>
+        <v>0.03609166666865349</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03545861318707466</v>
+        <v>0.03546628355979919</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03495082259178162</v>
+        <v>0.03495741635560989</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03461356461048126</v>
+        <v>0.03461987525224686</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0348496250808239</v>
+        <v>0.03485554084181786</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03421996906399727</v>
+        <v>0.03422541543841362</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03328653424978256</v>
+        <v>0.03329106420278549</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03239406645298004</v>
+        <v>0.03239807859063148</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03232502192258835</v>
+        <v>0.03232886269688606</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03292563930153847</v>
+        <v>0.03292922675609589</v>
       </c>
       <c r="P2" t="n">
-        <v>0.04760325700044632</v>
+        <v>0.0476154051721096</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05878948420286179</v>
+        <v>0.05880490690469742</v>
       </c>
       <c r="R2" t="n">
-        <v>0.06146269664168358</v>
+        <v>0.06147834658622742</v>
       </c>
       <c r="S2" t="n">
-        <v>0.06261806935071945</v>
+        <v>0.06263219565153122</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06386692821979523</v>
+        <v>0.06388075649738312</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06174229457974434</v>
+        <v>0.06175458058714867</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06260819733142853</v>
+        <v>0.06261925399303436</v>
       </c>
       <c r="W2" t="n">
-        <v>0.06225846707820892</v>
+        <v>0.06226851791143417</v>
       </c>
       <c r="X2" t="n">
-        <v>0.06171952933073044</v>
+        <v>0.06172877550125122</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.06137227639555931</v>
+        <v>0.06138107553124428</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.05845445021986961</v>
+        <v>0.05846141651272774</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.05631150677800179</v>
+        <v>0.05631787702441216</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05613159388303757</v>
+        <v>0.05613766610622406</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.05758493393659592</v>
+        <v>0.05759108811616898</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.07858078926801682</v>
+        <v>0.07860284298658371</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.09026516973972321</v>
+        <v>0.09028822183609009</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.09025275707244873</v>
+        <v>0.09027501940727234</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.09254399687051773</v>
+        <v>0.0925636887550354</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.09284494817256927</v>
+        <v>0.09286299347877502</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.09228677302598953</v>
+        <v>0.09230312705039978</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.08932642638683319</v>
+        <v>0.08934057503938675</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.08849737793207169</v>
+        <v>0.08851012587547302</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.08873917162418365</v>
+        <v>0.08875125646591187</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.08585985749959946</v>
+        <v>0.08587131649255753</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.08191736042499542</v>
+        <v>0.08192665874958038</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.08004794269800186</v>
+        <v>0.08005589991807938</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.08216211199760437</v>
+        <v>0.0821702629327774</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.082937091588974</v>
+        <v>0.08294441550970078</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.1072096303105354</v>
+        <v>0.1072365939617157</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.1139610856771469</v>
+        <v>0.1139889135956764</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.1148864701390266</v>
+        <v>0.1149114593863487</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.1169114783406258</v>
+        <v>0.116933137178421</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.1147407367825508</v>
+        <v>0.1147620305418968</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.110943391919136</v>
+        <v>0.1109604611992836</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1114783138036728</v>
+        <v>0.1114946156740189</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.1107744798064232</v>
+        <v>0.1107892990112305</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1093958765268326</v>
+        <v>0.1094097197055817</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.1059109345078468</v>
+        <v>0.1059237271547318</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.1015538573265076</v>
+        <v>0.1015644669532776</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.09993547946214676</v>
+        <v>0.09994494915008545</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.09865274280309677</v>
+        <v>0.09866204857826233</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.1017197594046593</v>
+        <v>0.1017283126711845</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.1351004391908646</v>
+        <v>0.1351334452629089</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.1370926201343536</v>
+        <v>0.1371238678693771</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.1368002742528915</v>
+        <v>0.1368269026279449</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.1336500346660614</v>
+        <v>0.1336728483438492</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.133740708231926</v>
+        <v>0.1337628364562988</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.1278859227895737</v>
+        <v>0.1279046982526779</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.127573624253273</v>
+        <v>0.1275899410247803</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.1251440197229385</v>
+        <v>0.1251594573259354</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.1233212500810623</v>
+        <v>0.1233353912830353</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.1247251555323601</v>
+        <v>0.1247384622693062</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1169379949569702</v>
+        <v>0.1169486567378044</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.1163929477334023</v>
+        <v>0.1164035797119141</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.1157632172107697</v>
+        <v>0.1157734096050262</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.1157199069857597</v>
+        <v>0.1157298609614372</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.1684931069612503</v>
+        <v>0.1685351133346558</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.1668725162744522</v>
+        <v>0.1669107675552368</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.1628894358873367</v>
+        <v>0.1629203110933304</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.163230299949646</v>
+        <v>0.1632556170225143</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.1618122905492783</v>
+        <v>0.1618364602327347</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.1579393446445465</v>
+        <v>0.1579618752002716</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.1543184667825699</v>
+        <v>0.1543361842632294</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.1515738666057587</v>
+        <v>0.1515912115573883</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.1497409790754318</v>
+        <v>0.1497572362422943</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.1458337306976318</v>
+        <v>0.1458484977483749</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.1424359828233719</v>
+        <v>0.1424486339092255</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.1360165327787399</v>
+        <v>0.1360276788473129</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.136158213019371</v>
+        <v>0.1361689120531082</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.1394181102514267</v>
+        <v>0.1394312381744385</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.194337859749794</v>
+        <v>0.1943769007921219</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.1921222805976868</v>
+        <v>0.1921573132276535</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.1897089779376984</v>
+        <v>0.1897385865449905</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.1862374395132065</v>
+        <v>0.1862630397081375</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.1827537268400192</v>
+        <v>0.1827769726514816</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.1764063388109207</v>
+        <v>0.1764276921749115</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.1772308200597763</v>
+        <v>0.1772505789995193</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.1711098253726959</v>
+        <v>0.1711273342370987</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.169726088643074</v>
+        <v>0.1697416752576828</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.1706794798374176</v>
+        <v>0.1706940233707428</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.1583409160375595</v>
+        <v>0.1583548486232758</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.1560250371694565</v>
+        <v>0.1560385227203369</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.1561156958341599</v>
+        <v>0.1561301052570343</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.1621867716312408</v>
+        <v>0.1622026115655899</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.2298655360937119</v>
+        <v>0.2298962622880936</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.2171445488929749</v>
+        <v>0.2171722501516342</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.2175662666559219</v>
+        <v>0.2175937741994858</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.2160788774490356</v>
+        <v>0.2161051630973816</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.2072250992059708</v>
+        <v>0.2072467058897018</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.2039921134710312</v>
+        <v>0.2040117681026459</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.2046656012535095</v>
+        <v>0.2046837657690048</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.2005384713411331</v>
+        <v>0.2005546092987061</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.2001926749944687</v>
+        <v>0.2002098560333252</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.1948353797197342</v>
+        <v>0.1948521584272385</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.1894027888774872</v>
+        <v>0.1894180923700333</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.1865028440952301</v>
+        <v>0.1865182667970657</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.1854920387268066</v>
+        <v>0.1855089664459229</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.1881078630685806</v>
+        <v>0.1881277412176132</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.2456707805395126</v>
+        <v>0.2457026988267899</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.2429291009902954</v>
+        <v>0.2429582476615906</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.2352909743785858</v>
+        <v>0.2353140264749527</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.2338630259037018</v>
+        <v>0.2338859736919403</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.2272153943777084</v>
+        <v>0.2272364050149918</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.228642612695694</v>
+        <v>0.2286606132984161</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.2231479436159134</v>
+        <v>0.2231659442186356</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.2173606306314468</v>
+        <v>0.2173775285482407</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.2160621136426926</v>
+        <v>0.216079443693161</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.2133421301841736</v>
+        <v>0.2133585810661316</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.2089820057153702</v>
+        <v>0.20899897813797</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.2079464197158813</v>
+        <v>0.2079651355743408</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.210182711482048</v>
+        <v>0.2102033048868179</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2123355716466904</v>
+        <v>0.2123578190803528</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.2629712522029877</v>
+        <v>0.2629976868629456</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.2533412277698517</v>
+        <v>0.253365695476532</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.2520176470279694</v>
+        <v>0.2520419657230377</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.2453045696020126</v>
+        <v>0.2453244030475616</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.2449193298816681</v>
+        <v>0.2449388056993484</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.2392343431711197</v>
+        <v>0.2392531633377075</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.2367789298295975</v>
+        <v>0.2367967814207077</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.2355188131332397</v>
+        <v>0.2355365455150604</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.2333745509386063</v>
+        <v>0.2333915680646896</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.2314517050981522</v>
+        <v>0.2314686924219131</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.2197874486446381</v>
+        <v>0.2198072671890259</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.2237004935741425</v>
+        <v>0.2237207144498825</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.2250559031963348</v>
+        <v>0.225079134106636</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.2264781892299652</v>
+        <v>0.2265021950006485</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.2740674614906311</v>
+        <v>0.2740885317325592</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.2712678611278534</v>
+        <v>0.2712883651256561</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.2673355937004089</v>
+        <v>0.2673562169075012</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.2608833312988281</v>
+        <v>0.26090407371521</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.2642111480236053</v>
+        <v>0.2642312049865723</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.2535958588123322</v>
+        <v>0.2536158859729767</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.2530747354030609</v>
+        <v>0.2530933320522308</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.2473413944244385</v>
+        <v>0.2473622858524323</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.2503488063812256</v>
+        <v>0.2503683269023895</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.2497832328081131</v>
+        <v>0.2498046159744263</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.2464046478271484</v>
+        <v>0.2464282959699631</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.246510848402977</v>
+        <v>0.2465350180864334</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.2465188056230545</v>
+        <v>0.2465448826551437</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.2578245103359222</v>
+        <v>0.2578552067279816</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.2822792530059814</v>
+        <v>0.2823008894920349</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.282794326543808</v>
+        <v>0.2828161716461182</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.2723481357097626</v>
+        <v>0.2723689079284668</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.2747621536254883</v>
+        <v>0.2747845649719238</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.2653319239616394</v>
+        <v>0.2653540074825287</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.2668420970439911</v>
+        <v>0.2668657302856445</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.2665213942527771</v>
+        <v>0.2665445506572723</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.263277679681778</v>
+        <v>0.2633013427257538</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.2588112354278564</v>
+        <v>0.2588341534137726</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.2575488090515137</v>
+        <v>0.2575714290142059</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.2598561942577362</v>
+        <v>0.259881317615509</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.2620880603790283</v>
+        <v>0.2621203362941742</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.2718251943588257</v>
+        <v>0.2718665897846222</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.2820400595664978</v>
+        <v>0.2820851802825928</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.286404937505722</v>
+        <v>0.286430835723877</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.2868222892284393</v>
+        <v>0.2868494987487793</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.2789212465286255</v>
+        <v>0.2789477407932281</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.2770764827728271</v>
+        <v>0.2771055996417999</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.2822732031345367</v>
+        <v>0.2822991013526917</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.2800260484218597</v>
+        <v>0.2800542116165161</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.2801549136638641</v>
+        <v>0.2801827490329742</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.2781893908977509</v>
+        <v>0.278217613697052</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.280017077922821</v>
+        <v>0.2800471484661102</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.2803669273853302</v>
+        <v>0.2803974747657776</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.2797638475894928</v>
+        <v>0.2798011898994446</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.2905439138412476</v>
+        <v>0.2905897200107574</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.2947646379470825</v>
+        <v>0.2948127686977386</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.3093152642250061</v>
+        <v>0.3093657195568085</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.3019087612628937</v>
+        <v>0.3019415438175201</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.3025695979595184</v>
+        <v>0.3026038408279419</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.3035299479961395</v>
+        <v>0.3035642504692078</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.303446888923645</v>
+        <v>0.3034815490245819</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.3016610145568848</v>
+        <v>0.3016965389251709</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.3001140356063843</v>
+        <v>0.3001497983932495</v>
       </c>
       <c r="GH2" t="n">
-        <v>0.2964870035648346</v>
+        <v>0.2965235412120819</v>
       </c>
       <c r="GI2" t="n">
-        <v>0.2974067628383636</v>
+        <v>0.2974481582641602</v>
       </c>
       <c r="GJ2" t="n">
-        <v>0.2975611686706543</v>
+        <v>0.2975994944572449</v>
       </c>
       <c r="GK2" t="n">
-        <v>0.3014009892940521</v>
+        <v>0.3014411628246307</v>
       </c>
       <c r="GL2" t="n">
-        <v>0.3081746697425842</v>
+        <v>0.3082178235054016</v>
       </c>
       <c r="GM2" t="n">
-        <v>0.3147278130054474</v>
+        <v>0.3147832453250885</v>
       </c>
       <c r="GN2" t="n">
-        <v>0.3299198150634766</v>
+        <v>0.3299796879291534</v>
       </c>
       <c r="GO2" t="n">
-        <v>0.3374398052692413</v>
+        <v>0.3374963104724884</v>
       </c>
       <c r="GP2" t="n">
-        <v>0.3302977681159973</v>
+        <v>0.3303388655185699</v>
       </c>
       <c r="GQ2" t="n">
-        <v>0.3275695443153381</v>
+        <v>0.3276134729385376</v>
       </c>
       <c r="GR2" t="n">
-        <v>0.3264770209789276</v>
+        <v>0.3265176713466644</v>
       </c>
       <c r="GS2" t="n">
-        <v>0.3248697817325592</v>
+        <v>0.3249114751815796</v>
       </c>
       <c r="GT2" t="n">
-        <v>0.3261143565177917</v>
+        <v>0.3261566162109375</v>
       </c>
       <c r="GU2" t="n">
-        <v>0.3204240202903748</v>
+        <v>0.3204669952392578</v>
       </c>
       <c r="GV2" t="n">
-        <v>0.3255017399787903</v>
+        <v>0.3255463540554047</v>
       </c>
       <c r="GW2" t="n">
-        <v>0.3206014931201935</v>
+        <v>0.3206498622894287</v>
       </c>
       <c r="GX2" t="n">
-        <v>0.3215974271297455</v>
+        <v>0.3216476738452911</v>
       </c>
       <c r="GY2" t="n">
-        <v>0.3218245208263397</v>
+        <v>0.3218763172626495</v>
       </c>
       <c r="GZ2" t="n">
-        <v>0.3350948095321655</v>
+        <v>0.3351599872112274</v>
       </c>
       <c r="HA2" t="n">
-        <v>0.348188728094101</v>
+        <v>0.3482485413551331</v>
       </c>
       <c r="HB2" t="n">
-        <v>0.3604071736335754</v>
+        <v>0.3604775369167328</v>
       </c>
       <c r="HC2" t="n">
-        <v>0.3552492260932922</v>
+        <v>0.355311393737793</v>
       </c>
       <c r="HD2" t="n">
-        <v>0.3423134684562683</v>
+        <v>0.3424038589000702</v>
       </c>
       <c r="HE2" t="n">
-        <v>0.3376105129718781</v>
+        <v>0.3377046883106232</v>
       </c>
       <c r="HF2" t="n">
-        <v>0.3391503691673279</v>
+        <v>0.3392382264137268</v>
       </c>
       <c r="HG2" t="n">
-        <v>0.3455822467803955</v>
+        <v>0.3456673324108124</v>
       </c>
       <c r="HH2" t="n">
-        <v>0.3442668318748474</v>
+        <v>0.3443499505519867</v>
       </c>
       <c r="HI2" t="n">
-        <v>0.342543751001358</v>
+        <v>0.3426263034343719</v>
       </c>
       <c r="HJ2" t="n">
-        <v>0.3449712693691254</v>
+        <v>0.3450498282909393</v>
       </c>
       <c r="HK2" t="n">
-        <v>0.3386459350585938</v>
+        <v>0.3387227654457092</v>
       </c>
       <c r="HL2" t="n">
-        <v>0.3402528762817383</v>
+        <v>0.3403235971927643</v>
       </c>
       <c r="HM2" t="n">
-        <v>0.3371365070343018</v>
+        <v>0.3371998369693756</v>
       </c>
       <c r="HN2" t="n">
-        <v>0.3604699671268463</v>
+        <v>0.3605459034442902</v>
       </c>
       <c r="HO2" t="n">
-        <v>0.3748538792133331</v>
+        <v>0.3749391436576843</v>
       </c>
       <c r="HP2" t="n">
-        <v>0.3554171025753021</v>
+        <v>0.3554947674274445</v>
       </c>
       <c r="HQ2" t="n">
-        <v>0.3445874750614166</v>
+        <v>0.3446590304374695</v>
       </c>
       <c r="HR2" t="inlineStr">
         <is>
@@ -2239,676 +2239,676 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02403736300766468</v>
+        <v>0.02405191585421562</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03268431127071381</v>
+        <v>0.03270101174712181</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03478322550654411</v>
+        <v>0.03480030223727226</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03633921220898628</v>
+        <v>0.0363558828830719</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03685170039534569</v>
+        <v>0.03686752170324326</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03617649525403976</v>
+        <v>0.03619140014052391</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03562358394265175</v>
+        <v>0.03563733771443367</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03527328372001648</v>
+        <v>0.03528682515025139</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03548984602093697</v>
+        <v>0.03550302982330322</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03482589870691299</v>
+        <v>0.03483851253986359</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03383029997348785</v>
+        <v>0.03384162858128548</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03286046162247658</v>
+        <v>0.03287098929286003</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03278001397848129</v>
+        <v>0.03279042989015579</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03336164355278015</v>
+        <v>0.03337197378277779</v>
       </c>
       <c r="P3" t="n">
-        <v>0.04881113022565842</v>
+        <v>0.04883667826652527</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.06010545417666435</v>
+        <v>0.06013280525803566</v>
       </c>
       <c r="R3" t="n">
-        <v>0.06281723827123642</v>
+        <v>0.06284528225660324</v>
       </c>
       <c r="S3" t="n">
-        <v>0.06386229395866394</v>
+        <v>0.06388801336288452</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06508804112672806</v>
+        <v>0.06511365622282028</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06282741576433182</v>
+        <v>0.0628509521484375</v>
       </c>
       <c r="V3" t="n">
-        <v>0.06366434693336487</v>
+        <v>0.06368649005889893</v>
       </c>
       <c r="W3" t="n">
-        <v>0.06323374062776566</v>
+        <v>0.06325487792491913</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0626879408955574</v>
+        <v>0.06270827353000641</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06229028478264809</v>
+        <v>0.06230984628200531</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.05926088243722916</v>
+        <v>0.0592779740691185</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.05701807886362076</v>
+        <v>0.05703460052609444</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.05683645606040955</v>
+        <v>0.05685289204120636</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.05825908482074738</v>
+        <v>0.05827568098902702</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0801626592874527</v>
+        <v>0.08019895851612091</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.09201088547706604</v>
+        <v>0.09204800426959991</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09201493859291077</v>
+        <v>0.09205201268196106</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.09412152320146561</v>
+        <v>0.09415488690137863</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0943567231297493</v>
+        <v>0.0943889394402504</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.09371022880077362</v>
+        <v>0.09374068677425385</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.09062837809324265</v>
+        <v>0.0906560868024826</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.08969345688819885</v>
+        <v>0.08971972018480301</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.08994735032320023</v>
+        <v>0.08997301012277603</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.08697987347841263</v>
+        <v>0.08700453490018845</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.08285900950431824</v>
+        <v>0.08288049697875977</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.08090169727802277</v>
+        <v>0.08092211931943893</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.08303873240947723</v>
+        <v>0.08306001871824265</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.08376631885766983</v>
+        <v>0.08378670364618301</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.1091117188334465</v>
+        <v>0.1091538444161415</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.1161143183708191</v>
+        <v>0.1161580681800842</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.1169031038880348</v>
+        <v>0.1169437617063522</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.1186548694968224</v>
+        <v>0.1186905801296234</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1165370345115662</v>
+        <v>0.1165757775306702</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1124853417277336</v>
+        <v>0.1125176921486855</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1129645109176636</v>
+        <v>0.1129965484142303</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.1121452376246452</v>
+        <v>0.1121756657958031</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1107555404305458</v>
+        <v>0.1107848510146141</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1071451455354691</v>
+        <v>0.107172816991806</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.1025878489017487</v>
+        <v>0.1026120036840439</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1008946746587753</v>
+        <v>0.1009183824062347</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0995999351143837</v>
+        <v>0.09962393343448639</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1026377826929092</v>
+        <v>0.1026612371206284</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1373292803764343</v>
+        <v>0.1373768448829651</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.1394054740667343</v>
+        <v>0.1394541710615158</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.1389108151197433</v>
+        <v>0.1389545500278473</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.1355937570333481</v>
+        <v>0.1356329172849655</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.1356373429298401</v>
+        <v>0.1356782466173172</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.1295626759529114</v>
+        <v>0.1295989155769348</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.1291056126356125</v>
+        <v>0.1291383802890778</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.126590222120285</v>
+        <v>0.1266226321458817</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.124741218984127</v>
+        <v>0.1247719824314117</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.126056119799614</v>
+        <v>0.1260854750871658</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1180354431271553</v>
+        <v>0.1180609688162804</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.1174057796597481</v>
+        <v>0.1174319833517075</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1167659237980843</v>
+        <v>0.116792157292366</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.1166694834828377</v>
+        <v>0.1166955307126045</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.1715077012777328</v>
+        <v>0.1715728789567947</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.1696706265211105</v>
+        <v>0.1697319895029068</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.1655589938163757</v>
+        <v>0.1656144857406616</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1656284779310226</v>
+        <v>0.1656759977340698</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.1639088243246078</v>
+        <v>0.1639546602964401</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.1599233895540237</v>
+        <v>0.1599681526422501</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.1561277806758881</v>
+        <v>0.1561660915613174</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.1532690525054932</v>
+        <v>0.1533068716526031</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.1513223797082901</v>
+        <v>0.1513582020998001</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.1472854316234589</v>
+        <v>0.1473185122013092</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.1436841189861298</v>
+        <v>0.1437142938375473</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.1371039748191833</v>
+        <v>0.1371326148509979</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.1372313499450684</v>
+        <v>0.1372598260641098</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.1404612958431244</v>
+        <v>0.1404928714036942</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.1973129361867905</v>
+        <v>0.1973782777786255</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.195155069231987</v>
+        <v>0.1952183395624161</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.1924538314342499</v>
+        <v>0.1925114691257477</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.1886333674192429</v>
+        <v>0.188684493303299</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.1850348114967346</v>
+        <v>0.1850838959217072</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.1784700453281403</v>
+        <v>0.1785162836313248</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.1791474223136902</v>
+        <v>0.1791909039020538</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1728761941194534</v>
+        <v>0.1729163974523544</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.1713966578245163</v>
+        <v>0.1714338213205338</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.172222763299942</v>
+        <v>0.1722574979066849</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.1595985889434814</v>
+        <v>0.1596313863992691</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.1571420580148697</v>
+        <v>0.1571747213602066</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.1571823060512543</v>
+        <v>0.1572158932685852</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.1632938235998154</v>
+        <v>0.1633301377296448</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.2327418029308319</v>
+        <v>0.2328028976917267</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.2200868725776672</v>
+        <v>0.2201471775770187</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.2201637327671051</v>
+        <v>0.2202210575342178</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.2185532450675964</v>
+        <v>0.2186102271080017</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.2094585597515106</v>
+        <v>0.2095086127519608</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.2060794830322266</v>
+        <v>0.2061264514923096</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.2066150158643723</v>
+        <v>0.2066592425107956</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.2022633999586105</v>
+        <v>0.2023029774427414</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.2018202990293503</v>
+        <v>0.2018609344959259</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.1963388621807098</v>
+        <v>0.1963778585195541</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.1906560808420181</v>
+        <v>0.1906921416521072</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.1876569390296936</v>
+        <v>0.1876928210258484</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.1865605115890503</v>
+        <v>0.1865975707769394</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.1891449987888336</v>
+        <v>0.1891862899065018</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.2487360090017319</v>
+        <v>0.2488055676221848</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.2456705719232559</v>
+        <v>0.2457352876663208</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.2377711832523346</v>
+        <v>0.2378259897232056</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.2362194508314133</v>
+        <v>0.236273318529129</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.229372575879097</v>
+        <v>0.229423314332962</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.2305525541305542</v>
+        <v>0.2305971831083298</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.2248708456754684</v>
+        <v>0.2249140292406082</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.2189718931913376</v>
+        <v>0.2190129905939102</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.217560350894928</v>
+        <v>0.2176013141870499</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.2147174328565598</v>
+        <v>0.214756652712822</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.2101765125989914</v>
+        <v>0.21021468937397</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.2089127749204636</v>
+        <v>0.2089504897594452</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.2111963778734207</v>
+        <v>0.2112379372119904</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.213293731212616</v>
+        <v>0.213337630033493</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.2656558454036713</v>
+        <v>0.2657179832458496</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.2558152675628662</v>
+        <v>0.2558729350566864</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.2544073462486267</v>
+        <v>0.2544648945331573</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.2473456114530563</v>
+        <v>0.2473939955234528</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.2467722445726395</v>
+        <v>0.2468192130327225</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.2409676760435104</v>
+        <v>0.241012766957283</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.2383814007043839</v>
+        <v>0.2384244948625565</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.2369943410158157</v>
+        <v>0.2370365709066391</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.234760195016861</v>
+        <v>0.2347999513149261</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.2327509075403214</v>
+        <v>0.2327899634838104</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.22091343998909</v>
+        <v>0.2209556102752686</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.2246876209974289</v>
+        <v>0.2247287929058075</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.2258951216936111</v>
+        <v>0.2259388864040375</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.2273673415184021</v>
+        <v>0.2274127751588821</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.2761740684509277</v>
+        <v>0.2762266993522644</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.2731142342090607</v>
+        <v>0.2731647193431854</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.2690387964248657</v>
+        <v>0.2690875828266144</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.2624013423919678</v>
+        <v>0.2624480724334717</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.2656601965427399</v>
+        <v>0.2657051980495453</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.2549009919166565</v>
+        <v>0.2549444735050201</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.2544876933097839</v>
+        <v>0.2545311450958252</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.2485672831535339</v>
+        <v>0.2486124038696289</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.2515194118022919</v>
+        <v>0.2515612244606018</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.250825434923172</v>
+        <v>0.250868558883667</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.2473686635494232</v>
+        <v>0.2474140226840973</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.2473495155572891</v>
+        <v>0.2473941445350647</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.2472549229860306</v>
+        <v>0.247301384806633</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.2586897909641266</v>
+        <v>0.2587440013885498</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.28341144323349</v>
+        <v>0.2834553420543671</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.2839339673519135</v>
+        <v>0.2839785218238831</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.2734111845493317</v>
+        <v>0.2734532356262207</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.2757969796657562</v>
+        <v>0.2758409380912781</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.2663018703460693</v>
+        <v>0.2663449347019196</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.2677898705005646</v>
+        <v>0.2678349316120148</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.2674729824066162</v>
+        <v>0.2675172686576843</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.2642072439193726</v>
+        <v>0.2642521560192108</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.259723961353302</v>
+        <v>0.2597677409648895</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.258452981710434</v>
+        <v>0.2584963142871857</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.260712593793869</v>
+        <v>0.2607592344284058</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.2627924084663391</v>
+        <v>0.2628453969955444</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.2725262641906738</v>
+        <v>0.2725896537303925</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.282757431268692</v>
+        <v>0.282825767993927</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.2875325083732605</v>
+        <v>0.2875833511352539</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.2878704965114594</v>
+        <v>0.2879217863082886</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.2799129486083984</v>
+        <v>0.2799627482891083</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.2780461311340332</v>
+        <v>0.2780987620353699</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.2833133935928345</v>
+        <v>0.2833632528781891</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.2810272574424744</v>
+        <v>0.281079888343811</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.2811841368675232</v>
+        <v>0.2812368273735046</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.2792186737060547</v>
+        <v>0.2792720794677734</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.2810329794883728</v>
+        <v>0.2810890078544617</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.2813921868801117</v>
+        <v>0.2814490795135498</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.2806530594825745</v>
+        <v>0.2807166278362274</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.2913436591625214</v>
+        <v>0.2914162874221802</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.2956440448760986</v>
+        <v>0.2957203388214111</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.310238391160965</v>
+        <v>0.3103179037570953</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.3032963871955872</v>
+        <v>0.3033605515956879</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.3039713501930237</v>
+        <v>0.3040377497673035</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.3050025403499603</v>
+        <v>0.3050703704357147</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.3049362897872925</v>
+        <v>0.305004894733429</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.3030867576599121</v>
+        <v>0.3031557500362396</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.3015005886554718</v>
+        <v>0.3015692830085754</v>
       </c>
       <c r="GH3" t="n">
-        <v>0.2978171408176422</v>
+        <v>0.2978866100311279</v>
       </c>
       <c r="GI3" t="n">
-        <v>0.2985761165618896</v>
+        <v>0.2986510694026947</v>
       </c>
       <c r="GJ3" t="n">
-        <v>0.298880398273468</v>
+        <v>0.2989525496959686</v>
       </c>
       <c r="GK3" t="n">
-        <v>0.3027136325836182</v>
+        <v>0.3027886152267456</v>
       </c>
       <c r="GL3" t="n">
-        <v>0.3093660771846771</v>
+        <v>0.3094443380832672</v>
       </c>
       <c r="GM3" t="n">
-        <v>0.3158293962478638</v>
+        <v>0.3159203231334686</v>
       </c>
       <c r="GN3" t="n">
-        <v>0.3310711979866028</v>
+        <v>0.3311673104763031</v>
       </c>
       <c r="GO3" t="n">
-        <v>0.3387307524681091</v>
+        <v>0.3388253748416901</v>
       </c>
       <c r="GP3" t="n">
-        <v>0.3316566348075867</v>
+        <v>0.3317328989505768</v>
       </c>
       <c r="GQ3" t="n">
-        <v>0.3287951648235321</v>
+        <v>0.328873336315155</v>
       </c>
       <c r="GR3" t="n">
-        <v>0.3277303576469421</v>
+        <v>0.3278042674064636</v>
       </c>
       <c r="GS3" t="n">
-        <v>0.3261202573776245</v>
+        <v>0.3261957764625549</v>
       </c>
       <c r="GT3" t="n">
-        <v>0.3274122476577759</v>
+        <v>0.3274896740913391</v>
       </c>
       <c r="GU3" t="n">
-        <v>0.321703165769577</v>
+        <v>0.3217816650867462</v>
       </c>
       <c r="GV3" t="n">
-        <v>0.3268398344516754</v>
+        <v>0.326921284198761</v>
       </c>
       <c r="GW3" t="n">
-        <v>0.3219268321990967</v>
+        <v>0.3220126330852509</v>
       </c>
       <c r="GX3" t="n">
-        <v>0.3229704797267914</v>
+        <v>0.3230592906475067</v>
       </c>
       <c r="GY3" t="n">
-        <v>0.3232182860374451</v>
+        <v>0.3233097791671753</v>
       </c>
       <c r="GZ3" t="n">
-        <v>0.3364503383636475</v>
+        <v>0.3365553915500641</v>
       </c>
       <c r="HA3" t="n">
-        <v>0.3494466245174408</v>
+        <v>0.3495443761348724</v>
       </c>
       <c r="HB3" t="n">
-        <v>0.3618087470531464</v>
+        <v>0.3619204461574554</v>
       </c>
       <c r="HC3" t="n">
-        <v>0.3563206791877747</v>
+        <v>0.3564166128635406</v>
       </c>
       <c r="HD3" t="n">
-        <v>0.3439424633979797</v>
+        <v>0.344081848859787</v>
       </c>
       <c r="HE3" t="n">
-        <v>0.3391883373260498</v>
+        <v>0.3393298089504242</v>
       </c>
       <c r="HF3" t="n">
-        <v>0.3407434821128845</v>
+        <v>0.3408785462379456</v>
       </c>
       <c r="HG3" t="n">
-        <v>0.3472295999526978</v>
+        <v>0.347362756729126</v>
       </c>
       <c r="HH3" t="n">
-        <v>0.3459930419921875</v>
+        <v>0.3461253643035889</v>
       </c>
       <c r="HI3" t="n">
-        <v>0.3443105816841125</v>
+        <v>0.3444430530071259</v>
       </c>
       <c r="HJ3" t="n">
-        <v>0.3468124866485596</v>
+        <v>0.3469416201114655</v>
       </c>
       <c r="HK3" t="n">
-        <v>0.3405162692070007</v>
+        <v>0.3406441211700439</v>
       </c>
       <c r="HL3" t="n">
-        <v>0.3421918451786041</v>
+        <v>0.3423140645027161</v>
       </c>
       <c r="HM3" t="n">
-        <v>0.3391367197036743</v>
+        <v>0.339251697063446</v>
       </c>
       <c r="HN3" t="n">
-        <v>0.3623929917812347</v>
+        <v>0.3625196218490601</v>
       </c>
       <c r="HO3" t="n">
-        <v>0.3766748607158661</v>
+        <v>0.3768110871315002</v>
       </c>
       <c r="HP3" t="n">
-        <v>0.3568394482135773</v>
+        <v>0.35695680975914</v>
       </c>
       <c r="HQ3" t="n">
-        <v>0.3455774784088135</v>
+        <v>0.345680445432663</v>
       </c>
       <c r="HR3" t="inlineStr">
         <is>
@@ -2923,676 +2923,676 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02437753230333328</v>
+        <v>0.02440276741981506</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03307131677865982</v>
+        <v>0.03309753909707069</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03517709299921989</v>
+        <v>0.03520361706614494</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03673115745186806</v>
+        <v>0.03675733506679535</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03722706437110901</v>
+        <v>0.03725187107920647</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03653419762849808</v>
+        <v>0.03655794635415077</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03596707805991173</v>
+        <v>0.0359896756708622</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03561608865857124</v>
+        <v>0.03563861921429634</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03582791611552238</v>
+        <v>0.0358501709997654</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03515220060944557</v>
+        <v>0.03517379984259605</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03413254022598267</v>
+        <v>0.03415244817733765</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0331319086253643</v>
+        <v>0.03315068781375885</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03304935246706009</v>
+        <v>0.03306810930371284</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03362719342112541</v>
+        <v>0.0336461029946804</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04936335980892181</v>
+        <v>0.04940467700362206</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06071508303284645</v>
+        <v>0.06075647473335266</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06345947831869125</v>
+        <v>0.06350231170654297</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06446430087089539</v>
+        <v>0.06450404971837997</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06569319218397141</v>
+        <v>0.06573321670293808</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06338246911764145</v>
+        <v>0.0634198933839798</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06420863419771194</v>
+        <v>0.06424456834793091</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06375516951084137</v>
+        <v>0.0637902095913887</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06320908665657043</v>
+        <v>0.06324338167905807</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06279201805591583</v>
+        <v>0.06282521039247513</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05971619486808777</v>
+        <v>0.05974619090557098</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05744044110178947</v>
+        <v>0.05746990814805031</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05726365000009537</v>
+        <v>0.05729334056377411</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.05867679044604301</v>
+        <v>0.05870673060417175</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.08088011294603348</v>
+        <v>0.08093292266130447</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0928155779838562</v>
+        <v>0.09286925941705704</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.09284955263137817</v>
+        <v>0.09290445595979691</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.09488756954669952</v>
+        <v>0.09493765234947205</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.09511453658342361</v>
+        <v>0.09516431391239166</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.09443815052509308</v>
+        <v>0.09448618441820145</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.09130929410457611</v>
+        <v>0.09135404974222183</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.09034101665019989</v>
+        <v>0.0903843492269516</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.09060243517160416</v>
+        <v>0.09064533561468124</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.08760279417037964</v>
+        <v>0.08764432370662689</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.08340121805667877</v>
+        <v>0.08343828469514847</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.08142037689685822</v>
+        <v>0.08145678043365479</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.08357962965965271</v>
+        <v>0.08361779153347015</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.08428898453712463</v>
+        <v>0.08432617038488388</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.1099752336740494</v>
+        <v>0.1100348308682442</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.1171000152826309</v>
+        <v>0.1171627789735794</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.1178496778011322</v>
+        <v>0.1179094016551971</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.1194952204823494</v>
+        <v>0.1195483282208443</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.1174564957618713</v>
+        <v>0.1175170168280602</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.1132812276482582</v>
+        <v>0.1133328080177307</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1137538105249405</v>
+        <v>0.113805778324604</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.1128964349627495</v>
+        <v>0.1129467263817787</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.111502394080162</v>
+        <v>0.1115514785051346</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.1078398525714874</v>
+        <v>0.1078865602612495</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.1031943187117577</v>
+        <v>0.1032358855009079</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.1014879196882248</v>
+        <v>0.1015299707651138</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.1001951023936272</v>
+        <v>0.1002379953861237</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.1032267734408379</v>
+        <v>0.1032694280147552</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.1383230090141296</v>
+        <v>0.1383874863386154</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.1404978185892105</v>
+        <v>0.1405677199363708</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.1399355083703995</v>
+        <v>0.1400004476308823</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.1365565061569214</v>
+        <v>0.1366162896156311</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.1366280168294907</v>
+        <v>0.1366926580667496</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.1304531842470169</v>
+        <v>0.1305115967988968</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.1299314796924591</v>
+        <v>0.1299852579832077</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.1273975670337677</v>
+        <v>0.1274517029523849</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.1255347281694412</v>
+        <v>0.1255868524312973</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.1268116533756256</v>
+        <v>0.1268616765737534</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.1186890825629234</v>
+        <v>0.1187338083982468</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.1180448308587074</v>
+        <v>0.1180911362171173</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.1174066588282585</v>
+        <v>0.1174536049365997</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.1172871515154839</v>
+        <v>0.1173339039087296</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.172948956489563</v>
+        <v>0.1730424165725708</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.1710716933012009</v>
+        <v>0.1711620837450027</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1669262498617172</v>
+        <v>0.1670127958059311</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.1668653786182404</v>
+        <v>0.1669413447380066</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.1650347113609314</v>
+        <v>0.1651082634925842</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.161016583442688</v>
+        <v>0.1610897928476334</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.1571288257837296</v>
+        <v>0.1571936160326004</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.1542331427335739</v>
+        <v>0.154297336935997</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.1522312313318253</v>
+        <v>0.1522922813892365</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.1481281369924545</v>
+        <v>0.1481848806142807</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.1444435715675354</v>
+        <v>0.14449642598629</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.1377999931573868</v>
+        <v>0.1378511786460876</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.1379231065511703</v>
+        <v>0.1379745006561279</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.1411562263965607</v>
+        <v>0.141211599111557</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.1988355070352554</v>
+        <v>0.1989339888095856</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.1967371255159378</v>
+        <v>0.1968365013599396</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.1939202398061752</v>
+        <v>0.1940137445926666</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.1899364441633224</v>
+        <v>0.1900204569101334</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.1863025426864624</v>
+        <v>0.1863849014043808</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.1796435117721558</v>
+        <v>0.1797218173742294</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.1802506893873215</v>
+        <v>0.1803247928619385</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.1739074885845184</v>
+        <v>0.1739770174026489</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.1723755151033401</v>
+        <v>0.1724406480789185</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.173135057091713</v>
+        <v>0.173196017742157</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.1603865474462509</v>
+        <v>0.1604437232017517</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.157878652215004</v>
+        <v>0.1579360812902451</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.157894179224968</v>
+        <v>0.1579524725675583</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.1640409231185913</v>
+        <v>0.164103627204895</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.2343120574951172</v>
+        <v>0.2344123870134354</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.2217084020376205</v>
+        <v>0.2218107283115387</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.2216231226921082</v>
+        <v>0.2217189520597458</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.2199798673391342</v>
+        <v>0.2200764268636703</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.2107605785131454</v>
+        <v>0.2108474224805832</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.20730921626091</v>
+        <v>0.2073915600776672</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.2077722102403641</v>
+        <v>0.2078501731157303</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.2032982856035233</v>
+        <v>0.2033682763576508</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.2028148919343948</v>
+        <v>0.2028858214616776</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.1972730606794357</v>
+        <v>0.197340801358223</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.1914774179458618</v>
+        <v>0.1915403008460999</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.1884278953075409</v>
+        <v>0.1884902268648148</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.1872885227203369</v>
+        <v>0.1873514652252197</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.1898734569549561</v>
+        <v>0.1899422854185104</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.250497967004776</v>
+        <v>0.2506159842014313</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.2472758144140244</v>
+        <v>0.2473863363265991</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.2392152398824692</v>
+        <v>0.2393111884593964</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.2376096099615097</v>
+        <v>0.2377034872770309</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.2306725233793259</v>
+        <v>0.2307617962360382</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.2317130863666534</v>
+        <v>0.2317923307418823</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.2259337902069092</v>
+        <v>0.2260095924139023</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.2199757397174835</v>
+        <v>0.2200481593608856</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.2185098528862</v>
+        <v>0.2185812443494797</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2156018018722534</v>
+        <v>0.2156702727079391</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.2109704166650772</v>
+        <v>0.2110359519720078</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.2095901072025299</v>
+        <v>0.2096523940563202</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.2119113057851791</v>
+        <v>0.2119797766208649</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.2139841318130493</v>
+        <v>0.2140558212995529</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.2672401070594788</v>
+        <v>0.2673483192920685</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.2572859525680542</v>
+        <v>0.2573865652084351</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.2558492720127106</v>
+        <v>0.2559497654438019</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.248583972454071</v>
+        <v>0.2486694157123566</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.2479169964790344</v>
+        <v>0.2479994744062424</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.2420516014099121</v>
+        <v>0.2421306818723679</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.2393913716077805</v>
+        <v>0.2394669651985168</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.2379438281059265</v>
+        <v>0.2380175590515137</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.2356542199850082</v>
+        <v>0.2357233166694641</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.23359714448452</v>
+        <v>0.2336646467447281</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.2216818630695343</v>
+        <v>0.2217526435852051</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.2253723740577698</v>
+        <v>0.2254403531551361</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.2265105098485947</v>
+        <v>0.2265805453062057</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.2280199974775314</v>
+        <v>0.2280928939580917</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.2774823904037476</v>
+        <v>0.2775758802890778</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.2742947638034821</v>
+        <v>0.274383932352066</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.2701354920864105</v>
+        <v>0.270220547914505</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.2633944451808929</v>
+        <v>0.2634746432304382</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.2666074931621552</v>
+        <v>0.2666846215724945</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.2557662725448608</v>
+        <v>0.2558398842811584</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.255401998758316</v>
+        <v>0.255477249622345</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.249385878443718</v>
+        <v>0.2494618594646454</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.252296507358551</v>
+        <v>0.252366840839386</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.2515410780906677</v>
+        <v>0.2516119778156281</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.2480572462081909</v>
+        <v>0.2481304258108139</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.2479638904333115</v>
+        <v>0.2480346113443375</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.2478194683790207</v>
+        <v>0.2478919178247452</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.2593254446983337</v>
+        <v>0.2594094574451447</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.2841794192790985</v>
+        <v>0.284251868724823</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.2847026884555817</v>
+        <v>0.2847763299942017</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.2741290032863617</v>
+        <v>0.2741981148719788</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.2765061557292938</v>
+        <v>0.2765775322914124</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.2669719755649567</v>
+        <v>0.2670416235923767</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.2684572339057922</v>
+        <v>0.26852947473526</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.2681372761726379</v>
+        <v>0.2682084143161774</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.2648627460002899</v>
+        <v>0.2649346888065338</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.2603661715984344</v>
+        <v>0.2604364156723022</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.259089320898056</v>
+        <v>0.2591589093208313</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.261337012052536</v>
+        <v>0.2614109218120575</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.2633358240127563</v>
+        <v>0.2634150683879852</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.2730754613876343</v>
+        <v>0.2731666564941406</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.2833247780799866</v>
+        <v>0.2834223806858063</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.2883075773715973</v>
+        <v>0.2883899509906769</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.2886005640029907</v>
+        <v>0.2886823117733002</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.280609518289566</v>
+        <v>0.2806888222694397</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.2787409424781799</v>
+        <v>0.2788233757019043</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.2840400338172913</v>
+        <v>0.2841203510761261</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.2817474603652954</v>
+        <v>0.2818311750888824</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.2819205522537231</v>
+        <v>0.2820048034191132</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.2799593508243561</v>
+        <v>0.2800447642803192</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.2817791998386383</v>
+        <v>0.2818682193756104</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.2821461856365204</v>
+        <v>0.2822365462779999</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.2813439071178436</v>
+        <v>0.2814408242702484</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.2919936180114746</v>
+        <v>0.2921002209186554</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.2963407933712006</v>
+        <v>0.2964527606964111</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.3109514117240906</v>
+        <v>0.311067670583725</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.3042811155319214</v>
+        <v>0.3043853342533112</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.3049759268760681</v>
+        <v>0.3050833642482758</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.306051105260849</v>
+        <v>0.3061617314815521</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.3059984445571899</v>
+        <v>0.306110292673111</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.3041193783283234</v>
+        <v>0.3042311072349548</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.3025108873844147</v>
+        <v>0.3026216626167297</v>
       </c>
       <c r="GH4" t="n">
-        <v>0.2988067269325256</v>
+        <v>0.2989183068275452</v>
       </c>
       <c r="GI4" t="n">
-        <v>0.2995030581951141</v>
+        <v>0.2996209263801575</v>
       </c>
       <c r="GJ4" t="n">
-        <v>0.29986971616745</v>
+        <v>0.2999850213527679</v>
       </c>
       <c r="GK4" t="n">
-        <v>0.303709089756012</v>
+        <v>0.3038284778594971</v>
       </c>
       <c r="GL4" t="n">
-        <v>0.3102986514568329</v>
+        <v>0.3104215860366821</v>
       </c>
       <c r="GM4" t="n">
-        <v>0.3167025744915009</v>
+        <v>0.3168385326862335</v>
       </c>
       <c r="GN4" t="n">
-        <v>0.3319773972034454</v>
+        <v>0.3321193754673004</v>
       </c>
       <c r="GO4" t="n">
-        <v>0.3397191166877747</v>
+        <v>0.339862048625946</v>
       </c>
       <c r="GP4" t="n">
-        <v>0.332664281129837</v>
+        <v>0.3327853381633759</v>
       </c>
       <c r="GQ4" t="n">
-        <v>0.329725056886673</v>
+        <v>0.3298467695713043</v>
       </c>
       <c r="GR4" t="n">
-        <v>0.3286799490451813</v>
+        <v>0.3287962973117828</v>
       </c>
       <c r="GS4" t="n">
-        <v>0.3270719051361084</v>
+        <v>0.3271905481815338</v>
       </c>
       <c r="GT4" t="n">
-        <v>0.3283932507038116</v>
+        <v>0.3285154402256012</v>
       </c>
       <c r="GU4" t="n">
-        <v>0.3226780295372009</v>
+        <v>0.3228018283843994</v>
       </c>
       <c r="GV4" t="n">
-        <v>0.327858954668045</v>
+        <v>0.3279872536659241</v>
       </c>
       <c r="GW4" t="n">
-        <v>0.3229392468929291</v>
+        <v>0.3230725824832916</v>
       </c>
       <c r="GX4" t="n">
-        <v>0.3240164816379547</v>
+        <v>0.3241543173789978</v>
       </c>
       <c r="GY4" t="n">
-        <v>0.3242863714694977</v>
+        <v>0.3244283199310303</v>
       </c>
       <c r="GZ4" t="n">
-        <v>0.3374826908111572</v>
+        <v>0.3376382291316986</v>
       </c>
       <c r="HA4" t="n">
-        <v>0.3504160940647125</v>
+        <v>0.3505618572235107</v>
       </c>
       <c r="HB4" t="n">
-        <v>0.3628751039505005</v>
+        <v>0.3630390167236328</v>
       </c>
       <c r="HC4" t="n">
-        <v>0.3571555912494659</v>
+        <v>0.3572942912578583</v>
       </c>
       <c r="HD4" t="n">
-        <v>0.3451954424381256</v>
+        <v>0.3453966379165649</v>
       </c>
       <c r="HE4" t="n">
-        <v>0.340386837720871</v>
+        <v>0.3405879139900208</v>
       </c>
       <c r="HF4" t="n">
-        <v>0.3419501781463623</v>
+        <v>0.3421447277069092</v>
       </c>
       <c r="HG4" t="n">
-        <v>0.3484826683998108</v>
+        <v>0.3486765623092651</v>
       </c>
       <c r="HH4" t="n">
-        <v>0.3473001420497894</v>
+        <v>0.3474946618080139</v>
       </c>
       <c r="HI4" t="n">
-        <v>0.3456463515758514</v>
+        <v>0.3458418846130371</v>
       </c>
       <c r="HJ4" t="n">
-        <v>0.3481968641281128</v>
+        <v>0.3483899831771851</v>
       </c>
       <c r="HK4" t="n">
-        <v>0.3419182002544403</v>
+        <v>0.3421105444431305</v>
       </c>
       <c r="HL4" t="n">
-        <v>0.3436374068260193</v>
+        <v>0.3438247740268707</v>
       </c>
       <c r="HM4" t="n">
-        <v>0.3406161963939667</v>
+        <v>0.3407966792583466</v>
       </c>
       <c r="HN4" t="n">
-        <v>0.3638316690921783</v>
+        <v>0.3640225231647491</v>
       </c>
       <c r="HO4" t="n">
-        <v>0.3780700266361237</v>
+        <v>0.3782707750797272</v>
       </c>
       <c r="HP4" t="n">
-        <v>0.3578901886940002</v>
+        <v>0.3580575287342072</v>
       </c>
       <c r="HQ4" t="n">
-        <v>0.3463298976421356</v>
+        <v>0.3464721739292145</v>
       </c>
       <c r="HR4" t="inlineStr">
         <is>
@@ -3607,676 +3607,676 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02473424561321735</v>
+        <v>0.0247703529894352</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0334492065012455</v>
+        <v>0.0334850549697876</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03554849326610565</v>
+        <v>0.03558462858200073</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03709160163998604</v>
+        <v>0.03712750598788261</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03756600618362427</v>
+        <v>0.03760004416108131</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03685631603002548</v>
+        <v>0.0368892140686512</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03627615049481392</v>
+        <v>0.03630797192454338</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03592483699321747</v>
+        <v>0.03595678135752678</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03613313660025597</v>
+        <v>0.03616492450237274</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03544807061553001</v>
+        <v>0.03547914698719978</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03440786898136139</v>
+        <v>0.0344369001686573</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03338335454463959</v>
+        <v>0.0334109365940094</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03330034762620926</v>
+        <v>0.03332802653312683</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03387786448001862</v>
+        <v>0.03390596434473991</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04992411658167839</v>
+        <v>0.04998144507408142</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06129197776317596</v>
+        <v>0.06134752556681633</v>
       </c>
       <c r="R5" t="n">
-        <v>0.06404837965965271</v>
+        <v>0.06410626322031021</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06500349193811417</v>
+        <v>0.06505760550498962</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06623115390539169</v>
+        <v>0.06628608703613281</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06387748569250107</v>
+        <v>0.06392937898635864</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06469292193651199</v>
+        <v>0.0647432878613472</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06422305852174759</v>
+        <v>0.06427273899316788</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06367705762386322</v>
+        <v>0.06372611969709396</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06324398517608643</v>
+        <v>0.06329162418842316</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.06013057753443718</v>
+        <v>0.06017433851957321</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05783393606543541</v>
+        <v>0.05787727981805801</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.05766382068395615</v>
+        <v>0.05770774185657501</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0590718612074852</v>
+        <v>0.05911615863442421</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.08157900720834732</v>
+        <v>0.08164829015731812</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.09353911876678467</v>
+        <v>0.09360940009355545</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.09358458966016769</v>
+        <v>0.09365761280059814</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.09555047005414963</v>
+        <v>0.09561777114868164</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.09577383100986481</v>
+        <v>0.09584184736013412</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.09507563710212708</v>
+        <v>0.09514205157756805</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.09190931916236877</v>
+        <v>0.09197200834751129</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.09091850370168686</v>
+        <v>0.0909799337387085</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.09118626266717911</v>
+        <v>0.09124746918678284</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.08816245943307877</v>
+        <v>0.0882219523191452</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.08389652520418167</v>
+        <v>0.08395025134086609</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0819060280919075</v>
+        <v>0.08195961266756058</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.08408896625041962</v>
+        <v>0.08414531499147415</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.08478716015815735</v>
+        <v>0.0848424881696701</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.110772393643856</v>
+        <v>0.1108492985367775</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.117948479950428</v>
+        <v>0.118030346930027</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.1186549663543701</v>
+        <v>0.1187340915203094</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1202029809355736</v>
+        <v>0.1202739924192429</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.1182569265365601</v>
+        <v>0.1183402538299561</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1139746606349945</v>
+        <v>0.1140464618802071</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1144488900899887</v>
+        <v>0.1145219281315804</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.1135661527514458</v>
+        <v>0.1136375665664673</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.1121685281395912</v>
+        <v>0.1122386530041695</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.1084656491875648</v>
+        <v>0.1085326969623566</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.1037491336464882</v>
+        <v>0.1038094237446785</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.1020457297563553</v>
+        <v>0.1021075770258904</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.1007596701383591</v>
+        <v>0.1008229702711105</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.103792279958725</v>
+        <v>0.1038557142019272</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.1391681581735611</v>
+        <v>0.1392492353916168</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.1414149105548859</v>
+        <v>0.1415064334869385</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.140798419713974</v>
+        <v>0.1408852189779282</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.1373688131570816</v>
+        <v>0.1374501138925552</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.1374891847372055</v>
+        <v>0.1375788748264313</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.1312344074249268</v>
+        <v>0.131316289305687</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.1306594759225845</v>
+        <v>0.1307355910539627</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1281214356422424</v>
+        <v>0.1281987726688385</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.126246377825737</v>
+        <v>0.1263213455677032</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.1274928003549576</v>
+        <v>0.1275649815797806</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.119292713701725</v>
+        <v>0.1193581223487854</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.1186502724885941</v>
+        <v>0.1187183409929276</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.1180193573236465</v>
+        <v>0.1180887073278427</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.1178862974047661</v>
+        <v>0.1179554834961891</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.1741607040166855</v>
+        <v>0.1742829978466034</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.1722531318664551</v>
+        <v>0.1723738163709641</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1681056618690491</v>
+        <v>0.1682248711585999</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.1679317206144333</v>
+        <v>0.1680377274751663</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.1660200208425522</v>
+        <v>0.1661230474710464</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.1619889885187149</v>
+        <v>0.162092536687851</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.158022940158844</v>
+        <v>0.158116027712822</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.1551036536693573</v>
+        <v>0.1551961451768875</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.1530552357435226</v>
+        <v>0.1531434059143066</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.1488943845033646</v>
+        <v>0.1489765793085098</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.1451498121023178</v>
+        <v>0.1452271640300751</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1384665071964264</v>
+        <v>0.138542115688324</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.1385907381772995</v>
+        <v>0.138666957616806</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.1418367773294449</v>
+        <v>0.1419179886579514</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.2001298815011978</v>
+        <v>0.200263187289238</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.1981054395437241</v>
+        <v>0.1982430666685104</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.1952088326215744</v>
+        <v>0.1953404694795609</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.191088855266571</v>
+        <v>0.1912079751491547</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.1874358505010605</v>
+        <v>0.1875538378953934</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.1807047575712204</v>
+        <v>0.1808174550533295</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.1812527626752853</v>
+        <v>0.1813597679138184</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.1748519092798233</v>
+        <v>0.1749530136585236</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.173272505402565</v>
+        <v>0.1733677685260773</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.1739727854728699</v>
+        <v>0.1740620583295822</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.1611292362213135</v>
+        <v>0.1612128168344498</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.1585946977138519</v>
+        <v>0.1586790084838867</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.1585933119058609</v>
+        <v>0.158678412437439</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.1647810488939285</v>
+        <v>0.1648723930120468</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.2357022762298584</v>
+        <v>0.2358445376157761</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.2231614738702774</v>
+        <v>0.223308801651001</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.2229323983192444</v>
+        <v>0.223069503903389</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.2212786376476288</v>
+        <v>0.2214177399873734</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.2119534313678741</v>
+        <v>0.2120799124240875</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.2084416151046753</v>
+        <v>0.2085620909929276</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.2088409811258316</v>
+        <v>0.2089553475379944</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.2042568773031235</v>
+        <v>0.2043597549200058</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.2037459760904312</v>
+        <v>0.2038496136665344</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.1981513202190399</v>
+        <v>0.1982501447200775</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.1922677010297775</v>
+        <v>0.1923597604036331</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.1891846507787704</v>
+        <v>0.1892757266759872</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.1880126893520355</v>
+        <v>0.1881038248538971</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1906143873929977</v>
+        <v>0.1907131671905518</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.252103716135025</v>
+        <v>0.2522738873958588</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.2487518936395645</v>
+        <v>0.2489116936922073</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.2405421286821365</v>
+        <v>0.2406823486089706</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.2388902604579926</v>
+        <v>0.23902727663517</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.2318815588951111</v>
+        <v>0.2320124357938766</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.2327949702739716</v>
+        <v>0.232911691069603</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.2269326895475388</v>
+        <v>0.2270437628030777</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.2209244221448898</v>
+        <v>0.2210307121276855</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.2194151878356934</v>
+        <v>0.2195195704698563</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.2164528965950012</v>
+        <v>0.2165530622005463</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.2117480933666229</v>
+        <v>0.2118433266878128</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.2102704793214798</v>
+        <v>0.2103595435619354</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.2126369625329971</v>
+        <v>0.2127347439527512</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.2147051244974136</v>
+        <v>0.2148070484399796</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.2687057256698608</v>
+        <v>0.2688635885715485</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.2586474418640137</v>
+        <v>0.258794367313385</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.2571913301944733</v>
+        <v>0.2573381662368774</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.2497382313013077</v>
+        <v>0.2498636841773987</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.2489964067935944</v>
+        <v>0.2491172701120377</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.2430776208639145</v>
+        <v>0.243193507194519</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.2403549551963806</v>
+        <v>0.2404656708240509</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.2388586848974228</v>
+        <v>0.2389665693044662</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.2365143150091171</v>
+        <v>0.2366152256727219</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.2344182729721069</v>
+        <v>0.2345166653394699</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.2224549055099487</v>
+        <v>0.2225567400455475</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.2260749936103821</v>
+        <v>0.2261720895767212</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.2271650731563568</v>
+        <v>0.2272636592388153</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.2287117093801498</v>
+        <v>0.2288144528865814</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.2787216305732727</v>
+        <v>0.2788593173027039</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.2754305601119995</v>
+        <v>0.2755616009235382</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.2711921334266663</v>
+        <v>0.2713164687156677</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.2643579542636871</v>
+        <v>0.264474481344223</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.2675286829471588</v>
+        <v>0.2676406502723694</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.2566152513027191</v>
+        <v>0.2567215263843536</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.2562942504882812</v>
+        <v>0.2564038336277008</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.2502084374427795</v>
+        <v>0.25031778216362</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.2530699670314789</v>
+        <v>0.2531711757183075</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.2522706687450409</v>
+        <v>0.2523717284202576</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.248770460486412</v>
+        <v>0.2488738298416138</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.2486128658056259</v>
+        <v>0.2487119287252426</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.2484370023012161</v>
+        <v>0.2485377043485641</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.2600231468677521</v>
+        <v>0.2601394355297089</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.28495192527771</v>
+        <v>0.2850553691387177</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.2854775488376617</v>
+        <v>0.2855826020240784</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.2748512029647827</v>
+        <v>0.2749496698379517</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.2772242724895477</v>
+        <v>0.2773253619670868</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.2676567435264587</v>
+        <v>0.2677552402019501</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.2691464424133301</v>
+        <v>0.2692481577396393</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.2688192129135132</v>
+        <v>0.2689194083213806</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.2655418515205383</v>
+        <v>0.2656430602073669</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.2610315382480621</v>
+        <v>0.2611303925514221</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.2597489953041077</v>
+        <v>0.2598470747470856</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.2620001137256622</v>
+        <v>0.2621036171913147</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.2639389336109161</v>
+        <v>0.2640466392040253</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.2736955881118774</v>
+        <v>0.2738169431686401</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.2839720249176025</v>
+        <v>0.2841013967990875</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.2891019284725189</v>
+        <v>0.28921839594841</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.2893575131893158</v>
+        <v>0.2894722521305084</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.2813363671302795</v>
+        <v>0.2814475297927856</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.2794696688652039</v>
+        <v>0.2795843780040741</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.2847945988178253</v>
+        <v>0.284907728433609</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.282505989074707</v>
+        <v>0.2826233208179474</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.2826950252056122</v>
+        <v>0.2828134596347809</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.2807415723800659</v>
+        <v>0.2808617055416107</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.2825758457183838</v>
+        <v>0.2827006578445435</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.2829523086547852</v>
+        <v>0.2830789387226105</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.2821109592914581</v>
+        <v>0.2822441160678864</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.2927426993846893</v>
+        <v>0.2928861975669861</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.2971336245536804</v>
+        <v>0.2972843050956726</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.3117671310901642</v>
+        <v>0.3119231462478638</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.305301159620285</v>
+        <v>0.3054488003253937</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.306020051240921</v>
+        <v>0.3061719834804535</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.3071399629116058</v>
+        <v>0.3072969913482666</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.3071010708808899</v>
+        <v>0.3072598874568939</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.3051995635032654</v>
+        <v>0.3053577542304993</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.3035706281661987</v>
+        <v>0.3037271201610565</v>
       </c>
       <c r="GH5" t="n">
-        <v>0.2998576760292053</v>
+        <v>0.3000150620937347</v>
       </c>
       <c r="GI5" t="n">
-        <v>0.3005278408527374</v>
+        <v>0.3006924986839294</v>
       </c>
       <c r="GJ5" t="n">
-        <v>0.3009279072284698</v>
+        <v>0.3010902106761932</v>
       </c>
       <c r="GK5" t="n">
-        <v>0.3047835230827332</v>
+        <v>0.3049511611461639</v>
       </c>
       <c r="GL5" t="n">
-        <v>0.3113354742527008</v>
+        <v>0.3115069270133972</v>
       </c>
       <c r="GM5" t="n">
-        <v>0.3177029192447662</v>
+        <v>0.3178876340389252</v>
       </c>
       <c r="GN5" t="n">
-        <v>0.3330078125</v>
+        <v>0.3331995606422424</v>
       </c>
       <c r="GO5" t="n">
-        <v>0.3408308327198029</v>
+        <v>0.3410261273384094</v>
       </c>
       <c r="GP5" t="n">
-        <v>0.3337568938732147</v>
+        <v>0.3339265584945679</v>
       </c>
       <c r="GQ5" t="n">
-        <v>0.3307538330554962</v>
+        <v>0.3309228122234344</v>
       </c>
       <c r="GR5" t="n">
-        <v>0.3297143876552582</v>
+        <v>0.3298769295215607</v>
       </c>
       <c r="GS5" t="n">
-        <v>0.3281114101409912</v>
+        <v>0.3282769918441772</v>
       </c>
       <c r="GT5" t="n">
-        <v>0.3294678032398224</v>
+        <v>0.329638659954071</v>
       </c>
       <c r="GU5" t="n">
-        <v>0.3237530291080475</v>
+        <v>0.3239259421825409</v>
       </c>
       <c r="GV5" t="n">
-        <v>0.3289771974086761</v>
+        <v>0.3291564583778381</v>
       </c>
       <c r="GW5" t="n">
-        <v>0.3240568935871124</v>
+        <v>0.3242418467998505</v>
       </c>
       <c r="GX5" t="n">
-        <v>0.3251685798168182</v>
+        <v>0.3253596127033234</v>
       </c>
       <c r="GY5" t="n">
-        <v>0.3254676163196564</v>
+        <v>0.3256643116474152</v>
       </c>
       <c r="GZ5" t="n">
-        <v>0.3386402726173401</v>
+        <v>0.3388505280017853</v>
       </c>
       <c r="HA5" t="n">
-        <v>0.3515217304229736</v>
+        <v>0.3517195880413055</v>
       </c>
       <c r="HB5" t="n">
-        <v>0.3640889823436737</v>
+        <v>0.3643094599246979</v>
       </c>
       <c r="HC5" t="n">
-        <v>0.3581225872039795</v>
+        <v>0.3583075404167175</v>
       </c>
       <c r="HD5" t="n">
-        <v>0.3466254472732544</v>
+        <v>0.3468936383724213</v>
       </c>
       <c r="HE5" t="n">
-        <v>0.3417514860630035</v>
+        <v>0.3420170247554779</v>
       </c>
       <c r="HF5" t="n">
-        <v>0.3433250188827515</v>
+        <v>0.3435839116573334</v>
       </c>
       <c r="HG5" t="n">
-        <v>0.3499063551425934</v>
+        <v>0.3501660525798798</v>
       </c>
       <c r="HH5" t="n">
-        <v>0.3487730026245117</v>
+        <v>0.34903484582901</v>
       </c>
       <c r="HI5" t="n">
-        <v>0.3471465706825256</v>
+        <v>0.3474104106426239</v>
       </c>
       <c r="HJ5" t="n">
-        <v>0.3497403860092163</v>
+        <v>0.3500028252601624</v>
       </c>
       <c r="HK5" t="n">
-        <v>0.3434751629829407</v>
+        <v>0.3437374532222748</v>
       </c>
       <c r="HL5" t="n">
-        <v>0.3452318608760834</v>
+        <v>0.3454899489879608</v>
       </c>
       <c r="HM5" t="n">
-        <v>0.3422358334064484</v>
+        <v>0.3424873948097229</v>
       </c>
       <c r="HN5" t="n">
-        <v>0.365431934595108</v>
+        <v>0.3656924664974213</v>
       </c>
       <c r="HO5" t="n">
-        <v>0.3796768486499786</v>
+        <v>0.3799476623535156</v>
       </c>
       <c r="HP5" t="n">
-        <v>0.3590731620788574</v>
+        <v>0.3592944741249084</v>
       </c>
       <c r="HQ5" t="n">
-        <v>0.3472077548503876</v>
+        <v>0.3473924994468689</v>
       </c>
       <c r="HR5" t="inlineStr">
         <is>
@@ -4291,676 +4291,676 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02517027035355568</v>
+        <v>0.02521757408976555</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03390568867325783</v>
+        <v>0.03395135328173637</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0359937883913517</v>
+        <v>0.03603967651724815</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03752041980624199</v>
+        <v>0.0375661700963974</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03797045722603798</v>
+        <v>0.03801379352807999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03723622858524323</v>
+        <v>0.03727835044264793</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03663580119609833</v>
+        <v>0.03667692840099335</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03628033399581909</v>
+        <v>0.03632178530097008</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03648064285516739</v>
+        <v>0.03652207180857658</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03578019142150879</v>
+        <v>0.03582087531685829</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03471130132675171</v>
+        <v>0.03474957868456841</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03364795446395874</v>
+        <v>0.03368453308939934</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03356102854013443</v>
+        <v>0.03359783440828323</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03413168340921402</v>
+        <v>0.03416922688484192</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05059117078781128</v>
+        <v>0.0506650023162365</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.06199358031153679</v>
+        <v>0.06206345930695534</v>
       </c>
       <c r="R6" t="n">
-        <v>0.06476221978664398</v>
+        <v>0.06483526527881622</v>
       </c>
       <c r="S6" t="n">
-        <v>0.06565439701080322</v>
+        <v>0.06572294980287552</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06687237322330475</v>
+        <v>0.06694225966930389</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06445284187793732</v>
+        <v>0.06451933830976486</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06525750458240509</v>
+        <v>0.0653223916888237</v>
       </c>
       <c r="W6" t="n">
-        <v>0.06475265324115753</v>
+        <v>0.0648171454668045</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06420805305242538</v>
+        <v>0.06427200883626938</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.06375232338905334</v>
+        <v>0.06381457298994064</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.06058697402477264</v>
+        <v>0.06064467504620552</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.05824310705065727</v>
+        <v>0.05830064788460732</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.05807656794786453</v>
+        <v>0.05813506245613098</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.05947072803974152</v>
+        <v>0.05952978506684303</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.08242946863174438</v>
+        <v>0.08251555263996124</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.09444043785333633</v>
+        <v>0.09452727437019348</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.09449511021375656</v>
+        <v>0.09458618611097336</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.09636625647544861</v>
+        <v>0.09645064175128937</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.09656621515750885</v>
+        <v>0.09665243327617645</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0958310142159462</v>
+        <v>0.09591584652662277</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.09261084347963333</v>
+        <v>0.09269154071807861</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.09157436341047287</v>
+        <v>0.09165404736995697</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.09185365587472916</v>
+        <v>0.09193328768014908</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.08878931403160095</v>
+        <v>0.08886697143316269</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.08443313837051392</v>
+        <v>0.08450378477573395</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.08240920305252075</v>
+        <v>0.08248037099838257</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.08461129665374756</v>
+        <v>0.0846862718462944</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.08528996258974075</v>
+        <v>0.08536392450332642</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.11175786703825</v>
+        <v>0.111852154135704</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.1190431639552116</v>
+        <v>0.1191437095403671</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.1196850091218948</v>
+        <v>0.1197831407189369</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1210983693599701</v>
+        <v>0.1211869344115257</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.1192083284258842</v>
+        <v>0.1193144544959068</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.114799827337265</v>
+        <v>0.1148917973041534</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1152571365237236</v>
+        <v>0.1153513118624687</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.1143246814608574</v>
+        <v>0.1144174039363861</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.1129268929362297</v>
+        <v>0.1130182221531868</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.1091615855693817</v>
+        <v>0.1092492192983627</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.1043476313352585</v>
+        <v>0.1044269278645515</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.1026198863983154</v>
+        <v>0.1027019992470741</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.1013308465480804</v>
+        <v>0.1014150902628899</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.1043569594621658</v>
+        <v>0.1044417768716812</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.1402755081653595</v>
+        <v>0.1403726488351822</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.1425859034061432</v>
+        <v>0.1426985412836075</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.1418839693069458</v>
+        <v>0.1419922411441803</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.1383897513151169</v>
+        <v>0.1384921371936798</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.1385088264942169</v>
+        <v>0.138623520731926</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.1321482360363007</v>
+        <v>0.1322536170482635</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.131505012512207</v>
+        <v>0.1316035240888596</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.1289339661598206</v>
+        <v>0.1290347129106522</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.1270501613616943</v>
+        <v>0.1271481513977051</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.1282549202442169</v>
+        <v>0.1283494979143143</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.1199388429522514</v>
+        <v>0.1200252994894981</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.1192646697163582</v>
+        <v>0.1193550676107407</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.1186324432492256</v>
+        <v>0.1187248378992081</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.1184758916497231</v>
+        <v>0.1185682117938995</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.1756868660449982</v>
+        <v>0.1758374869823456</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.1737150251865387</v>
+        <v>0.1738655716180801</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1695346087217331</v>
+        <v>0.1696862429380417</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.1692365109920502</v>
+        <v>0.1693722605705261</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.1671721786260605</v>
+        <v>0.1673047095537186</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.1630957126617432</v>
+        <v>0.1632298231124878</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.1590452790260315</v>
+        <v>0.1591668426990509</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.1560741662979126</v>
+        <v>0.1561952382326126</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.1539663821458817</v>
+        <v>0.1540819853544235</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.1497351080179214</v>
+        <v>0.1498430818319321</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.1458946913480759</v>
+        <v>0.145997017621994</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.1391339004039764</v>
+        <v>0.1392346322536469</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.1392532140016556</v>
+        <v>0.1393549740314484</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.1424949169158936</v>
+        <v>0.1426028460264206</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.2017002254724503</v>
+        <v>0.2018680423498154</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.1997593492269516</v>
+        <v>0.1999349892139435</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.196725532412529</v>
+        <v>0.1968953162431717</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.1924320310354233</v>
+        <v>0.1925863027572632</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.1887281537055969</v>
+        <v>0.188881978392601</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.1818870007991791</v>
+        <v>0.1820344477891922</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.1823597401380539</v>
+        <v>0.1825000643730164</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.175884023308754</v>
+        <v>0.1760171502828598</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.1742534339427948</v>
+        <v>0.1743792146444321</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.1748865246772766</v>
+        <v>0.1750044822692871</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.1618905663490295</v>
+        <v>0.1620012223720551</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.1592942625284195</v>
+        <v>0.1594063341617584</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.1592655032873154</v>
+        <v>0.15937839448452</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.1654880344867706</v>
+        <v>0.1656090617179871</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.2373227030038834</v>
+        <v>0.2375070005655289</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.2248379290103912</v>
+        <v>0.2250304669141769</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.2244160622358322</v>
+        <v>0.2245948165655136</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.22270867228508</v>
+        <v>0.2228909134864807</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.2132620811462402</v>
+        <v>0.2134287357330322</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.2096738666296005</v>
+        <v>0.2098330408334732</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.2099954038858414</v>
+        <v>0.2101467400789261</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.2052874714136124</v>
+        <v>0.2054237574338913</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.2047180384397507</v>
+        <v>0.2048550993204117</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.1990575939416885</v>
+        <v>0.199188306927681</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.1930471360683441</v>
+        <v>0.1931692659854889</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.1899202615022659</v>
+        <v>0.1900410652160645</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.1887011229991913</v>
+        <v>0.1888215243816376</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1912973076105118</v>
+        <v>0.1914273053407669</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.2538783252239227</v>
+        <v>0.254101425409317</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.2503506541252136</v>
+        <v>0.2505606114864349</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.2419986575841904</v>
+        <v>0.2421837449073792</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.2402803748846054</v>
+        <v>0.2404612153768539</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.2331690788269043</v>
+        <v>0.2333423495292664</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.2339465469121933</v>
+        <v>0.2341014295816422</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.2279724925756454</v>
+        <v>0.2281196415424347</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.2219017297029495</v>
+        <v>0.2220427691936493</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.2203277349472046</v>
+        <v>0.2204660624265671</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.2172947227954865</v>
+        <v>0.217427596449852</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.2125006020069122</v>
+        <v>0.212626576423645</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.2109066843986511</v>
+        <v>0.2110236585140228</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.2133041620254517</v>
+        <v>0.2134325802326202</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.2153546512126923</v>
+        <v>0.2154882252216339</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.2702871859073639</v>
+        <v>0.270495593547821</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.2601118683815002</v>
+        <v>0.2603059113025665</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.2586128413677216</v>
+        <v>0.2588069438934326</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.2509625554084778</v>
+        <v>0.2511288225650787</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.2501133680343628</v>
+        <v>0.2502735257148743</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.2441295832395554</v>
+        <v>0.2442832142114639</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.2413292825222015</v>
+        <v>0.2414761632680893</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.2397630214691162</v>
+        <v>0.2399061322212219</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.2373691350221634</v>
+        <v>0.237502858042717</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.2352266907691956</v>
+        <v>0.2353569865226746</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.223178505897522</v>
+        <v>0.2233127057552338</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.2267205268144608</v>
+        <v>0.2268480062484741</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.2277393043041229</v>
+        <v>0.2278678864240646</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.229321226477623</v>
+        <v>0.229455292224884</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.2800047695636749</v>
+        <v>0.2801878154277802</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.2765672206878662</v>
+        <v>0.2767415046691895</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.2722381055355072</v>
+        <v>0.2724029719829559</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.2652986347675323</v>
+        <v>0.2654527425765991</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.2684291303157806</v>
+        <v>0.2685771584510803</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.2574326395988464</v>
+        <v>0.2575728297233582</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.2571607530117035</v>
+        <v>0.257305920124054</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.2509787976741791</v>
+        <v>0.251122921705246</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.2538011968135834</v>
+        <v>0.2539345324039459</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.252942681312561</v>
+        <v>0.2530752122402191</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.2494074404239655</v>
+        <v>0.2495424896478653</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.2491776496171951</v>
+        <v>0.2493065744638443</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.2489554733037949</v>
+        <v>0.2490860521793365</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.2606185078620911</v>
+        <v>0.260768860578537</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.2856768071651459</v>
+        <v>0.2858125269412994</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.2862003445625305</v>
+        <v>0.2863382697105408</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.2755213677883148</v>
+        <v>0.2756505012512207</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.2778791189193726</v>
+        <v>0.2780113518238068</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.2682745754718781</v>
+        <v>0.2684032618999481</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.2697590589523315</v>
+        <v>0.269891768693924</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.2694273889064789</v>
+        <v>0.2695581018924713</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.2661428153514862</v>
+        <v>0.2662748396396637</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.2616214156150818</v>
+        <v>0.2617504298686981</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.2603337466716766</v>
+        <v>0.2604617178440094</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.2625720202922821</v>
+        <v>0.2627067267894745</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.264435887336731</v>
+        <v>0.2645737528800964</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.2741957902908325</v>
+        <v>0.2743491530418396</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.284490704536438</v>
+        <v>0.2846538126468658</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.2898118197917938</v>
+        <v>0.2899641394615173</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.2900266945362091</v>
+        <v>0.2901760935783386</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.2819755077362061</v>
+        <v>0.2821202278137207</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.2801013588905334</v>
+        <v>0.2802501022815704</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.2854619026184082</v>
+        <v>0.2856096625328064</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.283163994550705</v>
+        <v>0.2833167612552643</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.2833713293075562</v>
+        <v>0.2835257053375244</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.2814222276210785</v>
+        <v>0.2815788388252258</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.2832598984241486</v>
+        <v>0.283422440290451</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.2836441695690155</v>
+        <v>0.2838090062141418</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.282743364572525</v>
+        <v>0.282914787530899</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.293340265750885</v>
+        <v>0.2935229539871216</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.2977731823921204</v>
+        <v>0.2979649007320404</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.3124336302280426</v>
+        <v>0.3126317858695984</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.3062102794647217</v>
+        <v>0.3064034879207611</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.3069462180137634</v>
+        <v>0.3071449100971222</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.308110386133194</v>
+        <v>0.3083160519599915</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.3080832064151764</v>
+        <v>0.3082912862300873</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.3061524033546448</v>
+        <v>0.3063593208789825</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.3045009076595306</v>
+        <v>0.304705411195755</v>
       </c>
       <c r="GH6" t="n">
-        <v>0.3007718324661255</v>
+        <v>0.300977349281311</v>
       </c>
       <c r="GI6" t="n">
-        <v>0.3013834655284882</v>
+        <v>0.3015974760055542</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.3018366396427155</v>
+        <v>0.3020483553409576</v>
       </c>
       <c r="GK6" t="n">
-        <v>0.3056978583335876</v>
+        <v>0.3059163689613342</v>
       </c>
       <c r="GL6" t="n">
-        <v>0.3121932148933411</v>
+        <v>0.3124160170555115</v>
       </c>
       <c r="GM6" t="n">
-        <v>0.3185144364833832</v>
+        <v>0.3187508881092072</v>
       </c>
       <c r="GN6" t="n">
-        <v>0.3338450193405151</v>
+        <v>0.3340894877910614</v>
       </c>
       <c r="GO6" t="n">
-        <v>0.3417546451091766</v>
+        <v>0.3420053422451019</v>
       </c>
       <c r="GP6" t="n">
-        <v>0.3346993625164032</v>
+        <v>0.3349202871322632</v>
       </c>
       <c r="GQ6" t="n">
-        <v>0.3316209614276886</v>
+        <v>0.3318398892879486</v>
       </c>
       <c r="GR6" t="n">
-        <v>0.3305988609790802</v>
+        <v>0.3308100998401642</v>
       </c>
       <c r="GS6" t="n">
-        <v>0.3289926052093506</v>
+        <v>0.3292076885700226</v>
       </c>
       <c r="GT6" t="n">
-        <v>0.3303811550140381</v>
+        <v>0.3306033909320831</v>
       </c>
       <c r="GU6" t="n">
-        <v>0.3246602118015289</v>
+        <v>0.3248850405216217</v>
       </c>
       <c r="GV6" t="n">
-        <v>0.3299208283424377</v>
+        <v>0.3301538527011871</v>
       </c>
       <c r="GW6" t="n">
-        <v>0.3249924778938293</v>
+        <v>0.3252320289611816</v>
       </c>
       <c r="GX6" t="n">
-        <v>0.3261333107948303</v>
+        <v>0.3263805508613586</v>
       </c>
       <c r="GY6" t="n">
-        <v>0.3264535963535309</v>
+        <v>0.3267081677913666</v>
       </c>
       <c r="GZ6" t="n">
-        <v>0.3395979702472687</v>
+        <v>0.3398661017417908</v>
       </c>
       <c r="HA6" t="n">
-        <v>0.3524379134178162</v>
+        <v>0.3526909351348877</v>
       </c>
       <c r="HB6" t="n">
-        <v>0.3650987148284912</v>
+        <v>0.3653792142868042</v>
       </c>
       <c r="HC6" t="n">
-        <v>0.3589125573635101</v>
+        <v>0.3591466546058655</v>
       </c>
       <c r="HD6" t="n">
-        <v>0.3477983772754669</v>
+        <v>0.3481375873088837</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.3428682088851929</v>
+        <v>0.3432022035121918</v>
       </c>
       <c r="HF6" t="n">
-        <v>0.3444595336914062</v>
+        <v>0.3447867631912231</v>
       </c>
       <c r="HG6" t="n">
-        <v>0.3510861396789551</v>
+        <v>0.351415604352951</v>
       </c>
       <c r="HH6" t="n">
-        <v>0.3499998152256012</v>
+        <v>0.3503330647945404</v>
       </c>
       <c r="HI6" t="n">
-        <v>0.3483987748622894</v>
+        <v>0.3487350642681122</v>
       </c>
       <c r="HJ6" t="n">
-        <v>0.3510391712188721</v>
+        <v>0.3513751327991486</v>
       </c>
       <c r="HK6" t="n">
-        <v>0.3447877764701843</v>
+        <v>0.3451241254806519</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.3465880155563354</v>
+        <v>0.3469209372997284</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.343626469373703</v>
+        <v>0.3439532220363617</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.3667944371700287</v>
+        <v>0.3671289086341858</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.3810324966907501</v>
+        <v>0.3813779056072235</v>
       </c>
       <c r="HP6" t="n">
-        <v>0.3600638508796692</v>
+        <v>0.3603424727916718</v>
       </c>
       <c r="HQ6" t="n">
-        <v>0.347919762134552</v>
+        <v>0.3481496274471283</v>
       </c>
       <c r="HR6" t="inlineStr">
         <is>
@@ -4975,676 +4975,676 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0255597960203886</v>
+        <v>0.02562039904296398</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03430443629622459</v>
+        <v>0.03436199948191643</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03638442978262901</v>
+        <v>0.03644195571541786</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03789756074547768</v>
+        <v>0.03795478865504265</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03832301497459412</v>
+        <v>0.0383770614862442</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0375671312212944</v>
+        <v>0.037619698792696</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03694754838943481</v>
+        <v>0.03699899092316628</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03658737242221832</v>
+        <v>0.0366392508149147</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03678059577941895</v>
+        <v>0.03683250397443771</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03606671467423439</v>
+        <v>0.03611774370074272</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03497065603733063</v>
+        <v>0.03501873463392258</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03387979790568352</v>
+        <v>0.03392582386732101</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03378975391387939</v>
+        <v>0.03383610770106316</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03435662761330605</v>
+        <v>0.03440399095416069</v>
       </c>
       <c r="P7" t="n">
-        <v>0.05119486525654793</v>
+        <v>0.05128848180174828</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.06260659545660019</v>
+        <v>0.06269396096467972</v>
       </c>
       <c r="R7" t="n">
-        <v>0.06538344919681549</v>
+        <v>0.06547448039054871</v>
       </c>
       <c r="S7" t="n">
-        <v>0.06621880084276199</v>
+        <v>0.0663040429353714</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06742691993713379</v>
+        <v>0.06751378625631332</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06495340168476105</v>
+        <v>0.06503617018461227</v>
       </c>
       <c r="V7" t="n">
-        <v>0.06574159115552902</v>
+        <v>0.06582243740558624</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06520871073007584</v>
+        <v>0.06528923660516739</v>
       </c>
       <c r="X7" t="n">
-        <v>0.06465854495763779</v>
+        <v>0.06473849713802338</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.06418120861053467</v>
+        <v>0.06425900012254715</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.06096899881958961</v>
+        <v>0.06104131415486336</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.05859620124101639</v>
+        <v>0.05866850912570953</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.05843108519911766</v>
+        <v>0.05850467458367348</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.05981758609414101</v>
+        <v>0.05989189445972443</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.08317751437425613</v>
+        <v>0.08328460901975632</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.09521894901990891</v>
+        <v>0.09532613307237625</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.09527397900819778</v>
+        <v>0.09538634121417999</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.09705764800310135</v>
+        <v>0.09716160595417023</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.09723789244890213</v>
+        <v>0.09734446555376053</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.09646984934806824</v>
+        <v>0.09657495468854904</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09319950640201569</v>
+        <v>0.09329971671104431</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.09212709218263626</v>
+        <v>0.0922262966632843</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.09240735322237015</v>
+        <v>0.09250655025243759</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.08931037038564682</v>
+        <v>0.08940716087818146</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.08488466590642929</v>
+        <v>0.08497299998998642</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.08283624053001404</v>
+        <v>0.08292557299137115</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.08505365252494812</v>
+        <v>0.08514782041311264</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0857163593173027</v>
+        <v>0.08580942451953888</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.1126214936375618</v>
+        <v>0.1127378791570663</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.1199617609381676</v>
+        <v>0.1200849041342735</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.1205420419573784</v>
+        <v>0.1206623315811157</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.121836744248867</v>
+        <v>0.1219452172517776</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.1200088784098625</v>
+        <v>0.1201401054859161</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.1154846474528313</v>
+        <v>0.1155985370278358</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1159283593297005</v>
+        <v>0.1160452142357826</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.1149565726518631</v>
+        <v>0.1150719001889229</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.1135494485497475</v>
+        <v>0.1136631146073341</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.1097384095191956</v>
+        <v>0.1098476201295853</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.1048423945903778</v>
+        <v>0.1049413979053497</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.1031012237071991</v>
+        <v>0.1032041609287262</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.1018156707286835</v>
+        <v>0.1019214391708374</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.1048344671726227</v>
+        <v>0.1049411445856094</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.1412141174077988</v>
+        <v>0.1413318514823914</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.1435617804527283</v>
+        <v>0.143699124455452</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.1427791863679886</v>
+        <v>0.1429117321968079</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.1392091363668442</v>
+        <v>0.1393347382545471</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.139349639415741</v>
+        <v>0.1394913643598557</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.132899284362793</v>
+        <v>0.1330298334360123</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.1321935057640076</v>
+        <v>0.1323157250881195</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.1296037435531616</v>
+        <v>0.1297291219234467</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.1277028769254684</v>
+        <v>0.1278249025344849</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.1288705468177795</v>
+        <v>0.1289883404970169</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1204682365059853</v>
+        <v>0.120576336979866</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.1197802573442459</v>
+        <v>0.1198935285210609</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.1191521510481834</v>
+        <v>0.1192681416869164</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.1189801841974258</v>
+        <v>0.1190961673855782</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.1769680678844452</v>
+        <v>0.1771517097949982</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.1749035716056824</v>
+        <v>0.1750873476266861</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1706942468881607</v>
+        <v>0.1708812564611435</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.1702648997306824</v>
+        <v>0.1704324632883072</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.1681053042411804</v>
+        <v>0.1682691723108292</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1640021950006485</v>
+        <v>0.1641685962677002</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.159868061542511</v>
+        <v>0.1600193679332733</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.1568614840507507</v>
+        <v>0.1570122838020325</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.1547061502933502</v>
+        <v>0.1548501998186111</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.1504178047180176</v>
+        <v>0.1505524218082428</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.1465041637420654</v>
+        <v>0.1466320902109146</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.13969786465168</v>
+        <v>0.1398243010044098</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.1398174613714218</v>
+        <v>0.1399453729391098</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.1430601924657822</v>
+        <v>0.1431953907012939</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.2029815912246704</v>
+        <v>0.2031872570514679</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.2010705918073654</v>
+        <v>0.2012870460748672</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.1979433447122574</v>
+        <v>0.1981537342071533</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.1935018450021744</v>
+        <v>0.1936931014060974</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.1897666901350021</v>
+        <v>0.1899580359458923</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.1828474402427673</v>
+        <v>0.1830311417579651</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.1832575052976608</v>
+        <v>0.1834324151277542</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.1767202168703079</v>
+        <v>0.1768864244222641</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.1750424206256866</v>
+        <v>0.1751995831727982</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.1756156086921692</v>
+        <v>0.1757629066705704</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.1625235974788666</v>
+        <v>0.1626619845628738</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.159891277551651</v>
+        <v>0.1600316762924194</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.1598492711782455</v>
+        <v>0.1599905043840408</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.1661005765199661</v>
+        <v>0.1662519127130508</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.2386047840118408</v>
+        <v>0.2388332933187485</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.226167231798172</v>
+        <v>0.2264071553945541</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.225603461265564</v>
+        <v>0.2258256822824478</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.2238731682300568</v>
+        <v>0.2241003215312958</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.2143159508705139</v>
+        <v>0.2145241051912308</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.210666224360466</v>
+        <v>0.2108652293682098</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.2109286338090897</v>
+        <v>0.2111179232597351</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.2061153054237366</v>
+        <v>0.2062857747077942</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.2055253535509109</v>
+        <v>0.2056968063116074</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1998106390237808</v>
+        <v>0.1999740153551102</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.1937065869569778</v>
+        <v>0.1938594430685043</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.1905433982610703</v>
+        <v>0.1906944215297699</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.1892968863248825</v>
+        <v>0.1894470900297165</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.1919040083885193</v>
+        <v>0.1920658499002457</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.2553183436393738</v>
+        <v>0.2555965483188629</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.2516646087169647</v>
+        <v>0.2519267499446869</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.2431714832782745</v>
+        <v>0.2434029430150986</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.2414038926362991</v>
+        <v>0.2416298687458038</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.2342167347669601</v>
+        <v>0.2344335615634918</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.2348729223012924</v>
+        <v>0.235066756606102</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.2288293242454529</v>
+        <v>0.2290134578943253</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.2227127552032471</v>
+        <v>0.2228893339633942</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.2211014628410339</v>
+        <v>0.2212746292352676</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.2180224508047104</v>
+        <v>0.2181889712810516</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.2131505459547043</v>
+        <v>0.2133079469203949</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.2114573270082474</v>
+        <v>0.2116026282310486</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.2138981372117996</v>
+        <v>0.2140577435493469</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.2159421741962433</v>
+        <v>0.2161080092191696</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.2715802192687988</v>
+        <v>0.271840900182724</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.2613039910793304</v>
+        <v>0.2615466415882111</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.2597813606262207</v>
+        <v>0.2600241899490356</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.2519573271274567</v>
+        <v>0.2521654069423676</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.2510431706905365</v>
+        <v>0.2512437403202057</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.245007112622261</v>
+        <v>0.2451994568109512</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.2421561181545258</v>
+        <v>0.242340162396431</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.2405451834201813</v>
+        <v>0.2407245337963104</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.2380972802639008</v>
+        <v>0.2382646501064301</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.2359197735786438</v>
+        <v>0.2360827475786209</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.2238257378339767</v>
+        <v>0.2239930033683777</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.2273090183734894</v>
+        <v>0.2274676263332367</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.2282796055078506</v>
+        <v>0.2284388840198517</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.2298880070447922</v>
+        <v>0.23005411028862</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.2810629904270172</v>
+        <v>0.2812923789024353</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.2775327861309052</v>
+        <v>0.2777513563632965</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.2731391489505768</v>
+        <v>0.2733457684516907</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.2661150693893433</v>
+        <v>0.2663077712059021</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.2692094445228577</v>
+        <v>0.2693944871425629</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.2581501305103302</v>
+        <v>0.2583251297473907</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.2579322159290314</v>
+        <v>0.2581141293048859</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.2516878843307495</v>
+        <v>0.2518678903579712</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.2544671893119812</v>
+        <v>0.2546336650848389</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.2535612881183624</v>
+        <v>0.2537261843681335</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.2500032782554626</v>
+        <v>0.2501708269119263</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.2497199922800064</v>
+        <v>0.2498795837163925</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.2494661957025528</v>
+        <v>0.2496273815631866</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.2612127065658569</v>
+        <v>0.2613981366157532</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.2863288521766663</v>
+        <v>0.2864977419376373</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.2868638336658478</v>
+        <v>0.2870355844497681</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.2761428654193878</v>
+        <v>0.2763036787509918</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.2784979641437531</v>
+        <v>0.2786624133586884</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.2688654959201813</v>
+        <v>0.2690254747867584</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.2703496515750885</v>
+        <v>0.2705143988132477</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.2700162529945374</v>
+        <v>0.2701785266399384</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.2667267024517059</v>
+        <v>0.2668905258178711</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.2621936500072479</v>
+        <v>0.2623538374900818</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.2609010636806488</v>
+        <v>0.2610599398612976</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.263135552406311</v>
+        <v>0.2633023858070374</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.2649430930614471</v>
+        <v>0.2651119828224182</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.2747223377227783</v>
+        <v>0.274908721446991</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.2850392758846283</v>
+        <v>0.2852371633052826</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.2905093431472778</v>
+        <v>0.2906988263130188</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.2906882762908936</v>
+        <v>0.290873646736145</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.2826077938079834</v>
+        <v>0.2827873229980469</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.2807307839393616</v>
+        <v>0.2809147238731384</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.2861185073852539</v>
+        <v>0.2863020300865173</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.2838149666786194</v>
+        <v>0.2840043306350708</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.2840349078178406</v>
+        <v>0.2842264473438263</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.2820902168750763</v>
+        <v>0.2822844684123993</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.2839339077472687</v>
+        <v>0.2841352224349976</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.2843254506587982</v>
+        <v>0.2845295965671539</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.2833825647830963</v>
+        <v>0.2835932970046997</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.2939605116844177</v>
+        <v>0.2941833436489105</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.2984379827976227</v>
+        <v>0.2986719012260437</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.3131251633167267</v>
+        <v>0.313366711139679</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.3070708811283112</v>
+        <v>0.307310938835144</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.3078208863735199</v>
+        <v>0.3080675303936005</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.309024304151535</v>
+        <v>0.3092799186706543</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.3090074956417084</v>
+        <v>0.3092661201953888</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.307050883769989</v>
+        <v>0.3073077499866486</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.3053809106349945</v>
+        <v>0.3056346476078033</v>
       </c>
       <c r="GH7" t="n">
-        <v>0.3016315996646881</v>
+        <v>0.301886260509491</v>
       </c>
       <c r="GI7" t="n">
-        <v>0.3022029995918274</v>
+        <v>0.3024672567844391</v>
       </c>
       <c r="GJ7" t="n">
-        <v>0.3027077913284302</v>
+        <v>0.3029700219631195</v>
       </c>
       <c r="GK7" t="n">
-        <v>0.306580513715744</v>
+        <v>0.3068509995937347</v>
       </c>
       <c r="GL7" t="n">
-        <v>0.3130449056625366</v>
+        <v>0.3133201599121094</v>
       </c>
       <c r="GM7" t="n">
-        <v>0.3193467855453491</v>
+        <v>0.3196362257003784</v>
       </c>
       <c r="GN7" t="n">
-        <v>0.3347069919109344</v>
+        <v>0.3350057005882263</v>
       </c>
       <c r="GO7" t="n">
-        <v>0.3426859676837921</v>
+        <v>0.3429937362670898</v>
       </c>
       <c r="GP7" t="n">
-        <v>0.3356075584888458</v>
+        <v>0.3358811736106873</v>
       </c>
       <c r="GQ7" t="n">
-        <v>0.3324775695800781</v>
+        <v>0.3327478766441345</v>
       </c>
       <c r="GR7" t="n">
-        <v>0.3314467966556549</v>
+        <v>0.3317080140113831</v>
       </c>
       <c r="GS7" t="n">
-        <v>0.3298490941524506</v>
+        <v>0.3301149606704712</v>
       </c>
       <c r="GT7" t="n">
-        <v>0.331270307302475</v>
+        <v>0.3315452337265015</v>
       </c>
       <c r="GU7" t="n">
-        <v>0.3255488574504852</v>
+        <v>0.3258269429206848</v>
       </c>
       <c r="GV7" t="n">
-        <v>0.3308460116386414</v>
+        <v>0.3311342895030975</v>
       </c>
       <c r="GW7" t="n">
-        <v>0.325922816991806</v>
+        <v>0.3262184262275696</v>
       </c>
       <c r="GX7" t="n">
-        <v>0.3270948231220245</v>
+        <v>0.3273998498916626</v>
       </c>
       <c r="GY7" t="n">
-        <v>0.3274365365505219</v>
+        <v>0.3277505338191986</v>
       </c>
       <c r="GZ7" t="n">
-        <v>0.3405782580375671</v>
+        <v>0.3409061431884766</v>
       </c>
       <c r="HA7" t="n">
-        <v>0.353360116481781</v>
+        <v>0.3536700010299683</v>
       </c>
       <c r="HB7" t="n">
-        <v>0.3661192953586578</v>
+        <v>0.3664619028568268</v>
       </c>
       <c r="HC7" t="n">
-        <v>0.3597228825092316</v>
+        <v>0.3600077331066132</v>
       </c>
       <c r="HD7" t="n">
-        <v>0.3490037024021149</v>
+        <v>0.3494166433811188</v>
       </c>
       <c r="HE7" t="n">
-        <v>0.3440364003181458</v>
+        <v>0.3444414734840393</v>
       </c>
       <c r="HF7" t="n">
-        <v>0.3456283211708069</v>
+        <v>0.3460263907909393</v>
       </c>
       <c r="HG7" t="n">
-        <v>0.3522845506668091</v>
+        <v>0.3526863753795624</v>
       </c>
       <c r="HH7" t="n">
-        <v>0.351238340139389</v>
+        <v>0.3516456484794617</v>
       </c>
       <c r="HI7" t="n">
-        <v>0.3496595621109009</v>
+        <v>0.3500709533691406</v>
       </c>
       <c r="HJ7" t="n">
-        <v>0.3523322939872742</v>
+        <v>0.3527444303035736</v>
       </c>
       <c r="HK7" t="n">
-        <v>0.346094161272049</v>
+        <v>0.3465072512626648</v>
       </c>
       <c r="HL7" t="n">
-        <v>0.3479207456111908</v>
+        <v>0.3483311235904694</v>
       </c>
       <c r="HM7" t="n">
-        <v>0.3449780941009521</v>
+        <v>0.3453826010227203</v>
       </c>
       <c r="HN7" t="n">
-        <v>0.3681227266788483</v>
+        <v>0.3685340285301208</v>
       </c>
       <c r="HO7" t="n">
-        <v>0.3823427259922028</v>
+        <v>0.3827657997608185</v>
       </c>
       <c r="HP7" t="n">
-        <v>0.3610783815383911</v>
+        <v>0.3614167869091034</v>
       </c>
       <c r="HQ7" t="n">
-        <v>0.3486778438091278</v>
+        <v>0.3489547371864319</v>
       </c>
       <c r="HR7" t="inlineStr">
         <is>
